--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4707692861557</t>
+    <t xml:space="preserve">1.47076916694641</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">1.48684310913086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424712657928</t>
+    <t xml:space="preserve">1.44424700737</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593269348145</t>
+    <t xml:space="preserve">1.37593257427216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414030075073</t>
+    <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744762420654</t>
+    <t xml:space="preserve">1.35744750499725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628830432892</t>
+    <t xml:space="preserve">1.36628818511963</t>
   </si>
   <si>
     <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3815586566925</t>
+    <t xml:space="preserve">1.38155853748322</t>
   </si>
   <si>
     <t xml:space="preserve">1.40647327899933</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">1.44585454463959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39843618869781</t>
+    <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
     <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726288795471</t>
+    <t xml:space="preserve">1.31726264953613</t>
   </si>
   <si>
     <t xml:space="preserve">1.31002938747406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217739105225</t>
+    <t xml:space="preserve">1.34217727184296</t>
   </si>
   <si>
     <t xml:space="preserve">1.35021436214447</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">1.43058431148529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693559646606</t>
+    <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889862537384</t>
+    <t xml:space="preserve">1.49889874458313</t>
   </si>
   <si>
     <t xml:space="preserve">1.47237658500671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49488019943237</t>
+    <t xml:space="preserve">1.49488008022308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274653434753</t>
+    <t xml:space="preserve">1.55274641513824</t>
   </si>
   <si>
     <t xml:space="preserve">1.61543500423431</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">1.67169392108917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490887641907</t>
+    <t xml:space="preserve">1.67490875720978</t>
   </si>
   <si>
     <t xml:space="preserve">1.6459755897522</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">1.55113911628723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702808380127</t>
+    <t xml:space="preserve">1.52702820301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630264282227</t>
+    <t xml:space="preserve">1.45630276203156</t>
   </si>
   <si>
     <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4120991230011</t>
+    <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
     <t xml:space="preserve">1.45601892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426251411438</t>
+    <t xml:space="preserve">1.43426239490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.40832185745239</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840492725372</t>
+    <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4133425951004</t>
+    <t xml:space="preserve">1.41334247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497469902039</t>
+    <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
     <t xml:space="preserve">1.36313498020172</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32547926902771</t>
+    <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213234901428</t>
+    <t xml:space="preserve">1.3221321105957</t>
   </si>
   <si>
     <t xml:space="preserve">1.26439356803894</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27192461490631</t>
+    <t xml:space="preserve">1.27192449569702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267839431763</t>
+    <t xml:space="preserve">1.25267827510834</t>
   </si>
   <si>
     <t xml:space="preserve">1.22506427764893</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845291137695</t>
+    <t xml:space="preserve">1.23845303058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008501529694</t>
+    <t xml:space="preserve">1.23008489608765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824529647827</t>
+    <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
     <t xml:space="preserve">1.14473223686218</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">1.22171711921692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816246509552</t>
+    <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
     <t xml:space="preserve">1.15226328372955</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966990470886</t>
+    <t xml:space="preserve">1.12966978549957</t>
   </si>
   <si>
     <t xml:space="preserve">1.11293411254883</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">1.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343880176544</t>
+    <t xml:space="preserve">1.03343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">1.02423405647278</t>
@@ -287,28 +287,28 @@
     <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364617824554</t>
+    <t xml:space="preserve">1.08364629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06440007686615</t>
+    <t xml:space="preserve">1.06439995765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07109451293945</t>
+    <t xml:space="preserve">1.07109427452087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03762292861938</t>
+    <t xml:space="preserve">1.0376228094101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0083349943161</t>
+    <t xml:space="preserve">1.00833511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067976474762</t>
+    <t xml:space="preserve">0.984068095684052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967098236084</t>
+    <t xml:space="preserve">0.999966979026794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251900196075</t>
+    <t xml:space="preserve">1.01251888275146</t>
   </si>
   <si>
     <t xml:space="preserve">1.00415110588074</t>
@@ -317,16 +317,16 @@
     <t xml:space="preserve">0.958127498626709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842553138733</t>
+    <t xml:space="preserve">0.969842433929443</t>
   </si>
   <si>
     <t xml:space="preserve">0.944738686084747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673722743988</t>
+    <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866080284118652</t>
+    <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
     <t xml:space="preserve">0.952269852161407</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.912103891372681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899551928043365</t>
+    <t xml:space="preserve">0.89955198764801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204769611359</t>
+    <t xml:space="preserve">0.896204829216003</t>
   </si>
   <si>
     <t xml:space="preserve">0.871937870979309</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">0.950596272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124629020691</t>
   </si>
   <si>
     <t xml:space="preserve">0.920471668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332243919373</t>
+    <t xml:space="preserve">0.967332124710083</t>
   </si>
   <si>
     <t xml:space="preserve">0.962311327457428</t>
@@ -365,28 +365,28 @@
     <t xml:space="preserve">1.05519533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599202156067</t>
+    <t xml:space="preserve">0.991599082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088773727417</t>
+    <t xml:space="preserve">0.989088654518127</t>
   </si>
   <si>
     <t xml:space="preserve">1.0016405582428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783090591431</t>
+    <t xml:space="preserve">0.99578320980072</t>
   </si>
   <si>
     <t xml:space="preserve">0.990762293338776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207698822021</t>
+    <t xml:space="preserve">0.937207579612732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394576072693</t>
+    <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391587257385</t>
+    <t xml:space="preserve">0.941391468048096</t>
   </si>
   <si>
     <t xml:space="preserve">0.988251984119415</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">0.972352802753448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96816873550415</t>
+    <t xml:space="preserve">0.968168973922729</t>
   </si>
   <si>
     <t xml:space="preserve">0.97570013999939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231067657471</t>
+    <t xml:space="preserve">0.98323118686676</t>
   </si>
   <si>
     <t xml:space="preserve">0.987415194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005763530731</t>
+    <t xml:space="preserve">0.969005644321442</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109451770782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943371772766</t>
+    <t xml:space="preserve">0.953943490982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854260921478</t>
+    <t xml:space="preserve">1.05854272842407</t>
   </si>
   <si>
     <t xml:space="preserve">1.05937933921814</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268514156342</t>
+    <t xml:space="preserve">1.05268502235413</t>
   </si>
   <si>
     <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636434078217</t>
+    <t xml:space="preserve">1.13636445999146</t>
   </si>
   <si>
     <t xml:space="preserve">1.1480792760849</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">1.19661331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602567195892</t>
+    <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
     <t xml:space="preserve">1.20581805706024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21334910392761</t>
+    <t xml:space="preserve">1.2133492231369</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753311157227</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242930412292</t>
+    <t xml:space="preserve">1.19242918491364</t>
   </si>
   <si>
     <t xml:space="preserve">1.19493973255157</t>
@@ -470,34 +470,34 @@
     <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1464056968689</t>
+    <t xml:space="preserve">1.14640557765961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19159257411957</t>
+    <t xml:space="preserve">1.19159245491028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314148902893</t>
+    <t xml:space="preserve">1.16314172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2376161813736</t>
+    <t xml:space="preserve">1.23761630058289</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2359424829483</t>
+    <t xml:space="preserve">1.23594260215759</t>
   </si>
   <si>
     <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13385403156281</t>
+    <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803780078888</t>
+    <t xml:space="preserve">1.13803791999817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799632549286</t>
+    <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
     <t xml:space="preserve">1.12130200862885</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">1.40581142902374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576995372772</t>
+    <t xml:space="preserve">1.39576983451843</t>
   </si>
   <si>
     <t xml:space="preserve">1.39911711215973</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865377902985</t>
+    <t xml:space="preserve">1.48865389823914</t>
   </si>
   <si>
     <t xml:space="preserve">1.48949074745178</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5355144739151</t>
+    <t xml:space="preserve">1.53551435470581</t>
   </si>
   <si>
     <t xml:space="preserve">1.57316994667053</t>
@@ -545,16 +545,16 @@
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174545764923</t>
+    <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
     <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550772666931</t>
+    <t xml:space="preserve">1.73550748825073</t>
   </si>
   <si>
     <t xml:space="preserve">1.75726413726807</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">1.65099167823792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60078394412994</t>
+    <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
     <t xml:space="preserve">1.67358493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003028392792</t>
+    <t xml:space="preserve">1.62003040313721</t>
   </si>
   <si>
     <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6166832447052</t>
+    <t xml:space="preserve">1.61668312549591</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664176940918</t>
@@ -593,46 +593,46 @@
     <t xml:space="preserve">1.68362665176392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7154244184494</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718118667603</t>
+    <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224351882935</t>
+    <t xml:space="preserve">1.75224363803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052846431732</t>
+    <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
     <t xml:space="preserve">1.723792552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601229667664</t>
+    <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220216274261</t>
+    <t xml:space="preserve">1.74220192432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7490611076355</t>
+    <t xml:space="preserve">1.74906098842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337317943573</t>
+    <t xml:space="preserve">1.84337329864502</t>
   </si>
   <si>
     <t xml:space="preserve">1.80050384998322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335654735565</t>
+    <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193007946014</t>
+    <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548327922821</t>
+    <t xml:space="preserve">1.95483303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323546409607</t>
+    <t xml:space="preserve">2.37323594093323</t>
   </si>
   <si>
     <t xml:space="preserve">2.46926283836365</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">2.82421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936310768127</t>
+    <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505163192749</t>
+    <t xml:space="preserve">2.73505139350891</t>
   </si>
   <si>
     <t xml:space="preserve">2.64416909217834</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">2.4624035358429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097730636597</t>
+    <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
     <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953444480896</t>
+    <t xml:space="preserve">2.41953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641037940979</t>
+    <t xml:space="preserve">2.48641061782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43496704101562</t>
+    <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45554447174072</t>
+    <t xml:space="preserve">2.4555447101593</t>
   </si>
   <si>
     <t xml:space="preserve">2.45725917816162</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897388458252</t>
+    <t xml:space="preserve">2.4589741230011</t>
   </si>
   <si>
     <t xml:space="preserve">2.47440695762634</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781973838806</t>
+    <t xml:space="preserve">2.41781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639327049255</t>
+    <t xml:space="preserve">2.42639350891113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38352417945862</t>
+    <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
     <t xml:space="preserve">2.33208155632019</t>
@@ -749,25 +749,25 @@
     <t xml:space="preserve">2.31321883201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26692056655884</t>
+    <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.126309633255</t>
+    <t xml:space="preserve">2.12630939483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12116527557373</t>
+    <t xml:space="preserve">2.12116503715515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800723075867</t>
+    <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
     <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09544396400452</t>
+    <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773586273193</t>
+    <t xml:space="preserve">2.11773562431335</t>
   </si>
   <si>
     <t xml:space="preserve">2.1280243396759</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08344030380249</t>
+    <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
     <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799036026001</t>
+    <t xml:space="preserve">2.00799059867859</t>
   </si>
   <si>
     <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342367172241</t>
+    <t xml:space="preserve">2.02342343330383</t>
   </si>
   <si>
     <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603778839111</t>
+    <t xml:space="preserve">2.17603802680969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172559738159</t>
+    <t xml:space="preserve">2.08172535896301</t>
   </si>
   <si>
     <t xml:space="preserve">2.10401773452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888977050781</t>
+    <t xml:space="preserve">2.15889000892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14345717430115</t>
+    <t xml:space="preserve">2.14345741271973</t>
   </si>
   <si>
     <t xml:space="preserve">2.12287998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15374565124512</t>
+    <t xml:space="preserve">2.1537458896637</t>
   </si>
   <si>
     <t xml:space="preserve">2.15203094482422</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27720904350281</t>
+    <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
     <t xml:space="preserve">2.22062158584595</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">2.18975567817688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2291955947876</t>
+    <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.24634289741516</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">2.34065532684326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25320243835449</t>
+    <t xml:space="preserve">2.25320219993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27034974098206</t>
+    <t xml:space="preserve">2.27034950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206492424011</t>
+    <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.20175933837891</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2034740447998</t>
+    <t xml:space="preserve">2.20347380638123</t>
   </si>
   <si>
     <t xml:space="preserve">2.24462819099426</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.5138463973999</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">2.32007837295532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32179284095764</t>
+    <t xml:space="preserve">2.32179307937622</t>
   </si>
   <si>
     <t xml:space="preserve">2.36809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33379602432251</t>
+    <t xml:space="preserve">2.33379626274109</t>
   </si>
   <si>
     <t xml:space="preserve">2.41439032554626</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">2.34922885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3578028678894</t>
+    <t xml:space="preserve">2.35780310630798</t>
   </si>
   <si>
     <t xml:space="preserve">2.40410137176514</t>
@@ -935,25 +935,25 @@
     <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3063600063324</t>
+    <t xml:space="preserve">2.30635976791382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38866853713989</t>
+    <t xml:space="preserve">2.38866877555847</t>
   </si>
   <si>
     <t xml:space="preserve">2.31493401527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832944869995</t>
+    <t xml:space="preserve">2.19832968711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430621147156</t>
+    <t xml:space="preserve">2.11430644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632626533508</t>
+    <t xml:space="preserve">2.18632650375366</t>
   </si>
   <si>
     <t xml:space="preserve">2.10058784484863</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">2.09201431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04057121276855</t>
+    <t xml:space="preserve">2.04057145118713</t>
   </si>
   <si>
     <t xml:space="preserve">2.01484942436218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914522171021</t>
+    <t xml:space="preserve">2.04914498329163</t>
   </si>
   <si>
     <t xml:space="preserve">1.90339004993439</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">1.97198057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053782939911</t>
+    <t xml:space="preserve">1.92053735256195</t>
   </si>
   <si>
     <t xml:space="preserve">1.98912811279297</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">1.86909472942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8519469499588</t>
+    <t xml:space="preserve">1.85194683074951</t>
   </si>
   <si>
     <t xml:space="preserve">1.94625902175903</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">1.96340680122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879186630249</t>
+    <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
     <t xml:space="preserve">2.04249358177185</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">1.85840618610382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470435142517</t>
+    <t xml:space="preserve">1.88470447063446</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866306781769</t>
+    <t xml:space="preserve">1.99866330623627</t>
   </si>
   <si>
     <t xml:space="preserve">1.94606685638428</t>
@@ -1040,25 +1040,25 @@
     <t xml:space="preserve">1.92853450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717236042023</t>
+    <t xml:space="preserve">1.86717247962952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223658084869</t>
+    <t xml:space="preserve">1.90223670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593853473663</t>
+    <t xml:space="preserve">1.87593841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334208488464</t>
+    <t xml:space="preserve">1.82334184646606</t>
   </si>
   <si>
     <t xml:space="preserve">1.91976881027222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84964001178741</t>
+    <t xml:space="preserve">1.8496401309967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.893470287323</t>
   </si>
   <si>
     <t xml:space="preserve">1.93730080127716</t>
@@ -1070,31 +1070,31 @@
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7882776260376</t>
+    <t xml:space="preserve">1.78827750682831</t>
   </si>
   <si>
     <t xml:space="preserve">1.77074551582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704356193542</t>
+    <t xml:space="preserve">1.79704368114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6173392534256</t>
+    <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542417526245</t>
+    <t xml:space="preserve">1.59542405605316</t>
   </si>
   <si>
     <t xml:space="preserve">1.6217223405838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65678656101227</t>
+    <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308484554291</t>
+    <t xml:space="preserve">1.68308472633362</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
@@ -1103,49 +1103,49 @@
     <t xml:space="preserve">1.66555273532867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69185078144073</t>
+    <t xml:space="preserve">1.69185090065002</t>
   </si>
   <si>
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789206504822</t>
+    <t xml:space="preserve">1.57789194583893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419034957886</t>
+    <t xml:space="preserve">1.60419023036957</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59980726242065</t>
+    <t xml:space="preserve">1.59980738162994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104108810425</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048851490021</t>
+    <t xml:space="preserve">1.63048839569092</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70061695575714</t>
+    <t xml:space="preserve">1.70061707496643</t>
   </si>
   <si>
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295640468597</t>
+    <t xml:space="preserve">1.61295628547668</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925457000732</t>
+    <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.58665800094604</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">1.29737794399261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24478137493134</t>
+    <t xml:space="preserve">1.24478149414062</t>
   </si>
   <si>
     <t xml:space="preserve">1.20971727371216</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065552711487</t>
+    <t xml:space="preserve">1.38065564632416</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1184,34 +1184,34 @@
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325197696686</t>
+    <t xml:space="preserve">1.43325185775757</t>
   </si>
   <si>
     <t xml:space="preserve">1.38942170143127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38503873348236</t>
+    <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874032974243</t>
+    <t xml:space="preserve">1.35874021053314</t>
   </si>
   <si>
     <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4464008808136</t>
+    <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45078408718109</t>
+    <t xml:space="preserve">1.4507839679718</t>
   </si>
   <si>
     <t xml:space="preserve">1.3938045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41133677959442</t>
+    <t xml:space="preserve">1.41133666038513</t>
   </si>
   <si>
     <t xml:space="preserve">1.36750638484955</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">1.51214647293091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52967870235443</t>
+    <t xml:space="preserve">1.52967858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721081256866</t>
+    <t xml:space="preserve">1.54721093177795</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">1.52091252803802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584842681885</t>
+    <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652956008911</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529561519623</t>
+    <t xml:space="preserve">1.52529573440552</t>
   </si>
   <si>
     <t xml:space="preserve">1.49899744987488</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">1.60545694828033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937921047211</t>
+    <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
     <t xml:space="preserve">1.54232108592987</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820447921753</t>
+    <t xml:space="preserve">1.48820459842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.461146235466</t>
+    <t xml:space="preserve">1.46114611625671</t>
   </si>
   <si>
     <t xml:space="preserve">1.50624334812164</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.40702962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38899075984955</t>
+    <t xml:space="preserve">1.38899087905884</t>
   </si>
   <si>
     <t xml:space="preserve">1.37095201015472</t>
@@ -1319,67 +1319,67 @@
     <t xml:space="preserve">1.3438937664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31683552265167</t>
+    <t xml:space="preserve">1.31683564186096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977715969086</t>
+    <t xml:space="preserve">1.28977727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271891593933</t>
+    <t xml:space="preserve">1.26271903514862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24468004703522</t>
+    <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
     <t xml:space="preserve">1.19056367874146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18154430389404</t>
+    <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252480983734</t>
+    <t xml:space="preserve">1.17252469062805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664141654968</t>
+    <t xml:space="preserve">1.22664129734039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762192249298</t>
+    <t xml:space="preserve">1.21762180328369</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879665374756</t>
+    <t xml:space="preserve">1.29879677295685</t>
   </si>
   <si>
     <t xml:space="preserve">1.36193263530731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37997138500214</t>
+    <t xml:space="preserve">1.37997150421143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781602859497</t>
+    <t xml:space="preserve">1.30781614780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32585489749908</t>
+    <t xml:space="preserve">1.32585501670837</t>
   </si>
   <si>
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566079139709</t>
+    <t xml:space="preserve">1.23566067218781</t>
   </si>
   <si>
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055418014526</t>
+    <t xml:space="preserve">1.65055406093597</t>
   </si>
   <si>
     <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153480529785</t>
+    <t xml:space="preserve">1.64153468608856</t>
   </si>
   <si>
     <t xml:space="preserve">1.63251519203186</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69565117359161</t>
+    <t xml:space="preserve">1.6956512928009</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">1.11840832233429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350543498993</t>
+    <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15448594093323</t>
+    <t xml:space="preserve">1.15448582172394</t>
   </si>
   <si>
     <t xml:space="preserve">1.1274276971817</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">1.19958305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25369954109192</t>
+    <t xml:space="preserve">1.25369966030121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546656608582</t>
+    <t xml:space="preserve">1.14546644687653</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233070373535</t>
+    <t xml:space="preserve">1.08233058452606</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1466,19 +1466,19 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136418819427</t>
+    <t xml:space="preserve">0.992136359214783</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097609519958</t>
+    <t xml:space="preserve">0.974097490310669</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078175067902</t>
+    <t xml:space="preserve">0.965078055858612</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">0.938019812107086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919981002807617</t>
+    <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947039186954498</t>
+    <t xml:space="preserve">0.947039127349854</t>
   </si>
   <si>
     <t xml:space="preserve">0.897432446479797</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983117043972015</t>
+    <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01919460296631</t>
+    <t xml:space="preserve">1.0191947221756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956058621406555</t>
+    <t xml:space="preserve">0.95605856180191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20860254764557</t>
+    <t xml:space="preserve">1.20860242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918498516083</t>
+    <t xml:space="preserve">1.47918510437012</t>
   </si>
   <si>
     <t xml:space="preserve">1.25098133087158</t>
@@ -66846,6 +66846,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.2916666667</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>580</v>
+      </c>
+      <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4707692861557</t>
+    <t xml:space="preserve">1.47076916694641</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236248493195</t>
+    <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
     <t xml:space="preserve">1.37593269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414030075073</t>
+    <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744762420654</t>
+    <t xml:space="preserve">1.35744738578796</t>
   </si>
   <si>
     <t xml:space="preserve">1.36628842353821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290271282196</t>
+    <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
     <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647327899933</t>
+    <t xml:space="preserve">1.40647315979004</t>
   </si>
   <si>
     <t xml:space="preserve">1.4458544254303</t>
@@ -86,58 +86,58 @@
     <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780323505402</t>
+    <t xml:space="preserve">1.34780311584473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726276874542</t>
+    <t xml:space="preserve">1.31726288795471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002950668335</t>
+    <t xml:space="preserve">1.31002926826477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217715263367</t>
+    <t xml:space="preserve">1.34217739105225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021424293518</t>
+    <t xml:space="preserve">1.35021436214447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128119468689</t>
+    <t xml:space="preserve">1.32128131389618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557696342468</t>
+    <t xml:space="preserve">1.38557720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273231506348</t>
+    <t xml:space="preserve">1.46273219585419</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693559646606</t>
+    <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889862537384</t>
+    <t xml:space="preserve">1.49889886379242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47237646579742</t>
+    <t xml:space="preserve">1.472376704216</t>
   </si>
   <si>
     <t xml:space="preserve">1.49488008022308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274653434753</t>
+    <t xml:space="preserve">1.55274665355682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543488502502</t>
+    <t xml:space="preserve">1.61543500423431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169392108917</t>
+    <t xml:space="preserve">1.67169380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490863800049</t>
+    <t xml:space="preserve">1.67490887641907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6459755897522</t>
+    <t xml:space="preserve">1.64597570896149</t>
   </si>
   <si>
     <t xml:space="preserve">1.55113911628723</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095402240753</t>
+    <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
     <t xml:space="preserve">1.45630264282227</t>
@@ -155,16 +155,16 @@
     <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4120991230011</t>
+    <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601904392242</t>
+    <t xml:space="preserve">1.45601892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426239490509</t>
+    <t xml:space="preserve">1.43426251411438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832185745239</t>
+    <t xml:space="preserve">1.4083217382431</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840480804443</t>
+    <t xml:space="preserve">1.42840492725372</t>
   </si>
   <si>
     <t xml:space="preserve">1.41334247589111</t>
@@ -185,82 +185,82 @@
     <t xml:space="preserve">1.36313498020172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560393333435</t>
+    <t xml:space="preserve">1.35560381412506</t>
   </si>
   <si>
     <t xml:space="preserve">1.3723396062851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886826038361</t>
+    <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288589000702</t>
+    <t xml:space="preserve">1.30288600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325479388237</t>
+    <t xml:space="preserve">1.32547950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213222980499</t>
+    <t xml:space="preserve">1.3221321105957</t>
   </si>
   <si>
     <t xml:space="preserve">1.26439356803894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702854156494</t>
+    <t xml:space="preserve">1.29702830314636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539631843567</t>
+    <t xml:space="preserve">1.30539619922638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397182941437</t>
+    <t xml:space="preserve">1.36397171020508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41250586509705</t>
+    <t xml:space="preserve">1.41250562667847</t>
   </si>
   <si>
     <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3305002450943</t>
+    <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267851352692</t>
+    <t xml:space="preserve">1.25267827510834</t>
   </si>
   <si>
     <t xml:space="preserve">1.22506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20498132705688</t>
+    <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916533470154</t>
+    <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841143608093</t>
+    <t xml:space="preserve">1.22841155529022</t>
   </si>
   <si>
     <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008501529694</t>
+    <t xml:space="preserve">1.23008513450623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824541568756</t>
+    <t xml:space="preserve">1.18824529647827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14473211765289</t>
+    <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171700000763</t>
+    <t xml:space="preserve">1.22171723842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.16816246509552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226328372955</t>
+    <t xml:space="preserve">1.15226316452026</t>
   </si>
   <si>
     <t xml:space="preserve">1.14222192764282</t>
@@ -269,31 +269,31 @@
     <t xml:space="preserve">1.17150950431824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966990470886</t>
+    <t xml:space="preserve">1.12967002391815</t>
   </si>
   <si>
     <t xml:space="preserve">1.11293399333954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04850113391876</t>
+    <t xml:space="preserve">1.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343880176544</t>
+    <t xml:space="preserve">1.03343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03929650783539</t>
+    <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
     <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364629745483</t>
+    <t xml:space="preserve">1.08364617824554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06439995765686</t>
+    <t xml:space="preserve">1.06440019607544</t>
   </si>
   <si>
     <t xml:space="preserve">1.07109439373016</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">1.03762269020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00833511352539</t>
+    <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067976474762</t>
+    <t xml:space="preserve">0.984068036079407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967038631439</t>
+    <t xml:space="preserve">0.999967157840729</t>
   </si>
   <si>
     <t xml:space="preserve">1.01251888275146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00415110588074</t>
+    <t xml:space="preserve">1.00415086746216</t>
   </si>
   <si>
     <t xml:space="preserve">0.958127439022064</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">0.969842612743378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738805294037</t>
+    <t xml:space="preserve">0.944738626480103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673722743988</t>
+    <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
     <t xml:space="preserve">0.866080224514008</t>
@@ -335,43 +335,43 @@
     <t xml:space="preserve">0.952269911766052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103950977325</t>
+    <t xml:space="preserve">0.912103772163391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899552047252655</t>
+    <t xml:space="preserve">0.89955198764801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204888820648</t>
+    <t xml:space="preserve">0.896204769611359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937811374664</t>
+    <t xml:space="preserve">0.871937870979309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756673336029</t>
+    <t xml:space="preserve">0.908756613731384</t>
   </si>
   <si>
     <t xml:space="preserve">0.950596272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124569416046</t>
+    <t xml:space="preserve">0.917124509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471906661987</t>
+    <t xml:space="preserve">0.920471727848053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332243919373</t>
+    <t xml:space="preserve">0.967332184314728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311327457428</t>
+    <t xml:space="preserve">0.962311446666718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519533157349</t>
+    <t xml:space="preserve">1.0551952123642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599142551422</t>
+    <t xml:space="preserve">0.991599082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088654518127</t>
+    <t xml:space="preserve">0.989088773727417</t>
   </si>
   <si>
     <t xml:space="preserve">1.0016405582428</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">0.99578320980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762531757355</t>
+    <t xml:space="preserve">0.99076247215271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207639217377</t>
+    <t xml:space="preserve">0.937207579612732</t>
   </si>
   <si>
     <t xml:space="preserve">0.982394456863403</t>
@@ -395,85 +395,85 @@
     <t xml:space="preserve">0.988251805305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352683544159</t>
+    <t xml:space="preserve">0.972352862358093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168973922729</t>
+    <t xml:space="preserve">0.968168914318085</t>
   </si>
   <si>
     <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231127262115</t>
+    <t xml:space="preserve">0.98323118686676</t>
   </si>
   <si>
     <t xml:space="preserve">0.987415075302124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005703926086</t>
+    <t xml:space="preserve">0.969005644321442</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943490982056</t>
+    <t xml:space="preserve">0.953943431377411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0585423707962</t>
+    <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937933921814</t>
+    <t xml:space="preserve">1.05937945842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507078647614</t>
+    <t xml:space="preserve">1.02507090568542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268502235413</t>
+    <t xml:space="preserve">1.05268490314484</t>
   </si>
   <si>
     <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636422157288</t>
+    <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
     <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577670097351</t>
+    <t xml:space="preserve">1.19577658176422</t>
   </si>
   <si>
     <t xml:space="preserve">1.19661331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602555274963</t>
+    <t xml:space="preserve">1.25602543354034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20581793785095</t>
+    <t xml:space="preserve">1.20581805706024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21334910392761</t>
+    <t xml:space="preserve">1.2133492231369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753323078156</t>
+    <t xml:space="preserve">1.21753299236298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644717216492</t>
+    <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1531001329422</t>
+    <t xml:space="preserve">1.15310001373291</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493985176086</t>
+    <t xml:space="preserve">1.19493973255157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1547737121582</t>
+    <t xml:space="preserve">1.15477359294891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1464056968689</t>
+    <t xml:space="preserve">1.14640557765961</t>
   </si>
   <si>
     <t xml:space="preserve">1.19159257411957</t>
@@ -482,34 +482,34 @@
     <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23761606216431</t>
+    <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518870353699</t>
+    <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23594272136688</t>
+    <t xml:space="preserve">1.23594260215759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146790981293</t>
+    <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13385391235352</t>
+    <t xml:space="preserve">1.13385403156281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803791999817</t>
+    <t xml:space="preserve">1.13803780078888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799632549286</t>
+    <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
     <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653024196625</t>
+    <t xml:space="preserve">1.17653036117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581142902374</t>
+    <t xml:space="preserve">1.40581130981445</t>
   </si>
   <si>
     <t xml:space="preserve">1.39576995372772</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">1.39911711215973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39744341373444</t>
+    <t xml:space="preserve">1.39744353294373</t>
   </si>
   <si>
     <t xml:space="preserve">1.46020293235779</t>
@@ -530,115 +530,115 @@
     <t xml:space="preserve">1.45685577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865377902985</t>
+    <t xml:space="preserve">1.48865389823914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4894905090332</t>
+    <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
     <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551435470581</t>
+    <t xml:space="preserve">1.5355144739151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57316982746124</t>
+    <t xml:space="preserve">1.57316994667053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58572173118591</t>
+    <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
     <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438019275665</t>
+    <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550760746002</t>
+    <t xml:space="preserve">1.73550748825073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726425647736</t>
+    <t xml:space="preserve">1.75726413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77399981021881</t>
+    <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78236794471741</t>
+    <t xml:space="preserve">1.7823680639267</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60078406333923</t>
+    <t xml:space="preserve">1.60078418254852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67358493804932</t>
+    <t xml:space="preserve">1.67358505725861</t>
   </si>
   <si>
     <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697369098663</t>
+    <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61668312549591</t>
+    <t xml:space="preserve">1.6166832447052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6066415309906</t>
+    <t xml:space="preserve">1.60664165019989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195295333862</t>
+    <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362677097321</t>
+    <t xml:space="preserve">1.68362653255463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542465686798</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7371814250946</t>
+    <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224375724792</t>
+    <t xml:space="preserve">1.75224363803864</t>
   </si>
   <si>
     <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72379267215729</t>
+    <t xml:space="preserve">1.72379231452942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601253509521</t>
+    <t xml:space="preserve">1.65601229667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7490611076355</t>
+    <t xml:space="preserve">1.74906098842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337306022644</t>
+    <t xml:space="preserve">1.84337329864502</t>
   </si>
   <si>
     <t xml:space="preserve">1.80050384998322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335642814636</t>
+    <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193031787872</t>
+    <t xml:space="preserve">1.79193007946014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548327922821</t>
+    <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323570251465</t>
+    <t xml:space="preserve">2.37323594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926259994507</t>
+    <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
     <t xml:space="preserve">2.82421922683716</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505139350891</t>
+    <t xml:space="preserve">2.73505163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64416909217834</t>
+    <t xml:space="preserve">2.64416885375977</t>
   </si>
   <si>
     <t xml:space="preserve">2.47783660888672</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067195892334</t>
+    <t xml:space="preserve">2.40067172050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48984003067017</t>
+    <t xml:space="preserve">2.48983979225159</t>
   </si>
   <si>
     <t xml:space="preserve">2.58929634094238</t>
@@ -677,31 +677,31 @@
     <t xml:space="preserve">2.67503428459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012850761414</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46240377426147</t>
+    <t xml:space="preserve">2.4624035358429</t>
   </si>
   <si>
     <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354128837585</t>
+    <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953444480896</t>
+    <t xml:space="preserve">2.41953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211482048035</t>
+    <t xml:space="preserve">2.45211505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52927923202515</t>
+    <t xml:space="preserve">2.5292797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214832305908</t>
+    <t xml:space="preserve">2.57214879989624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641037940979</t>
+    <t xml:space="preserve">2.48641061782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349672794342</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">2.4572594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613877296448</t>
+    <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4589741230011</t>
+    <t xml:space="preserve">2.45897388458252</t>
   </si>
   <si>
     <t xml:space="preserve">2.47440695762634</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">2.38180994987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639350891113</t>
+    <t xml:space="preserve">2.42639327049255</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208155632019</t>
+    <t xml:space="preserve">2.33208131790161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836342811584</t>
+    <t xml:space="preserve">2.31836366653442</t>
   </si>
   <si>
     <t xml:space="preserve">2.2806384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865190505981</t>
+    <t xml:space="preserve">2.32865214347839</t>
   </si>
   <si>
     <t xml:space="preserve">2.31321907043457</t>
@@ -758,49 +758,49 @@
     <t xml:space="preserve">2.126309633255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12116527557373</t>
+    <t xml:space="preserve">2.12116503715515</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05771923065186</t>
+    <t xml:space="preserve">2.0577187538147</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544396400452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773586273193</t>
+    <t xml:space="preserve">2.11773562431335</t>
   </si>
   <si>
     <t xml:space="preserve">2.1280243396759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515524864197</t>
+    <t xml:space="preserve">2.08515501022339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629276275635</t>
+    <t xml:space="preserve">2.06629300117493</t>
   </si>
   <si>
     <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887313842773</t>
+    <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
     <t xml:space="preserve">2.00799083709717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0508599281311</t>
+    <t xml:space="preserve">2.05086016654968</t>
   </si>
   <si>
     <t xml:space="preserve">2.02342343330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20690369606018</t>
+    <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603778839111</t>
+    <t xml:space="preserve">2.17603802680969</t>
   </si>
   <si>
     <t xml:space="preserve">2.08172559738159</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15889000892639</t>
+    <t xml:space="preserve">2.15888977050781</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12288022041321</t>
+    <t xml:space="preserve">2.12287974357605</t>
   </si>
   <si>
     <t xml:space="preserve">2.15374565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15203094482422</t>
+    <t xml:space="preserve">2.15203070640564</t>
   </si>
   <si>
     <t xml:space="preserve">2.16917848587036</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">2.25491714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28235292434692</t>
+    <t xml:space="preserve">2.28235340118408</t>
   </si>
   <si>
     <t xml:space="preserve">2.23776912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233653068542</t>
+    <t xml:space="preserve">2.22233629226685</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089366912842</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">2.18975591659546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2291955947876</t>
+    <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634337425232</t>
+    <t xml:space="preserve">2.24634313583374</t>
   </si>
   <si>
     <t xml:space="preserve">2.34065556526184</t>
@@ -881,31 +881,31 @@
     <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462819099426</t>
+    <t xml:space="preserve">2.24462842941284</t>
   </si>
   <si>
     <t xml:space="preserve">2.4366819858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527262687683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384663581848</t>
+    <t xml:space="preserve">2.51384687423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50355792045593</t>
+    <t xml:space="preserve">2.50355815887451</t>
   </si>
   <si>
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326944351196</t>
+    <t xml:space="preserve">2.49326920509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47269248962402</t>
+    <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
     <t xml:space="preserve">2.32007813453674</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809158325195</t>
+    <t xml:space="preserve">2.36809134483337</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379626274109</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922909736633</t>
+    <t xml:space="preserve">2.34922885894775</t>
   </si>
   <si>
     <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410137176514</t>
+    <t xml:space="preserve">2.40410161018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.39038348197937</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430621147156</t>
+    <t xml:space="preserve">2.11430644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632626533508</t>
+    <t xml:space="preserve">2.18632650375366</t>
   </si>
   <si>
     <t xml:space="preserve">2.10058808326721</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9033899307251</t>
+    <t xml:space="preserve">1.90339004993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.9805543422699</t>
@@ -983,106 +983,106 @@
     <t xml:space="preserve">1.97198069095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053771018982</t>
+    <t xml:space="preserve">1.92053759098053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912823200226</t>
+    <t xml:space="preserve">1.98912811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196370124817</t>
+    <t xml:space="preserve">1.91196393966675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911148071289</t>
+    <t xml:space="preserve">1.92911171913147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624238967896</t>
+    <t xml:space="preserve">1.88624227046967</t>
   </si>
   <si>
     <t xml:space="preserve">1.89481616020203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8690949678421</t>
+    <t xml:space="preserve">1.86909461021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194718837738</t>
+    <t xml:space="preserve">1.85194706916809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625914096832</t>
+    <t xml:space="preserve">1.94625926017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340692043304</t>
+    <t xml:space="preserve">1.96340680122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879186630249</t>
+    <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
     <t xml:space="preserve">2.04249358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236502170563</t>
+    <t xml:space="preserve">1.97236526012421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9110027551651</t>
+    <t xml:space="preserve">1.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840606689453</t>
+    <t xml:space="preserve">1.85840594768524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470423221588</t>
+    <t xml:space="preserve">1.88470458984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866318702698</t>
+    <t xml:space="preserve">1.99866330623627</t>
   </si>
   <si>
     <t xml:space="preserve">1.94606673717499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853486537933</t>
+    <t xml:space="preserve">1.92853474617004</t>
   </si>
   <si>
     <t xml:space="preserve">1.86717224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9022364616394</t>
+    <t xml:space="preserve">1.90223670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593853473663</t>
+    <t xml:space="preserve">1.87593841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334184646606</t>
+    <t xml:space="preserve">1.82334172725677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976857185364</t>
+    <t xml:space="preserve">1.91976881027222</t>
   </si>
   <si>
     <t xml:space="preserve">1.84964001178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347064495087</t>
+    <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730080127716</t>
+    <t xml:space="preserve">1.93730056285858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989713191986</t>
+    <t xml:space="preserve">1.98989737033844</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78827774524689</t>
+    <t xml:space="preserve">1.7882776260376</t>
   </si>
   <si>
     <t xml:space="preserve">1.77074551582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704368114471</t>
+    <t xml:space="preserve">1.797043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76197946071625</t>
+    <t xml:space="preserve">1.76197957992554</t>
   </si>
   <si>
     <t xml:space="preserve">1.61733937263489</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">1.59542429447174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6217223405838</t>
+    <t xml:space="preserve">1.62172245979309</t>
   </si>
   <si>
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308484554291</t>
+    <t xml:space="preserve">1.68308472633362</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789206504822</t>
+    <t xml:space="preserve">1.57789194583893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419034957886</t>
+    <t xml:space="preserve">1.60419023036957</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104132652283</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6699355840683</t>
+    <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048839569092</t>
+    <t xml:space="preserve">1.63048851490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295640468597</t>
+    <t xml:space="preserve">1.61295628547668</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925457000732</t>
+    <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58665800094604</t>
+    <t xml:space="preserve">1.58665812015533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597698688507</t>
+    <t xml:space="preserve">1.55597686767578</t>
   </si>
   <si>
     <t xml:space="preserve">1.42010283470154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42448592185974</t>
+    <t xml:space="preserve">1.42448580265045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32367610931396</t>
+    <t xml:space="preserve">1.32367599010468</t>
   </si>
   <si>
     <t xml:space="preserve">1.29737794399261</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">1.24478149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20971715450287</t>
+    <t xml:space="preserve">1.20971727371216</t>
   </si>
   <si>
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065576553345</t>
+    <t xml:space="preserve">1.38065564632416</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325197696686</t>
+    <t xml:space="preserve">1.43325185775757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38942158222198</t>
+    <t xml:space="preserve">1.38942170143127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38503861427307</t>
+    <t xml:space="preserve">1.38503873348236</t>
   </si>
   <si>
     <t xml:space="preserve">1.35874032974243</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45078408718109</t>
+    <t xml:space="preserve">1.4507839679718</t>
   </si>
   <si>
     <t xml:space="preserve">1.39380466938019</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36750638484955</t>
+    <t xml:space="preserve">1.36750650405884</t>
   </si>
   <si>
     <t xml:space="preserve">1.53406167030334</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">1.5121465921402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52967882156372</t>
+    <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
     <t xml:space="preserve">1.54721081256866</t>
@@ -1235,67 +1235,67 @@
     <t xml:space="preserve">1.54282772541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55159378051758</t>
+    <t xml:space="preserve">1.55159389972687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035983562469</t>
+    <t xml:space="preserve">1.56035995483398</t>
   </si>
   <si>
     <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584842681885</t>
+    <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5165296792984</t>
+    <t xml:space="preserve">1.51652956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5691260099411</t>
+    <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776362419128</t>
+    <t xml:space="preserve">1.50776338577271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529549598694</t>
+    <t xml:space="preserve">1.52529573440552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899744987488</t>
+    <t xml:space="preserve">1.49899733066559</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545694828033</t>
+    <t xml:space="preserve">1.60545706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937921047211</t>
+    <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232108592987</t>
+    <t xml:space="preserve">1.54232096672058</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820447921753</t>
+    <t xml:space="preserve">1.48820459842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.461146235466</t>
+    <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624334812164</t>
+    <t xml:space="preserve">1.50624322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016572952271</t>
+    <t xml:space="preserve">1.47016561031342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310748577118</t>
+    <t xml:space="preserve">1.44310736656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604912281036</t>
+    <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801025390625</t>
+    <t xml:space="preserve">1.39801013469696</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702962875366</t>
+    <t xml:space="preserve">1.40702974796295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38899075984955</t>
+    <t xml:space="preserve">1.38899087905884</t>
   </si>
   <si>
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35291314125061</t>
+    <t xml:space="preserve">1.3529132604599</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1325,25 +1325,25 @@
     <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977715969086</t>
+    <t xml:space="preserve">1.28977727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271891593933</t>
+    <t xml:space="preserve">1.26271903514862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24468004703522</t>
+    <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
     <t xml:space="preserve">1.19056367874146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18154430389404</t>
+    <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252480983734</t>
+    <t xml:space="preserve">1.17252469062805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664141654968</t>
+    <t xml:space="preserve">1.22664129734039</t>
   </si>
   <si>
     <t xml:space="preserve">1.21762192249298</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879665374756</t>
+    <t xml:space="preserve">1.29879677295685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193263530731</t>
+    <t xml:space="preserve">1.36193251609802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37997138500214</t>
+    <t xml:space="preserve">1.37997150421143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781602859497</t>
+    <t xml:space="preserve">1.30781614780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32585489749908</t>
+    <t xml:space="preserve">1.32585501670837</t>
   </si>
   <si>
     <t xml:space="preserve">1.27173840999603</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055418014526</t>
+    <t xml:space="preserve">1.65055406093597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859292984009</t>
+    <t xml:space="preserve">1.66859304904938</t>
   </si>
   <si>
     <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251519203186</t>
+    <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
     <t xml:space="preserve">1.59643757343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486489295959</t>
+    <t xml:space="preserve">1.79486477375031</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
@@ -1400,16 +1400,13 @@
     <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369004249573</t>
+    <t xml:space="preserve">1.71369016170502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349581718445</t>
+    <t xml:space="preserve">1.62349569797516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55134057998657</t>
+    <t xml:space="preserve">1.55134046077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
@@ -1424,7 +1421,7 @@
     <t xml:space="preserve">1.11840832233429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350543498993</t>
+    <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
     <t xml:space="preserve">1.15448594093323</t>
@@ -1439,7 +1436,7 @@
     <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546656608582</t>
+    <t xml:space="preserve">1.14546644687653</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1448,10 +1445,10 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09134995937347</t>
+    <t xml:space="preserve">1.09135007858276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233070373535</t>
+    <t xml:space="preserve">1.08233058452606</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1463,7 +1460,7 @@
     <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527234077454</t>
+    <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1472,13 +1469,13 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136418819427</t>
+    <t xml:space="preserve">0.992136359214783</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097609519958</t>
+    <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
@@ -1490,22 +1487,22 @@
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019812107086</t>
+    <t xml:space="preserve">0.938019752502441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919981002807617</t>
+    <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432446479797</t>
+    <t xml:space="preserve">0.897432386875153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91096156835556</t>
+    <t xml:space="preserve">0.910961508750916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983117043972015</t>
+    <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
     <t xml:space="preserve">1.01919460296631</t>
@@ -1520,7 +1517,7 @@
     <t xml:space="preserve">1.47918498516083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098133087158</t>
+    <t xml:space="preserve">1.25098145008087</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1550,7 +1547,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12124991416931</t>
+    <t xml:space="preserve">1.1212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1568,22 +1565,25 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051640987396</t>
+    <t xml:space="preserve">1.13051652908325</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19538223743439</t>
+    <t xml:space="preserve">1.1953821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198353767395</t>
+    <t xml:space="preserve">1.11198341846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -29071,7 +29071,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1037" t="s">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1039" t="s">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29227,7 +29227,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29253,7 +29253,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1044" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29305,7 +29305,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1046" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1051" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1061" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1062" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1065" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1068" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29903,7 +29903,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1069" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29929,7 +29929,7 @@
         <v>1.25</v>
       </c>
       <c r="G1070" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29955,7 +29955,7 @@
         <v>1.25</v>
       </c>
       <c r="G1071" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29981,7 +29981,7 @@
         <v>1.25</v>
       </c>
       <c r="G1072" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>1.25</v>
       </c>
       <c r="G1073" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1080" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1081" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>1.25</v>
       </c>
       <c r="G1084" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1088" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30449,7 +30449,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30501,7 +30501,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1092" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30527,7 +30527,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30553,7 +30553,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1094" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30579,7 +30579,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30605,7 +30605,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30631,7 +30631,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30657,7 +30657,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1098" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30683,7 +30683,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1099" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30709,7 +30709,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1100" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30735,7 +30735,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1101" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30761,7 +30761,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1103" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1104" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30839,7 +30839,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1105" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30865,7 +30865,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30891,7 +30891,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1107" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30943,7 +30943,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1109" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1110" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1111" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1112" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31047,7 +31047,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1113" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31073,7 +31073,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1114" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31099,7 +31099,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1117" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31203,7 +31203,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1119" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1120" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1121" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1122" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1125" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1126" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1128" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1129" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1130" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1131" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31541,7 +31541,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1133" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1134" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1136" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1137" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>1.25</v>
       </c>
       <c r="G1138" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1139" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31749,7 +31749,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1140" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31775,7 +31775,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1141" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31801,7 +31801,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1142" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31827,7 +31827,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1143" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31879,7 +31879,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1145" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31931,7 +31931,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1147" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31957,7 +31957,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1148" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31983,7 +31983,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1149" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32009,7 +32009,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1150" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32035,7 +32035,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1151" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1152" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1153" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32113,7 +32113,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1154" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32139,7 +32139,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32165,7 +32165,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1156" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32191,7 +32191,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1157" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32217,7 +32217,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1158" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32243,7 +32243,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1159" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32269,7 +32269,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1160" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32295,7 +32295,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1161" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32321,7 +32321,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1162" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32347,7 +32347,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1163" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32373,7 +32373,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1164" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32399,7 +32399,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1165" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32425,7 +32425,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1166" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32451,7 +32451,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1167" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32477,7 +32477,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1168" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32503,7 +32503,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32529,7 +32529,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1170" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32555,7 +32555,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32581,7 +32581,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1172" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32607,7 +32607,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1173" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32633,7 +32633,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1174" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32659,7 +32659,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1175" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32685,7 +32685,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1176" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32711,7 +32711,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1177" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32737,7 +32737,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32763,7 +32763,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1179" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32789,7 +32789,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1180" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32815,7 +32815,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32841,7 +32841,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1182" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32867,7 +32867,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1183" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32893,7 +32893,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1184" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32919,7 +32919,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1185" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32945,7 +32945,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1186" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32971,7 +32971,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1187" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32997,7 +32997,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1188" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33023,7 +33023,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1189" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33049,7 +33049,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1190" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33075,7 +33075,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33101,7 +33101,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33127,7 +33127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33153,7 +33153,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1194" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33179,7 +33179,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1195" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33205,7 +33205,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1196" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33231,7 +33231,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33257,7 +33257,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1198" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33283,7 +33283,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33309,7 +33309,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33335,7 +33335,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1201" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33361,7 +33361,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1202" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33387,7 +33387,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33413,7 +33413,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1204" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33439,7 +33439,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33465,7 +33465,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33491,7 +33491,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33517,7 +33517,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1208" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33543,7 +33543,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33569,7 +33569,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33595,7 +33595,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1211" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33621,7 +33621,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1212" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33647,7 +33647,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1213" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33673,7 +33673,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1214" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33699,7 +33699,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33725,7 +33725,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33751,7 +33751,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33777,7 +33777,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1218" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33803,7 +33803,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1219" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33829,7 +33829,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1220" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33855,7 +33855,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1221" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33881,7 +33881,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1222" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33907,7 +33907,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1223" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33933,7 +33933,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1224" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33959,7 +33959,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1225" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33985,7 +33985,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1226" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34011,7 +34011,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1227" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34037,7 +34037,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1228" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34063,7 +34063,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1229" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34089,7 +34089,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1230" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34115,7 +34115,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34141,7 +34141,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34167,7 +34167,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1233" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34193,7 +34193,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1234" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34219,7 +34219,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34245,7 +34245,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34271,7 +34271,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1237" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34297,7 +34297,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1238" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34323,7 +34323,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1239" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34349,7 +34349,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1240" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34375,7 +34375,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34401,7 +34401,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1242" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34427,7 +34427,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1243" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34453,7 +34453,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1244" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34479,7 +34479,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34505,7 +34505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1246" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34531,7 +34531,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1247" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34557,7 +34557,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34583,7 +34583,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1249" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34609,7 +34609,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1250" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34635,7 +34635,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1251" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34661,7 +34661,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34687,7 +34687,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1253" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34713,7 +34713,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1254" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34739,7 +34739,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1255" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34765,7 +34765,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1256" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34791,7 +34791,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1257" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34817,7 +34817,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1258" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34843,7 +34843,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1259" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34869,7 +34869,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1260" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34895,7 +34895,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1261" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34921,7 +34921,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1262" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34947,7 +34947,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34973,7 +34973,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1264" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34999,7 +34999,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1265" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35025,7 +35025,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1266" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35051,7 +35051,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35077,7 +35077,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1268" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35103,7 +35103,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1269" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35129,7 +35129,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1270" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35155,7 +35155,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1271" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35181,7 +35181,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1272" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35207,7 +35207,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1273" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35233,7 +35233,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1274" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35259,7 +35259,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1275" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35285,7 +35285,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1276" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35311,7 +35311,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1277" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35337,7 +35337,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1278" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35363,7 +35363,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1279" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35389,7 +35389,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1280" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35415,7 +35415,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1281" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35441,7 +35441,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1282" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35467,7 +35467,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1283" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35493,7 +35493,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1284" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35519,7 +35519,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1285" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35545,7 +35545,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1286" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35571,7 +35571,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35597,7 +35597,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35623,7 +35623,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1289" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35649,7 +35649,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1290" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35675,7 +35675,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1291" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35701,7 +35701,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1292" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35727,7 +35727,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1293" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35753,7 +35753,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1294" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35779,7 +35779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1295" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35805,7 +35805,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1296" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35831,7 +35831,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1297" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35857,7 +35857,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35883,7 +35883,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35909,7 +35909,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1300" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35935,7 +35935,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1301" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35961,7 +35961,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1302" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35987,7 +35987,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1303" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36013,7 +36013,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1304" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36039,7 +36039,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1305" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36065,7 +36065,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1306" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36091,7 +36091,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1307" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36117,7 +36117,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1308" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36143,7 +36143,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1309" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36169,7 +36169,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1310" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36195,7 +36195,7 @@
         <v>1.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36221,7 +36221,7 @@
         <v>1.25</v>
       </c>
       <c r="G1312" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36247,7 +36247,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1313" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36273,7 +36273,7 @@
         <v>1.25</v>
       </c>
       <c r="G1314" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36299,7 +36299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1315" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36325,7 +36325,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1316" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36351,7 +36351,7 @@
         <v>1.25</v>
       </c>
       <c r="G1317" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36377,7 +36377,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36429,7 +36429,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36455,7 +36455,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1321" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36481,7 +36481,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1322" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36507,7 +36507,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1323" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36533,7 +36533,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1324" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36559,7 +36559,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1325" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36585,7 +36585,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36611,7 +36611,7 @@
         <v>1.25</v>
       </c>
       <c r="G1327" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36637,7 +36637,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1328" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36663,7 +36663,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1329" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36689,7 +36689,7 @@
         <v>1.25</v>
       </c>
       <c r="G1330" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36715,7 +36715,7 @@
         <v>1.25</v>
       </c>
       <c r="G1331" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36741,7 +36741,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36767,7 +36767,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36845,7 +36845,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1336" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37053,7 +37053,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1344" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37105,7 +37105,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1346" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37261,7 +37261,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1352" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37287,7 +37287,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1353" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37365,7 +37365,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1356" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37391,7 +37391,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1357" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37443,7 +37443,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1359" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37469,7 +37469,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1360" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37521,7 +37521,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37547,7 +37547,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37573,7 +37573,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38197,7 +38197,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1388" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38223,7 +38223,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1389" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38249,7 +38249,7 @@
         <v>1.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38275,7 +38275,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1391" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38301,7 +38301,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1392" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38353,7 +38353,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1394" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38379,7 +38379,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1395" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38405,7 +38405,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1396" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38431,7 +38431,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1397" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38561,7 +38561,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38587,7 +38587,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38613,7 +38613,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38639,7 +38639,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1405" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38665,7 +38665,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38691,7 +38691,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1407" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38717,7 +38717,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1408" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38743,7 +38743,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1409" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38769,7 +38769,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1410" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38795,7 +38795,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1411" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38821,7 +38821,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1412" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38847,7 +38847,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1413" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38873,7 +38873,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1414" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38899,7 +38899,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1415" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38925,7 +38925,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1416" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38951,7 +38951,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1417" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38977,7 +38977,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1418" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39003,7 +39003,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1419" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39055,7 +39055,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1421" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39081,7 +39081,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1422" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39107,7 +39107,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1423" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39133,7 +39133,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1424" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39159,7 +39159,7 @@
         <v>1.25</v>
       </c>
       <c r="G1425" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39185,7 +39185,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39211,7 +39211,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1427" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39237,7 +39237,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1428" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39263,7 +39263,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1429" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39289,7 +39289,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1430" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39315,7 +39315,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39341,7 +39341,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1432" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39367,7 +39367,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1433" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39471,7 +39471,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39497,7 +39497,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1438" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39523,7 +39523,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1439" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39549,7 +39549,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1440" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39575,7 +39575,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1441" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39601,7 +39601,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1442" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39627,7 +39627,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1443" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39653,7 +39653,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1444" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39679,7 +39679,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1445" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39705,7 +39705,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1446" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39731,7 +39731,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1447" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39757,7 +39757,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1448" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39783,7 +39783,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1449" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39809,7 +39809,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1450" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39835,7 +39835,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1451" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39861,7 +39861,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1452" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39887,7 +39887,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1453" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39913,7 +39913,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1454" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39939,7 +39939,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1455" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39965,7 +39965,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1456" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39991,7 +39991,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1457" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40173,7 +40173,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1464" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40251,7 +40251,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1467" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40277,7 +40277,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1468" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40537,7 +40537,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41213,7 +41213,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1504" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41525,7 +41525,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1516" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41603,7 +41603,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1519" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41629,7 +41629,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41655,7 +41655,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1521" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41681,7 +41681,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1522" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41785,7 +41785,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1526" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41811,7 +41811,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1527" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41915,7 +41915,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1531" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41941,7 +41941,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1532" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42123,7 +42123,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1539" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42175,7 +42175,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1541" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42279,7 +42279,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1545" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42331,7 +42331,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1547" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42357,7 +42357,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1548" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42383,7 +42383,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1549" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42409,7 +42409,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1550" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42435,7 +42435,7 @@
         <v>1.25</v>
       </c>
       <c r="G1551" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42461,7 +42461,7 @@
         <v>1.25</v>
       </c>
       <c r="G1552" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42487,7 +42487,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1553" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42513,7 +42513,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1554" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42539,7 +42539,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1555" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42565,7 +42565,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1556" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42591,7 +42591,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42617,7 +42617,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1558" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42643,7 +42643,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42669,7 +42669,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1560" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42695,7 +42695,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42721,7 +42721,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1562" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42799,7 +42799,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42825,7 +42825,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1566" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42851,7 +42851,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1567" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42877,7 +42877,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42903,7 +42903,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1569" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42929,7 +42929,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1570" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42955,7 +42955,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1571" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42981,7 +42981,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1572" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43007,7 +43007,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1573" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43033,7 +43033,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1574" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43059,7 +43059,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1575" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43085,7 +43085,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1576" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43111,7 +43111,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1577" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43137,7 +43137,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1578" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43163,7 +43163,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1579" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43189,7 +43189,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1580" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43215,7 +43215,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1581" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43241,7 +43241,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1582" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43267,7 +43267,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1583" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43293,7 +43293,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1584" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43319,7 +43319,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1585" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43345,7 +43345,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1586" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43371,7 +43371,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43527,7 +43527,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1593" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43553,7 +43553,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1594" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43605,7 +43605,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1596" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43631,7 +43631,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43683,7 +43683,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1599" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43787,7 +43787,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43813,7 +43813,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1604" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43839,7 +43839,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43865,7 +43865,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1606" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43891,7 +43891,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1607" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43917,7 +43917,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43943,7 +43943,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1609" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44021,7 +44021,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1612" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44047,7 +44047,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1613" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44073,7 +44073,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44099,7 +44099,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1615" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44125,7 +44125,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1616" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44177,7 +44177,7 @@
         <v>1.25</v>
       </c>
       <c r="G1618" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44203,7 +44203,7 @@
         <v>1.25</v>
       </c>
       <c r="G1619" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44229,7 +44229,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1620" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44255,7 +44255,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44307,7 +44307,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44437,7 +44437,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1628" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44489,7 +44489,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1630" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44619,7 +44619,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1635" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44645,7 +44645,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44671,7 +44671,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1637" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44697,7 +44697,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44723,7 +44723,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1639" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44749,7 +44749,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1640" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44775,7 +44775,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1641" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44801,7 +44801,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45009,7 +45009,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45061,7 +45061,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1652" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45087,7 +45087,7 @@
         <v>1.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45113,7 +45113,7 @@
         <v>1.25</v>
       </c>
       <c r="G1654" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45139,7 +45139,7 @@
         <v>1.25</v>
       </c>
       <c r="G1655" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45165,7 +45165,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1656" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45191,7 +45191,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1657" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45217,7 +45217,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45243,7 +45243,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45269,7 +45269,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1660" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45295,7 +45295,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1661" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45321,7 +45321,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1662" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45347,7 +45347,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1663" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45373,7 +45373,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45425,7 +45425,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45451,7 +45451,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45477,7 +45477,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45503,7 +45503,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45555,7 +45555,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1671" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45581,7 +45581,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1672" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45633,7 +45633,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1674" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45685,7 +45685,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1676" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45737,7 +45737,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45815,7 +45815,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1681" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45867,7 +45867,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1683" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45893,7 +45893,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1684" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45919,7 +45919,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1685" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45997,7 +45997,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1688" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46153,7 +46153,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1694" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46179,7 +46179,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1695" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46205,7 +46205,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1696" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46231,7 +46231,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46283,7 +46283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1699" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46335,7 +46335,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46465,7 +46465,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1706" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46517,7 +46517,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1708" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46621,7 +46621,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1712" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46673,7 +46673,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1714" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46699,7 +46699,7 @@
         <v>1.25</v>
       </c>
       <c r="G1715" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46725,7 +46725,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1716" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46751,7 +46751,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46777,7 +46777,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46803,7 +46803,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46829,7 +46829,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46855,7 +46855,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46881,7 +46881,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46907,7 +46907,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46959,7 +46959,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1725" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46985,7 +46985,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1726" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47011,7 +47011,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1727" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47141,7 +47141,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1732" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47193,7 +47193,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1734" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47219,7 +47219,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47401,7 +47401,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1742" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47427,7 +47427,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1743" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47453,7 +47453,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1744" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47479,7 +47479,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1745" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47505,7 +47505,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1746" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47531,7 +47531,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1747" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47557,7 +47557,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1748" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47583,7 +47583,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1749" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47609,7 +47609,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1750" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47635,7 +47635,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1751" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47661,7 +47661,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1752" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47687,7 +47687,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1753" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47713,7 +47713,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1754" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47739,7 +47739,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1755" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47895,7 +47895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1761" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47947,7 +47947,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47999,7 +47999,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1765" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48025,7 +48025,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1766" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48051,7 +48051,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1767" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48077,7 +48077,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1768" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48103,7 +48103,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1769" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48233,7 +48233,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1774" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48259,7 +48259,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1775" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48389,7 +48389,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1780" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48493,7 +48493,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1784" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48519,7 +48519,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1785" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48545,7 +48545,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1786" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48571,7 +48571,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1787" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48597,7 +48597,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1788" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48623,7 +48623,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1789" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48675,7 +48675,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1791" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48701,7 +48701,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1792" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48935,7 +48935,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1801" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48961,7 +48961,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48987,7 +48987,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1803" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49013,7 +49013,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1804" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49039,7 +49039,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1805" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49065,7 +49065,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49091,7 +49091,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1807" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49117,7 +49117,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1808" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49143,7 +49143,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1809" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49169,7 +49169,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1810" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49195,7 +49195,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1811" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49221,7 +49221,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1812" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49247,7 +49247,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1813" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49325,7 +49325,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49351,7 +49351,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1817" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49377,7 +49377,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1818" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49403,7 +49403,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1819" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49429,7 +49429,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1820" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49455,7 +49455,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1821" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49481,7 +49481,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1822" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49507,7 +49507,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1823" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49533,7 +49533,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1824" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49559,7 +49559,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1825" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49585,7 +49585,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1826" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49611,7 +49611,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49637,7 +49637,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1828" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49663,7 +49663,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1829" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49689,7 +49689,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49715,7 +49715,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49741,7 +49741,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49767,7 +49767,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49793,7 +49793,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1834" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49819,7 +49819,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1835" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49845,7 +49845,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1836" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49871,7 +49871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1837" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49897,7 +49897,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1838" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49923,7 +49923,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49949,7 +49949,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49975,7 +49975,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50001,7 +50001,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1842" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50027,7 +50027,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1843" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50053,7 +50053,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1844" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50079,7 +50079,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1845" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50105,7 +50105,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1846" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50131,7 +50131,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1847" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50157,7 +50157,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1848" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50183,7 +50183,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1849" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50209,7 +50209,7 @@
         <v>1.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50235,7 +50235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1851" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50391,7 +50391,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50443,7 +50443,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1859" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50495,7 +50495,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50651,7 +50651,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50677,7 +50677,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50859,7 +50859,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1875" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50885,7 +50885,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1876" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50911,7 +50911,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1877" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50937,7 +50937,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1878" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50963,7 +50963,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1879" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50989,7 +50989,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1880" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51015,7 +51015,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1881" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51041,7 +51041,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1882" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51067,7 +51067,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1883" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51093,7 +51093,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1884" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51119,7 +51119,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1885" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51145,7 +51145,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1886" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51171,7 +51171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1887" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51197,7 +51197,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1888" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51223,7 +51223,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1889" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51249,7 +51249,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1890" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51275,7 +51275,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1891" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51301,7 +51301,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1892" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51327,7 +51327,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1893" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51353,7 +51353,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1894" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51379,7 +51379,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1895" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51405,7 +51405,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1896" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51431,7 +51431,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1897" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51457,7 +51457,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1898" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51483,7 +51483,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1899" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51509,7 +51509,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1900" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51535,7 +51535,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1901" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51561,7 +51561,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1902" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51587,7 +51587,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1903" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51613,7 +51613,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1904" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51639,7 +51639,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1905" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51665,7 +51665,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1906" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51691,7 +51691,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1907" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51717,7 +51717,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1908" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51743,7 +51743,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1909" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51769,7 +51769,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1910" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51795,7 +51795,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51821,7 +51821,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1912" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51847,7 +51847,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51873,7 +51873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51899,7 +51899,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1915" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51925,7 +51925,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1916" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51951,7 +51951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1917" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51977,7 +51977,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52003,7 +52003,7 @@
         <v>1.25</v>
       </c>
       <c r="G1919" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52029,7 +52029,7 @@
         <v>1.25</v>
       </c>
       <c r="G1920" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52055,7 +52055,7 @@
         <v>1.25</v>
       </c>
       <c r="G1921" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52081,7 +52081,7 @@
         <v>1.25</v>
       </c>
       <c r="G1922" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52107,7 +52107,7 @@
         <v>1.25</v>
       </c>
       <c r="G1923" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52133,7 +52133,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1924" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52159,7 +52159,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1925" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52185,7 +52185,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52211,7 +52211,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52237,7 +52237,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52263,7 +52263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52289,7 +52289,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1930" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52315,7 +52315,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1931" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52341,7 +52341,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1932" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52367,7 +52367,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52393,7 +52393,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52419,7 +52419,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52445,7 +52445,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1936" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52471,7 +52471,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1937" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52497,7 +52497,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1938" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52523,7 +52523,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1939" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52549,7 +52549,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1940" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52575,7 +52575,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1941" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52601,7 +52601,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1942" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52627,7 +52627,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1943" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52653,7 +52653,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1944" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52679,7 +52679,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1945" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52705,7 +52705,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1946" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52731,7 +52731,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1947" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52757,7 +52757,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1948" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52783,7 +52783,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1949" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52809,7 +52809,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1950" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52835,7 +52835,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1951" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52861,7 +52861,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1952" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52887,7 +52887,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1953" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52913,7 +52913,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1954" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52939,7 +52939,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1955" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52965,7 +52965,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1956" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52991,7 +52991,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53017,7 +53017,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1958" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53043,7 +53043,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53069,7 +53069,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53095,7 +53095,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1961" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53121,7 +53121,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1962" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53147,7 +53147,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1963" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53173,7 +53173,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53199,7 +53199,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1965" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53225,7 +53225,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1966" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53251,7 +53251,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1967" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53277,7 +53277,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1968" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53303,7 +53303,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1969" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53329,7 +53329,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1970" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53355,7 +53355,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1971" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53381,7 +53381,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1972" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53407,7 +53407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1973" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53433,7 +53433,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1974" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53459,7 +53459,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1975" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53485,7 +53485,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1976" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53511,7 +53511,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53537,7 +53537,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53563,7 +53563,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53589,7 +53589,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53615,7 +53615,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53641,7 +53641,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53667,7 +53667,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53693,7 +53693,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1984" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53719,7 +53719,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53745,7 +53745,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53771,7 +53771,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1987" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53797,7 +53797,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1988" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53823,7 +53823,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1989" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53849,7 +53849,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1990" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53875,7 +53875,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53901,7 +53901,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1992" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53927,7 +53927,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53953,7 +53953,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1994" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53979,7 +53979,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1995" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54005,7 +54005,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1996" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54031,7 +54031,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1997" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54057,7 +54057,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54083,7 +54083,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1999" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54109,7 +54109,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54135,7 +54135,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2001" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54161,7 +54161,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2002" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54187,7 +54187,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2003" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54213,7 +54213,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2004" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54239,7 +54239,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2005" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54265,7 +54265,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2006" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54291,7 +54291,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54317,7 +54317,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54343,7 +54343,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2009" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54369,7 +54369,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2010" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54395,7 +54395,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2011" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54421,7 +54421,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2012" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54447,7 +54447,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2013" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54473,7 +54473,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2014" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54499,7 +54499,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54525,7 +54525,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2016" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54551,7 +54551,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2017" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54577,7 +54577,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2018" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54603,7 +54603,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2019" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54629,7 +54629,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2020" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54655,7 +54655,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2021" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54681,7 +54681,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54707,7 +54707,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2023" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54733,7 +54733,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2024" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54759,7 +54759,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2025" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54785,7 +54785,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54811,7 +54811,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54837,7 +54837,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54863,7 +54863,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2029" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54889,7 +54889,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2030" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54915,7 +54915,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2031" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54941,7 +54941,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2032" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54967,7 +54967,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2033" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54993,7 +54993,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2034" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55019,7 +55019,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2035" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55045,7 +55045,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2036" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55071,7 +55071,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2037" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55097,7 +55097,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2038" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55123,7 +55123,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2039" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55149,7 +55149,7 @@
         <v>1.25</v>
       </c>
       <c r="G2040" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55175,7 +55175,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55201,7 +55201,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55227,7 +55227,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2043" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55253,7 +55253,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2044" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55279,7 +55279,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2045" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55305,7 +55305,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2046" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55331,7 +55331,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55357,7 +55357,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55383,7 +55383,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55409,7 +55409,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2050" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55435,7 +55435,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55461,7 +55461,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2052" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55487,7 +55487,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55513,7 +55513,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2054" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55539,7 +55539,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2055" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55565,7 +55565,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55591,7 +55591,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55617,7 +55617,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2058" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55643,7 +55643,7 @@
         <v>1.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55669,7 +55669,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2060" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55695,7 +55695,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55721,7 +55721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2062" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55747,7 +55747,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2063" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55773,7 +55773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2064" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55799,7 +55799,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2065" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55825,7 +55825,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2066" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55851,7 +55851,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2067" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55877,7 +55877,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2068" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55903,7 +55903,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2069" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55929,7 +55929,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55955,7 +55955,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2071" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55981,7 +55981,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2072" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56007,7 +56007,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2073" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56033,7 +56033,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2074" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56059,7 +56059,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2075" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56085,7 +56085,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2076" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56111,7 +56111,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2077" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56137,7 +56137,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2078" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56163,7 +56163,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2079" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56189,7 +56189,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2080" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56215,7 +56215,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56241,7 +56241,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56267,7 +56267,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2083" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56293,7 +56293,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2084" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56319,7 +56319,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2085" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56345,7 +56345,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2086" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56371,7 +56371,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2087" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56397,7 +56397,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2088" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56423,7 +56423,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2089" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56449,7 +56449,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2090" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56475,7 +56475,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2091" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56501,7 +56501,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2092" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56527,7 +56527,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2093" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56553,7 +56553,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2094" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56579,7 +56579,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2095" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56605,7 +56605,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2096" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56631,7 +56631,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2097" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56657,7 +56657,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2098" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56683,7 +56683,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2099" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56709,7 +56709,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2100" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56735,7 +56735,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56761,7 +56761,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2102" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56787,7 +56787,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2103" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56813,7 +56813,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2104" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56839,7 +56839,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56865,7 +56865,7 @@
         <v>1.25</v>
       </c>
       <c r="G2106" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56891,7 +56891,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2107" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56917,7 +56917,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2108" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56943,7 +56943,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2109" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56969,7 +56969,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2110" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56995,7 +56995,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2111" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57021,7 +57021,7 @@
         <v>1.25</v>
       </c>
       <c r="G2112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57047,7 +57047,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2113" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57073,7 +57073,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2114" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57099,7 +57099,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2115" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57125,7 +57125,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2116" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57151,7 +57151,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2117" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57177,7 +57177,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2118" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57203,7 +57203,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2119" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57229,7 +57229,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2120" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57255,7 +57255,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57281,7 +57281,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2122" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57307,7 +57307,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2123" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57333,7 +57333,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2124" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57359,7 +57359,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57385,7 +57385,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2126" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57411,7 +57411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2127" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57437,7 +57437,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57463,7 +57463,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2129" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57489,7 +57489,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2130" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57515,7 +57515,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57541,7 +57541,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57567,7 +57567,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2133" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57593,7 +57593,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -66909,7 +66909,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6307523148</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>2000</v>
@@ -66930,6 +66930,32 @@
         <v>588</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6240046296</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>578</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47076916694641</t>
+    <t xml:space="preserve">1.4707692861557</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
@@ -50,103 +50,103 @@
     <t xml:space="preserve">1.48684322834015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424736499786</t>
+    <t xml:space="preserve">1.44424712657928</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236224651337</t>
+    <t xml:space="preserve">1.38236248493195</t>
   </si>
   <si>
     <t xml:space="preserve">1.37593269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414041996002</t>
+    <t xml:space="preserve">1.33414030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744750499725</t>
+    <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628842353821</t>
+    <t xml:space="preserve">1.36628830432892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290283203125</t>
+    <t xml:space="preserve">1.41290295124054</t>
   </si>
   <si>
     <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647327899933</t>
+    <t xml:space="preserve">1.40647315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44585454463959</t>
+    <t xml:space="preserve">1.4458544254303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39843642711639</t>
+    <t xml:space="preserve">1.39843618869781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780335426331</t>
+    <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726264953613</t>
+    <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002926826477</t>
+    <t xml:space="preserve">1.31002950668335</t>
   </si>
   <si>
     <t xml:space="preserve">1.34217739105225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021424293518</t>
+    <t xml:space="preserve">1.35021436214447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3212810754776</t>
+    <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557708263397</t>
+    <t xml:space="preserve">1.38557696342468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273243427277</t>
+    <t xml:space="preserve">1.46273231506348</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693583488464</t>
+    <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889862537384</t>
+    <t xml:space="preserve">1.49889874458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.472376704216</t>
+    <t xml:space="preserve">1.47237646579742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49488008022308</t>
+    <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274665355682</t>
+    <t xml:space="preserve">1.55274641513824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543488502502</t>
+    <t xml:space="preserve">1.61543500423431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169392108917</t>
+    <t xml:space="preserve">1.67169380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490887641907</t>
+    <t xml:space="preserve">1.67490875720978</t>
   </si>
   <si>
     <t xml:space="preserve">1.64597570896149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113911628723</t>
+    <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702808380127</t>
+    <t xml:space="preserve">1.52702820301056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095426082611</t>
+    <t xml:space="preserve">1.51095402240753</t>
   </si>
   <si>
     <t xml:space="preserve">1.45630264282227</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601916313171</t>
+    <t xml:space="preserve">1.45601892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426239490509</t>
+    <t xml:space="preserve">1.43426251411438</t>
   </si>
   <si>
     <t xml:space="preserve">1.4083217382431</t>
@@ -170,52 +170,52 @@
     <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091523647308</t>
+    <t xml:space="preserve">1.43091511726379</t>
   </si>
   <si>
     <t xml:space="preserve">1.42840492725372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41334247589111</t>
+    <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497469902039</t>
+    <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
     <t xml:space="preserve">1.36313498020172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560381412506</t>
+    <t xml:space="preserve">1.35560393333435</t>
   </si>
   <si>
     <t xml:space="preserve">1.37233972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886802196503</t>
+    <t xml:space="preserve">1.33886814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288600921631</t>
+    <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32547950744629</t>
+    <t xml:space="preserve">1.32547926902771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3221321105957</t>
+    <t xml:space="preserve">1.32213222980499</t>
   </si>
   <si>
     <t xml:space="preserve">1.26439356803894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702830314636</t>
+    <t xml:space="preserve">1.29702842235565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539619922638</t>
+    <t xml:space="preserve">1.30539631843567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397171020508</t>
+    <t xml:space="preserve">1.36397182941437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41250574588776</t>
+    <t xml:space="preserve">1.41250586509705</t>
   </si>
   <si>
     <t xml:space="preserve">1.3807076215744</t>
@@ -224,49 +224,49 @@
     <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2719247341156</t>
+    <t xml:space="preserve">1.27192461490631</t>
   </si>
   <si>
     <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506415843964</t>
+    <t xml:space="preserve">1.22506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20498132705688</t>
+    <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
     <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841155529022</t>
+    <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845291137695</t>
+    <t xml:space="preserve">1.23845303058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.23008513450623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824541568756</t>
+    <t xml:space="preserve">1.18824529647827</t>
   </si>
   <si>
     <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171723842621</t>
+    <t xml:space="preserve">1.22171711921692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816246509552</t>
+    <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226316452026</t>
+    <t xml:space="preserve">1.15226340293884</t>
   </si>
   <si>
     <t xml:space="preserve">1.14222192764282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150938510895</t>
+    <t xml:space="preserve">1.17150950431824</t>
   </si>
   <si>
     <t xml:space="preserve">1.12967002391815</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">1.11293399333954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04850113391876</t>
+    <t xml:space="preserve">1.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343880176544</t>
+    <t xml:space="preserve">1.03343892097473</t>
   </si>
   <si>
     <t xml:space="preserve">1.02423405647278</t>
@@ -287,25 +287,25 @@
     <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435860157013</t>
+    <t xml:space="preserve">1.05435848236084</t>
   </si>
   <si>
     <t xml:space="preserve">1.08364617824554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06440007686615</t>
+    <t xml:space="preserve">1.06440019607544</t>
   </si>
   <si>
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0376228094101</t>
+    <t xml:space="preserve">1.03762269020081</t>
   </si>
   <si>
     <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984068155288696</t>
+    <t xml:space="preserve">0.984068095684052</t>
   </si>
   <si>
     <t xml:space="preserve">0.999967157840729</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">1.01251900196075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00415086746216</t>
+    <t xml:space="preserve">1.00415110588074</t>
   </si>
   <si>
     <t xml:space="preserve">0.958127379417419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842612743378</t>
+    <t xml:space="preserve">0.969842553138733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738686084747</t>
+    <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
     <t xml:space="preserve">0.888673663139343</t>
@@ -332,85 +332,85 @@
     <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269911766052</t>
+    <t xml:space="preserve">0.952269852161407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103891372681</t>
+    <t xml:space="preserve">0.912103950977325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89955198764801</t>
+    <t xml:space="preserve">0.899552047252655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204829216003</t>
+    <t xml:space="preserve">0.896204888820648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937870979309</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90875655412674</t>
+    <t xml:space="preserve">0.908756613731384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596332550049</t>
+    <t xml:space="preserve">0.950596392154694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124629020691</t>
   </si>
   <si>
     <t xml:space="preserve">0.920471847057343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332184314728</t>
+    <t xml:space="preserve">0.967332065105438</t>
   </si>
   <si>
     <t xml:space="preserve">0.962311327457428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0551952123642</t>
+    <t xml:space="preserve">1.05519545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599082946777</t>
+    <t xml:space="preserve">0.991599023342133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088773727417</t>
+    <t xml:space="preserve">0.989088714122772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0016405582428</t>
+    <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783090591431</t>
+    <t xml:space="preserve">0.995783030986786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99076235294342</t>
+    <t xml:space="preserve">0.99076247215271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207520008087</t>
+    <t xml:space="preserve">0.937207698822021</t>
   </si>
   <si>
     <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391587257385</t>
+    <t xml:space="preserve">0.94139164686203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251805305481</t>
+    <t xml:space="preserve">0.988251864910126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352862358093</t>
+    <t xml:space="preserve">0.972352802753448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168795108795</t>
+    <t xml:space="preserve">0.968168973922729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9757000207901</t>
+    <t xml:space="preserve">0.975700080394745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98323118686676</t>
+    <t xml:space="preserve">0.983231008052826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415075302124</t>
+    <t xml:space="preserve">0.987415134906769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005763530731</t>
+    <t xml:space="preserve">0.969005703926086</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">0.953943431377411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854249000549</t>
+    <t xml:space="preserve">1.0585423707962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937933921814</t>
+    <t xml:space="preserve">1.05937945842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507078647614</t>
+    <t xml:space="preserve">1.02507090568542</t>
   </si>
   <si>
     <t xml:space="preserve">1.05268502235413</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1480792760849</t>
+    <t xml:space="preserve">1.14807915687561</t>
   </si>
   <si>
     <t xml:space="preserve">1.19577658176422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661319255829</t>
+    <t xml:space="preserve">1.19661331176758</t>
   </si>
   <si>
     <t xml:space="preserve">1.25602555274963</t>
@@ -452,25 +452,25 @@
     <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2133492231369</t>
+    <t xml:space="preserve">1.21334910392761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753299236298</t>
+    <t xml:space="preserve">1.21753323078156</t>
   </si>
   <si>
     <t xml:space="preserve">1.15644717216492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15310001373291</t>
+    <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493961334229</t>
+    <t xml:space="preserve">1.19493973255157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15477359294891</t>
+    <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
     <t xml:space="preserve">1.1464056968689</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314148902893</t>
+    <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2376161813736</t>
+    <t xml:space="preserve">1.23761606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518870353699</t>
+    <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
     <t xml:space="preserve">1.23594260215759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146802902222</t>
+    <t xml:space="preserve">1.16146790981293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13385379314423</t>
+    <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
     <t xml:space="preserve">1.13803780078888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799644470215</t>
+    <t xml:space="preserve">1.12799632549286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130212783813</t>
+    <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.17653036117554</t>
@@ -512,28 +512,28 @@
     <t xml:space="preserve">1.40581130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576983451843</t>
+    <t xml:space="preserve">1.39577007293701</t>
   </si>
   <si>
     <t xml:space="preserve">1.39911711215973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39744353294373</t>
+    <t xml:space="preserve">1.39744341373444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46020293235779</t>
+    <t xml:space="preserve">1.4602028131485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534821510315</t>
+    <t xml:space="preserve">1.49534809589386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685589313507</t>
+    <t xml:space="preserve">1.45685577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865389823914</t>
+    <t xml:space="preserve">1.48865377902985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48949074745178</t>
+    <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
     <t xml:space="preserve">1.47275471687317</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174545764923</t>
+    <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684902667999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438031196594</t>
+    <t xml:space="preserve">1.66438019275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550748825073</t>
+    <t xml:space="preserve">1.73550772666931</t>
   </si>
   <si>
     <t xml:space="preserve">1.75726425647736</t>
@@ -572,19 +572,19 @@
     <t xml:space="preserve">1.65099167823792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60078430175781</t>
+    <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
     <t xml:space="preserve">1.67358505725861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003040313721</t>
+    <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
     <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6166832447052</t>
+    <t xml:space="preserve">1.61668312549591</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664165019989</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362653255463</t>
+    <t xml:space="preserve">1.68362665176392</t>
   </si>
   <si>
     <t xml:space="preserve">1.71542465686798</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">1.73718118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224363803864</t>
+    <t xml:space="preserve">1.75224375724792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052834510803</t>
+    <t xml:space="preserve">1.74052846431732</t>
   </si>
   <si>
     <t xml:space="preserve">1.72379243373871</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220216274261</t>
+    <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
     <t xml:space="preserve">1.74906098842621</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">1.8005039691925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335618972778</t>
+    <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193019866943</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323570251465</t>
+    <t xml:space="preserve">2.37323594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926283836365</t>
+    <t xml:space="preserve">2.46926259994507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421922683716</t>
+    <t xml:space="preserve">2.82421898841858</t>
   </si>
   <si>
     <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505163192749</t>
+    <t xml:space="preserve">2.73505139350891</t>
   </si>
   <si>
     <t xml:space="preserve">2.64416885375977</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">2.47783660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46068859100342</t>
+    <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067172050476</t>
+    <t xml:space="preserve">2.40067195892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.36466193199158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929634094238</t>
+    <t xml:space="preserve">2.5892961025238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78649425506592</t>
+    <t xml:space="preserve">2.7864944934845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503428459167</t>
+    <t xml:space="preserve">2.67503452301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4624035358429</t>
+    <t xml:space="preserve">2.46240377426147</t>
   </si>
   <si>
     <t xml:space="preserve">2.47097754478455</t>
@@ -689,64 +689,64 @@
     <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953468322754</t>
+    <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211482048035</t>
+    <t xml:space="preserve">2.45211505889893</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214879989624</t>
+    <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641061782837</t>
+    <t xml:space="preserve">2.48641014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4349672794342</t>
+    <t xml:space="preserve">2.43496775627136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4555447101593</t>
+    <t xml:space="preserve">2.45554447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4572594165802</t>
+    <t xml:space="preserve">2.45725917816162</t>
   </si>
   <si>
     <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897388458252</t>
+    <t xml:space="preserve">2.4589741230011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440695762634</t>
+    <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56186008453369</t>
+    <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781973838806</t>
+    <t xml:space="preserve">2.41781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639327049255</t>
+    <t xml:space="preserve">2.42639350891113</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208131790161</t>
+    <t xml:space="preserve">2.33208155632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.31836342811584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28063869476318</t>
+    <t xml:space="preserve">2.2806384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865214347839</t>
+    <t xml:space="preserve">2.32865190505981</t>
   </si>
   <si>
     <t xml:space="preserve">2.31321883201599</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0577187538147</t>
+    <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544372558594</t>
@@ -776,22 +776,22 @@
     <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515501022339</t>
+    <t xml:space="preserve">2.08515524864197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629300117493</t>
+    <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
     <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887337684631</t>
+    <t xml:space="preserve">2.09887313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799059867859</t>
+    <t xml:space="preserve">2.00799083709717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05086016654968</t>
+    <t xml:space="preserve">2.05085968971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.02342343330383</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603802680969</t>
+    <t xml:space="preserve">2.17603778839111</t>
   </si>
   <si>
     <t xml:space="preserve">2.08172559738159</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888977050781</t>
+    <t xml:space="preserve">2.15889000892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12287974357605</t>
+    <t xml:space="preserve">2.12287998199463</t>
   </si>
   <si>
     <t xml:space="preserve">2.1537458896637</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">2.15203094482422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917848587036</t>
+    <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062134742737</t>
+    <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491714477539</t>
+    <t xml:space="preserve">2.25491690635681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28235340118408</t>
+    <t xml:space="preserve">2.2823531627655</t>
   </si>
   <si>
     <t xml:space="preserve">2.23776912689209</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.22233629226685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089366912842</t>
+    <t xml:space="preserve">2.17089343070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.18975591659546</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634289741516</t>
+    <t xml:space="preserve">2.24634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065556526184</t>
+    <t xml:space="preserve">2.34065508842468</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206468582153</t>
+    <t xml:space="preserve">2.27206492424011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175957679749</t>
+    <t xml:space="preserve">2.20175933837891</t>
   </si>
   <si>
     <t xml:space="preserve">2.2086181640625</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462819099426</t>
+    <t xml:space="preserve">2.24462842941284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4366819858551</t>
+    <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471254348755</t>
+    <t xml:space="preserve">2.54471206665039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384663581848</t>
+    <t xml:space="preserve">2.5138463973999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50355815887451</t>
+    <t xml:space="preserve">2.50355792045593</t>
   </si>
   <si>
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326920509338</t>
+    <t xml:space="preserve">2.49326968193054</t>
   </si>
   <si>
     <t xml:space="preserve">2.47269225120544</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922885894775</t>
+    <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3578028678894</t>
+    <t xml:space="preserve">2.35780262947083</t>
   </si>
   <si>
     <t xml:space="preserve">2.40410161018372</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3063600063324</t>
+    <t xml:space="preserve">2.30636024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38866853713989</t>
+    <t xml:space="preserve">2.38866877555847</t>
   </si>
   <si>
     <t xml:space="preserve">2.31493401527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832921028137</t>
+    <t xml:space="preserve">2.19832968711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.1348831653595</t>
@@ -971,43 +971,43 @@
     <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914546012878</t>
+    <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90339004993439</t>
+    <t xml:space="preserve">1.9033899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805543422699</t>
+    <t xml:space="preserve">1.98055481910706</t>
   </si>
   <si>
     <t xml:space="preserve">1.97198069095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053747177124</t>
+    <t xml:space="preserve">1.92053759098053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912811279297</t>
+    <t xml:space="preserve">1.98912823200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196405887604</t>
+    <t xml:space="preserve">1.91196382045746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911159992218</t>
+    <t xml:space="preserve">1.92911148071289</t>
   </si>
   <si>
     <t xml:space="preserve">1.88624238967896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481604099274</t>
+    <t xml:space="preserve">1.89481627941132</t>
   </si>
   <si>
     <t xml:space="preserve">1.86909472942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194706916809</t>
+    <t xml:space="preserve">1.85194730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625926017761</t>
+    <t xml:space="preserve">1.94625902175903</t>
   </si>
   <si>
     <t xml:space="preserve">1.96340680122375</t>
@@ -1016,64 +1016,64 @@
     <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249334335327</t>
+    <t xml:space="preserve">2.04249358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236502170563</t>
+    <t xml:space="preserve">1.97236514091492</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840606689453</t>
+    <t xml:space="preserve">1.85840618610382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470447063446</t>
+    <t xml:space="preserve">1.88470435142517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02496147155762</t>
+    <t xml:space="preserve">2.0249617099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866330623627</t>
+    <t xml:space="preserve">1.99866306781769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606697559357</t>
+    <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853462696075</t>
+    <t xml:space="preserve">1.92853474617004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717224121094</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223670005798</t>
+    <t xml:space="preserve">1.90223658084869</t>
   </si>
   <si>
     <t xml:space="preserve">1.87593841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334184646606</t>
+    <t xml:space="preserve">1.82334196567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976892948151</t>
+    <t xml:space="preserve">1.91976857185364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84964001178741</t>
+    <t xml:space="preserve">1.84963989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730056285858</t>
+    <t xml:space="preserve">1.93730080127716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989737033844</t>
+    <t xml:space="preserve">1.98989701271057</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78827774524689</t>
+    <t xml:space="preserve">1.7882776260376</t>
   </si>
   <si>
     <t xml:space="preserve">1.77074551582336</t>
@@ -1085,28 +1085,28 @@
     <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733937263489</t>
+    <t xml:space="preserve">1.6173392534256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542429447174</t>
+    <t xml:space="preserve">1.59542417526245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62172245979309</t>
+    <t xml:space="preserve">1.6217223405838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65678668022156</t>
+    <t xml:space="preserve">1.65678656101227</t>
   </si>
   <si>
     <t xml:space="preserve">1.68308484554291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63487160205841</t>
+    <t xml:space="preserve">1.63487148284912</t>
   </si>
   <si>
     <t xml:space="preserve">1.66555273532867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69185090065002</t>
+    <t xml:space="preserve">1.69185078144073</t>
   </si>
   <si>
     <t xml:space="preserve">1.66116964817047</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419023036957</t>
+    <t xml:space="preserve">1.60419034957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104108810425</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993570327759</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">1.70061707496643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64363753795624</t>
+    <t xml:space="preserve">1.64363765716553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295628547668</t>
+    <t xml:space="preserve">1.61295640468597</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">1.58665800094604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597674846649</t>
+    <t xml:space="preserve">1.55597686767578</t>
   </si>
   <si>
     <t xml:space="preserve">1.42010283470154</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">1.24478149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20971727371216</t>
+    <t xml:space="preserve">1.20971715450287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2929949760437</t>
+    <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
     <t xml:space="preserve">1.38065552711487</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325185775757</t>
+    <t xml:space="preserve">1.43325197696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38942170143127</t>
+    <t xml:space="preserve">1.38942158222198</t>
   </si>
   <si>
     <t xml:space="preserve">1.38503861427307</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763482570648</t>
+    <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44640100002289</t>
+    <t xml:space="preserve">1.4464008808136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201791286469</t>
+    <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4507839679718</t>
+    <t xml:space="preserve">1.45078408718109</t>
   </si>
   <si>
     <t xml:space="preserve">1.39380466938019</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406155109406</t>
+    <t xml:space="preserve">1.53406178951263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5121465921402</t>
+    <t xml:space="preserve">1.51214647293091</t>
   </si>
   <si>
     <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721069335938</t>
+    <t xml:space="preserve">1.54721081256866</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">1.55159378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035995483398</t>
+    <t xml:space="preserve">1.56035983562469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091264724731</t>
+    <t xml:space="preserve">1.52091252803802</t>
   </si>
   <si>
     <t xml:space="preserve">1.48584830760956</t>
@@ -1250,52 +1250,52 @@
     <t xml:space="preserve">1.51652956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56912589073181</t>
+    <t xml:space="preserve">1.5691260099411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776350498199</t>
+    <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529573440552</t>
+    <t xml:space="preserve">1.52529561519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899733066559</t>
+    <t xml:space="preserve">1.49899744987488</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545706748962</t>
+    <t xml:space="preserve">1.60545694828033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5693793296814</t>
+    <t xml:space="preserve">1.56937921047211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232096672058</t>
+    <t xml:space="preserve">1.54232108592987</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46114635467529</t>
+    <t xml:space="preserve">1.461146235466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624322891235</t>
+    <t xml:space="preserve">1.50624334812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016561031342</t>
+    <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310736656189</t>
+    <t xml:space="preserve">1.44310748577118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604924201965</t>
+    <t xml:space="preserve">1.41604912281036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801013469696</t>
+    <t xml:space="preserve">1.39801025390625</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702974796295</t>
+    <t xml:space="preserve">1.40702962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38899087905884</t>
+    <t xml:space="preserve">1.38899075984955</t>
   </si>
   <si>
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3529132604599</t>
+    <t xml:space="preserve">1.35291314125061</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1325,25 +1325,25 @@
     <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271903514862</t>
+    <t xml:space="preserve">1.26271891593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24468016624451</t>
+    <t xml:space="preserve">1.24468004703522</t>
   </si>
   <si>
     <t xml:space="preserve">1.19056367874146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18154418468475</t>
+    <t xml:space="preserve">1.18154430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664129734039</t>
+    <t xml:space="preserve">1.22664141654968</t>
   </si>
   <si>
     <t xml:space="preserve">1.21762192249298</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193251609802</t>
+    <t xml:space="preserve">1.36193263530731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37997150421143</t>
+    <t xml:space="preserve">1.37997138500214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781614780426</t>
+    <t xml:space="preserve">1.30781602859497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32585501670837</t>
+    <t xml:space="preserve">1.32585489749908</t>
   </si>
   <si>
     <t xml:space="preserve">1.27173840999603</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055406093597</t>
+    <t xml:space="preserve">1.65055418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859304904938</t>
+    <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
     <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251531124115</t>
+    <t xml:space="preserve">1.63251519203186</t>
   </si>
   <si>
     <t xml:space="preserve">1.59643757343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486477375031</t>
+    <t xml:space="preserve">1.79486489295959</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
@@ -1400,13 +1400,16 @@
     <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369016170502</t>
+    <t xml:space="preserve">1.71369004249573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349569797516</t>
+    <t xml:space="preserve">1.62349581718445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55134046077728</t>
+    <t xml:space="preserve">1.56035995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55134057998657</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
@@ -1421,7 +1424,7 @@
     <t xml:space="preserve">1.11840832233429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350531578064</t>
+    <t xml:space="preserve">1.16350543498993</t>
   </si>
   <si>
     <t xml:space="preserve">1.15448594093323</t>
@@ -1436,7 +1439,7 @@
     <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1445,10 +1448,10 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09135007858276</t>
+    <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233058452606</t>
+    <t xml:space="preserve">1.08233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1460,7 +1463,7 @@
     <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527222156525</t>
+    <t xml:space="preserve">1.05527234077454</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1469,13 +1472,13 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097549915314</t>
+    <t xml:space="preserve">0.974097609519958</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
@@ -1487,22 +1490,22 @@
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019752502441</t>
+    <t xml:space="preserve">0.938019812107086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919980943202972</t>
+    <t xml:space="preserve">0.919981002807617</t>
   </si>
   <si>
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432386875153</t>
+    <t xml:space="preserve">0.897432446479797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910961508750916</t>
+    <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983116924762726</t>
+    <t xml:space="preserve">0.983117043972015</t>
   </si>
   <si>
     <t xml:space="preserve">1.01919460296631</t>
@@ -1517,7 +1520,7 @@
     <t xml:space="preserve">1.47918498516083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098145008087</t>
+    <t xml:space="preserve">1.25098133087158</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1547,7 +1550,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1212500333786</t>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1565,25 +1568,22 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051652908325</t>
+    <t xml:space="preserve">1.13051640987396</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1953821182251</t>
+    <t xml:space="preserve">1.19538223743439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198341846466</t>
+    <t xml:space="preserve">1.11198353767395</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -29071,7 +29071,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1037" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1039" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29227,7 +29227,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29253,7 +29253,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1044" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29305,7 +29305,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1046" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1051" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1061" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1062" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1065" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1068" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29903,7 +29903,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1069" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29929,7 +29929,7 @@
         <v>1.25</v>
       </c>
       <c r="G1070" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29955,7 +29955,7 @@
         <v>1.25</v>
       </c>
       <c r="G1071" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29981,7 +29981,7 @@
         <v>1.25</v>
       </c>
       <c r="G1072" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>1.25</v>
       </c>
       <c r="G1073" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1080" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1081" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>1.25</v>
       </c>
       <c r="G1084" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1088" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30449,7 +30449,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30501,7 +30501,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1092" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30527,7 +30527,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30553,7 +30553,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1094" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30579,7 +30579,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30605,7 +30605,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30631,7 +30631,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30657,7 +30657,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1098" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30683,7 +30683,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1099" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30709,7 +30709,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1100" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30735,7 +30735,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1101" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30761,7 +30761,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1103" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1104" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30839,7 +30839,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1105" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30865,7 +30865,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30891,7 +30891,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1107" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30943,7 +30943,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1109" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1110" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1111" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1112" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31047,7 +31047,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1113" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31073,7 +31073,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1114" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31099,7 +31099,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1115" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1117" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31203,7 +31203,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1119" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1120" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1121" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1122" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1125" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1126" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1128" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1129" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1130" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1131" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31541,7 +31541,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1133" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1134" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1136" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1137" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>1.25</v>
       </c>
       <c r="G1138" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1139" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31749,7 +31749,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1140" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31775,7 +31775,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1141" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31801,7 +31801,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1142" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31827,7 +31827,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1143" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31879,7 +31879,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1145" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31931,7 +31931,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1147" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31957,7 +31957,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1148" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31983,7 +31983,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1149" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32009,7 +32009,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1150" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32035,7 +32035,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1151" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1152" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1153" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32113,7 +32113,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1154" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32139,7 +32139,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1155" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32165,7 +32165,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1156" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32191,7 +32191,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1157" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32217,7 +32217,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1158" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32243,7 +32243,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1159" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32269,7 +32269,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1160" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32295,7 +32295,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1161" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32321,7 +32321,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1162" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32347,7 +32347,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1163" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32373,7 +32373,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1164" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32399,7 +32399,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1165" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32425,7 +32425,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1166" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32451,7 +32451,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1167" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32477,7 +32477,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1168" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32503,7 +32503,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32529,7 +32529,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1170" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32555,7 +32555,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32581,7 +32581,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1172" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32607,7 +32607,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1173" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32633,7 +32633,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1174" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32659,7 +32659,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1175" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32685,7 +32685,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1176" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32711,7 +32711,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1177" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32737,7 +32737,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32763,7 +32763,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1179" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32789,7 +32789,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1180" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32815,7 +32815,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32841,7 +32841,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1182" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32867,7 +32867,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1183" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32893,7 +32893,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1184" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32919,7 +32919,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1185" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32945,7 +32945,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1186" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32971,7 +32971,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1187" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32997,7 +32997,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1188" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33023,7 +33023,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1189" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33049,7 +33049,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1190" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33075,7 +33075,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33101,7 +33101,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33127,7 +33127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33153,7 +33153,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1194" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33179,7 +33179,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1195" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33205,7 +33205,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1196" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33231,7 +33231,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33257,7 +33257,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1198" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33283,7 +33283,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33309,7 +33309,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33335,7 +33335,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1201" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33361,7 +33361,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1202" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33387,7 +33387,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33413,7 +33413,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1204" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33439,7 +33439,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33465,7 +33465,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33491,7 +33491,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33517,7 +33517,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1208" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33543,7 +33543,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33569,7 +33569,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33595,7 +33595,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1211" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33621,7 +33621,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1212" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33647,7 +33647,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1213" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33673,7 +33673,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33699,7 +33699,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33725,7 +33725,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33751,7 +33751,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33777,7 +33777,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1218" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33803,7 +33803,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1219" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33829,7 +33829,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1220" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33855,7 +33855,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1221" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33881,7 +33881,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33907,7 +33907,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33933,7 +33933,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33959,7 +33959,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33985,7 +33985,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1226" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34011,7 +34011,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1227" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34037,7 +34037,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1228" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34063,7 +34063,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1229" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34089,7 +34089,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1230" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34115,7 +34115,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34141,7 +34141,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34167,7 +34167,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1233" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34193,7 +34193,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1234" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34219,7 +34219,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34245,7 +34245,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34271,7 +34271,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1237" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34297,7 +34297,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1238" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34323,7 +34323,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1239" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34349,7 +34349,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1240" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34375,7 +34375,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34401,7 +34401,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1242" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34427,7 +34427,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1243" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34453,7 +34453,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1244" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34479,7 +34479,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34505,7 +34505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1246" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34531,7 +34531,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1247" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34557,7 +34557,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34583,7 +34583,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1249" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34609,7 +34609,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1250" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34635,7 +34635,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1251" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34661,7 +34661,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34687,7 +34687,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1253" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34713,7 +34713,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1254" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34739,7 +34739,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1255" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34765,7 +34765,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1256" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34791,7 +34791,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1257" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34817,7 +34817,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1258" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34843,7 +34843,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1259" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34869,7 +34869,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1260" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34895,7 +34895,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1261" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34921,7 +34921,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1262" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34947,7 +34947,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34973,7 +34973,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1264" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34999,7 +34999,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1265" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35025,7 +35025,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1266" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35051,7 +35051,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35077,7 +35077,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1268" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35103,7 +35103,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1269" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35129,7 +35129,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1270" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35155,7 +35155,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1271" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35181,7 +35181,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1272" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35207,7 +35207,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1273" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35233,7 +35233,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1274" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35259,7 +35259,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1275" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35285,7 +35285,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1276" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35311,7 +35311,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1277" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35337,7 +35337,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1278" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35363,7 +35363,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1279" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35389,7 +35389,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1280" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35415,7 +35415,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1281" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35441,7 +35441,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1282" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35467,7 +35467,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1283" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35493,7 +35493,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1284" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35519,7 +35519,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1285" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35545,7 +35545,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1286" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35571,7 +35571,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35597,7 +35597,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35623,7 +35623,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1289" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35649,7 +35649,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1290" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35675,7 +35675,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1291" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35701,7 +35701,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1292" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35727,7 +35727,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1293" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35753,7 +35753,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1294" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35779,7 +35779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1295" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35805,7 +35805,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1296" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35831,7 +35831,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1297" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35857,7 +35857,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35883,7 +35883,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35909,7 +35909,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1300" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35935,7 +35935,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1301" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35961,7 +35961,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1302" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35987,7 +35987,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1303" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36013,7 +36013,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1304" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36039,7 +36039,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1305" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36065,7 +36065,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1306" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36091,7 +36091,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1307" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36117,7 +36117,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1308" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36143,7 +36143,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1309" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36169,7 +36169,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1310" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36195,7 +36195,7 @@
         <v>1.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36221,7 +36221,7 @@
         <v>1.25</v>
       </c>
       <c r="G1312" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36247,7 +36247,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1313" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36273,7 +36273,7 @@
         <v>1.25</v>
       </c>
       <c r="G1314" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36299,7 +36299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1315" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36325,7 +36325,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1316" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36351,7 +36351,7 @@
         <v>1.25</v>
       </c>
       <c r="G1317" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36377,7 +36377,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36429,7 +36429,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36455,7 +36455,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1321" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36481,7 +36481,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1322" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36507,7 +36507,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1323" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36533,7 +36533,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1324" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36559,7 +36559,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1325" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36585,7 +36585,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36611,7 +36611,7 @@
         <v>1.25</v>
       </c>
       <c r="G1327" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36637,7 +36637,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1328" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36663,7 +36663,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1329" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36689,7 +36689,7 @@
         <v>1.25</v>
       </c>
       <c r="G1330" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36715,7 +36715,7 @@
         <v>1.25</v>
       </c>
       <c r="G1331" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36741,7 +36741,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36767,7 +36767,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36845,7 +36845,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1336" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37053,7 +37053,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1344" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37105,7 +37105,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1346" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37261,7 +37261,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1352" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37287,7 +37287,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1353" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37365,7 +37365,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1356" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37391,7 +37391,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1357" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37443,7 +37443,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1359" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37469,7 +37469,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1360" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37521,7 +37521,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37547,7 +37547,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37573,7 +37573,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38197,7 +38197,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1388" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38223,7 +38223,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1389" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38249,7 +38249,7 @@
         <v>1.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38275,7 +38275,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1391" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38301,7 +38301,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1392" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38353,7 +38353,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1394" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38379,7 +38379,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1395" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38405,7 +38405,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1396" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38431,7 +38431,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1397" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38561,7 +38561,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38587,7 +38587,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38613,7 +38613,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38639,7 +38639,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1405" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38665,7 +38665,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38691,7 +38691,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1407" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38717,7 +38717,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1408" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38743,7 +38743,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1409" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38769,7 +38769,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1410" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38795,7 +38795,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1411" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38821,7 +38821,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1412" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38847,7 +38847,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1413" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38873,7 +38873,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1414" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38899,7 +38899,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1415" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38925,7 +38925,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1416" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38951,7 +38951,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1417" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38977,7 +38977,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1418" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39003,7 +39003,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1419" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39055,7 +39055,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1421" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39081,7 +39081,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1422" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39107,7 +39107,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1423" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39133,7 +39133,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1424" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39159,7 +39159,7 @@
         <v>1.25</v>
       </c>
       <c r="G1425" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39185,7 +39185,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39211,7 +39211,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1427" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39237,7 +39237,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1428" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39263,7 +39263,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1429" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39289,7 +39289,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1430" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39315,7 +39315,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39341,7 +39341,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1432" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39367,7 +39367,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1433" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39471,7 +39471,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39497,7 +39497,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1438" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39523,7 +39523,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1439" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39549,7 +39549,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1440" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39575,7 +39575,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1441" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39601,7 +39601,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1442" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39627,7 +39627,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1443" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39653,7 +39653,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1444" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39679,7 +39679,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1445" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39705,7 +39705,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1446" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39731,7 +39731,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1447" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39757,7 +39757,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1448" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39783,7 +39783,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1449" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39809,7 +39809,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1450" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39835,7 +39835,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1451" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39861,7 +39861,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1452" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39887,7 +39887,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1453" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39913,7 +39913,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1454" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39939,7 +39939,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1455" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39965,7 +39965,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1456" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39991,7 +39991,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1457" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40173,7 +40173,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1464" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40251,7 +40251,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1467" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40277,7 +40277,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1468" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40537,7 +40537,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41213,7 +41213,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1504" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41525,7 +41525,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1516" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41603,7 +41603,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1519" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41629,7 +41629,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41655,7 +41655,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1521" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41681,7 +41681,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1522" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41785,7 +41785,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1526" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41811,7 +41811,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1527" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41915,7 +41915,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1531" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41941,7 +41941,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1532" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42123,7 +42123,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1539" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42175,7 +42175,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1541" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42279,7 +42279,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1545" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42331,7 +42331,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1547" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42357,7 +42357,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1548" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42383,7 +42383,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1549" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42409,7 +42409,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1550" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42435,7 +42435,7 @@
         <v>1.25</v>
       </c>
       <c r="G1551" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42461,7 +42461,7 @@
         <v>1.25</v>
       </c>
       <c r="G1552" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42487,7 +42487,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1553" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42513,7 +42513,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1554" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42539,7 +42539,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1555" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42565,7 +42565,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1556" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42591,7 +42591,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42617,7 +42617,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1558" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42643,7 +42643,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42669,7 +42669,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1560" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42695,7 +42695,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42721,7 +42721,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1562" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42799,7 +42799,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42825,7 +42825,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1566" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42851,7 +42851,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1567" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42877,7 +42877,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42903,7 +42903,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1569" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42929,7 +42929,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1570" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42955,7 +42955,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1571" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42981,7 +42981,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1572" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43007,7 +43007,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1573" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43033,7 +43033,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1574" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43059,7 +43059,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1575" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43085,7 +43085,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1576" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43111,7 +43111,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1577" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43137,7 +43137,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1578" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43163,7 +43163,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1579" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43189,7 +43189,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1580" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43215,7 +43215,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1581" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43241,7 +43241,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1582" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43267,7 +43267,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1583" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43293,7 +43293,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1584" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43319,7 +43319,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1585" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43345,7 +43345,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1586" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43371,7 +43371,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43527,7 +43527,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1593" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43553,7 +43553,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1594" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43605,7 +43605,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1596" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43631,7 +43631,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43683,7 +43683,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1599" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43787,7 +43787,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43813,7 +43813,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1604" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43839,7 +43839,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43865,7 +43865,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1606" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43891,7 +43891,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1607" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43917,7 +43917,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43943,7 +43943,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1609" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44021,7 +44021,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1612" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44047,7 +44047,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1613" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44073,7 +44073,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44099,7 +44099,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1615" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44125,7 +44125,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1616" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44177,7 +44177,7 @@
         <v>1.25</v>
       </c>
       <c r="G1618" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44203,7 +44203,7 @@
         <v>1.25</v>
       </c>
       <c r="G1619" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44229,7 +44229,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1620" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44255,7 +44255,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44307,7 +44307,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44437,7 +44437,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1628" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44489,7 +44489,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1630" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44619,7 +44619,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1635" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44645,7 +44645,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44671,7 +44671,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1637" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44697,7 +44697,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44723,7 +44723,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1639" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44749,7 +44749,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1640" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44775,7 +44775,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1641" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44801,7 +44801,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45009,7 +45009,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45061,7 +45061,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1652" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45087,7 +45087,7 @@
         <v>1.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45113,7 +45113,7 @@
         <v>1.25</v>
       </c>
       <c r="G1654" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45139,7 +45139,7 @@
         <v>1.25</v>
       </c>
       <c r="G1655" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45165,7 +45165,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1656" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45191,7 +45191,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1657" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45217,7 +45217,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45243,7 +45243,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45269,7 +45269,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1660" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45295,7 +45295,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1661" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45321,7 +45321,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1662" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45347,7 +45347,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1663" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45373,7 +45373,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45425,7 +45425,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45451,7 +45451,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45477,7 +45477,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45503,7 +45503,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45555,7 +45555,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1671" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45581,7 +45581,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1672" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45633,7 +45633,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1674" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45685,7 +45685,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1676" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45737,7 +45737,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45815,7 +45815,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1681" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45867,7 +45867,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1683" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45893,7 +45893,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1684" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45919,7 +45919,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1685" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45997,7 +45997,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1688" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46153,7 +46153,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1694" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46179,7 +46179,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1695" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46205,7 +46205,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1696" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46231,7 +46231,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46283,7 +46283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1699" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46335,7 +46335,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46465,7 +46465,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1706" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46517,7 +46517,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1708" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46621,7 +46621,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1712" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46673,7 +46673,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1714" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46699,7 +46699,7 @@
         <v>1.25</v>
       </c>
       <c r="G1715" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46725,7 +46725,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1716" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46751,7 +46751,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46777,7 +46777,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46803,7 +46803,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46829,7 +46829,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46855,7 +46855,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46881,7 +46881,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46907,7 +46907,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46959,7 +46959,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1725" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46985,7 +46985,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1726" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47011,7 +47011,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1727" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47141,7 +47141,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1732" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47193,7 +47193,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1734" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47219,7 +47219,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47401,7 +47401,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1742" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47427,7 +47427,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1743" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47453,7 +47453,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1744" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47479,7 +47479,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1745" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47505,7 +47505,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1746" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47531,7 +47531,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1747" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47557,7 +47557,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1748" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47583,7 +47583,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1749" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47609,7 +47609,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1750" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47635,7 +47635,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1751" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47661,7 +47661,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1752" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47687,7 +47687,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1753" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47713,7 +47713,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1754" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47739,7 +47739,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1755" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47895,7 +47895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1761" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47947,7 +47947,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47999,7 +47999,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1765" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48025,7 +48025,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1766" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48051,7 +48051,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1767" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48077,7 +48077,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1768" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48103,7 +48103,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1769" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48233,7 +48233,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1774" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48259,7 +48259,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1775" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48389,7 +48389,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1780" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48493,7 +48493,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1784" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48519,7 +48519,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1785" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48545,7 +48545,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1786" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48571,7 +48571,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1787" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48597,7 +48597,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1788" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48623,7 +48623,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1789" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48675,7 +48675,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1791" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48701,7 +48701,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1792" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48935,7 +48935,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1801" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48961,7 +48961,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48987,7 +48987,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1803" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49013,7 +49013,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1804" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49039,7 +49039,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1805" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49065,7 +49065,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49091,7 +49091,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1807" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49117,7 +49117,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1808" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49143,7 +49143,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1809" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49169,7 +49169,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1810" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49195,7 +49195,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1811" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49221,7 +49221,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1812" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49247,7 +49247,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1813" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49325,7 +49325,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49351,7 +49351,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1817" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49377,7 +49377,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1818" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49403,7 +49403,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1819" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49429,7 +49429,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1820" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49455,7 +49455,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1821" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49481,7 +49481,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1822" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49507,7 +49507,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1823" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49533,7 +49533,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1824" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49559,7 +49559,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1825" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49585,7 +49585,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49611,7 +49611,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49637,7 +49637,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1828" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49663,7 +49663,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1829" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49689,7 +49689,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49715,7 +49715,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49741,7 +49741,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49767,7 +49767,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49793,7 +49793,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1834" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49819,7 +49819,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1835" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49845,7 +49845,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1836" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49871,7 +49871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1837" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49897,7 +49897,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1838" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49923,7 +49923,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49949,7 +49949,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49975,7 +49975,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50001,7 +50001,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1842" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50027,7 +50027,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1843" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50053,7 +50053,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1844" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50079,7 +50079,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1845" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50105,7 +50105,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1846" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50131,7 +50131,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1847" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50157,7 +50157,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1848" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50183,7 +50183,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1849" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50209,7 +50209,7 @@
         <v>1.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50235,7 +50235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1851" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50391,7 +50391,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50443,7 +50443,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1859" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50495,7 +50495,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50651,7 +50651,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50677,7 +50677,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50859,7 +50859,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1875" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50885,7 +50885,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1876" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50911,7 +50911,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1877" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50937,7 +50937,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1878" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50963,7 +50963,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1879" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50989,7 +50989,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1880" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51015,7 +51015,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1881" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51041,7 +51041,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1882" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51067,7 +51067,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1883" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51093,7 +51093,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1884" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51119,7 +51119,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1885" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51145,7 +51145,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1886" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51171,7 +51171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1887" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51197,7 +51197,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1888" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51223,7 +51223,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1889" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51249,7 +51249,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1890" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51275,7 +51275,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1891" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51301,7 +51301,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1892" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51327,7 +51327,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1893" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51353,7 +51353,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1894" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51379,7 +51379,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1895" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51405,7 +51405,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1896" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51431,7 +51431,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1897" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51457,7 +51457,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1898" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51483,7 +51483,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1899" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51509,7 +51509,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1900" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51535,7 +51535,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1901" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51561,7 +51561,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1902" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51587,7 +51587,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1903" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51613,7 +51613,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1904" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51639,7 +51639,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1905" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51665,7 +51665,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1906" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51691,7 +51691,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1907" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51717,7 +51717,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1908" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51743,7 +51743,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1909" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51769,7 +51769,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1910" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51795,7 +51795,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51821,7 +51821,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1912" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51847,7 +51847,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51873,7 +51873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51899,7 +51899,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1915" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51925,7 +51925,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1916" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51951,7 +51951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1917" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51977,7 +51977,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52003,7 +52003,7 @@
         <v>1.25</v>
       </c>
       <c r="G1919" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52029,7 +52029,7 @@
         <v>1.25</v>
       </c>
       <c r="G1920" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52055,7 +52055,7 @@
         <v>1.25</v>
       </c>
       <c r="G1921" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52081,7 +52081,7 @@
         <v>1.25</v>
       </c>
       <c r="G1922" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52107,7 +52107,7 @@
         <v>1.25</v>
       </c>
       <c r="G1923" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52133,7 +52133,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1924" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52159,7 +52159,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1925" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52185,7 +52185,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52211,7 +52211,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52237,7 +52237,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52263,7 +52263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52289,7 +52289,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1930" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52315,7 +52315,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1931" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52341,7 +52341,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1932" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52367,7 +52367,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52393,7 +52393,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52419,7 +52419,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52445,7 +52445,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1936" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52471,7 +52471,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1937" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52497,7 +52497,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1938" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52523,7 +52523,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1939" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52549,7 +52549,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1940" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52575,7 +52575,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1941" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52601,7 +52601,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1942" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52627,7 +52627,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1943" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52653,7 +52653,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1944" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52679,7 +52679,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1945" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52705,7 +52705,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1946" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52731,7 +52731,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1947" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52757,7 +52757,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1948" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52783,7 +52783,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1949" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52809,7 +52809,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1950" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52835,7 +52835,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1951" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52861,7 +52861,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1952" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52887,7 +52887,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1953" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52913,7 +52913,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1954" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52939,7 +52939,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1955" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52965,7 +52965,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1956" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52991,7 +52991,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53017,7 +53017,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1958" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53043,7 +53043,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53069,7 +53069,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53095,7 +53095,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1961" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53121,7 +53121,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1962" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53147,7 +53147,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1963" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53173,7 +53173,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53199,7 +53199,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1965" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53225,7 +53225,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1966" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53251,7 +53251,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1967" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53277,7 +53277,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1968" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53303,7 +53303,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1969" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53329,7 +53329,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1970" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53355,7 +53355,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1971" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53381,7 +53381,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1972" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53407,7 +53407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1973" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53433,7 +53433,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1974" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53459,7 +53459,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1975" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53485,7 +53485,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1976" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53511,7 +53511,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53537,7 +53537,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53563,7 +53563,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53589,7 +53589,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53615,7 +53615,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53641,7 +53641,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53667,7 +53667,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53693,7 +53693,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1984" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53719,7 +53719,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53745,7 +53745,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53771,7 +53771,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1987" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53797,7 +53797,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1988" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53823,7 +53823,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1989" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53849,7 +53849,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1990" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53875,7 +53875,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53901,7 +53901,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1992" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53927,7 +53927,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53953,7 +53953,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1994" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53979,7 +53979,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1995" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54005,7 +54005,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1996" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54031,7 +54031,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1997" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54057,7 +54057,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54083,7 +54083,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1999" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54109,7 +54109,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54135,7 +54135,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2001" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54161,7 +54161,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2002" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54187,7 +54187,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2003" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54213,7 +54213,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2004" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54239,7 +54239,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2005" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54265,7 +54265,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2006" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54291,7 +54291,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54317,7 +54317,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54343,7 +54343,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2009" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54369,7 +54369,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2010" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54395,7 +54395,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2011" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54421,7 +54421,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2012" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54447,7 +54447,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2013" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54473,7 +54473,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2014" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54499,7 +54499,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54525,7 +54525,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2016" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54551,7 +54551,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2017" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54577,7 +54577,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2018" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54603,7 +54603,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2019" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54629,7 +54629,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2020" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54655,7 +54655,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2021" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54681,7 +54681,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54707,7 +54707,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2023" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54733,7 +54733,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2024" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54759,7 +54759,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2025" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54785,7 +54785,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54811,7 +54811,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54837,7 +54837,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54863,7 +54863,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2029" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54889,7 +54889,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2030" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54915,7 +54915,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2031" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54941,7 +54941,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2032" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54967,7 +54967,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2033" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54993,7 +54993,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2034" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55019,7 +55019,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2035" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55045,7 +55045,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2036" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55071,7 +55071,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2037" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55097,7 +55097,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2038" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55123,7 +55123,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2039" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55149,7 +55149,7 @@
         <v>1.25</v>
       </c>
       <c r="G2040" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55175,7 +55175,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55201,7 +55201,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55227,7 +55227,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2043" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55253,7 +55253,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2044" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55279,7 +55279,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2045" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55305,7 +55305,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2046" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55331,7 +55331,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55357,7 +55357,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55383,7 +55383,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55409,7 +55409,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2050" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55435,7 +55435,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55461,7 +55461,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2052" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55487,7 +55487,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55513,7 +55513,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2054" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55539,7 +55539,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2055" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55565,7 +55565,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55591,7 +55591,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55617,7 +55617,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2058" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55643,7 +55643,7 @@
         <v>1.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55669,7 +55669,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2060" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55695,7 +55695,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55721,7 +55721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2062" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55747,7 +55747,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2063" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55773,7 +55773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2064" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55799,7 +55799,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2065" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55825,7 +55825,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2066" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55851,7 +55851,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2067" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55877,7 +55877,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2068" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55903,7 +55903,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2069" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55929,7 +55929,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55955,7 +55955,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2071" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55981,7 +55981,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2072" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56007,7 +56007,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2073" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56033,7 +56033,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2074" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56059,7 +56059,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2075" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56085,7 +56085,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2076" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56111,7 +56111,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2077" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56137,7 +56137,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2078" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56163,7 +56163,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2079" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56189,7 +56189,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2080" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56215,7 +56215,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56241,7 +56241,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56267,7 +56267,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2083" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56293,7 +56293,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2084" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56319,7 +56319,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2085" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56345,7 +56345,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2086" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56371,7 +56371,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2087" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56397,7 +56397,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2088" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56423,7 +56423,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2089" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56449,7 +56449,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2090" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56475,7 +56475,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2091" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56501,7 +56501,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2092" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56527,7 +56527,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2093" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56553,7 +56553,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2094" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56579,7 +56579,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2095" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56605,7 +56605,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2096" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56631,7 +56631,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2097" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56657,7 +56657,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2098" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56683,7 +56683,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2099" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56709,7 +56709,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2100" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56735,7 +56735,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56761,7 +56761,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2102" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56787,7 +56787,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2103" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56813,7 +56813,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2104" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56839,7 +56839,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2105" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56865,7 +56865,7 @@
         <v>1.25</v>
       </c>
       <c r="G2106" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56891,7 +56891,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2107" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56917,7 +56917,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2108" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56943,7 +56943,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2109" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56969,7 +56969,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2110" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56995,7 +56995,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2111" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57021,7 +57021,7 @@
         <v>1.25</v>
       </c>
       <c r="G2112" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57047,7 +57047,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2113" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57073,7 +57073,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2114" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57099,7 +57099,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2115" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57125,7 +57125,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2116" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57151,7 +57151,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2117" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57177,7 +57177,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2118" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57203,7 +57203,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2119" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57229,7 +57229,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2120" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57255,7 +57255,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57281,7 +57281,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2122" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57307,7 +57307,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2123" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57333,7 +57333,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2124" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57359,7 +57359,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57385,7 +57385,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2126" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57411,7 +57411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2127" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57437,7 +57437,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57463,7 +57463,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2129" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57489,7 +57489,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2130" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57515,7 +57515,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2131" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57541,7 +57541,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57567,7 +57567,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2133" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57593,7 +57593,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -66987,7 +66987,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.5486226852</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>16800</v>
@@ -67008,6 +67008,32 @@
         <v>578</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.4514236111</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>400</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>588</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4707692861557</t>
+    <t xml:space="preserve">1.47076916694641</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781745433807</t>
+    <t xml:space="preserve">1.43781757354736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684322834015</t>
+    <t xml:space="preserve">1.48684310913086</t>
   </si>
   <si>
     <t xml:space="preserve">1.44424712657928</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236248493195</t>
+    <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593269348145</t>
+    <t xml:space="preserve">1.37593281269073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414041996002</t>
+    <t xml:space="preserve">1.33414030075073</t>
   </si>
   <si>
     <t xml:space="preserve">1.35744762420654</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38155853748322</t>
+    <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647327899933</t>
+    <t xml:space="preserve">1.40647315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4458544254303</t>
+    <t xml:space="preserve">1.44585454463959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3984363079071</t>
+    <t xml:space="preserve">1.39843618869781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780311584473</t>
+    <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726264953613</t>
+    <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002926826477</t>
+    <t xml:space="preserve">1.31002950668335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217739105225</t>
+    <t xml:space="preserve">1.34217727184296</t>
   </si>
   <si>
     <t xml:space="preserve">1.35021436214447</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">1.32128131389618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557696342468</t>
+    <t xml:space="preserve">1.38557708263397</t>
   </si>
   <si>
     <t xml:space="preserve">1.46273231506348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43058407306671</t>
+    <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693571567535</t>
+    <t xml:space="preserve">1.50693559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889850616455</t>
+    <t xml:space="preserve">1.49889862537384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47237658500671</t>
+    <t xml:space="preserve">1.472376704216</t>
   </si>
   <si>
     <t xml:space="preserve">1.49488008022308</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">1.55274665355682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543500423431</t>
+    <t xml:space="preserve">1.61543476581573</t>
   </si>
   <si>
     <t xml:space="preserve">1.67169392108917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490875720978</t>
+    <t xml:space="preserve">1.67490863800049</t>
   </si>
   <si>
     <t xml:space="preserve">1.64597570896149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113887786865</t>
+    <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702820301056</t>
+    <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095414161682</t>
+    <t xml:space="preserve">1.51095402240753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630252361298</t>
+    <t xml:space="preserve">1.45630276203156</t>
   </si>
   <si>
     <t xml:space="preserve">1.43862128257751</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">1.45601880550385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426239490509</t>
+    <t xml:space="preserve">1.4342622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832185745239</t>
+    <t xml:space="preserve">1.40832161903381</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091523647308</t>
+    <t xml:space="preserve">1.43091511726379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840492725372</t>
+    <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
     <t xml:space="preserve">1.41334247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497481822968</t>
+    <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313498020172</t>
+    <t xml:space="preserve">1.36313486099243</t>
   </si>
   <si>
     <t xml:space="preserve">1.35560381412506</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288600921631</t>
+    <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325479388237</t>
+    <t xml:space="preserve">1.32547926902771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213222980499</t>
+    <t xml:space="preserve">1.32213199138641</t>
   </si>
   <si>
     <t xml:space="preserve">1.26439344882965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702842235565</t>
+    <t xml:space="preserve">1.29702854156494</t>
   </si>
   <si>
     <t xml:space="preserve">1.30539631843567</t>
@@ -221,28 +221,28 @@
     <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050012588501</t>
+    <t xml:space="preserve">1.3305002450943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2719247341156</t>
+    <t xml:space="preserve">1.27192461490631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267827510834</t>
+    <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506415843964</t>
+    <t xml:space="preserve">1.22506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20498132705688</t>
+    <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916521549225</t>
+    <t xml:space="preserve">1.20916533470154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841143608093</t>
+    <t xml:space="preserve">1.22841131687164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845303058624</t>
+    <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
     <t xml:space="preserve">1.23008501529694</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.22171700000763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816258430481</t>
+    <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
     <t xml:space="preserve">1.15226328372955</t>
@@ -266,94 +266,94 @@
     <t xml:space="preserve">1.14222180843353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150962352753</t>
+    <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
     <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293399333954</t>
+    <t xml:space="preserve">1.11293411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04850113391876</t>
+    <t xml:space="preserve">1.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343880176544</t>
+    <t xml:space="preserve">1.03343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">1.02423393726349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03929626941681</t>
+    <t xml:space="preserve">1.0392963886261</t>
   </si>
   <si>
     <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364617824554</t>
+    <t xml:space="preserve">1.08364629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06440007686615</t>
+    <t xml:space="preserve">1.06439995765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07109451293945</t>
+    <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0376228094101</t>
+    <t xml:space="preserve">1.03762269020081</t>
   </si>
   <si>
     <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984068036079407</t>
+    <t xml:space="preserve">0.984067976474762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967217445374</t>
+    <t xml:space="preserve">0.999967038631439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251876354218</t>
+    <t xml:space="preserve">1.01251912117004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00415110588074</t>
+    <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
     <t xml:space="preserve">0.958127439022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842493534088</t>
+    <t xml:space="preserve">0.969842553138733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738745689392</t>
+    <t xml:space="preserve">0.944738566875458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673663139343</t>
+    <t xml:space="preserve">0.888673722743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866080224514008</t>
+    <t xml:space="preserve">0.866080343723297</t>
   </si>
   <si>
     <t xml:space="preserve">0.952269971370697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103891372681</t>
+    <t xml:space="preserve">0.912103831768036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899551928043365</t>
+    <t xml:space="preserve">0.899551868438721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204888820648</t>
+    <t xml:space="preserve">0.896204710006714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87193775177002</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756613731384</t>
+    <t xml:space="preserve">0.90875655412674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596332550049</t>
+    <t xml:space="preserve">0.950596392154694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
     <t xml:space="preserve">0.920471787452698</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">0.967332184314728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311446666718</t>
+    <t xml:space="preserve">0.962311387062073</t>
   </si>
   <si>
     <t xml:space="preserve">1.05519545078278</t>
@@ -371,37 +371,37 @@
     <t xml:space="preserve">0.991599023342133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088833332062</t>
+    <t xml:space="preserve">0.989088773727417</t>
   </si>
   <si>
     <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99578320980072</t>
+    <t xml:space="preserve">0.995783090591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99076235294342</t>
+    <t xml:space="preserve">0.990762412548065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207579612732</t>
+    <t xml:space="preserve">0.937207698822021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394397258759</t>
+    <t xml:space="preserve">0.982394337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391706466675</t>
+    <t xml:space="preserve">0.941391587257385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251864910126</t>
+    <t xml:space="preserve">0.98825204372406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352862358093</t>
+    <t xml:space="preserve">0.972352921962738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168914318085</t>
+    <t xml:space="preserve">0.968168795108795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975699961185455</t>
+    <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
     <t xml:space="preserve">0.983231127262115</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">0.987415075302124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005763530731</t>
+    <t xml:space="preserve">0.969005882740021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994109451770782</t>
+    <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943431377411</t>
+    <t xml:space="preserve">0.953943490982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854249000549</t>
+    <t xml:space="preserve">1.05854260921478</t>
   </si>
   <si>
     <t xml:space="preserve">1.05937933921814</t>
@@ -437,52 +437,52 @@
     <t xml:space="preserve">1.13636422157288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1480792760849</t>
+    <t xml:space="preserve">1.14807939529419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577658176422</t>
+    <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661331176758</t>
+    <t xml:space="preserve">1.19661343097687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602555274963</t>
+    <t xml:space="preserve">1.25602567195892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20581805706024</t>
+    <t xml:space="preserve">1.20581817626953</t>
   </si>
   <si>
     <t xml:space="preserve">1.21334910392761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753323078156</t>
+    <t xml:space="preserve">1.21753311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644729137421</t>
+    <t xml:space="preserve">1.1564474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15310025215149</t>
+    <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493961334229</t>
+    <t xml:space="preserve">1.19493985176086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15477359294891</t>
+    <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
     <t xml:space="preserve">1.1464056968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19159245491028</t>
+    <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314160823822</t>
+    <t xml:space="preserve">1.16314172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23761606216431</t>
+    <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518870353699</t>
@@ -491,28 +491,28 @@
     <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146790981293</t>
+    <t xml:space="preserve">1.16146814823151</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803791999817</t>
+    <t xml:space="preserve">1.13803780078888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799620628357</t>
+    <t xml:space="preserve">1.12799632549286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130188941956</t>
+    <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653012275696</t>
+    <t xml:space="preserve">1.17653024196625</t>
   </si>
   <si>
     <t xml:space="preserve">1.40581142902374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576995372772</t>
+    <t xml:space="preserve">1.39576983451843</t>
   </si>
   <si>
     <t xml:space="preserve">1.39911723136902</t>
@@ -521,106 +521,106 @@
     <t xml:space="preserve">1.39744341373444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46020305156708</t>
+    <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534809589386</t>
+    <t xml:space="preserve">1.49534833431244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685589313507</t>
+    <t xml:space="preserve">1.45685577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865377902985</t>
+    <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4894905090332</t>
+    <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275483608246</t>
+    <t xml:space="preserve">1.47275471687317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551435470581</t>
+    <t xml:space="preserve">1.5355144739151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57317006587982</t>
+    <t xml:space="preserve">1.57316982746124</t>
   </si>
   <si>
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174533843994</t>
+    <t xml:space="preserve">1.63174557685852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684914588928</t>
+    <t xml:space="preserve">1.65684926509857</t>
   </si>
   <si>
     <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550748825073</t>
+    <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
     <t xml:space="preserve">1.75726425647736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77400016784668</t>
+    <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
     <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6509917974472</t>
+    <t xml:space="preserve">1.65099167823792</t>
   </si>
   <si>
     <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67358505725861</t>
+    <t xml:space="preserve">1.67358493804932</t>
   </si>
   <si>
     <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697369098663</t>
+    <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
     <t xml:space="preserve">1.6166832447052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664165019989</t>
+    <t xml:space="preserve">1.60664141178131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195307254791</t>
+    <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362653255463</t>
+    <t xml:space="preserve">1.68362677097321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542465686798</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
     <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224363803864</t>
+    <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052834510803</t>
+    <t xml:space="preserve">1.74052822589874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72379243373871</t>
+    <t xml:space="preserve">1.723792552948</t>
   </si>
   <si>
     <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220216274261</t>
+    <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
     <t xml:space="preserve">1.74906098842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337317943573</t>
+    <t xml:space="preserve">1.84337329864502</t>
   </si>
   <si>
     <t xml:space="preserve">1.8005039691925</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193019866943</t>
+    <t xml:space="preserve">1.79193031787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95483291149139</t>
+    <t xml:space="preserve">1.9548327922821</t>
   </si>
   <si>
     <t xml:space="preserve">2.37323570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926283836365</t>
+    <t xml:space="preserve">2.46926259994507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421898841858</t>
+    <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
     <t xml:space="preserve">2.82936334609985</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067219734192</t>
+    <t xml:space="preserve">2.40067195892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48984003067017</t>
+    <t xml:space="preserve">2.48983979225159</t>
   </si>
   <si>
     <t xml:space="preserve">2.58929634094238</t>
@@ -683,25 +683,25 @@
     <t xml:space="preserve">2.46240377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097754478455</t>
+    <t xml:space="preserve">2.47097730636597</t>
   </si>
   <si>
     <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953444480896</t>
+    <t xml:space="preserve">2.41953468322754</t>
   </si>
   <si>
     <t xml:space="preserve">2.45211505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52927947044373</t>
+    <t xml:space="preserve">2.52927923202515</t>
   </si>
   <si>
     <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641014099121</t>
+    <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
     <t xml:space="preserve">2.43496751785278</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56186008453369</t>
+    <t xml:space="preserve">2.56186032295227</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781973838806</t>
@@ -746,13 +746,13 @@
     <t xml:space="preserve">2.2806384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865190505981</t>
+    <t xml:space="preserve">2.32865214347839</t>
   </si>
   <si>
     <t xml:space="preserve">2.31321907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26692032814026</t>
+    <t xml:space="preserve">2.26692056655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.126309633255</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05771899223328</t>
+    <t xml:space="preserve">2.05771923065186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09544372558594</t>
+    <t xml:space="preserve">2.09544396400452</t>
   </si>
   <si>
     <t xml:space="preserve">2.11773586273193</t>
@@ -779,22 +779,22 @@
     <t xml:space="preserve">2.08515524864197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629276275635</t>
+    <t xml:space="preserve">2.06629300117493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08344030380249</t>
+    <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
     <t xml:space="preserve">2.09887313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799083709717</t>
+    <t xml:space="preserve">2.00799059867859</t>
   </si>
   <si>
     <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342343330383</t>
+    <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.2069034576416</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401773452759</t>
+    <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888977050781</t>
+    <t xml:space="preserve">2.15889000892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12287998199463</t>
+    <t xml:space="preserve">2.12288022041321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15374565124512</t>
+    <t xml:space="preserve">2.1537458896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15203094482422</t>
+    <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.16917848587036</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062134742737</t>
+    <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
     <t xml:space="preserve">2.25491714477539</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">2.23776936531067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233629226685</t>
+    <t xml:space="preserve">2.22233653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089343070984</t>
+    <t xml:space="preserve">2.17089366912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.18975567817688</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634313583374</t>
+    <t xml:space="preserve">2.24634289741516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065532684326</t>
+    <t xml:space="preserve">2.34065556526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206492424011</t>
+    <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.20175933837891</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2034740447998</t>
+    <t xml:space="preserve">2.20347380638123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462819099426</t>
+    <t xml:space="preserve">2.24462842941284</t>
   </si>
   <si>
     <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471206665039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527286529541</t>
+    <t xml:space="preserve">2.50527262687683</t>
   </si>
   <si>
     <t xml:space="preserve">2.51384663581848</t>
@@ -899,34 +899,34 @@
     <t xml:space="preserve">2.50355792045593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55500078201294</t>
+    <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326968193054</t>
+    <t xml:space="preserve">2.49326944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47269225120544</t>
+    <t xml:space="preserve">2.47269248962402</t>
   </si>
   <si>
     <t xml:space="preserve">2.32007813453674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32179260253906</t>
+    <t xml:space="preserve">2.32179284095764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809158325195</t>
+    <t xml:space="preserve">2.36809182167053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33379578590393</t>
+    <t xml:space="preserve">2.33379602432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439032554626</t>
+    <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
     <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3578028678894</t>
+    <t xml:space="preserve">2.35780262947083</t>
   </si>
   <si>
     <t xml:space="preserve">2.40410137176514</t>
@@ -935,31 +935,31 @@
     <t xml:space="preserve">2.39038348197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33551096916199</t>
+    <t xml:space="preserve">2.33551073074341</t>
   </si>
   <si>
     <t xml:space="preserve">2.30636024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38866877555847</t>
+    <t xml:space="preserve">2.38866853713989</t>
   </si>
   <si>
     <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832944869995</t>
+    <t xml:space="preserve">2.19832968711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430621147156</t>
+    <t xml:space="preserve">2.11430597305298</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632626533508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10058784484863</t>
+    <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
     <t xml:space="preserve">2.09201431274414</t>
@@ -971,10 +971,10 @@
     <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914546012878</t>
+    <t xml:space="preserve">2.04914498329163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9033899307251</t>
+    <t xml:space="preserve">1.90338981151581</t>
   </si>
   <si>
     <t xml:space="preserve">1.98055458068848</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">1.97198069095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053759098053</t>
+    <t xml:space="preserve">1.92053747177124</t>
   </si>
   <si>
     <t xml:space="preserve">1.98912823200226</t>
@@ -992,88 +992,88 @@
     <t xml:space="preserve">1.91196382045746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911171913147</t>
+    <t xml:space="preserve">1.92911159992218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624238967896</t>
+    <t xml:space="preserve">1.88624250888824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481616020203</t>
+    <t xml:space="preserve">1.89481639862061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909472942352</t>
+    <t xml:space="preserve">1.86909484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194718837738</t>
+    <t xml:space="preserve">1.8519469499588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625902175903</t>
+    <t xml:space="preserve">1.94625914096832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340680122375</t>
+    <t xml:space="preserve">1.96340668201447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879162788391</t>
+    <t xml:space="preserve">2.06879186630249</t>
   </si>
   <si>
     <t xml:space="preserve">2.04249358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236514091492</t>
+    <t xml:space="preserve">1.97236502170563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100263595581</t>
+    <t xml:space="preserve">1.9110027551651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840618610382</t>
+    <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470435142517</t>
+    <t xml:space="preserve">1.88470423221588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0249617099762</t>
+    <t xml:space="preserve">2.02496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866306781769</t>
+    <t xml:space="preserve">1.99866318702698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606685638428</t>
+    <t xml:space="preserve">1.94606673717499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853474617004</t>
+    <t xml:space="preserve">1.92853486537933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717236042023</t>
+    <t xml:space="preserve">1.86717224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223658084869</t>
+    <t xml:space="preserve">1.9022364616394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593841552734</t>
+    <t xml:space="preserve">1.87593853473663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334196567535</t>
+    <t xml:space="preserve">1.82334184646606</t>
   </si>
   <si>
     <t xml:space="preserve">1.91976857185364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84963989257812</t>
+    <t xml:space="preserve">1.84964001178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347052574158</t>
+    <t xml:space="preserve">1.89347064495087</t>
   </si>
   <si>
     <t xml:space="preserve">1.93730080127716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989701271057</t>
+    <t xml:space="preserve">1.98989713191986</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7882776260376</t>
+    <t xml:space="preserve">1.78827774524689</t>
   </si>
   <si>
     <t xml:space="preserve">1.77074551582336</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6173392534256</t>
+    <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542417526245</t>
+    <t xml:space="preserve">1.59542429447174</t>
   </si>
   <si>
     <t xml:space="preserve">1.6217223405838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65678656101227</t>
+    <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
     <t xml:space="preserve">1.68308484554291</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">1.66555273532867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69185078144073</t>
+    <t xml:space="preserve">1.69185090065002</t>
   </si>
   <si>
     <t xml:space="preserve">1.66116964817047</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104120731354</t>
+    <t xml:space="preserve">1.59104132652283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993570327759</t>
+    <t xml:space="preserve">1.6699355840683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048851490021</t>
+    <t xml:space="preserve">1.63048839569092</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">1.70061707496643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64363765716553</t>
+    <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
     <t xml:space="preserve">1.61295640468597</t>
@@ -1148,19 +1148,19 @@
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925445079803</t>
+    <t xml:space="preserve">1.63925457000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.58665800094604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597686767578</t>
+    <t xml:space="preserve">1.55597698688507</t>
   </si>
   <si>
     <t xml:space="preserve">1.42010283470154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42448580265045</t>
+    <t xml:space="preserve">1.42448592185974</t>
   </si>
   <si>
     <t xml:space="preserve">1.32367610931396</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065552711487</t>
+    <t xml:space="preserve">1.38065576553345</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763494491577</t>
+    <t xml:space="preserve">1.43763482570648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4464008808136</t>
+    <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201803207397</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406178951263</t>
+    <t xml:space="preserve">1.53406167030334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214647293091</t>
+    <t xml:space="preserve">1.5121465921402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52967870235443</t>
+    <t xml:space="preserve">1.52967882156372</t>
   </si>
   <si>
     <t xml:space="preserve">1.54721081256866</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">1.56035983562469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091252803802</t>
+    <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584830760956</t>
+    <t xml:space="preserve">1.48584842681885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51652956008911</t>
+    <t xml:space="preserve">1.5165296792984</t>
   </si>
   <si>
     <t xml:space="preserve">1.5691260099411</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529561519623</t>
+    <t xml:space="preserve">1.52529549598694</t>
   </si>
   <si>
     <t xml:space="preserve">1.49899744987488</t>
@@ -67063,6 +67063,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.3333333333</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>582</v>
+      </c>
+      <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47076916694641</t>
+    <t xml:space="preserve">1.4707692861557</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593281269073</t>
+    <t xml:space="preserve">1.37593269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414030075073</t>
+    <t xml:space="preserve">1.33414053916931</t>
   </si>
   <si>
     <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628842353821</t>
+    <t xml:space="preserve">1.36628830432892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290283203125</t>
+    <t xml:space="preserve">1.41290271282196</t>
   </si>
   <si>
     <t xml:space="preserve">1.3815586566925</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">1.40647315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44585454463959</t>
+    <t xml:space="preserve">1.44585466384888</t>
   </si>
   <si>
     <t xml:space="preserve">1.39843618869781</t>
@@ -92,31 +92,31 @@
     <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002950668335</t>
+    <t xml:space="preserve">1.31002938747406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217727184296</t>
+    <t xml:space="preserve">1.34217751026154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021436214447</t>
+    <t xml:space="preserve">1.35021424293518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128131389618</t>
+    <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
     <t xml:space="preserve">1.38557708263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273231506348</t>
+    <t xml:space="preserve">1.46273219585419</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693559646606</t>
+    <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889862537384</t>
+    <t xml:space="preserve">1.49889874458313</t>
   </si>
   <si>
     <t xml:space="preserve">1.472376704216</t>
@@ -128,49 +128,49 @@
     <t xml:space="preserve">1.55274665355682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543476581573</t>
+    <t xml:space="preserve">1.61543500423431</t>
   </si>
   <si>
     <t xml:space="preserve">1.67169392108917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490863800049</t>
+    <t xml:space="preserve">1.67490875720978</t>
   </si>
   <si>
     <t xml:space="preserve">1.64597570896149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113899707794</t>
+    <t xml:space="preserve">1.55113911628723</t>
   </si>
   <si>
     <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095402240753</t>
+    <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630276203156</t>
+    <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
     <t xml:space="preserve">1.43862128257751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4120991230011</t>
+    <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601880550385</t>
+    <t xml:space="preserve">1.45601904392242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4342622756958</t>
+    <t xml:space="preserve">1.43426251411438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832161903381</t>
+    <t xml:space="preserve">1.4083217382431</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091511726379</t>
+    <t xml:space="preserve">1.43091535568237</t>
   </si>
   <si>
     <t xml:space="preserve">1.42840480804443</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32547926902771</t>
+    <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213199138641</t>
+    <t xml:space="preserve">1.3221321105957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439344882965</t>
+    <t xml:space="preserve">1.26439356803894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702854156494</t>
+    <t xml:space="preserve">1.29702842235565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539631843567</t>
+    <t xml:space="preserve">1.30539619922638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397182941437</t>
+    <t xml:space="preserve">1.36397171020508</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3807076215744</t>
+    <t xml:space="preserve">1.38070774078369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3305002450943</t>
+    <t xml:space="preserve">1.33050000667572</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267839431763</t>
+    <t xml:space="preserve">1.25267827510834</t>
   </si>
   <si>
     <t xml:space="preserve">1.22506427764893</t>
@@ -236,43 +236,43 @@
     <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916533470154</t>
+    <t xml:space="preserve">1.20916509628296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841131687164</t>
+    <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
     <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008501529694</t>
+    <t xml:space="preserve">1.23008513450623</t>
   </si>
   <si>
     <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14473211765289</t>
+    <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171700000763</t>
+    <t xml:space="preserve">1.22171723842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226328372955</t>
+    <t xml:space="preserve">1.15226316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14222180843353</t>
+    <t xml:space="preserve">1.14222168922424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150938510895</t>
+    <t xml:space="preserve">1.17150962352753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966990470886</t>
+    <t xml:space="preserve">1.12966978549957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293411254883</t>
+    <t xml:space="preserve">1.11293399333954</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850101470947</t>
@@ -281,94 +281,94 @@
     <t xml:space="preserve">1.03343868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02423393726349</t>
+    <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
     <t xml:space="preserve">1.0392963886261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435860157013</t>
+    <t xml:space="preserve">1.05435848236084</t>
   </si>
   <si>
     <t xml:space="preserve">1.08364629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06439995765686</t>
+    <t xml:space="preserve">1.06440007686615</t>
   </si>
   <si>
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03762269020081</t>
+    <t xml:space="preserve">1.0376228094101</t>
   </si>
   <si>
     <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067976474762</t>
+    <t xml:space="preserve">0.984068036079407</t>
   </si>
   <si>
     <t xml:space="preserve">0.999967038631439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251912117004</t>
+    <t xml:space="preserve">1.01251900196075</t>
   </si>
   <si>
     <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127439022064</t>
+    <t xml:space="preserve">0.958127319812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842553138733</t>
+    <t xml:space="preserve">0.969842612743378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738566875458</t>
+    <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
     <t xml:space="preserve">0.888673722743988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866080343723297</t>
+    <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269971370697</t>
+    <t xml:space="preserve">0.952269911766052</t>
   </si>
   <si>
     <t xml:space="preserve">0.912103831768036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899551868438721</t>
+    <t xml:space="preserve">0.899552047252655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204710006714</t>
+    <t xml:space="preserve">0.896204829216003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937811374664</t>
+    <t xml:space="preserve">0.871937870979309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90875655412674</t>
+    <t xml:space="preserve">0.908756673336029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596392154694</t>
+    <t xml:space="preserve">0.950596272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124569416046</t>
+    <t xml:space="preserve">0.917124509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471787452698</t>
+    <t xml:space="preserve">0.920471727848053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332184314728</t>
+    <t xml:space="preserve">0.967332065105438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311387062073</t>
+    <t xml:space="preserve">0.962311446666718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519545078278</t>
+    <t xml:space="preserve">1.05519533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599023342133</t>
+    <t xml:space="preserve">0.991598963737488</t>
   </si>
   <si>
     <t xml:space="preserve">0.989088773727417</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">0.995783090591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762412548065</t>
+    <t xml:space="preserve">0.99076235294342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207698822021</t>
+    <t xml:space="preserve">0.937207579612732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394337654114</t>
+    <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
     <t xml:space="preserve">0.941391587257385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98825204372406</t>
+    <t xml:space="preserve">0.988251924514771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352921962738</t>
+    <t xml:space="preserve">0.972352862358093</t>
   </si>
   <si>
     <t xml:space="preserve">0.968168795108795</t>
@@ -404,70 +404,70 @@
     <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231127262115</t>
+    <t xml:space="preserve">0.98323118686676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415075302124</t>
+    <t xml:space="preserve">0.987414956092834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005882740021</t>
+    <t xml:space="preserve">0.969005644321442</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943490982056</t>
+    <t xml:space="preserve">0.953943431377411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854260921478</t>
+    <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937933921814</t>
+    <t xml:space="preserve">1.05937945842743</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268502235413</t>
+    <t xml:space="preserve">1.05268490314484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10456609725952</t>
+    <t xml:space="preserve">1.10456621646881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636422157288</t>
+    <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14807939529419</t>
+    <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
     <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661343097687</t>
+    <t xml:space="preserve">1.19661319255829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602567195892</t>
+    <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20581817626953</t>
+    <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21334910392761</t>
+    <t xml:space="preserve">1.2133492231369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753311157227</t>
+    <t xml:space="preserve">1.21753299236298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1564474105835</t>
+    <t xml:space="preserve">1.15644717216492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1531001329422</t>
+    <t xml:space="preserve">1.15310025215149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242930412292</t>
+    <t xml:space="preserve">1.19242918491364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493985176086</t>
+    <t xml:space="preserve">1.19493973255157</t>
   </si>
   <si>
     <t xml:space="preserve">1.1547737121582</t>
@@ -479,28 +479,28 @@
     <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314172744751</t>
+    <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
     <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518870353699</t>
+    <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
     <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146814823151</t>
+    <t xml:space="preserve">1.16146790981293</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803780078888</t>
+    <t xml:space="preserve">1.13803768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799632549286</t>
+    <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
     <t xml:space="preserve">1.12130200862885</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534833431244</t>
+    <t xml:space="preserve">1.49534809589386</t>
   </si>
   <si>
     <t xml:space="preserve">1.45685577392578</t>
@@ -533,22 +533,22 @@
     <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48949062824249</t>
+    <t xml:space="preserve">1.4894905090332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275471687317</t>
+    <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5355144739151</t>
+    <t xml:space="preserve">1.53551423549652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57316982746124</t>
+    <t xml:space="preserve">1.57316994667053</t>
   </si>
   <si>
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174557685852</t>
+    <t xml:space="preserve">1.63174545764923</t>
   </si>
   <si>
     <t xml:space="preserve">1.65684926509857</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550760746002</t>
+    <t xml:space="preserve">1.73550748825073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726425647736</t>
+    <t xml:space="preserve">1.75726413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77400004863739</t>
+    <t xml:space="preserve">1.7739999294281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78236818313599</t>
+    <t xml:space="preserve">1.78236830234528</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6166832447052</t>
+    <t xml:space="preserve">1.61668312549591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664141178131</t>
+    <t xml:space="preserve">1.60664165019989</t>
   </si>
   <si>
     <t xml:space="preserve">1.68195283412933</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">1.68362677097321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542453765869</t>
+    <t xml:space="preserve">1.71542465686798</t>
   </si>
   <si>
     <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224351882935</t>
+    <t xml:space="preserve">1.75224363803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052822589874</t>
+    <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
     <t xml:space="preserve">1.723792552948</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">1.74906098842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337329864502</t>
+    <t xml:space="preserve">1.84337341785431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8005039691925</t>
+    <t xml:space="preserve">1.80050384998322</t>
   </si>
   <si>
     <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193031787872</t>
+    <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548327922821</t>
+    <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323570251465</t>
+    <t xml:space="preserve">2.37323617935181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926259994507</t>
+    <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
     <t xml:space="preserve">2.82421922683716</t>
@@ -647,67 +647,67 @@
     <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505163192749</t>
+    <t xml:space="preserve">2.73505139350891</t>
   </si>
   <si>
     <t xml:space="preserve">2.64416885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47783660888672</t>
+    <t xml:space="preserve">2.47783637046814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.460688829422</t>
+    <t xml:space="preserve">2.46068859100342</t>
   </si>
   <si>
     <t xml:space="preserve">2.40067195892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.364661693573</t>
+    <t xml:space="preserve">2.36466193199158</t>
   </si>
   <si>
     <t xml:space="preserve">2.48983979225159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929634094238</t>
+    <t xml:space="preserve">2.58929657936096</t>
   </si>
   <si>
     <t xml:space="preserve">2.78649425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503452301025</t>
+    <t xml:space="preserve">2.67503428459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012850761414</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
     <t xml:space="preserve">2.46240377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097730636597</t>
+    <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
     <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953468322754</t>
+    <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
     <t xml:space="preserve">2.45211505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52927923202515</t>
+    <t xml:space="preserve">2.52927947044373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214856147766</t>
+    <t xml:space="preserve">2.57214879989624</t>
   </si>
   <si>
     <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43496751785278</t>
+    <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45554447174072</t>
+    <t xml:space="preserve">2.4555447101593</t>
   </si>
   <si>
     <t xml:space="preserve">2.45725917816162</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56186032295227</t>
+    <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781973838806</t>
@@ -731,19 +731,19 @@
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639350891113</t>
+    <t xml:space="preserve">2.42639327049255</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208155632019</t>
+    <t xml:space="preserve">2.33208131790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.31836342811584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2806384563446</t>
+    <t xml:space="preserve">2.28063869476318</t>
   </si>
   <si>
     <t xml:space="preserve">2.32865214347839</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">2.31321907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26692056655884</t>
+    <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.126309633255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12116503715515</t>
+    <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05771923065186</t>
+    <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544396400452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773586273193</t>
+    <t xml:space="preserve">2.11773562431335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1280243396759</t>
+    <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515524864197</t>
+    <t xml:space="preserve">2.08515501022339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629300117493</t>
+    <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08344054222107</t>
+    <t xml:space="preserve">2.08344030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887313842773</t>
+    <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
     <t xml:space="preserve">2.00799059867859</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342367172241</t>
+    <t xml:space="preserve">2.02342343330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2069034576416</t>
+    <t xml:space="preserve">2.20690321922302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603754997253</t>
+    <t xml:space="preserve">2.17603802680969</t>
   </si>
   <si>
     <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401749610901</t>
+    <t xml:space="preserve">2.10401773452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.15889000892639</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12288022041321</t>
+    <t xml:space="preserve">2.12287974357605</t>
   </si>
   <si>
     <t xml:space="preserve">2.1537458896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1520311832428</t>
+    <t xml:space="preserve">2.15203094482422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917848587036</t>
+    <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491714477539</t>
+    <t xml:space="preserve">2.25491738319397</t>
   </si>
   <si>
     <t xml:space="preserve">2.2823531627655</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">2.18975567817688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22919535636902</t>
+    <t xml:space="preserve">2.22919511795044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634289741516</t>
+    <t xml:space="preserve">2.24634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065556526184</t>
+    <t xml:space="preserve">2.34065532684326</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206468582153</t>
+    <t xml:space="preserve">2.27206492424011</t>
   </si>
   <si>
     <t xml:space="preserve">2.20175933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2086181640625</t>
+    <t xml:space="preserve">2.20861840248108</t>
   </si>
   <si>
     <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20347380638123</t>
+    <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
     <t xml:space="preserve">2.24462842941284</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471206665039</t>
+    <t xml:space="preserve">2.54471230506897</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527262687683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384663581848</t>
+    <t xml:space="preserve">2.51384687423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.50355792045593</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326944351196</t>
+    <t xml:space="preserve">2.49326920509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47269248962402</t>
+    <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
     <t xml:space="preserve">2.32007813453674</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">2.32179284095764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809182167053</t>
+    <t xml:space="preserve">2.36809134483337</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379602432251</t>
@@ -923,157 +923,157 @@
     <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922909736633</t>
+    <t xml:space="preserve">2.34922885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35780262947083</t>
+    <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410137176514</t>
+    <t xml:space="preserve">2.40410161018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39038348197937</t>
+    <t xml:space="preserve">2.39038372039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33551073074341</t>
+    <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30636024475098</t>
+    <t xml:space="preserve">2.3063600063324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38866853713989</t>
+    <t xml:space="preserve">2.38866877555847</t>
   </si>
   <si>
     <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832968711853</t>
+    <t xml:space="preserve">2.19832944869995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13488340377808</t>
+    <t xml:space="preserve">2.1348831653595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430597305298</t>
+    <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632626533508</t>
+    <t xml:space="preserve">2.18632650375366</t>
   </si>
   <si>
     <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201431274414</t>
+    <t xml:space="preserve">2.09201407432556</t>
   </si>
   <si>
     <t xml:space="preserve">2.04057145118713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01484966278076</t>
+    <t xml:space="preserve">2.01484942436218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914498329163</t>
+    <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
     <t xml:space="preserve">1.90338981151581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98055458068848</t>
+    <t xml:space="preserve">1.9805543422699</t>
   </si>
   <si>
     <t xml:space="preserve">1.97198069095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053747177124</t>
+    <t xml:space="preserve">1.92053759098053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912823200226</t>
+    <t xml:space="preserve">1.98912835121155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196382045746</t>
+    <t xml:space="preserve">1.91196393966675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911159992218</t>
+    <t xml:space="preserve">1.92911148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624250888824</t>
+    <t xml:space="preserve">1.88624227046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481639862061</t>
+    <t xml:space="preserve">1.89481616020203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909484863281</t>
+    <t xml:space="preserve">1.86909461021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8519469499588</t>
+    <t xml:space="preserve">1.85194706916809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625914096832</t>
+    <t xml:space="preserve">1.94625902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340668201447</t>
+    <t xml:space="preserve">1.96340680122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879186630249</t>
+    <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249334335327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236502170563</t>
+    <t xml:space="preserve">1.97236526012421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9110027551651</t>
+    <t xml:space="preserve">1.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840606689453</t>
+    <t xml:space="preserve">1.85840594768524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470423221588</t>
+    <t xml:space="preserve">1.88470458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02496147155762</t>
+    <t xml:space="preserve">2.02496123313904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866318702698</t>
+    <t xml:space="preserve">1.99866330623627</t>
   </si>
   <si>
     <t xml:space="preserve">1.94606673717499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853486537933</t>
+    <t xml:space="preserve">1.92853474617004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717224121094</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9022364616394</t>
+    <t xml:space="preserve">1.90223670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593853473663</t>
+    <t xml:space="preserve">1.87593829631805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334184646606</t>
+    <t xml:space="preserve">1.82334172725677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976857185364</t>
+    <t xml:space="preserve">1.91976881027222</t>
   </si>
   <si>
     <t xml:space="preserve">1.84964001178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347064495087</t>
+    <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
     <t xml:space="preserve">1.93730080127716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989713191986</t>
+    <t xml:space="preserve">1.98989737033844</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78827774524689</t>
+    <t xml:space="preserve">1.7882776260376</t>
   </si>
   <si>
     <t xml:space="preserve">1.77074551582336</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542429447174</t>
+    <t xml:space="preserve">1.59542417526245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6217223405838</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789206504822</t>
+    <t xml:space="preserve">1.57789194583893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419034957886</t>
+    <t xml:space="preserve">1.60419023036957</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104132652283</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6699355840683</t>
+    <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
     <t xml:space="preserve">1.63048839569092</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295640468597</t>
+    <t xml:space="preserve">1.61295628547668</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925457000732</t>
+    <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.58665800094604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597698688507</t>
+    <t xml:space="preserve">1.55597686767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42010283470154</t>
+    <t xml:space="preserve">1.42010271549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42448592185974</t>
+    <t xml:space="preserve">1.42448580265045</t>
   </si>
   <si>
     <t xml:space="preserve">1.32367610931396</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">1.24478149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20971715450287</t>
+    <t xml:space="preserve">1.20971727371216</t>
   </si>
   <si>
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065576553345</t>
+    <t xml:space="preserve">1.38065564632416</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1187,52 +1187,52 @@
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325197696686</t>
+    <t xml:space="preserve">1.43325185775757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38942158222198</t>
+    <t xml:space="preserve">1.38942170143127</t>
   </si>
   <si>
     <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874032974243</t>
+    <t xml:space="preserve">1.35874044895172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763482570648</t>
+    <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
     <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201803207397</t>
+    <t xml:space="preserve">1.44201791286469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45078408718109</t>
+    <t xml:space="preserve">1.4507839679718</t>
   </si>
   <si>
     <t xml:space="preserve">1.39380466938019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41133677959442</t>
+    <t xml:space="preserve">1.41133666038513</t>
   </si>
   <si>
     <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406167030334</t>
+    <t xml:space="preserve">1.53406178951263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5121465921402</t>
+    <t xml:space="preserve">1.51214647293091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52967882156372</t>
+    <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
     <t xml:space="preserve">1.54721081256866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54282772541046</t>
+    <t xml:space="preserve">1.54282784461975</t>
   </si>
   <si>
     <t xml:space="preserve">1.55159378051758</t>
@@ -1244,40 +1244,40 @@
     <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584842681885</t>
+    <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5165296792984</t>
+    <t xml:space="preserve">1.51652956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5691260099411</t>
+    <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776362419128</t>
+    <t xml:space="preserve">1.50776350498199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529549598694</t>
+    <t xml:space="preserve">1.52529573440552</t>
   </si>
   <si>
     <t xml:space="preserve">1.49899744987488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57839870452881</t>
+    <t xml:space="preserve">1.5783988237381</t>
   </si>
   <si>
     <t xml:space="preserve">1.60545694828033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937921047211</t>
+    <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
     <t xml:space="preserve">1.54232108592987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51526272296906</t>
+    <t xml:space="preserve">1.51526284217834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820447921753</t>
+    <t xml:space="preserve">1.48820459842682</t>
   </si>
   <si>
     <t xml:space="preserve">1.461146235466</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310748577118</t>
+    <t xml:space="preserve">1.44310736656189</t>
   </si>
   <si>
     <t xml:space="preserve">1.41604912281036</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">1.39801025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42506861686707</t>
+    <t xml:space="preserve">1.42506849765778</t>
   </si>
   <si>
     <t xml:space="preserve">1.43408799171448</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">1.40702962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38899075984955</t>
+    <t xml:space="preserve">1.38899087905884</t>
   </si>
   <si>
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35291314125061</t>
+    <t xml:space="preserve">1.3529132604599</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1325,85 +1325,85 @@
     <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977715969086</t>
+    <t xml:space="preserve">1.28977727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271891593933</t>
+    <t xml:space="preserve">1.26271903514862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24468004703522</t>
+    <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
     <t xml:space="preserve">1.19056367874146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18154430389404</t>
+    <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252480983734</t>
+    <t xml:space="preserve">1.17252469062805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664141654968</t>
+    <t xml:space="preserve">1.2266411781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762192249298</t>
+    <t xml:space="preserve">1.21762180328369</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879665374756</t>
+    <t xml:space="preserve">1.29879677295685</t>
   </si>
   <si>
     <t xml:space="preserve">1.36193263530731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37997138500214</t>
+    <t xml:space="preserve">1.37997150421143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781602859497</t>
+    <t xml:space="preserve">1.30781614780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32585489749908</t>
+    <t xml:space="preserve">1.32585501670837</t>
   </si>
   <si>
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566079139709</t>
+    <t xml:space="preserve">1.23566067218781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45212686061859</t>
+    <t xml:space="preserve">1.4521267414093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055418014526</t>
+    <t xml:space="preserve">1.65055406093597</t>
   </si>
   <si>
     <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153480529785</t>
+    <t xml:space="preserve">1.64153468608856</t>
   </si>
   <si>
     <t xml:space="preserve">1.63251519203186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59643757343292</t>
+    <t xml:space="preserve">1.59643745422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486489295959</t>
+    <t xml:space="preserve">1.79486477375031</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72270941734314</t>
+    <t xml:space="preserve">1.72270953655243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369004249573</t>
+    <t xml:space="preserve">1.71369016170502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349581718445</t>
+    <t xml:space="preserve">1.62349569797516</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035995483398</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">1.55134057998657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58741807937622</t>
+    <t xml:space="preserve">1.58741819858551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69565117359161</t>
+    <t xml:space="preserve">1.6956512928009</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">1.11840832233429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350543498993</t>
+    <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
     <t xml:space="preserve">1.15448594093323</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546656608582</t>
+    <t xml:space="preserve">1.14546644687653</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09134995937347</t>
+    <t xml:space="preserve">1.09135007858276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233070373535</t>
+    <t xml:space="preserve">1.08233058452606</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527234077454</t>
+    <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1472,43 +1472,43 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136418819427</t>
+    <t xml:space="preserve">0.992136359214783</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097609519958</t>
+    <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078175067902</t>
+    <t xml:space="preserve">0.965078115463257</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019812107086</t>
+    <t xml:space="preserve">0.938019752502441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919981002807617</t>
+    <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432446479797</t>
+    <t xml:space="preserve">0.897432386875153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91096156835556</t>
+    <t xml:space="preserve">0.910961508750916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983117043972015</t>
+    <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01919460296631</t>
+    <t xml:space="preserve">1.0191947221756</t>
   </si>
   <si>
     <t xml:space="preserve">0.956058621406555</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">1.20860254764557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918498516083</t>
+    <t xml:space="preserve">1.47918510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098133087158</t>
+    <t xml:space="preserve">1.25098145008087</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12124991416931</t>
+    <t xml:space="preserve">1.1212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1568,22 +1568,25 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051640987396</t>
+    <t xml:space="preserve">1.13051652908325</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19538223743439</t>
+    <t xml:space="preserve">1.1953821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198353767395</t>
+    <t xml:space="preserve">1.11198341846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -57593,7 +57596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57619,7 +57622,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2135" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57645,7 +57648,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2136" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57671,7 +57674,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2137" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57697,7 +57700,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2138" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57723,7 +57726,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2139" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57749,7 +57752,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2140" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57775,7 +57778,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57801,7 +57804,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2142" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57827,7 +57830,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2143" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57853,7 +57856,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57879,7 +57882,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57905,7 +57908,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57931,7 +57934,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2147" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57957,7 +57960,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57983,7 +57986,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2149" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58009,7 +58012,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2150" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58035,7 +58038,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2151" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58061,7 +58064,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2152" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58087,7 +58090,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2153" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58113,7 +58116,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2154" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58139,7 +58142,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2155" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58165,7 +58168,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2156" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58191,7 +58194,7 @@
         <v>1</v>
       </c>
       <c r="G2157" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58217,7 +58220,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58243,7 +58246,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2159" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58269,7 +58272,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2160" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58295,7 +58298,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2161" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58321,7 +58324,7 @@
         <v>1</v>
       </c>
       <c r="G2162" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58347,7 +58350,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2163" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58373,7 +58376,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2164" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58399,7 +58402,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58425,7 +58428,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2166" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58451,7 +58454,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2167" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58477,7 +58480,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2168" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58503,7 +58506,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58529,7 +58532,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58555,7 +58558,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2171" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58581,7 +58584,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2172" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58607,7 +58610,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58633,7 +58636,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2174" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58659,7 +58662,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2175" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58685,7 +58688,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2176" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58711,7 +58714,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2177" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58737,7 +58740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2178" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58763,7 +58766,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2179" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58789,7 +58792,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58815,7 +58818,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2181" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58841,7 +58844,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2182" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58867,7 +58870,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2183" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58893,7 +58896,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2184" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58919,7 +58922,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2185" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58945,7 +58948,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2186" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58971,7 +58974,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2187" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58997,7 +59000,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59023,7 +59026,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2189" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59049,7 +59052,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2190" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59075,7 +59078,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2191" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59101,7 +59104,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2192" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59127,7 +59130,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2193" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59153,7 +59156,7 @@
         <v>1</v>
       </c>
       <c r="G2194" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59179,7 +59182,7 @@
         <v>1</v>
       </c>
       <c r="G2195" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59205,7 +59208,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2196" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59231,7 +59234,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59257,7 +59260,7 @@
         <v>1</v>
       </c>
       <c r="G2198" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59283,7 +59286,7 @@
         <v>1</v>
       </c>
       <c r="G2199" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59309,7 +59312,7 @@
         <v>1</v>
       </c>
       <c r="G2200" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59335,7 +59338,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2201" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59361,7 +59364,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59387,7 +59390,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59413,7 +59416,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59439,7 +59442,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59465,7 +59468,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59491,7 +59494,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59517,7 +59520,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2208" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59543,7 +59546,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2209" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59569,7 +59572,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2210" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59595,7 +59598,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2211" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59621,7 +59624,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2212" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59647,7 +59650,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2213" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59673,7 +59676,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2214" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59699,7 +59702,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59725,7 +59728,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2216" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59751,7 +59754,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2217" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59777,7 +59780,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59803,7 +59806,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2219" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59829,7 +59832,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2220" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59855,7 +59858,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2221" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59881,7 +59884,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59907,7 +59910,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2223" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59933,7 +59936,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2224" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59959,7 +59962,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2225" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59985,7 +59988,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60011,7 +60014,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2227" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60037,7 +60040,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2228" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60063,7 +60066,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2229" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60089,7 +60092,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2230" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60115,7 +60118,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2231" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60141,7 +60144,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2232" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60167,7 +60170,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2233" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60193,7 +60196,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2234" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60219,7 +60222,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2235" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60245,7 +60248,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G2236" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60271,7 +60274,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2237" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60297,7 +60300,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2238" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60323,7 +60326,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2239" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60349,7 +60352,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60375,7 +60378,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60401,7 +60404,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2242" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60427,7 +60430,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2243" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60453,7 +60456,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2244" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60479,7 +60482,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2245" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60505,7 +60508,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60531,7 +60534,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2247" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60557,7 +60560,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2248" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60583,7 +60586,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2249" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60609,7 +60612,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2250" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60635,7 +60638,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2251" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60661,7 +60664,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2252" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60687,7 +60690,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2253" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60713,7 +60716,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2254" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60739,7 +60742,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2255" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60765,7 +60768,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2256" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60791,7 +60794,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2257" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60817,7 +60820,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2258" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60843,7 +60846,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2259" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60869,7 +60872,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2260" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60895,7 +60898,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2261" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60921,7 +60924,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2262" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60947,7 +60950,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2263" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60973,7 +60976,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2264" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60999,7 +61002,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2265" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61025,7 +61028,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2266" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61051,7 +61054,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2267" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61077,7 +61080,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2268" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61103,7 +61106,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2269" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61129,7 +61132,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2270" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61155,7 +61158,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61181,7 +61184,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2272" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61207,7 +61210,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2273" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61233,7 +61236,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2274" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61259,7 +61262,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2275" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61285,7 +61288,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2276" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61311,7 +61314,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2277" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61337,7 +61340,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2278" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61363,7 +61366,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2279" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61389,7 +61392,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2280" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61415,7 +61418,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2281" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61441,7 +61444,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2282" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61467,7 +61470,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61493,7 +61496,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2284" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61519,7 +61522,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2285" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61545,7 +61548,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2286" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61571,7 +61574,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2287" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61597,7 +61600,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2288" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61623,7 +61626,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2289" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61649,7 +61652,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2290" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61675,7 +61678,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2291" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61701,7 +61704,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2292" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61727,7 +61730,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2293" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61753,7 +61756,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2294" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61779,7 +61782,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61805,7 +61808,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2296" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61831,7 +61834,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2297" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61857,7 +61860,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2298" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61883,7 +61886,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2299" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61909,7 +61912,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61935,7 +61938,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2301" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61961,7 +61964,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2302" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61987,7 +61990,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2303" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62013,7 +62016,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2304" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62039,7 +62042,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2305" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62065,7 +62068,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2306" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62091,7 +62094,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2307" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62117,7 +62120,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2308" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62143,7 +62146,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2309" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62169,7 +62172,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2310" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62195,7 +62198,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2311" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62221,7 +62224,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2312" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62247,7 +62250,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2313" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62273,7 +62276,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2314" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62299,7 +62302,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62325,7 +62328,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2316" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62351,7 +62354,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2317" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62377,7 +62380,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2318" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62403,7 +62406,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2319" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62429,7 +62432,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2320" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62455,7 +62458,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2321" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62481,7 +62484,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2322" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62507,7 +62510,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2323" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62533,7 +62536,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2324" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62559,7 +62562,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2325" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62585,7 +62588,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2326" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62611,7 +62614,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2327" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62637,7 +62640,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2328" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62663,7 +62666,7 @@
         <v>0.875</v>
       </c>
       <c r="G2329" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62689,7 +62692,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2330" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62715,7 +62718,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2331" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62741,7 +62744,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2332" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62767,7 +62770,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2333" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62793,7 +62796,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2334" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62819,7 +62822,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2335" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62845,7 +62848,7 @@
         <v>0.875</v>
       </c>
       <c r="G2336" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62871,7 +62874,7 @@
         <v>0.875</v>
       </c>
       <c r="G2337" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62897,7 +62900,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2338" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62923,7 +62926,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2339" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62949,7 +62952,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2340" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62975,7 +62978,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2341" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63001,7 +63004,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2342" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63027,7 +63030,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2343" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63053,7 +63056,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2344" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63079,7 +63082,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2345" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63105,7 +63108,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2346" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63131,7 +63134,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2347" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63157,7 +63160,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2348" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63183,7 +63186,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2349" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63209,7 +63212,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2350" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63235,7 +63238,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2351" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63261,7 +63264,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2352" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63287,7 +63290,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2353" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63313,7 +63316,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2354" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63339,7 +63342,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2355" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63365,7 +63368,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2356" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63391,7 +63394,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2357" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63417,7 +63420,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2358" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63443,7 +63446,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2359" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63469,7 +63472,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2360" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63495,7 +63498,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2361" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63521,7 +63524,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2362" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63547,7 +63550,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2363" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63573,7 +63576,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2364" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63599,7 +63602,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2365" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63625,7 +63628,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2366" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63651,7 +63654,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2367" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63677,7 +63680,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G2368" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63703,7 +63706,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2369" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63729,7 +63732,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2370" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63755,7 +63758,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2371" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63781,7 +63784,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2372" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63807,7 +63810,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2373" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63833,7 +63836,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2374" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63859,7 +63862,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2375" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63885,7 +63888,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2376" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63911,7 +63914,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2377" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63937,7 +63940,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2378" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63963,7 +63966,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2379" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63989,7 +63992,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2380" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64015,7 +64018,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64041,7 +64044,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2382" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64067,7 +64070,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2383" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64093,7 +64096,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64119,7 +64122,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64145,7 +64148,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2386" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64171,7 +64174,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2387" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64197,7 +64200,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2388" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64223,7 +64226,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2389" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64249,7 +64252,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2390" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64275,7 +64278,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2391" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64301,7 +64304,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2392" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64327,7 +64330,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2393" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64353,7 +64356,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2394" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64379,7 +64382,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2395" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64405,7 +64408,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2396" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64431,7 +64434,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2397" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64457,7 +64460,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2398" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64483,7 +64486,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2399" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64509,7 +64512,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2400" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64535,7 +64538,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2401" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64561,7 +64564,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2402" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64587,7 +64590,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2403" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64613,7 +64616,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2404" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64639,7 +64642,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2405" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64665,7 +64668,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2406" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64691,7 +64694,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2407" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64717,7 +64720,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2408" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64743,7 +64746,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2409" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64769,7 +64772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2410" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64795,7 +64798,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2411" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64821,7 +64824,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2412" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64847,7 +64850,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2413" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64873,7 +64876,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2414" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64899,7 +64902,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2415" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64925,7 +64928,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2416" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64951,7 +64954,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2417" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64977,7 +64980,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2418" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65003,7 +65006,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2419" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65029,7 +65032,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65055,7 +65058,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2421" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65081,7 +65084,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2422" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65107,7 +65110,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2423" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65133,7 +65136,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2424" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65159,7 +65162,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2425" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65185,7 +65188,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2426" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65211,7 +65214,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2427" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65237,7 +65240,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2428" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65263,7 +65266,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2429" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65289,7 +65292,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2430" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65315,7 +65318,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2431" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65341,7 +65344,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2432" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65367,7 +65370,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2433" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65393,7 +65396,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2434" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65419,7 +65422,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2435" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65445,7 +65448,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2436" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65471,7 +65474,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2437" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65497,7 +65500,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2438" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65523,7 +65526,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2439" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65549,7 +65552,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2440" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65575,7 +65578,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2441" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65601,7 +65604,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2442" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65627,7 +65630,7 @@
         <v>1</v>
       </c>
       <c r="G2443" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65653,7 +65656,7 @@
         <v>1</v>
       </c>
       <c r="G2444" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65679,7 +65682,7 @@
         <v>1</v>
       </c>
       <c r="G2445" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65705,7 +65708,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65731,7 +65734,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65757,7 +65760,7 @@
         <v>1</v>
       </c>
       <c r="G2448" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65783,7 +65786,7 @@
         <v>1</v>
       </c>
       <c r="G2449" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65809,7 +65812,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2450" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65835,7 +65838,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65861,7 +65864,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2452" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65887,7 +65890,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2453" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65913,7 +65916,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2454" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65939,7 +65942,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65965,7 +65968,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2456" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65991,7 +65994,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2457" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66017,7 +66020,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2458" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66043,7 +66046,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2459" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66069,7 +66072,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2460" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66095,7 +66098,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2461" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66121,7 +66124,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2462" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66147,7 +66150,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2463" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66173,7 +66176,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2464" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66199,7 +66202,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2465" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66225,7 +66228,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66251,7 +66254,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2467" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66277,7 +66280,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66303,7 +66306,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2469" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66329,7 +66332,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2470" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66355,7 +66358,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2471" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66381,7 +66384,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2472" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66407,7 +66410,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2473" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66433,7 +66436,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2474" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66459,7 +66462,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2475" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66485,7 +66488,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2476" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66511,7 +66514,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2477" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66537,7 +66540,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66563,7 +66566,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2479" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66589,7 +66592,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2480" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66615,7 +66618,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66641,7 +66644,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G2482" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66667,7 +66670,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2483" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66693,7 +66696,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2484" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66719,7 +66722,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2485" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66745,7 +66748,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2486" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66771,7 +66774,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2487" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66797,7 +66800,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2488" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66823,7 +66826,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2489" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66849,7 +66852,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2490" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66875,7 +66878,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2491" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66901,7 +66904,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2492" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66927,7 +66930,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2493" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66953,7 +66956,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2494" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66979,7 +66982,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2495" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67005,7 +67008,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2496" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67031,7 +67034,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2497" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67057,7 +67060,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2498" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67083,9 +67086,61 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2499" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.3333333333</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>583</v>
+      </c>
+      <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.5500578704</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>589</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4707692861557</t>
+    <t xml:space="preserve">1.47076916694641</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781757354736</t>
+    <t xml:space="preserve">1.43781745433807</t>
   </si>
   <si>
     <t xml:space="preserve">1.48684310913086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424712657928</t>
+    <t xml:space="preserve">1.44424724578857</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236236572266</t>
+    <t xml:space="preserve">1.38236248493195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593269348145</t>
+    <t xml:space="preserve">1.37593281269073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414053916931</t>
+    <t xml:space="preserve">1.33414030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744762420654</t>
+    <t xml:space="preserve">1.35744786262512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628830432892</t>
+    <t xml:space="preserve">1.36628842353821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290271282196</t>
+    <t xml:space="preserve">1.41290295124054</t>
   </si>
   <si>
     <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647315979004</t>
+    <t xml:space="preserve">1.40647327899933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44585466384888</t>
+    <t xml:space="preserve">1.44585454463959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39843618869781</t>
+    <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
     <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726276874542</t>
+    <t xml:space="preserve">1.31726264953613</t>
   </si>
   <si>
     <t xml:space="preserve">1.31002938747406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217751026154</t>
+    <t xml:space="preserve">1.34217739105225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021424293518</t>
+    <t xml:space="preserve">1.35021436214447</t>
   </si>
   <si>
     <t xml:space="preserve">1.32128119468689</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889874458313</t>
+    <t xml:space="preserve">1.49889850616455</t>
   </si>
   <si>
     <t xml:space="preserve">1.472376704216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49488008022308</t>
+    <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274665355682</t>
+    <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
     <t xml:space="preserve">1.61543500423431</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">1.67490875720978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64597570896149</t>
+    <t xml:space="preserve">1.6459755897522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113911628723</t>
+    <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702808380127</t>
+    <t xml:space="preserve">1.52702820301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095414161682</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862128257751</t>
+    <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
     <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601904392242</t>
+    <t xml:space="preserve">1.45601880550385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426251411438</t>
+    <t xml:space="preserve">1.4342622756958</t>
   </si>
   <si>
     <t xml:space="preserve">1.4083217382431</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091535568237</t>
+    <t xml:space="preserve">1.43091511726379</t>
   </si>
   <si>
     <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41334247589111</t>
+    <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
     <t xml:space="preserve">1.4049745798111</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325479388237</t>
+    <t xml:space="preserve">1.32547926902771</t>
   </si>
   <si>
     <t xml:space="preserve">1.3221321105957</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">1.29702842235565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539619922638</t>
+    <t xml:space="preserve">1.30539631843567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397171020508</t>
+    <t xml:space="preserve">1.36397182941437</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38070774078369</t>
+    <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050000667572</t>
+    <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27192461490631</t>
+    <t xml:space="preserve">1.2719247341156</t>
   </si>
   <si>
     <t xml:space="preserve">1.25267827510834</t>
@@ -236,40 +236,40 @@
     <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916509628296</t>
+    <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841143608093</t>
+    <t xml:space="preserve">1.22841131687164</t>
   </si>
   <si>
     <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008513450623</t>
+    <t xml:space="preserve">1.23008501529694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824541568756</t>
+    <t xml:space="preserve">1.18824529647827</t>
   </si>
   <si>
     <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171723842621</t>
+    <t xml:space="preserve">1.22171700000763</t>
   </si>
   <si>
     <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226316452026</t>
+    <t xml:space="preserve">1.15226340293884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14222168922424</t>
+    <t xml:space="preserve">1.14222180843353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150962352753</t>
+    <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966978549957</t>
+    <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
     <t xml:space="preserve">1.11293399333954</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0392963886261</t>
+    <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435848236084</t>
+    <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
     <t xml:space="preserve">1.08364629745483</t>
@@ -299,88 +299,88 @@
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0376228094101</t>
+    <t xml:space="preserve">1.03762269020081</t>
   </si>
   <si>
     <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984068036079407</t>
+    <t xml:space="preserve">0.984068095684052</t>
   </si>
   <si>
     <t xml:space="preserve">0.999967038631439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251900196075</t>
+    <t xml:space="preserve">1.01251912117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127319812775</t>
+    <t xml:space="preserve">0.958127379417419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842612743378</t>
+    <t xml:space="preserve">0.969842553138733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738745689392</t>
+    <t xml:space="preserve">0.944738686084747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673722743988</t>
+    <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
     <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269911766052</t>
+    <t xml:space="preserve">0.952269971370697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103831768036</t>
+    <t xml:space="preserve">0.912103891372681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899552047252655</t>
+    <t xml:space="preserve">0.899551868438721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204829216003</t>
+    <t xml:space="preserve">0.896204710006714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937870979309</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756673336029</t>
+    <t xml:space="preserve">0.90875655412674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596272945404</t>
+    <t xml:space="preserve">0.950596392154694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471727848053</t>
+    <t xml:space="preserve">0.920471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.967332065105438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311446666718</t>
+    <t xml:space="preserve">0.962311327457428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519533157349</t>
+    <t xml:space="preserve">1.05519545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991598963737488</t>
+    <t xml:space="preserve">0.991599023342133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088773727417</t>
+    <t xml:space="preserve">0.989088892936707</t>
   </si>
   <si>
     <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783090591431</t>
+    <t xml:space="preserve">0.995783150196075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99076235294342</t>
+    <t xml:space="preserve">0.99076247215271</t>
   </si>
   <si>
     <t xml:space="preserve">0.937207579612732</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391587257385</t>
+    <t xml:space="preserve">0.94139164686203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251924514771</t>
+    <t xml:space="preserve">0.988251984119415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352862358093</t>
+    <t xml:space="preserve">0.972352802753448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168795108795</t>
+    <t xml:space="preserve">0.96816885471344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9757000207901</t>
+    <t xml:space="preserve">0.975700080394745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98323118686676</t>
+    <t xml:space="preserve">0.983231008052826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987414956092834</t>
+    <t xml:space="preserve">0.987415134906769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005644321442</t>
+    <t xml:space="preserve">0.969005823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994109511375427</t>
+    <t xml:space="preserve">0.994109630584717</t>
   </si>
   <si>
     <t xml:space="preserve">0.953943431377411</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937945842743</t>
+    <t xml:space="preserve">1.05937933921814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507078647614</t>
+    <t xml:space="preserve">1.02507090568542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268490314484</t>
+    <t xml:space="preserve">1.05268502235413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10456621646881</t>
+    <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636434078217</t>
+    <t xml:space="preserve">1.13636422157288</t>
   </si>
   <si>
     <t xml:space="preserve">1.1480792760849</t>
@@ -443,34 +443,34 @@
     <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661319255829</t>
+    <t xml:space="preserve">1.19661331176758</t>
   </si>
   <si>
     <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20581793785095</t>
+    <t xml:space="preserve">1.20581805706024</t>
   </si>
   <si>
     <t xml:space="preserve">1.2133492231369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753299236298</t>
+    <t xml:space="preserve">1.21753323078156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644717216492</t>
+    <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15310025215149</t>
+    <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242918491364</t>
+    <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
     <t xml:space="preserve">1.19493973255157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1547737121582</t>
+    <t xml:space="preserve">1.15477359294891</t>
   </si>
   <si>
     <t xml:space="preserve">1.1464056968689</t>
@@ -485,22 +485,22 @@
     <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518882274628</t>
+    <t xml:space="preserve">1.25518870353699</t>
   </si>
   <si>
     <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146790981293</t>
+    <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803768157959</t>
+    <t xml:space="preserve">1.13803780078888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799644470215</t>
+    <t xml:space="preserve">1.12799632549286</t>
   </si>
   <si>
     <t xml:space="preserve">1.12130200862885</t>
@@ -509,10 +509,10 @@
     <t xml:space="preserve">1.17653024196625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581142902374</t>
+    <t xml:space="preserve">1.40581130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576983451843</t>
+    <t xml:space="preserve">1.39576995372772</t>
   </si>
   <si>
     <t xml:space="preserve">1.39911723136902</t>
@@ -521,25 +521,25 @@
     <t xml:space="preserve">1.39744341373444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46020293235779</t>
+    <t xml:space="preserve">1.4602028131485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534809589386</t>
+    <t xml:space="preserve">1.49534821510315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685577392578</t>
+    <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
     <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4894905090332</t>
+    <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275483608246</t>
+    <t xml:space="preserve">1.47275471687317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551423549652</t>
+    <t xml:space="preserve">1.53551435470581</t>
   </si>
   <si>
     <t xml:space="preserve">1.57316994667053</t>
@@ -548,25 +548,25 @@
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174545764923</t>
+    <t xml:space="preserve">1.63174557685852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438031196594</t>
+    <t xml:space="preserve">1.66438019275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550748825073</t>
+    <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726413726807</t>
+    <t xml:space="preserve">1.75726425647736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7739999294281</t>
+    <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78236830234528</t>
+    <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61668312549591</t>
+    <t xml:space="preserve">1.61668336391449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664165019989</t>
+    <t xml:space="preserve">1.6066415309906</t>
   </si>
   <si>
     <t xml:space="preserve">1.68195283412933</t>
@@ -596,22 +596,22 @@
     <t xml:space="preserve">1.68362677097321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542465686798</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718130588531</t>
+    <t xml:space="preserve">1.73718106746674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224363803864</t>
+    <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
     <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.723792552948</t>
+    <t xml:space="preserve">1.72379243373871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601241588593</t>
+    <t xml:space="preserve">1.65601229667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.74220204353333</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">1.74906098842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337341785431</t>
+    <t xml:space="preserve">1.84337329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80050384998322</t>
+    <t xml:space="preserve">1.8005039691925</t>
   </si>
   <si>
     <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193019866943</t>
+    <t xml:space="preserve">1.79193031787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323617935181</t>
+    <t xml:space="preserve">2.37323570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926283836365</t>
+    <t xml:space="preserve">2.46926259994507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421922683716</t>
+    <t xml:space="preserve">2.82421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936334609985</t>
+    <t xml:space="preserve">2.82936310768127</t>
   </si>
   <si>
     <t xml:space="preserve">2.73505139350891</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">2.64416885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47783637046814</t>
+    <t xml:space="preserve">2.47783660888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.46068859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067195892334</t>
+    <t xml:space="preserve">2.40067219734192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36466193199158</t>
+    <t xml:space="preserve">2.36466217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929657936096</t>
+    <t xml:space="preserve">2.5892961025238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78649425506592</t>
+    <t xml:space="preserve">2.7864944934845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503428459167</t>
+    <t xml:space="preserve">2.67503476142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.50012826919556</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">2.52927947044373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214879989624</t>
+    <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641037940979</t>
+    <t xml:space="preserve">2.48641014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4349672794342</t>
+    <t xml:space="preserve">2.43496775627136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4555447101593</t>
+    <t xml:space="preserve">2.45554447174072</t>
   </si>
   <si>
     <t xml:space="preserve">2.45725917816162</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56185984611511</t>
+    <t xml:space="preserve">2.56186008453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781973838806</t>
@@ -731,34 +731,34 @@
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639327049255</t>
+    <t xml:space="preserve">2.42639350891113</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208131790161</t>
+    <t xml:space="preserve">2.33208155632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.31836342811584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28063869476318</t>
+    <t xml:space="preserve">2.2806384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865214347839</t>
+    <t xml:space="preserve">2.32865190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31321907043457</t>
+    <t xml:space="preserve">2.31321883201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26692032814026</t>
+    <t xml:space="preserve">2.26692056655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.126309633255</t>
+    <t xml:space="preserve">2.12630939483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12116527557373</t>
+    <t xml:space="preserve">2.12116503715515</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800746917725</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09544396400452</t>
+    <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.11773562431335</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515501022339</t>
+    <t xml:space="preserve">2.08515524864197</t>
   </si>
   <si>
     <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08344030380249</t>
+    <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887337684631</t>
+    <t xml:space="preserve">2.09887313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799059867859</t>
+    <t xml:space="preserve">2.00799083709717</t>
   </si>
   <si>
     <t xml:space="preserve">2.0508599281311</t>
@@ -797,67 +797,67 @@
     <t xml:space="preserve">2.02342343330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20690321922302</t>
+    <t xml:space="preserve">2.20690369606018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603802680969</t>
+    <t xml:space="preserve">2.17603778839111</t>
   </si>
   <si>
     <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401773452759</t>
+    <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15889000892639</t>
+    <t xml:space="preserve">2.15888977050781</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12287974357605</t>
+    <t xml:space="preserve">2.12288022041321</t>
   </si>
   <si>
     <t xml:space="preserve">2.1537458896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15203094482422</t>
+    <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917872428894</t>
+    <t xml:space="preserve">2.16917848587036</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062158584595</t>
+    <t xml:space="preserve">2.22062182426453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491738319397</t>
+    <t xml:space="preserve">2.25491714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.2823531627655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23776936531067</t>
+    <t xml:space="preserve">2.23776912689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.22233653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089366912842</t>
+    <t xml:space="preserve">2.17089319229126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975567817688</t>
+    <t xml:space="preserve">2.18975591659546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22919511795044</t>
+    <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634313583374</t>
+    <t xml:space="preserve">2.24634289741516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065532684326</t>
+    <t xml:space="preserve">2.34065508842468</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206492424011</t>
+    <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.20175933837891</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2034740447998</t>
+    <t xml:space="preserve">2.20347380638123</t>
   </si>
   <si>
     <t xml:space="preserve">2.24462842941284</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471206665039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384687423706</t>
+    <t xml:space="preserve">2.5138463973999</t>
   </si>
   <si>
     <t xml:space="preserve">2.50355792045593</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326920509338</t>
+    <t xml:space="preserve">2.49326968193054</t>
   </si>
   <si>
     <t xml:space="preserve">2.47269225120544</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">2.32179284095764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809134483337</t>
+    <t xml:space="preserve">2.36809182167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379602432251</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922885894775</t>
+    <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3578028678894</t>
+    <t xml:space="preserve">2.35780262947083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410161018372</t>
+    <t xml:space="preserve">2.40410137176514</t>
   </si>
   <si>
     <t xml:space="preserve">2.39038372039795</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3063600063324</t>
+    <t xml:space="preserve">2.30636024475098</t>
   </si>
   <si>
     <t xml:space="preserve">2.38866877555847</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832944869995</t>
+    <t xml:space="preserve">2.19832968711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.1348831653595</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632650375366</t>
+    <t xml:space="preserve">2.18632626533508</t>
   </si>
   <si>
     <t xml:space="preserve">2.10058808326721</t>
@@ -968,25 +968,25 @@
     <t xml:space="preserve">2.04057145118713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01484942436218</t>
+    <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
     <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90338981151581</t>
+    <t xml:space="preserve">1.9033899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805543422699</t>
+    <t xml:space="preserve">1.98055481910706</t>
   </si>
   <si>
     <t xml:space="preserve">1.97198069095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053759098053</t>
+    <t xml:space="preserve">1.92053735256195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912835121155</t>
+    <t xml:space="preserve">1.98912823200226</t>
   </si>
   <si>
     <t xml:space="preserve">1.91196393966675</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">1.92911148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624238967896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481616020203</t>
+    <t xml:space="preserve">1.89481627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909461021423</t>
+    <t xml:space="preserve">1.86909484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194706916809</t>
+    <t xml:space="preserve">1.85194718837738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625902175903</t>
+    <t xml:space="preserve">1.94625926017761</t>
   </si>
   <si>
     <t xml:space="preserve">1.96340680122375</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249334335327</t>
+    <t xml:space="preserve">2.04249358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236526012421</t>
+    <t xml:space="preserve">1.97236514091492</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840594768524</t>
+    <t xml:space="preserve">1.85840618610382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470458984375</t>
+    <t xml:space="preserve">1.88470435142517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02496123313904</t>
+    <t xml:space="preserve">2.0249617099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866330623627</t>
+    <t xml:space="preserve">1.99866306781769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606673717499</t>
+    <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
     <t xml:space="preserve">1.92853474617004</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223670005798</t>
+    <t xml:space="preserve">1.90223658084869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593829631805</t>
+    <t xml:space="preserve">1.87593841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334172725677</t>
+    <t xml:space="preserve">1.82334196567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976881027222</t>
+    <t xml:space="preserve">1.91976857185364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84964001178741</t>
+    <t xml:space="preserve">1.84963989257812</t>
   </si>
   <si>
     <t xml:space="preserve">1.89347052574158</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">1.93730080127716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989737033844</t>
+    <t xml:space="preserve">1.98989701271057</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733937263489</t>
+    <t xml:space="preserve">1.6173392534256</t>
   </si>
   <si>
     <t xml:space="preserve">1.59542417526245</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">1.6217223405838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65678668022156</t>
+    <t xml:space="preserve">1.65678656101227</t>
   </si>
   <si>
     <t xml:space="preserve">1.68308484554291</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">1.66555273532867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69185090065002</t>
+    <t xml:space="preserve">1.69185078144073</t>
   </si>
   <si>
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789194583893</t>
+    <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419023036957</t>
+    <t xml:space="preserve">1.60419034957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048839569092</t>
+    <t xml:space="preserve">1.63048851490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">1.70061707496643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64363753795624</t>
+    <t xml:space="preserve">1.64363765716553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295628547668</t>
+    <t xml:space="preserve">1.61295640468597</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">1.55597686767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42010271549225</t>
+    <t xml:space="preserve">1.42010283470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.42448580265045</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">1.24478149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20971727371216</t>
+    <t xml:space="preserve">1.20971715450287</t>
   </si>
   <si>
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065564632416</t>
+    <t xml:space="preserve">1.38065552711487</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1187,34 +1187,34 @@
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325185775757</t>
+    <t xml:space="preserve">1.43325197696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38942170143127</t>
+    <t xml:space="preserve">1.38942158222198</t>
   </si>
   <si>
     <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874044895172</t>
+    <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
     <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44640100002289</t>
+    <t xml:space="preserve">1.4464008808136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201791286469</t>
+    <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4507839679718</t>
+    <t xml:space="preserve">1.45078408718109</t>
   </si>
   <si>
     <t xml:space="preserve">1.39380466938019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41133666038513</t>
+    <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
     <t xml:space="preserve">1.36750638484955</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">1.54721081256866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54282784461975</t>
+    <t xml:space="preserve">1.54282772541046</t>
   </si>
   <si>
     <t xml:space="preserve">1.55159378051758</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">1.56035983562469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091264724731</t>
+    <t xml:space="preserve">1.52091252803802</t>
   </si>
   <si>
     <t xml:space="preserve">1.48584830760956</t>
@@ -1250,34 +1250,34 @@
     <t xml:space="preserve">1.51652956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56912589073181</t>
+    <t xml:space="preserve">1.5691260099411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776350498199</t>
+    <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529573440552</t>
+    <t xml:space="preserve">1.52529561519623</t>
   </si>
   <si>
     <t xml:space="preserve">1.49899744987488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5783988237381</t>
+    <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.60545694828033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5693793296814</t>
+    <t xml:space="preserve">1.56937921047211</t>
   </si>
   <si>
     <t xml:space="preserve">1.54232108592987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51526284217834</t>
+    <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
     <t xml:space="preserve">1.461146235466</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310736656189</t>
+    <t xml:space="preserve">1.44310748577118</t>
   </si>
   <si>
     <t xml:space="preserve">1.41604912281036</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">1.39801025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42506849765778</t>
+    <t xml:space="preserve">1.42506861686707</t>
   </si>
   <si>
     <t xml:space="preserve">1.43408799171448</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">1.40702962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38899087905884</t>
+    <t xml:space="preserve">1.38899075984955</t>
   </si>
   <si>
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3529132604599</t>
+    <t xml:space="preserve">1.35291314125061</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1325,85 +1325,85 @@
     <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271903514862</t>
+    <t xml:space="preserve">1.26271891593933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24468016624451</t>
+    <t xml:space="preserve">1.24468004703522</t>
   </si>
   <si>
     <t xml:space="preserve">1.19056367874146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18154418468475</t>
+    <t xml:space="preserve">1.18154430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2266411781311</t>
+    <t xml:space="preserve">1.22664141654968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762180328369</t>
+    <t xml:space="preserve">1.21762192249298</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
     <t xml:space="preserve">1.36193263530731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37997150421143</t>
+    <t xml:space="preserve">1.37997138500214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781614780426</t>
+    <t xml:space="preserve">1.30781602859497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32585501670837</t>
+    <t xml:space="preserve">1.32585489749908</t>
   </si>
   <si>
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566067218781</t>
+    <t xml:space="preserve">1.23566079139709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4521267414093</t>
+    <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055406093597</t>
+    <t xml:space="preserve">1.65055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153468608856</t>
+    <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
     <t xml:space="preserve">1.63251519203186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59643745422363</t>
+    <t xml:space="preserve">1.59643757343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486477375031</t>
+    <t xml:space="preserve">1.79486489295959</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72270953655243</t>
+    <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369016170502</t>
+    <t xml:space="preserve">1.71369004249573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349569797516</t>
+    <t xml:space="preserve">1.62349581718445</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035995483398</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">1.55134057998657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58741819858551</t>
+    <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6956512928009</t>
+    <t xml:space="preserve">1.69565117359161</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">1.11840832233429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350531578064</t>
+    <t xml:space="preserve">1.16350543498993</t>
   </si>
   <si>
     <t xml:space="preserve">1.15448594093323</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09135007858276</t>
+    <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233058452606</t>
+    <t xml:space="preserve">1.08233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527222156525</t>
+    <t xml:space="preserve">1.05527234077454</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1472,43 +1472,43 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097549915314</t>
+    <t xml:space="preserve">0.974097609519958</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078115463257</t>
+    <t xml:space="preserve">0.965078175067902</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019752502441</t>
+    <t xml:space="preserve">0.938019812107086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919980943202972</t>
+    <t xml:space="preserve">0.919981002807617</t>
   </si>
   <si>
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432386875153</t>
+    <t xml:space="preserve">0.897432446479797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910961508750916</t>
+    <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983116924762726</t>
+    <t xml:space="preserve">0.983117043972015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0191947221756</t>
+    <t xml:space="preserve">1.01919460296631</t>
   </si>
   <si>
     <t xml:space="preserve">0.956058621406555</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">1.20860254764557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918510437012</t>
+    <t xml:space="preserve">1.47918498516083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098145008087</t>
+    <t xml:space="preserve">1.25098133087158</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1212500333786</t>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1568,25 +1568,22 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051652908325</t>
+    <t xml:space="preserve">1.13051640987396</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1953821182251</t>
+    <t xml:space="preserve">1.19538223743439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198341846466</t>
+    <t xml:space="preserve">1.11198353767395</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -57596,7 +57593,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57622,7 +57619,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2135" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57648,7 +57645,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2136" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57674,7 +57671,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2137" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57700,7 +57697,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2138" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57726,7 +57723,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2139" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57752,7 +57749,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2140" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57778,7 +57775,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57804,7 +57801,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2142" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57830,7 +57827,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2143" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57856,7 +57853,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57882,7 +57879,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57908,7 +57905,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57934,7 +57931,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57960,7 +57957,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57986,7 +57983,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2149" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58012,7 +58009,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2150" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58038,7 +58035,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2151" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58064,7 +58061,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2152" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58090,7 +58087,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2153" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58116,7 +58113,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2154" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58142,7 +58139,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2155" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58168,7 +58165,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2156" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58194,7 +58191,7 @@
         <v>1</v>
       </c>
       <c r="G2157" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58220,7 +58217,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58246,7 +58243,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2159" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58272,7 +58269,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2160" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58298,7 +58295,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2161" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58324,7 +58321,7 @@
         <v>1</v>
       </c>
       <c r="G2162" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58350,7 +58347,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2163" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58376,7 +58373,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2164" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58402,7 +58399,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58428,7 +58425,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2166" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58454,7 +58451,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2167" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58480,7 +58477,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2168" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58506,7 +58503,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58532,7 +58529,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58558,7 +58555,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2171" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58584,7 +58581,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2172" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58610,7 +58607,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58636,7 +58633,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2174" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58662,7 +58659,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2175" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58688,7 +58685,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2176" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58714,7 +58711,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2177" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58740,7 +58737,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2178" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58766,7 +58763,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2179" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58792,7 +58789,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58818,7 +58815,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2181" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58844,7 +58841,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2182" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58870,7 +58867,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2183" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58896,7 +58893,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2184" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58922,7 +58919,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2185" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58948,7 +58945,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2186" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58974,7 +58971,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2187" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59000,7 +58997,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59026,7 +59023,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2189" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59052,7 +59049,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2190" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59078,7 +59075,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2191" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59104,7 +59101,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2192" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59130,7 +59127,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2193" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59156,7 +59153,7 @@
         <v>1</v>
       </c>
       <c r="G2194" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59182,7 +59179,7 @@
         <v>1</v>
       </c>
       <c r="G2195" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59208,7 +59205,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2196" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59234,7 +59231,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59260,7 +59257,7 @@
         <v>1</v>
       </c>
       <c r="G2198" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59286,7 +59283,7 @@
         <v>1</v>
       </c>
       <c r="G2199" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59312,7 +59309,7 @@
         <v>1</v>
       </c>
       <c r="G2200" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59338,7 +59335,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2201" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59364,7 +59361,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59390,7 +59387,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59416,7 +59413,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59442,7 +59439,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59468,7 +59465,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59494,7 +59491,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59520,7 +59517,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2208" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59546,7 +59543,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2209" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59572,7 +59569,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2210" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59598,7 +59595,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2211" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59624,7 +59621,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2212" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59650,7 +59647,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2213" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59676,7 +59673,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2214" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59702,7 +59699,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59728,7 +59725,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2216" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59754,7 +59751,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2217" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59780,7 +59777,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59806,7 +59803,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2219" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59832,7 +59829,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2220" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59858,7 +59855,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2221" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59884,7 +59881,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59910,7 +59907,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2223" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59936,7 +59933,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2224" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59962,7 +59959,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2225" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59988,7 +59985,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60014,7 +60011,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2227" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60040,7 +60037,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2228" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60066,7 +60063,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2229" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60092,7 +60089,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2230" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60118,7 +60115,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2231" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60144,7 +60141,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2232" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60170,7 +60167,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2233" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60196,7 +60193,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2234" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60222,7 +60219,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2235" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60248,7 +60245,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G2236" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60274,7 +60271,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2237" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60300,7 +60297,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2238" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60326,7 +60323,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2239" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60352,7 +60349,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60378,7 +60375,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60404,7 +60401,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2242" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60430,7 +60427,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2243" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60456,7 +60453,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2244" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60482,7 +60479,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2245" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60508,7 +60505,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60534,7 +60531,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2247" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60560,7 +60557,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2248" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60586,7 +60583,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2249" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60612,7 +60609,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2250" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60638,7 +60635,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2251" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60664,7 +60661,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2252" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60690,7 +60687,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2253" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60716,7 +60713,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2254" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60742,7 +60739,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2255" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60768,7 +60765,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2256" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60794,7 +60791,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2257" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60820,7 +60817,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2258" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60846,7 +60843,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2259" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60872,7 +60869,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2260" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60898,7 +60895,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2261" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60924,7 +60921,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2262" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60950,7 +60947,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2263" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60976,7 +60973,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2264" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61002,7 +60999,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2265" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61028,7 +61025,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2266" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61054,7 +61051,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2267" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61080,7 +61077,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2268" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61106,7 +61103,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2269" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61132,7 +61129,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2270" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61158,7 +61155,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61184,7 +61181,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2272" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61210,7 +61207,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2273" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61236,7 +61233,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2274" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61262,7 +61259,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2275" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61288,7 +61285,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2276" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61314,7 +61311,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2277" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61340,7 +61337,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2278" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61366,7 +61363,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2279" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61392,7 +61389,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2280" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61418,7 +61415,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2281" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61444,7 +61441,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2282" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61470,7 +61467,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61496,7 +61493,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2284" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61522,7 +61519,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2285" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61548,7 +61545,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2286" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61574,7 +61571,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2287" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61600,7 +61597,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2288" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61626,7 +61623,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2289" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61652,7 +61649,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2290" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61678,7 +61675,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2291" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61704,7 +61701,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2292" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61730,7 +61727,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2293" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61756,7 +61753,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2294" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61782,7 +61779,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61808,7 +61805,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2296" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61834,7 +61831,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2297" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61860,7 +61857,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2298" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61886,7 +61883,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2299" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61912,7 +61909,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61938,7 +61935,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2301" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61964,7 +61961,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2302" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61990,7 +61987,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2303" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62016,7 +62013,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2304" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62042,7 +62039,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2305" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62068,7 +62065,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2306" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62094,7 +62091,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2307" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62120,7 +62117,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2308" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62146,7 +62143,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2309" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62172,7 +62169,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2310" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62198,7 +62195,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2311" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62224,7 +62221,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2312" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62250,7 +62247,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2313" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62276,7 +62273,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2314" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62302,7 +62299,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62328,7 +62325,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2316" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62354,7 +62351,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2317" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62380,7 +62377,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2318" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62406,7 +62403,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2319" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62432,7 +62429,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2320" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62458,7 +62455,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2321" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62484,7 +62481,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2322" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62510,7 +62507,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2323" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62536,7 +62533,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2324" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62562,7 +62559,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2325" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62588,7 +62585,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2326" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62614,7 +62611,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2327" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62640,7 +62637,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2328" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62666,7 +62663,7 @@
         <v>0.875</v>
       </c>
       <c r="G2329" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62692,7 +62689,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2330" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62718,7 +62715,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2331" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62744,7 +62741,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2332" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62770,7 +62767,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2333" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62796,7 +62793,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2334" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62822,7 +62819,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2335" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62848,7 +62845,7 @@
         <v>0.875</v>
       </c>
       <c r="G2336" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62874,7 +62871,7 @@
         <v>0.875</v>
       </c>
       <c r="G2337" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62900,7 +62897,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2338" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62926,7 +62923,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2339" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62952,7 +62949,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2340" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62978,7 +62975,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2341" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63004,7 +63001,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2342" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63030,7 +63027,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2343" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63056,7 +63053,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2344" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63082,7 +63079,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2345" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63108,7 +63105,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2346" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63134,7 +63131,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2347" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63160,7 +63157,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2348" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63186,7 +63183,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2349" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63212,7 +63209,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2350" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63238,7 +63235,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2351" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63264,7 +63261,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2352" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63290,7 +63287,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2353" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63316,7 +63313,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2354" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63342,7 +63339,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2355" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63368,7 +63365,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2356" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63394,7 +63391,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2357" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63420,7 +63417,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2358" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63446,7 +63443,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2359" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63472,7 +63469,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2360" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63498,7 +63495,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2361" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63524,7 +63521,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2362" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63550,7 +63547,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2363" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63576,7 +63573,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2364" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63602,7 +63599,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2365" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63628,7 +63625,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2366" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63654,7 +63651,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2367" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63680,7 +63677,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G2368" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63706,7 +63703,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2369" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63732,7 +63729,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2370" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63758,7 +63755,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2371" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63784,7 +63781,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2372" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63810,7 +63807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2373" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63836,7 +63833,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2374" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63862,7 +63859,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2375" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63888,7 +63885,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2376" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63914,7 +63911,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2377" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63940,7 +63937,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2378" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63966,7 +63963,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2379" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63992,7 +63989,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2380" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64018,7 +64015,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64044,7 +64041,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2382" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64070,7 +64067,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2383" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64096,7 +64093,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64122,7 +64119,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64148,7 +64145,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2386" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64174,7 +64171,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2387" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64200,7 +64197,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2388" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64226,7 +64223,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2389" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64252,7 +64249,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2390" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64278,7 +64275,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2391" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64304,7 +64301,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2392" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64330,7 +64327,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2393" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64356,7 +64353,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2394" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64382,7 +64379,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2395" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64408,7 +64405,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2396" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64434,7 +64431,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2397" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64460,7 +64457,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2398" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64486,7 +64483,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2399" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64512,7 +64509,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2400" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64538,7 +64535,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2401" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64564,7 +64561,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2402" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64590,7 +64587,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2403" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64616,7 +64613,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2404" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64642,7 +64639,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2405" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64668,7 +64665,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2406" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64694,7 +64691,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2407" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64720,7 +64717,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2408" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64746,7 +64743,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2409" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64772,7 +64769,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2410" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64798,7 +64795,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2411" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64824,7 +64821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2412" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64850,7 +64847,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2413" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64876,7 +64873,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2414" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64902,7 +64899,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2415" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64928,7 +64925,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2416" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64954,7 +64951,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2417" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64980,7 +64977,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2418" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65006,7 +65003,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2419" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65032,7 +65029,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65058,7 +65055,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2421" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65084,7 +65081,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2422" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65110,7 +65107,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2423" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65136,7 +65133,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2424" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65162,7 +65159,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2425" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65188,7 +65185,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2426" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65214,7 +65211,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2427" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65240,7 +65237,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2428" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65266,7 +65263,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2429" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65292,7 +65289,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2430" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65318,7 +65315,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2431" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65344,7 +65341,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2432" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65370,7 +65367,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2433" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65396,7 +65393,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2434" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65422,7 +65419,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2435" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65448,7 +65445,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2436" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65474,7 +65471,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2437" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65500,7 +65497,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2438" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65526,7 +65523,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2439" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65552,7 +65549,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2440" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65578,7 +65575,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2441" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65604,7 +65601,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2442" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65630,7 +65627,7 @@
         <v>1</v>
       </c>
       <c r="G2443" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65656,7 +65653,7 @@
         <v>1</v>
       </c>
       <c r="G2444" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65682,7 +65679,7 @@
         <v>1</v>
       </c>
       <c r="G2445" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65708,7 +65705,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65734,7 +65731,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65760,7 +65757,7 @@
         <v>1</v>
       </c>
       <c r="G2448" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65786,7 +65783,7 @@
         <v>1</v>
       </c>
       <c r="G2449" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65812,7 +65809,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2450" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65838,7 +65835,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65864,7 +65861,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2452" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65890,7 +65887,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2453" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65916,7 +65913,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2454" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65942,7 +65939,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65968,7 +65965,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2456" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65994,7 +65991,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2457" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66020,7 +66017,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2458" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66046,7 +66043,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2459" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66072,7 +66069,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2460" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66098,7 +66095,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2461" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66124,7 +66121,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2462" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66150,7 +66147,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2463" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66176,7 +66173,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2464" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66202,7 +66199,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2465" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66228,7 +66225,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66254,7 +66251,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2467" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66280,7 +66277,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66306,7 +66303,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2469" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66332,7 +66329,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2470" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66358,7 +66355,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2471" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66384,7 +66381,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2472" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66410,7 +66407,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2473" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66436,7 +66433,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2474" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66462,7 +66459,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2475" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66488,7 +66485,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2476" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66514,7 +66511,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2477" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66540,7 +66537,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66566,7 +66563,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2479" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66592,7 +66589,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2480" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66618,7 +66615,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66644,7 +66641,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G2482" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66670,7 +66667,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2483" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66696,7 +66693,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2484" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66722,7 +66719,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2485" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66748,7 +66745,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2486" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66774,7 +66771,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2487" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66800,7 +66797,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2488" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66826,7 +66823,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2489" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66852,7 +66849,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2490" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66878,7 +66875,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2491" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66904,7 +66901,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2492" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66930,7 +66927,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2493" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66956,7 +66953,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2494" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66982,7 +66979,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2495" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67008,7 +67005,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2496" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67034,7 +67031,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2497" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67060,7 +67057,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2498" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67086,7 +67083,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2499" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67112,7 +67109,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2500" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67120,7 +67117,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.5500578704</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>2400</v>
@@ -67138,9 +67135,35 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2501" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.5104050926</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>578</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4707692861557</t>
+    <t xml:space="preserve">1.47076916694641</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">1.48684322834015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424712657928</t>
+    <t xml:space="preserve">1.44424724578857</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236236572266</t>
+    <t xml:space="preserve">1.38236248493195</t>
   </si>
   <si>
     <t xml:space="preserve">1.37593281269073</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744774341583</t>
+    <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628842353821</t>
+    <t xml:space="preserve">1.36628818511963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290271282196</t>
+    <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
     <t xml:space="preserve">1.3815586566925</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780323505402</t>
+    <t xml:space="preserve">1.34780335426331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726264953613</t>
+    <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
     <t xml:space="preserve">1.31002938747406</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">1.35021424293518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128131389618</t>
+    <t xml:space="preserve">1.3212810754776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557696342468</t>
+    <t xml:space="preserve">1.38557708263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273231506348</t>
+    <t xml:space="preserve">1.46273219585419</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
@@ -116,37 +116,37 @@
     <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889874458313</t>
+    <t xml:space="preserve">1.49889862537384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47237634658813</t>
+    <t xml:space="preserve">1.47237658500671</t>
   </si>
   <si>
     <t xml:space="preserve">1.49488008022308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274641513824</t>
+    <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543500423431</t>
+    <t xml:space="preserve">1.61543476581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169404029846</t>
+    <t xml:space="preserve">1.67169392108917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490875720978</t>
+    <t xml:space="preserve">1.67490887641907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64597570896149</t>
+    <t xml:space="preserve">1.64597547054291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113911628723</t>
+    <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702796459198</t>
+    <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095402240753</t>
+    <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
     <t xml:space="preserve">1.45630264282227</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4120991230011</t>
+    <t xml:space="preserve">1.41209900379181</t>
   </si>
   <si>
     <t xml:space="preserve">1.45601892471313</t>
@@ -164,49 +164,49 @@
     <t xml:space="preserve">1.43426239490509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832185745239</t>
+    <t xml:space="preserve">1.40832161903381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091523647308</t>
+    <t xml:space="preserve">1.43091511726379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840480804443</t>
+    <t xml:space="preserve">1.42840468883514</t>
   </si>
   <si>
     <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497469902039</t>
+    <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
     <t xml:space="preserve">1.36313486099243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560369491577</t>
+    <t xml:space="preserve">1.35560393333435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37233984470367</t>
+    <t xml:space="preserve">1.37233972549438</t>
   </si>
   <si>
     <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288589000702</t>
+    <t xml:space="preserve">1.30288600921631</t>
   </si>
   <si>
     <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3221321105957</t>
+    <t xml:space="preserve">1.32213199138641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439344882965</t>
+    <t xml:space="preserve">1.26439356803894</t>
   </si>
   <si>
     <t xml:space="preserve">1.29702830314636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539619922638</t>
+    <t xml:space="preserve">1.30539643764496</t>
   </si>
   <si>
     <t xml:space="preserve">1.36397182941437</t>
@@ -215,40 +215,40 @@
     <t xml:space="preserve">1.41250574588776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38070774078369</t>
+    <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
     <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2719247341156</t>
+    <t xml:space="preserve">1.27192449569702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267839431763</t>
+    <t xml:space="preserve">1.25267827510834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506427764893</t>
+    <t xml:space="preserve">1.22506415843964</t>
   </si>
   <si>
     <t xml:space="preserve">1.20498132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916533470154</t>
+    <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841131687164</t>
+    <t xml:space="preserve">1.22841155529022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845303058624</t>
+    <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008513450623</t>
+    <t xml:space="preserve">1.23008501529694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824553489685</t>
+    <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14473223686218</t>
+    <t xml:space="preserve">1.14473211765289</t>
   </si>
   <si>
     <t xml:space="preserve">1.22171711921692</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">1.14222180843353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150950431824</t>
+    <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
     <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293399333954</t>
+    <t xml:space="preserve">1.11293411254883</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850101470947</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0392963886261</t>
+    <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
     <t xml:space="preserve">1.05435860157013</t>
@@ -290,58 +290,58 @@
     <t xml:space="preserve">1.08364629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06440007686615</t>
+    <t xml:space="preserve">1.06439995765686</t>
   </si>
   <si>
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03762269020081</t>
+    <t xml:space="preserve">1.0376228094101</t>
   </si>
   <si>
     <t xml:space="preserve">1.00833511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067976474762</t>
+    <t xml:space="preserve">0.984067916870117</t>
   </si>
   <si>
     <t xml:space="preserve">0.999966979026794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251912117004</t>
+    <t xml:space="preserve">1.01251888275146</t>
   </si>
   <si>
     <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127379417419</t>
+    <t xml:space="preserve">0.958127439022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842433929443</t>
+    <t xml:space="preserve">0.969842553138733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738626480103</t>
+    <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673782348633</t>
+    <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
     <t xml:space="preserve">0.866080284118652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269911766052</t>
+    <t xml:space="preserve">0.952269971370697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103831768036</t>
+    <t xml:space="preserve">0.912103772163391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899552047252655</t>
+    <t xml:space="preserve">0.899551928043365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204829216003</t>
+    <t xml:space="preserve">0.896204710006714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937930583954</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
     <t xml:space="preserve">0.908756613731384</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">0.950596272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471787452698</t>
+    <t xml:space="preserve">0.920471847057343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332065105438</t>
+    <t xml:space="preserve">0.967332124710083</t>
   </si>
   <si>
     <t xml:space="preserve">0.962311387062073</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">1.05519533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599023342133</t>
+    <t xml:space="preserve">0.991599202156067</t>
   </si>
   <si>
     <t xml:space="preserve">0.989088654518127</t>
@@ -374,46 +374,46 @@
     <t xml:space="preserve">1.0016405582428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783090591431</t>
+    <t xml:space="preserve">0.995783150196075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762412548065</t>
+    <t xml:space="preserve">0.990762293338776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207639217377</t>
+    <t xml:space="preserve">0.937207520008087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394456863403</t>
+    <t xml:space="preserve">0.982394397258759</t>
   </si>
   <si>
     <t xml:space="preserve">0.94139152765274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251924514771</t>
+    <t xml:space="preserve">0.988252103328705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352683544159</t>
+    <t xml:space="preserve">0.972352981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96816885471344</t>
+    <t xml:space="preserve">0.968168914318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9757000207901</t>
+    <t xml:space="preserve">0.97570013999939</t>
   </si>
   <si>
     <t xml:space="preserve">0.983231127262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415194511414</t>
+    <t xml:space="preserve">0.987415134906769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005644321442</t>
+    <t xml:space="preserve">0.969005763530731</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943371772766</t>
+    <t xml:space="preserve">0.953943490982056</t>
   </si>
   <si>
     <t xml:space="preserve">1.05854260921478</t>
@@ -434,67 +434,67 @@
     <t xml:space="preserve">1.13636422157288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14807939529419</t>
+    <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577658176422</t>
+    <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661331176758</t>
+    <t xml:space="preserve">1.19661319255829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602567195892</t>
+    <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
     <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2133492231369</t>
+    <t xml:space="preserve">1.21334910392761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753311157227</t>
+    <t xml:space="preserve">1.21753323078156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644717216492</t>
+    <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15310001373291</t>
+    <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242930412292</t>
+    <t xml:space="preserve">1.19242918491364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493985176086</t>
+    <t xml:space="preserve">1.19493961334229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1547737121582</t>
+    <t xml:space="preserve">1.15477383136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14640557765961</t>
+    <t xml:space="preserve">1.1464056968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19159269332886</t>
+    <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314160823822</t>
+    <t xml:space="preserve">1.16314148902893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2376161813736</t>
+    <t xml:space="preserve">1.23761606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518870353699</t>
+    <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23594272136688</t>
+    <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
     <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13385391235352</t>
+    <t xml:space="preserve">1.13385379314423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803780078888</t>
+    <t xml:space="preserve">1.13803791999817</t>
   </si>
   <si>
     <t xml:space="preserve">1.12799644470215</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653024196625</t>
+    <t xml:space="preserve">1.17653036117554</t>
   </si>
   <si>
     <t xml:space="preserve">1.40581142902374</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">1.39576983451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911711215973</t>
+    <t xml:space="preserve">1.39911699295044</t>
   </si>
   <si>
     <t xml:space="preserve">1.39744341373444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46020293235779</t>
+    <t xml:space="preserve">1.4602028131485</t>
   </si>
   <si>
     <t xml:space="preserve">1.49534821510315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685577392578</t>
+    <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865389823914</t>
+    <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48949062824249</t>
+    <t xml:space="preserve">1.4894905090332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275483608246</t>
+    <t xml:space="preserve">1.47275495529175</t>
   </si>
   <si>
     <t xml:space="preserve">1.53551423549652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57317006587982</t>
+    <t xml:space="preserve">1.57316994667053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58572173118591</t>
+    <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
     <t xml:space="preserve">1.63174545764923</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438031196594</t>
+    <t xml:space="preserve">1.66438043117523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550748825073</t>
+    <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726425647736</t>
+    <t xml:space="preserve">1.75726401805878</t>
   </si>
   <si>
     <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78236830234528</t>
+    <t xml:space="preserve">1.7823680639267</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
@@ -572,37 +572,37 @@
     <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67358493804932</t>
+    <t xml:space="preserve">1.6735851764679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003040313721</t>
+    <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697357177734</t>
+    <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6166832447052</t>
+    <t xml:space="preserve">1.61668312549591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664165019989</t>
+    <t xml:space="preserve">1.6066415309906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195295333862</t>
+    <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362665176392</t>
+    <t xml:space="preserve">1.68362653255463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7154244184494</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718130588531</t>
+    <t xml:space="preserve">1.73718118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224363803864</t>
+    <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052846431732</t>
+    <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
     <t xml:space="preserve">1.723792552948</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220192432404</t>
+    <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74906086921692</t>
+    <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337341785431</t>
+    <t xml:space="preserve">1.84337306022644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8005039691925</t>
+    <t xml:space="preserve">1.80050384998322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335642814636</t>
+    <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193019866943</t>
+    <t xml:space="preserve">1.79193007946014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548327922821</t>
+    <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
     <t xml:space="preserve">2.37323570251465</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421946525574</t>
+    <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
     <t xml:space="preserve">2.82936358451843</t>
@@ -656,40 +656,40 @@
     <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067195892334</t>
+    <t xml:space="preserve">2.40067172050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.58929634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78649425506592</t>
+    <t xml:space="preserve">2.78649401664734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503428459167</t>
+    <t xml:space="preserve">2.67503476142883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012850761414</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
     <t xml:space="preserve">2.46240377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097754478455</t>
+    <t xml:space="preserve">2.47097730636597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354128837585</t>
+    <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953468322754</t>
+    <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
@@ -698,55 +698,55 @@
     <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641061782837</t>
+    <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43496751785278</t>
+    <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45554447174072</t>
+    <t xml:space="preserve">2.4555447101593</t>
   </si>
   <si>
     <t xml:space="preserve">2.4572594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613877296448</t>
+    <t xml:space="preserve">2.53613829612732</t>
   </si>
   <si>
     <t xml:space="preserve">2.45897436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440719604492</t>
+    <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56186008453369</t>
+    <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781973838806</t>
+    <t xml:space="preserve">2.41781997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3818097114563</t>
+    <t xml:space="preserve">2.38180994987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639350891113</t>
+    <t xml:space="preserve">2.42639327049255</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208131790161</t>
+    <t xml:space="preserve">2.33208155632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836342811584</t>
+    <t xml:space="preserve">2.31836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2806384563446</t>
+    <t xml:space="preserve">2.28063869476318</t>
   </si>
   <si>
     <t xml:space="preserve">2.32865190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31321907043457</t>
+    <t xml:space="preserve">2.31321883201599</t>
   </si>
   <si>
     <t xml:space="preserve">2.26692032814026</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800770759583</t>
+    <t xml:space="preserve">2.06800723075867</t>
   </si>
   <si>
     <t xml:space="preserve">2.05771899223328</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1280243396759</t>
+    <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515524864197</t>
+    <t xml:space="preserve">2.08515501022339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629300117493</t>
+    <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
     <t xml:space="preserve">2.08344054222107</t>
@@ -785,28 +785,28 @@
     <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799059867859</t>
+    <t xml:space="preserve">2.00799036026001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05085968971252</t>
+    <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342343330383</t>
+    <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20690321922302</t>
+    <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
     <t xml:space="preserve">2.17603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172559738159</t>
+    <t xml:space="preserve">2.08172535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401773452759</t>
+    <t xml:space="preserve">2.10401725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15889024734497</t>
+    <t xml:space="preserve">2.15889000892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917872428894</t>
+    <t xml:space="preserve">2.16917896270752</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491714477539</t>
+    <t xml:space="preserve">2.25491690635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.2823531627655</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">2.23776936531067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233653068542</t>
+    <t xml:space="preserve">2.22233629226685</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089366912842</t>
@@ -860,37 +860,37 @@
     <t xml:space="preserve">2.25320219993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27034950256348</t>
+    <t xml:space="preserve">2.27034997940063</t>
   </si>
   <si>
     <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175933837891</t>
+    <t xml:space="preserve">2.20175957679749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2086181640625</t>
+    <t xml:space="preserve">2.20861840248108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28749775886536</t>
+    <t xml:space="preserve">2.2874972820282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20347380638123</t>
+    <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462842941284</t>
+    <t xml:space="preserve">2.24462866783142</t>
   </si>
   <si>
     <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384687423706</t>
+    <t xml:space="preserve">2.51384663581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.50355815887451</t>
@@ -899,16 +899,16 @@
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326944351196</t>
+    <t xml:space="preserve">2.49326920509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47269248962402</t>
+    <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32007813453674</t>
+    <t xml:space="preserve">2.32007789611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32179284095764</t>
+    <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
     <t xml:space="preserve">2.36809158325195</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">2.33379602432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439008712769</t>
+    <t xml:space="preserve">2.41439032554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922885894775</t>
+    <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.3578028678894</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">2.40410137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39038324356079</t>
+    <t xml:space="preserve">2.39038348197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33551073074341</t>
+    <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
     <t xml:space="preserve">2.3063600063324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38866853713989</t>
+    <t xml:space="preserve">2.38866877555847</t>
   </si>
   <si>
     <t xml:space="preserve">2.31493377685547</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632650375366</t>
+    <t xml:space="preserve">2.18632626533508</t>
   </si>
   <si>
     <t xml:space="preserve">2.10058808326721</t>
@@ -962,37 +962,37 @@
     <t xml:space="preserve">2.09201455116272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04057145118713</t>
+    <t xml:space="preserve">2.04057121276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914474487305</t>
+    <t xml:space="preserve">2.04914498329163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90338981151581</t>
+    <t xml:space="preserve">1.90339004993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.9805543422699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198069095612</t>
+    <t xml:space="preserve">1.97198057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053771018982</t>
+    <t xml:space="preserve">1.92053747177124</t>
   </si>
   <si>
     <t xml:space="preserve">1.98912823200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196382045746</t>
+    <t xml:space="preserve">1.91196405887604</t>
   </si>
   <si>
     <t xml:space="preserve">1.9291113615036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624250888824</t>
   </si>
   <si>
     <t xml:space="preserve">1.89481616020203</t>
@@ -1001,25 +1001,25 @@
     <t xml:space="preserve">1.86909461021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194706916809</t>
+    <t xml:space="preserve">1.85194718837738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625914096832</t>
+    <t xml:space="preserve">1.94625926017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340668201447</t>
+    <t xml:space="preserve">1.96340692043304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879186630249</t>
+    <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249334335327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236502170563</t>
+    <t xml:space="preserve">1.97236514091492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100251674652</t>
+    <t xml:space="preserve">1.91100263595581</t>
   </si>
   <si>
     <t xml:space="preserve">1.85840594768524</t>
@@ -1034,34 +1034,34 @@
     <t xml:space="preserve">1.99866318702698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606673717499</t>
+    <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853474617004</t>
+    <t xml:space="preserve">1.92853462696075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717247962952</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223670005798</t>
+    <t xml:space="preserve">1.9022364616394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593829631805</t>
+    <t xml:space="preserve">1.87593853473663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334184646606</t>
+    <t xml:space="preserve">1.82334196567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976881027222</t>
+    <t xml:space="preserve">1.91976869106293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8496401309967</t>
+    <t xml:space="preserve">1.84963989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730080127716</t>
+    <t xml:space="preserve">1.93730068206787</t>
   </si>
   <si>
     <t xml:space="preserve">1.98989713191986</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7882776260376</t>
+    <t xml:space="preserve">1.78827774524689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77074551582336</t>
+    <t xml:space="preserve">1.77074539661407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704356193542</t>
+    <t xml:space="preserve">1.79704368114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733949184418</t>
+    <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
     <t xml:space="preserve">1.59542417526245</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">1.69185090065002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66116964817047</t>
+    <t xml:space="preserve">1.66116976737976</t>
   </si>
   <si>
     <t xml:space="preserve">1.57789206504822</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104132652283</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048839569092</t>
+    <t xml:space="preserve">1.63048851490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295628547668</t>
+    <t xml:space="preserve">1.61295640468597</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">1.63925457000732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58665800094604</t>
+    <t xml:space="preserve">1.58665812015533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597698688507</t>
+    <t xml:space="preserve">1.55597674846649</t>
   </si>
   <si>
     <t xml:space="preserve">1.42010271549225</t>
@@ -1175,40 +1175,40 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065576553345</t>
+    <t xml:space="preserve">1.38065552711487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41571974754333</t>
+    <t xml:space="preserve">1.41571986675262</t>
   </si>
   <si>
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325197696686</t>
+    <t xml:space="preserve">1.43325185775757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38942158222198</t>
+    <t xml:space="preserve">1.38942170143127</t>
   </si>
   <si>
     <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874032974243</t>
+    <t xml:space="preserve">1.35874044895172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763494491577</t>
+    <t xml:space="preserve">1.43763506412506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44640111923218</t>
+    <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201803207397</t>
+    <t xml:space="preserve">1.44201791286469</t>
   </si>
   <si>
     <t xml:space="preserve">1.4507839679718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39380466938019</t>
+    <t xml:space="preserve">1.3938045501709</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133677959442</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406167030334</t>
+    <t xml:space="preserve">1.53406178951263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214647293091</t>
+    <t xml:space="preserve">1.5121465921402</t>
   </si>
   <si>
     <t xml:space="preserve">1.52967870235443</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">1.55159378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035983562469</t>
+    <t xml:space="preserve">1.56035995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091252803802</t>
+    <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
     <t xml:space="preserve">1.48584842681885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5165296792984</t>
+    <t xml:space="preserve">1.51652944087982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5691260099411</t>
+    <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776362419128</t>
+    <t xml:space="preserve">1.50776350498199</t>
   </si>
   <si>
     <t xml:space="preserve">1.52529561519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899744987488</t>
+    <t xml:space="preserve">1.49899733066559</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
@@ -1274,22 +1274,22 @@
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46114611625671</t>
+    <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624334812164</t>
+    <t xml:space="preserve">1.50624322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016572952271</t>
+    <t xml:space="preserve">1.47016561031342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310748577118</t>
+    <t xml:space="preserve">1.44310736656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604912281036</t>
+    <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
     <t xml:space="preserve">1.39801025390625</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35291314125061</t>
+    <t xml:space="preserve">1.3529132604599</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1322,37 +1322,37 @@
     <t xml:space="preserve">1.31683564186096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271903514862</t>
+    <t xml:space="preserve">1.26271891593933</t>
   </si>
   <si>
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056367874146</t>
+    <t xml:space="preserve">1.19056355953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
     <t xml:space="preserve">1.22664129734039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762180328369</t>
+    <t xml:space="preserve">1.21762192249298</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193263530731</t>
+    <t xml:space="preserve">1.36193251609802</t>
   </si>
   <si>
     <t xml:space="preserve">1.37997150421143</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566067218781</t>
+    <t xml:space="preserve">1.23566079139709</t>
   </si>
   <si>
     <t xml:space="preserve">1.45212686061859</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153468608856</t>
+    <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251519203186</t>
+    <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
     <t xml:space="preserve">1.59643757343292</t>
@@ -1397,13 +1397,10 @@
     <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369004249573</t>
+    <t xml:space="preserve">1.71369016170502</t>
   </si>
   <si>
     <t xml:space="preserve">1.62349581718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56035995483398</t>
   </si>
   <si>
     <t xml:space="preserve">1.55134057998657</t>
@@ -1418,16 +1415,16 @@
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840832233429</t>
+    <t xml:space="preserve">1.118408203125</t>
   </si>
   <si>
     <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15448582172394</t>
+    <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1274276971817</t>
+    <t xml:space="preserve">1.12742757797241</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
@@ -1436,7 +1433,7 @@
     <t xml:space="preserve">1.25369966030121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1445,22 +1442,22 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09134995937347</t>
+    <t xml:space="preserve">1.09135007858276</t>
   </si>
   <si>
     <t xml:space="preserve">1.08233058452606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04625284671783</t>
+    <t xml:space="preserve">1.04625272750854</t>
   </si>
   <si>
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331120967865</t>
+    <t xml:space="preserve">1.07331132888794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527234077454</t>
+    <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1469,19 +1466,19 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0101752281189</t>
+    <t xml:space="preserve">1.01017510890961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097490310669</t>
+    <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00115573406219</t>
+    <t xml:space="preserve">1.00115585327148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078055858612</t>
+    <t xml:space="preserve">0.965078175067902</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
@@ -1493,22 +1490,22 @@
     <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947039127349854</t>
+    <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
     <t xml:space="preserve">0.897432446479797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91096156835556</t>
+    <t xml:space="preserve">0.910961508750916</t>
   </si>
   <si>
     <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0191947221756</t>
+    <t xml:space="preserve">1.01919460296631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95605856180191</t>
+    <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
     <t xml:space="preserve">1.20860242843628</t>
@@ -1517,7 +1514,7 @@
     <t xml:space="preserve">1.47918510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098133087158</t>
+    <t xml:space="preserve">1.25098145008087</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1547,7 +1544,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12124991416931</t>
+    <t xml:space="preserve">1.1212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1565,22 +1562,25 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051640987396</t>
+    <t xml:space="preserve">1.13051652908325</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19538223743439</t>
+    <t xml:space="preserve">1.1953821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198353767395</t>
+    <t xml:space="preserve">1.11198341846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -29068,7 +29068,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1037" t="s">
-        <v>463</v>
+        <v>407</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29120,7 +29120,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1039" t="s">
-        <v>463</v>
+        <v>407</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29224,7 +29224,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29250,7 +29250,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1044" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29302,7 +29302,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1046" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29432,7 +29432,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1051" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29692,7 +29692,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1061" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29718,7 +29718,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1062" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29744,7 +29744,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29770,7 +29770,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29796,7 +29796,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1065" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29822,7 +29822,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29848,7 +29848,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29874,7 +29874,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1068" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29900,7 +29900,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1069" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29926,7 +29926,7 @@
         <v>1.25</v>
       </c>
       <c r="G1070" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29952,7 +29952,7 @@
         <v>1.25</v>
       </c>
       <c r="G1071" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29978,7 +29978,7 @@
         <v>1.25</v>
       </c>
       <c r="G1072" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30004,7 +30004,7 @@
         <v>1.25</v>
       </c>
       <c r="G1073" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30186,7 +30186,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1080" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30212,7 +30212,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1081" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30238,7 +30238,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30290,7 +30290,7 @@
         <v>1.25</v>
       </c>
       <c r="G1084" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30394,7 +30394,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1088" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30446,7 +30446,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30498,7 +30498,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1092" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30524,7 +30524,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30550,7 +30550,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1094" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30576,7 +30576,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30602,7 +30602,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30628,7 +30628,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30654,7 +30654,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1098" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30680,7 +30680,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1099" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30706,7 +30706,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1100" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30732,7 +30732,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1101" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30758,7 +30758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30784,7 +30784,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1103" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30810,7 +30810,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1104" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30836,7 +30836,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1105" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30862,7 +30862,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30888,7 +30888,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1107" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30914,7 +30914,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30940,7 +30940,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30966,7 +30966,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1110" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30992,7 +30992,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1111" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31018,7 +31018,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1112" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31044,7 +31044,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1113" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31070,7 +31070,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1114" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31096,7 +31096,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1115" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31122,7 +31122,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31148,7 +31148,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1117" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31174,7 +31174,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31200,7 +31200,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1119" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31226,7 +31226,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1120" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31252,7 +31252,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1121" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31278,7 +31278,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1122" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31304,7 +31304,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31330,7 +31330,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31356,7 +31356,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1125" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31382,7 +31382,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1126" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31408,7 +31408,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31434,7 +31434,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1128" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31460,7 +31460,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1129" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31486,7 +31486,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1130" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31512,7 +31512,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1131" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31538,7 +31538,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31564,7 +31564,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1133" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31590,7 +31590,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1134" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31616,7 +31616,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31642,7 +31642,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1136" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31668,7 +31668,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1137" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31694,7 +31694,7 @@
         <v>1.25</v>
       </c>
       <c r="G1138" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31720,7 +31720,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1139" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31746,7 +31746,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1140" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31772,7 +31772,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1141" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31798,7 +31798,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1142" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31824,7 +31824,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1143" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31850,7 +31850,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31876,7 +31876,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1145" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31902,7 +31902,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31928,7 +31928,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1147" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31954,7 +31954,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1148" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31980,7 +31980,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1149" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32006,7 +32006,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1150" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32032,7 +32032,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1151" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32058,7 +32058,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1152" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32084,7 +32084,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1153" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32110,7 +32110,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1154" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32136,7 +32136,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32162,7 +32162,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1156" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32188,7 +32188,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1157" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32214,7 +32214,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1158" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32240,7 +32240,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1159" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32266,7 +32266,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1160" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32292,7 +32292,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1161" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32318,7 +32318,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1162" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32344,7 +32344,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1163" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32370,7 +32370,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1164" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32396,7 +32396,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1165" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32422,7 +32422,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1166" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32448,7 +32448,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1167" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32474,7 +32474,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1168" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32500,7 +32500,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32526,7 +32526,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1170" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32552,7 +32552,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32578,7 +32578,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1172" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32604,7 +32604,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1173" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32630,7 +32630,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1174" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32656,7 +32656,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1175" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32682,7 +32682,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1176" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32708,7 +32708,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1177" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32734,7 +32734,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32760,7 +32760,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1179" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32786,7 +32786,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1180" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32812,7 +32812,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32838,7 +32838,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1182" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32864,7 +32864,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1183" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32890,7 +32890,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1184" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32916,7 +32916,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1185" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32942,7 +32942,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1186" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32968,7 +32968,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1187" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32994,7 +32994,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1188" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33020,7 +33020,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1189" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33046,7 +33046,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1190" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33072,7 +33072,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33098,7 +33098,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33124,7 +33124,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33150,7 +33150,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1194" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33176,7 +33176,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1195" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33202,7 +33202,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1196" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33228,7 +33228,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33254,7 +33254,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1198" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33280,7 +33280,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33306,7 +33306,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33332,7 +33332,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1201" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33358,7 +33358,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1202" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33384,7 +33384,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33410,7 +33410,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1204" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33436,7 +33436,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33462,7 +33462,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33488,7 +33488,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33514,7 +33514,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1208" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33540,7 +33540,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33566,7 +33566,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33592,7 +33592,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33618,7 +33618,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1212" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33644,7 +33644,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1213" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33670,7 +33670,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1214" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33696,7 +33696,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33722,7 +33722,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33748,7 +33748,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33774,7 +33774,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1218" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33800,7 +33800,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1219" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33826,7 +33826,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1220" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33852,7 +33852,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1221" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33878,7 +33878,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1222" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33904,7 +33904,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1223" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33930,7 +33930,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1224" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33956,7 +33956,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1225" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33982,7 +33982,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1226" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34008,7 +34008,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1227" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34034,7 +34034,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1228" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34060,7 +34060,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1229" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34086,7 +34086,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1230" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34112,7 +34112,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34138,7 +34138,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34164,7 +34164,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1233" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34190,7 +34190,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1234" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34216,7 +34216,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34242,7 +34242,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34268,7 +34268,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1237" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34294,7 +34294,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1238" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34320,7 +34320,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1239" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34346,7 +34346,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1240" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34372,7 +34372,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34398,7 +34398,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1242" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34424,7 +34424,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1243" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34450,7 +34450,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1244" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34476,7 +34476,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34502,7 +34502,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1246" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34528,7 +34528,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1247" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34554,7 +34554,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34580,7 +34580,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1249" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34606,7 +34606,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1250" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34632,7 +34632,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1251" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34658,7 +34658,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34684,7 +34684,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1253" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34710,7 +34710,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1254" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34736,7 +34736,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1255" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34762,7 +34762,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1256" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34788,7 +34788,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1257" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34814,7 +34814,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1258" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34840,7 +34840,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1259" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34866,7 +34866,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1260" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34892,7 +34892,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1261" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34918,7 +34918,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1262" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34944,7 +34944,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34970,7 +34970,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1264" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34996,7 +34996,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1265" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35022,7 +35022,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1266" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35048,7 +35048,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35074,7 +35074,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1268" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35100,7 +35100,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1269" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35126,7 +35126,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1270" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35152,7 +35152,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1271" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35178,7 +35178,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1272" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35204,7 +35204,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1273" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35230,7 +35230,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1274" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35256,7 +35256,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1275" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35282,7 +35282,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1276" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35308,7 +35308,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1277" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35334,7 +35334,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1278" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35360,7 +35360,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1279" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35386,7 +35386,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1280" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35412,7 +35412,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1281" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35438,7 +35438,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1282" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35464,7 +35464,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1283" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35490,7 +35490,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1284" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35516,7 +35516,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1285" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35542,7 +35542,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1286" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35568,7 +35568,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35594,7 +35594,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35620,7 +35620,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1289" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35646,7 +35646,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1290" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35672,7 +35672,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1291" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35698,7 +35698,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1292" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35724,7 +35724,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1293" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35750,7 +35750,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1294" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35776,7 +35776,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1295" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35802,7 +35802,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1296" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35828,7 +35828,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1297" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35854,7 +35854,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35880,7 +35880,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35906,7 +35906,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1300" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35932,7 +35932,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1301" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35958,7 +35958,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1302" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35984,7 +35984,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1303" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36010,7 +36010,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1304" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36036,7 +36036,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1305" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36062,7 +36062,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1306" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36088,7 +36088,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1307" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36114,7 +36114,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1308" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36140,7 +36140,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1309" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36166,7 +36166,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1310" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36192,7 +36192,7 @@
         <v>1.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36218,7 +36218,7 @@
         <v>1.25</v>
       </c>
       <c r="G1312" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36244,7 +36244,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1313" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36270,7 +36270,7 @@
         <v>1.25</v>
       </c>
       <c r="G1314" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36296,7 +36296,7 @@
         <v>1.25</v>
       </c>
       <c r="G1315" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36322,7 +36322,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1316" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36348,7 +36348,7 @@
         <v>1.25</v>
       </c>
       <c r="G1317" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36374,7 +36374,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36426,7 +36426,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36452,7 +36452,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1321" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36478,7 +36478,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1322" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36504,7 +36504,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1323" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36530,7 +36530,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1324" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36556,7 +36556,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1325" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36582,7 +36582,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36608,7 +36608,7 @@
         <v>1.25</v>
       </c>
       <c r="G1327" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36634,7 +36634,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1328" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36660,7 +36660,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1329" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36686,7 +36686,7 @@
         <v>1.25</v>
       </c>
       <c r="G1330" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36712,7 +36712,7 @@
         <v>1.25</v>
       </c>
       <c r="G1331" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36738,7 +36738,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36764,7 +36764,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36842,7 +36842,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1336" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37050,7 +37050,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1344" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37102,7 +37102,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1346" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37258,7 +37258,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1352" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37284,7 +37284,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1353" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37362,7 +37362,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1356" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37388,7 +37388,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1357" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37440,7 +37440,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1359" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37466,7 +37466,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1360" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37518,7 +37518,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37544,7 +37544,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37570,7 +37570,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38194,7 +38194,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1388" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38220,7 +38220,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1389" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38246,7 +38246,7 @@
         <v>1.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38272,7 +38272,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1391" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38298,7 +38298,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1392" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38350,7 +38350,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1394" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38376,7 +38376,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1395" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38402,7 +38402,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1396" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38428,7 +38428,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1397" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38558,7 +38558,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38584,7 +38584,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38610,7 +38610,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38636,7 +38636,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1405" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38662,7 +38662,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38688,7 +38688,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1407" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38714,7 +38714,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1408" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38740,7 +38740,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1409" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38766,7 +38766,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1410" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38792,7 +38792,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1411" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38818,7 +38818,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1412" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38844,7 +38844,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1413" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38870,7 +38870,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1414" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38896,7 +38896,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1415" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38922,7 +38922,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1416" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38948,7 +38948,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1417" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38974,7 +38974,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1418" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39000,7 +39000,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1419" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39052,7 +39052,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1421" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39078,7 +39078,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1422" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39104,7 +39104,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1423" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39130,7 +39130,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1424" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39156,7 +39156,7 @@
         <v>1.25</v>
       </c>
       <c r="G1425" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39182,7 +39182,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39208,7 +39208,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1427" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39234,7 +39234,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1428" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39260,7 +39260,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1429" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39286,7 +39286,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1430" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39312,7 +39312,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39338,7 +39338,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1432" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39364,7 +39364,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1433" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39468,7 +39468,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39494,7 +39494,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1438" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39520,7 +39520,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1439" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39546,7 +39546,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1440" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39572,7 +39572,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1441" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39598,7 +39598,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1442" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39624,7 +39624,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1443" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39650,7 +39650,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1444" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39676,7 +39676,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1445" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39702,7 +39702,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1446" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39728,7 +39728,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1447" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39754,7 +39754,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1448" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39780,7 +39780,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1449" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39806,7 +39806,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1450" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39832,7 +39832,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1451" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39858,7 +39858,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1452" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39884,7 +39884,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1453" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39910,7 +39910,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1454" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39936,7 +39936,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1455" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39962,7 +39962,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1456" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39988,7 +39988,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1457" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40170,7 +40170,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1464" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40248,7 +40248,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1467" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40274,7 +40274,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1468" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40534,7 +40534,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41210,7 +41210,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1504" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41522,7 +41522,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1516" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41600,7 +41600,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1519" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41626,7 +41626,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41652,7 +41652,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1521" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41678,7 +41678,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1522" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41782,7 +41782,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1526" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41808,7 +41808,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1527" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41912,7 +41912,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1531" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41938,7 +41938,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1532" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42120,7 +42120,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1539" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42172,7 +42172,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1541" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42276,7 +42276,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1545" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42328,7 +42328,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1547" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42354,7 +42354,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1548" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42380,7 +42380,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1549" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42406,7 +42406,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1550" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42432,7 +42432,7 @@
         <v>1.25</v>
       </c>
       <c r="G1551" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42458,7 +42458,7 @@
         <v>1.25</v>
       </c>
       <c r="G1552" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42484,7 +42484,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1553" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42510,7 +42510,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1554" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42536,7 +42536,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1555" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42562,7 +42562,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1556" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42588,7 +42588,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42614,7 +42614,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1558" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42640,7 +42640,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42666,7 +42666,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1560" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42692,7 +42692,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42718,7 +42718,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1562" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42796,7 +42796,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42822,7 +42822,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1566" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42848,7 +42848,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1567" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42874,7 +42874,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42900,7 +42900,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1569" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42926,7 +42926,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1570" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42952,7 +42952,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1571" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42978,7 +42978,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1572" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43004,7 +43004,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1573" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43030,7 +43030,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1574" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43056,7 +43056,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1575" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43082,7 +43082,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1576" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43108,7 +43108,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1577" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43134,7 +43134,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1578" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43160,7 +43160,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1579" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43186,7 +43186,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1580" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43212,7 +43212,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1581" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43238,7 +43238,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1582" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43264,7 +43264,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1583" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43290,7 +43290,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1584" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43316,7 +43316,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1585" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43342,7 +43342,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1586" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43368,7 +43368,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43524,7 +43524,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1593" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43550,7 +43550,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1594" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43602,7 +43602,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1596" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43628,7 +43628,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43680,7 +43680,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1599" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43784,7 +43784,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43810,7 +43810,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1604" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43836,7 +43836,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43862,7 +43862,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1606" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43888,7 +43888,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1607" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43914,7 +43914,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43940,7 +43940,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1609" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44018,7 +44018,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1612" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44044,7 +44044,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1613" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44070,7 +44070,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44096,7 +44096,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1615" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44122,7 +44122,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1616" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44174,7 +44174,7 @@
         <v>1.25</v>
       </c>
       <c r="G1618" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44200,7 +44200,7 @@
         <v>1.25</v>
       </c>
       <c r="G1619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44226,7 +44226,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1620" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44252,7 +44252,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44304,7 +44304,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44434,7 +44434,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1628" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44486,7 +44486,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1630" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44616,7 +44616,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1635" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44642,7 +44642,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44668,7 +44668,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1637" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44694,7 +44694,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44720,7 +44720,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1639" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44746,7 +44746,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1640" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44772,7 +44772,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1641" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44798,7 +44798,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45006,7 +45006,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45058,7 +45058,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1652" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45084,7 +45084,7 @@
         <v>1.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45110,7 +45110,7 @@
         <v>1.25</v>
       </c>
       <c r="G1654" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45136,7 +45136,7 @@
         <v>1.25</v>
       </c>
       <c r="G1655" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45162,7 +45162,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1656" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45188,7 +45188,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1657" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45214,7 +45214,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45240,7 +45240,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45266,7 +45266,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1660" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45292,7 +45292,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1661" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45318,7 +45318,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1662" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45344,7 +45344,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1663" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45370,7 +45370,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45422,7 +45422,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45448,7 +45448,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45474,7 +45474,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45500,7 +45500,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45552,7 +45552,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1671" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45578,7 +45578,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1672" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45630,7 +45630,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1674" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45682,7 +45682,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1676" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45734,7 +45734,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45812,7 +45812,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1681" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45864,7 +45864,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1683" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45890,7 +45890,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1684" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45916,7 +45916,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1685" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45994,7 +45994,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1688" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46150,7 +46150,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1694" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46176,7 +46176,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1695" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46202,7 +46202,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1696" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46228,7 +46228,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46280,7 +46280,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1699" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46332,7 +46332,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46462,7 +46462,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1706" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46514,7 +46514,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1708" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46618,7 +46618,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1712" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46670,7 +46670,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1714" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46696,7 +46696,7 @@
         <v>1.25</v>
       </c>
       <c r="G1715" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46722,7 +46722,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1716" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46748,7 +46748,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46774,7 +46774,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46800,7 +46800,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46826,7 +46826,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46852,7 +46852,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46878,7 +46878,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46904,7 +46904,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46956,7 +46956,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1725" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46982,7 +46982,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1726" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47008,7 +47008,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1727" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47138,7 +47138,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1732" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47190,7 +47190,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1734" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47216,7 +47216,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47398,7 +47398,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1742" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47424,7 +47424,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1743" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47450,7 +47450,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1744" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47476,7 +47476,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1745" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47502,7 +47502,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1746" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47528,7 +47528,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1747" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47554,7 +47554,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1748" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47580,7 +47580,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1749" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47606,7 +47606,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1750" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47632,7 +47632,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1751" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47658,7 +47658,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1752" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47684,7 +47684,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1753" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47710,7 +47710,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1754" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47736,7 +47736,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1755" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47892,7 +47892,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1761" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47944,7 +47944,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47996,7 +47996,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1765" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48022,7 +48022,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1766" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48048,7 +48048,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1767" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48074,7 +48074,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1768" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48100,7 +48100,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1769" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48230,7 +48230,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1774" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48256,7 +48256,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1775" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48386,7 +48386,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1780" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48490,7 +48490,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1784" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48516,7 +48516,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1785" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48542,7 +48542,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1786" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48568,7 +48568,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1787" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48594,7 +48594,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1788" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48620,7 +48620,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1789" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48672,7 +48672,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1791" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48698,7 +48698,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1792" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48932,7 +48932,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1801" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48958,7 +48958,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48984,7 +48984,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1803" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49010,7 +49010,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1804" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49036,7 +49036,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1805" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49062,7 +49062,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49088,7 +49088,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1807" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49114,7 +49114,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1808" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49140,7 +49140,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1809" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49166,7 +49166,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1810" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49192,7 +49192,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1811" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49218,7 +49218,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1812" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49244,7 +49244,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1813" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49322,7 +49322,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49348,7 +49348,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1817" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49374,7 +49374,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1818" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49400,7 +49400,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1819" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49426,7 +49426,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1820" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49452,7 +49452,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1821" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49478,7 +49478,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1822" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49504,7 +49504,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1823" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49530,7 +49530,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1824" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49556,7 +49556,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1825" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49582,7 +49582,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1826" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49608,7 +49608,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49634,7 +49634,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1828" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49660,7 +49660,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1829" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49686,7 +49686,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49712,7 +49712,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49738,7 +49738,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49764,7 +49764,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49790,7 +49790,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1834" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49816,7 +49816,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1835" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49842,7 +49842,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1836" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49868,7 +49868,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1837" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49894,7 +49894,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1838" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49920,7 +49920,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49946,7 +49946,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49972,7 +49972,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49998,7 +49998,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1842" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50024,7 +50024,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1843" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50050,7 +50050,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1844" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50076,7 +50076,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1845" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50102,7 +50102,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1846" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50128,7 +50128,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1847" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50154,7 +50154,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1848" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50180,7 +50180,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1849" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50206,7 +50206,7 @@
         <v>1.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50232,7 +50232,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1851" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50388,7 +50388,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50440,7 +50440,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1859" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50492,7 +50492,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50648,7 +50648,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50674,7 +50674,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50856,7 +50856,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1875" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50882,7 +50882,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1876" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50908,7 +50908,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1877" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50934,7 +50934,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1878" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50960,7 +50960,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1879" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50986,7 +50986,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1880" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51012,7 +51012,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1881" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51038,7 +51038,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1882" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51064,7 +51064,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1883" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51090,7 +51090,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1884" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51116,7 +51116,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1885" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51142,7 +51142,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1886" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51168,7 +51168,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1887" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51194,7 +51194,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1888" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51220,7 +51220,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1889" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51246,7 +51246,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1890" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51272,7 +51272,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1891" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51298,7 +51298,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1892" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51324,7 +51324,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1893" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51350,7 +51350,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1894" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51376,7 +51376,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1895" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51402,7 +51402,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1896" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51428,7 +51428,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1897" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51454,7 +51454,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1898" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51480,7 +51480,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1899" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51506,7 +51506,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1900" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51532,7 +51532,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1901" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51558,7 +51558,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1902" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51584,7 +51584,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1903" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51610,7 +51610,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1904" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51636,7 +51636,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1905" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51662,7 +51662,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1906" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51688,7 +51688,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1907" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51714,7 +51714,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1908" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51740,7 +51740,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1909" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51766,7 +51766,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1910" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51792,7 +51792,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51818,7 +51818,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1912" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51844,7 +51844,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51870,7 +51870,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51896,7 +51896,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1915" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51922,7 +51922,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1916" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51948,7 +51948,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1917" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51974,7 +51974,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52000,7 +52000,7 @@
         <v>1.25</v>
       </c>
       <c r="G1919" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52026,7 +52026,7 @@
         <v>1.25</v>
       </c>
       <c r="G1920" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52052,7 +52052,7 @@
         <v>1.25</v>
       </c>
       <c r="G1921" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52078,7 +52078,7 @@
         <v>1.25</v>
       </c>
       <c r="G1922" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52104,7 +52104,7 @@
         <v>1.25</v>
       </c>
       <c r="G1923" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52130,7 +52130,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1924" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52156,7 +52156,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1925" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52182,7 +52182,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52208,7 +52208,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52234,7 +52234,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52260,7 +52260,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52286,7 +52286,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1930" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52312,7 +52312,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1931" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52338,7 +52338,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1932" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52364,7 +52364,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52390,7 +52390,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52416,7 +52416,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52442,7 +52442,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1936" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52468,7 +52468,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1937" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52494,7 +52494,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1938" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52520,7 +52520,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1939" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52546,7 +52546,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1940" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52572,7 +52572,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1941" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52598,7 +52598,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1942" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52624,7 +52624,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1943" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52650,7 +52650,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1944" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52676,7 +52676,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1945" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52702,7 +52702,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1946" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52728,7 +52728,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1947" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52754,7 +52754,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1948" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52780,7 +52780,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1949" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52806,7 +52806,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1950" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52832,7 +52832,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1951" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52858,7 +52858,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1952" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52884,7 +52884,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1953" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52910,7 +52910,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1954" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52936,7 +52936,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1955" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52962,7 +52962,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1956" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52988,7 +52988,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53014,7 +53014,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1958" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53040,7 +53040,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53066,7 +53066,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53092,7 +53092,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1961" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53118,7 +53118,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1962" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53144,7 +53144,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1963" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53170,7 +53170,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53196,7 +53196,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1965" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53222,7 +53222,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1966" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53248,7 +53248,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1967" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53274,7 +53274,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1968" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53300,7 +53300,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1969" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53326,7 +53326,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1970" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53352,7 +53352,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1971" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53378,7 +53378,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1972" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53404,7 +53404,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1973" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53430,7 +53430,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1974" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53456,7 +53456,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1975" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53482,7 +53482,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1976" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53508,7 +53508,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53534,7 +53534,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53560,7 +53560,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53586,7 +53586,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53612,7 +53612,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53638,7 +53638,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53664,7 +53664,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53690,7 +53690,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1984" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53716,7 +53716,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53742,7 +53742,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53768,7 +53768,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1987" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53794,7 +53794,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1988" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53820,7 +53820,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1989" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53846,7 +53846,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1990" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53872,7 +53872,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53898,7 +53898,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1992" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53924,7 +53924,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53950,7 +53950,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1994" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53976,7 +53976,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1995" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54002,7 +54002,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1996" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54028,7 +54028,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1997" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54054,7 +54054,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54080,7 +54080,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1999" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54106,7 +54106,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54132,7 +54132,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2001" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54158,7 +54158,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2002" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54184,7 +54184,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2003" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54210,7 +54210,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2004" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54236,7 +54236,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2005" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54262,7 +54262,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2006" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54288,7 +54288,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54314,7 +54314,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54340,7 +54340,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2009" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54366,7 +54366,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2010" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54392,7 +54392,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2011" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54418,7 +54418,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2012" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54444,7 +54444,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2013" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54470,7 +54470,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2014" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54496,7 +54496,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54522,7 +54522,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2016" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54548,7 +54548,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2017" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54574,7 +54574,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2018" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54600,7 +54600,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2019" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54626,7 +54626,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2020" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54652,7 +54652,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2021" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54678,7 +54678,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54704,7 +54704,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2023" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54730,7 +54730,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2024" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54756,7 +54756,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2025" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54782,7 +54782,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54808,7 +54808,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54834,7 +54834,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54860,7 +54860,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2029" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54886,7 +54886,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2030" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54912,7 +54912,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2031" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54938,7 +54938,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2032" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54964,7 +54964,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2033" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54990,7 +54990,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2034" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55016,7 +55016,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2035" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55042,7 +55042,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2036" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55068,7 +55068,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2037" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55094,7 +55094,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2038" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55120,7 +55120,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2039" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55146,7 +55146,7 @@
         <v>1.25</v>
       </c>
       <c r="G2040" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55172,7 +55172,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55198,7 +55198,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55224,7 +55224,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2043" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55250,7 +55250,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2044" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55276,7 +55276,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2045" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55302,7 +55302,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2046" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55328,7 +55328,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55354,7 +55354,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55380,7 +55380,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55406,7 +55406,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2050" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55432,7 +55432,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55458,7 +55458,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2052" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55484,7 +55484,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55510,7 +55510,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2054" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55536,7 +55536,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2055" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55562,7 +55562,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55588,7 +55588,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55614,7 +55614,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2058" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55640,7 +55640,7 @@
         <v>1.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55666,7 +55666,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2060" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55692,7 +55692,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55718,7 +55718,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2062" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55744,7 +55744,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2063" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55770,7 +55770,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2064" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55796,7 +55796,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2065" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55822,7 +55822,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2066" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55848,7 +55848,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2067" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55874,7 +55874,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2068" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55900,7 +55900,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2069" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55926,7 +55926,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55952,7 +55952,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2071" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55978,7 +55978,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2072" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56004,7 +56004,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2073" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56030,7 +56030,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2074" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56056,7 +56056,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2075" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56082,7 +56082,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2076" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56108,7 +56108,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2077" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56134,7 +56134,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2078" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56160,7 +56160,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2079" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56186,7 +56186,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2080" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56212,7 +56212,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56238,7 +56238,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56264,7 +56264,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2083" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56290,7 +56290,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2084" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56316,7 +56316,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2085" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56342,7 +56342,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2086" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56368,7 +56368,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2087" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56394,7 +56394,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2088" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56420,7 +56420,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2089" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56446,7 +56446,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2090" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56472,7 +56472,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2091" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56498,7 +56498,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2092" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56524,7 +56524,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2093" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56550,7 +56550,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2094" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56576,7 +56576,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2095" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56602,7 +56602,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2096" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56628,7 +56628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2097" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56654,7 +56654,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2098" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56680,7 +56680,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2099" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56706,7 +56706,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2100" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56732,7 +56732,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56758,7 +56758,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2102" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56784,7 +56784,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2103" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56810,7 +56810,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2104" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56836,7 +56836,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56862,7 +56862,7 @@
         <v>1.25</v>
       </c>
       <c r="G2106" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56888,7 +56888,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2107" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56914,7 +56914,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2108" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56940,7 +56940,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2109" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56966,7 +56966,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2110" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56992,7 +56992,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2111" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57018,7 +57018,7 @@
         <v>1.25</v>
       </c>
       <c r="G2112" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57044,7 +57044,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2113" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57070,7 +57070,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2114" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57096,7 +57096,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2115" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57122,7 +57122,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2116" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57148,7 +57148,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2117" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57174,7 +57174,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2118" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57200,7 +57200,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2119" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57226,7 +57226,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2120" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57252,7 +57252,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57278,7 +57278,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2122" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57304,7 +57304,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2123" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57330,7 +57330,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2124" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57356,7 +57356,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57382,7 +57382,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2126" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57408,7 +57408,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2127" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57434,7 +57434,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57460,7 +57460,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2129" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57486,7 +57486,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2130" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57512,7 +57512,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2131" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57538,7 +57538,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57564,7 +57564,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2133" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57590,7 +57590,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -67213,6 +67213,32 @@
         <v>577</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45967.3998148148</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>577</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47076916694641</t>
+    <t xml:space="preserve">1.47076904773712</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781757354736</t>
+    <t xml:space="preserve">1.43781745433807</t>
   </si>
   <si>
     <t xml:space="preserve">1.48684310913086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424712657928</t>
+    <t xml:space="preserve">1.44424700737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42254734039307</t>
+    <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236248493195</t>
+    <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
     <t xml:space="preserve">1.37593269348145</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">1.33414030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744774341583</t>
+    <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3662885427475</t>
+    <t xml:space="preserve">1.36628842353821</t>
   </si>
   <si>
     <t xml:space="preserve">1.41290283203125</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726264953613</t>
+    <t xml:space="preserve">1.31726288795471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002950668335</t>
+    <t xml:space="preserve">1.31002962589264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217727184296</t>
+    <t xml:space="preserve">1.34217739105225</t>
   </si>
   <si>
     <t xml:space="preserve">1.35021424293518</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557720184326</t>
+    <t xml:space="preserve">1.38557696342468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273219585419</t>
+    <t xml:space="preserve">1.46273231506348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.430584192276</t>
+    <t xml:space="preserve">1.43058431148529</t>
   </si>
   <si>
     <t xml:space="preserve">1.50693571567535</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">1.49889862537384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.472376704216</t>
+    <t xml:space="preserve">1.47237658500671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49488019943237</t>
+    <t xml:space="preserve">1.49488008022308</t>
   </si>
   <si>
     <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543500423431</t>
+    <t xml:space="preserve">1.61543476581573</t>
   </si>
   <si>
     <t xml:space="preserve">1.67169380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490863800049</t>
+    <t xml:space="preserve">1.67490875720978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64597570896149</t>
+    <t xml:space="preserve">1.6459755897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.55113911628723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702820301056</t>
+    <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095414161682</t>
@@ -152,40 +152,40 @@
     <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862128257751</t>
+    <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
     <t xml:space="preserve">1.4120991230011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601892471313</t>
+    <t xml:space="preserve">1.45601904392242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426239490509</t>
+    <t xml:space="preserve">1.4342622756958</t>
   </si>
   <si>
     <t xml:space="preserve">1.4083217382431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42254745960236</t>
+    <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091511726379</t>
+    <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
     <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41334271430969</t>
+    <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4049745798111</t>
+    <t xml:space="preserve">1.40497481822968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313486099243</t>
+    <t xml:space="preserve">1.36313498020172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560393333435</t>
+    <t xml:space="preserve">1.35560381412506</t>
   </si>
   <si>
     <t xml:space="preserve">1.37233972549438</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288589000702</t>
+    <t xml:space="preserve">1.30288600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325479388237</t>
+    <t xml:space="preserve">1.32547926902771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3221321105957</t>
+    <t xml:space="preserve">1.32213222980499</t>
   </si>
   <si>
     <t xml:space="preserve">1.26439356803894</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">1.30539631843567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397182941437</t>
+    <t xml:space="preserve">1.36397194862366</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
@@ -221,19 +221,19 @@
     <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3305002450943</t>
+    <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267851352692</t>
+    <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506415843964</t>
+    <t xml:space="preserve">1.22506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20498132705688</t>
+    <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
     <t xml:space="preserve">1.20916533470154</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">1.23845303058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008489608765</t>
+    <t xml:space="preserve">1.23008501529694</t>
   </si>
   <si>
     <t xml:space="preserve">1.18824529647827</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226328372955</t>
+    <t xml:space="preserve">1.15226316452026</t>
   </si>
   <si>
     <t xml:space="preserve">1.14222168922424</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966978549957</t>
+    <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
     <t xml:space="preserve">1.11293399333954</t>
@@ -284,19 +284,19 @@
     <t xml:space="preserve">1.02423393726349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03929626941681</t>
+    <t xml:space="preserve">1.0392963886261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435860157013</t>
+    <t xml:space="preserve">1.05435848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364617824554</t>
+    <t xml:space="preserve">1.08364629745483</t>
   </si>
   <si>
     <t xml:space="preserve">1.06440007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07109439373016</t>
+    <t xml:space="preserve">1.07109427452087</t>
   </si>
   <si>
     <t xml:space="preserve">1.03762257099152</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">0.984067976474762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967157840729</t>
+    <t xml:space="preserve">0.999967277050018</t>
   </si>
   <si>
     <t xml:space="preserve">1.01251900196075</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">0.958127439022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842553138733</t>
+    <t xml:space="preserve">0.969842612743378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738686084747</t>
+    <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673722743988</t>
+    <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
     <t xml:space="preserve">0.866080284118652</t>
@@ -353,25 +353,25 @@
     <t xml:space="preserve">0.950596392154694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
     <t xml:space="preserve">0.920471727848053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332065105438</t>
+    <t xml:space="preserve">0.967332184314728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311387062073</t>
+    <t xml:space="preserve">0.962311267852783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519545078278</t>
+    <t xml:space="preserve">1.05519556999207</t>
   </si>
   <si>
     <t xml:space="preserve">0.991599023342133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088773727417</t>
+    <t xml:space="preserve">0.989088892936707</t>
   </si>
   <si>
     <t xml:space="preserve">1.0016405582428</t>
@@ -380,52 +380,52 @@
     <t xml:space="preserve">0.995783090591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762412548065</t>
+    <t xml:space="preserve">0.990762531757355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207698822021</t>
+    <t xml:space="preserve">0.937207579612732</t>
   </si>
   <si>
     <t xml:space="preserve">0.982394337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391706466675</t>
+    <t xml:space="preserve">0.941391587257385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251924514771</t>
+    <t xml:space="preserve">0.98825204372406</t>
   </si>
   <si>
     <t xml:space="preserve">0.972352802753448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168914318085</t>
+    <t xml:space="preserve">0.96816885471344</t>
   </si>
   <si>
     <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231127262115</t>
+    <t xml:space="preserve">0.983231246471405</t>
   </si>
   <si>
     <t xml:space="preserve">0.987415194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005763530731</t>
+    <t xml:space="preserve">0.969005823135376</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943490982056</t>
+    <t xml:space="preserve">0.953943431377411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854260921478</t>
+    <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
     <t xml:space="preserve">1.05937933921814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507066726685</t>
+    <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
     <t xml:space="preserve">1.05268502235413</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">1.10456621646881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636422157288</t>
+    <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14807951450348</t>
+    <t xml:space="preserve">1.14807939529419</t>
   </si>
   <si>
     <t xml:space="preserve">1.19577658176422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661331176758</t>
+    <t xml:space="preserve">1.19661343097687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602567195892</t>
+    <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20581805706024</t>
+    <t xml:space="preserve">1.20581817626953</t>
   </si>
   <si>
     <t xml:space="preserve">1.2133492231369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753299236298</t>
+    <t xml:space="preserve">1.21753311157227</t>
   </si>
   <si>
     <t xml:space="preserve">1.15644729137421</t>
@@ -467,55 +467,55 @@
     <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493985176086</t>
+    <t xml:space="preserve">1.19493973255157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15477359294891</t>
+    <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
     <t xml:space="preserve">1.14640581607819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19159257411957</t>
+    <t xml:space="preserve">1.19159245491028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314172744751</t>
+    <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
     <t xml:space="preserve">1.23761606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518882274628</t>
+    <t xml:space="preserve">1.25518870353699</t>
   </si>
   <si>
     <t xml:space="preserve">1.23594260215759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146814823151</t>
+    <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803791999817</t>
+    <t xml:space="preserve">1.13803780078888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799632549286</t>
+    <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130212783813</t>
+    <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653024196625</t>
+    <t xml:space="preserve">1.17653036117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581130981445</t>
+    <t xml:space="preserve">1.40581142902374</t>
   </si>
   <si>
     <t xml:space="preserve">1.39576995372772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911723136902</t>
+    <t xml:space="preserve">1.39911711215973</t>
   </si>
   <si>
     <t xml:space="preserve">1.39744341373444</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534821510315</t>
+    <t xml:space="preserve">1.49534809589386</t>
   </si>
   <si>
     <t xml:space="preserve">1.45685577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865401744843</t>
+    <t xml:space="preserve">1.48865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">1.48949062824249</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174557685852</t>
+    <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
     <t xml:space="preserve">1.65684926509857</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550772666931</t>
+    <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
     <t xml:space="preserve">1.75726425647736</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">1.62003016471863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697381019592</t>
+    <t xml:space="preserve">1.68697369098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.6166832447052</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">1.6066415309906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195295333862</t>
+    <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
     <t xml:space="preserve">1.68362665176392</t>
@@ -599,55 +599,55 @@
     <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718130588531</t>
+    <t xml:space="preserve">1.73718118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224351882935</t>
+    <t xml:space="preserve">1.75224363803864</t>
   </si>
   <si>
     <t xml:space="preserve">1.74052822589874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72379267215729</t>
+    <t xml:space="preserve">1.723792552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601241588593</t>
+    <t xml:space="preserve">1.65601253509521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220192432404</t>
+    <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74906098842621</t>
+    <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
     <t xml:space="preserve">1.84337317943573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80050384998322</t>
+    <t xml:space="preserve">1.80050373077393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335642814636</t>
+    <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193007946014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548327922821</t>
+    <t xml:space="preserve">1.95483303070068</t>
   </si>
   <si>
     <t xml:space="preserve">2.37323570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926283836365</t>
+    <t xml:space="preserve">2.46926259994507</t>
   </si>
   <si>
     <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936358451843</t>
+    <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505139350891</t>
+    <t xml:space="preserve">2.73505163192749</t>
   </si>
   <si>
     <t xml:space="preserve">2.64416885375977</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">2.47783660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46068906784058</t>
+    <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
     <t xml:space="preserve">2.40067172050476</t>
@@ -671,40 +671,40 @@
     <t xml:space="preserve">2.58929657936096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78649425506592</t>
+    <t xml:space="preserve">2.7864944934845</t>
   </si>
   <si>
     <t xml:space="preserve">2.67503452301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012874603271</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46240377426147</t>
+    <t xml:space="preserve">2.4624035358429</t>
   </si>
   <si>
     <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354128837585</t>
+    <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
     <t xml:space="preserve">2.41953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214832305908</t>
+    <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641061782837</t>
+    <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43496751785278</t>
+    <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
     <t xml:space="preserve">2.4555447101593</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897436141968</t>
+    <t xml:space="preserve">2.4589741230011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440695762634</t>
+    <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
     <t xml:space="preserve">2.56186008453369</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">2.41781973838806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3818097114563</t>
+    <t xml:space="preserve">2.38180994987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639350891113</t>
+    <t xml:space="preserve">2.42639327049255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38352417945862</t>
+    <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
     <t xml:space="preserve">2.33208155632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836318969727</t>
+    <t xml:space="preserve">2.31836342811584</t>
   </si>
   <si>
     <t xml:space="preserve">2.28063869476318</t>
@@ -755,58 +755,58 @@
     <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.126309633255</t>
+    <t xml:space="preserve">2.12630939483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800770759583</t>
+    <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05771899223328</t>
+    <t xml:space="preserve">2.0577187538147</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773586273193</t>
+    <t xml:space="preserve">2.11773562431335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1280243396759</t>
+    <t xml:space="preserve">2.12802410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515524864197</t>
+    <t xml:space="preserve">2.08515501022339</t>
   </si>
   <si>
     <t xml:space="preserve">2.06629300117493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08344078063965</t>
+    <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887337684631</t>
+    <t xml:space="preserve">2.09887313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799036026001</t>
+    <t xml:space="preserve">2.00799059867859</t>
   </si>
   <si>
     <t xml:space="preserve">2.05085968971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342343330383</t>
+    <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603778839111</t>
+    <t xml:space="preserve">2.17603802680969</t>
   </si>
   <si>
     <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401749610901</t>
+    <t xml:space="preserve">2.10401725769043</t>
   </si>
   <si>
     <t xml:space="preserve">2.15889024734497</t>
@@ -824,28 +824,28 @@
     <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917848587036</t>
+    <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062134742737</t>
+    <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
     <t xml:space="preserve">2.25491714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2823531627655</t>
+    <t xml:space="preserve">2.28235340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23776960372925</t>
+    <t xml:space="preserve">2.23776936531067</t>
   </si>
   <si>
     <t xml:space="preserve">2.22233653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089366912842</t>
+    <t xml:space="preserve">2.170893907547</t>
   </si>
   <si>
     <t xml:space="preserve">2.18975567817688</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">2.20175933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2086181640625</t>
+    <t xml:space="preserve">2.20861840248108</t>
   </si>
   <si>
     <t xml:space="preserve">2.28749775886536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20347380638123</t>
+    <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462842941284</t>
+    <t xml:space="preserve">2.24462866783142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43668222427368</t>
+    <t xml:space="preserve">2.4366819858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527262687683</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">2.50355815887451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55500102043152</t>
+    <t xml:space="preserve">2.5550012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326944351196</t>
+    <t xml:space="preserve">2.49326920509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47269248962402</t>
+    <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
     <t xml:space="preserve">2.32007813453674</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809158325195</t>
+    <t xml:space="preserve">2.36809182167053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33379602432251</t>
+    <t xml:space="preserve">2.33379626274109</t>
   </si>
   <si>
     <t xml:space="preserve">2.41439008712769</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">2.34922885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35780262947083</t>
+    <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.40410137176514</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.39038324356079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33551073074341</t>
+    <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
     <t xml:space="preserve">2.3063600063324</t>
@@ -956,25 +956,25 @@
     <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632626533508</t>
+    <t xml:space="preserve">2.18632650375366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10058808326721</t>
+    <t xml:space="preserve">2.10058784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201455116272</t>
+    <t xml:space="preserve">2.09201431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04057121276855</t>
+    <t xml:space="preserve">2.04057145118713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01484942436218</t>
+    <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914474487305</t>
+    <t xml:space="preserve">2.04914498329163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90339004993439</t>
+    <t xml:space="preserve">1.90339016914368</t>
   </si>
   <si>
     <t xml:space="preserve">1.9805543422699</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">1.97198045253754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053771018982</t>
+    <t xml:space="preserve">1.92053759098053</t>
   </si>
   <si>
     <t xml:space="preserve">1.98912823200226</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">1.91196382045746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9291113615036</t>
+    <t xml:space="preserve">1.92911148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624215126038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481639862061</t>
+    <t xml:space="preserve">1.89481627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909461021423</t>
+    <t xml:space="preserve">1.86909472942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194706916809</t>
+    <t xml:space="preserve">1.85194718837738</t>
   </si>
   <si>
     <t xml:space="preserve">1.94625914096832</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">2.06879186630249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249382019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.97236502170563</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">1.91100251674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840594768524</t>
+    <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
     <t xml:space="preserve">1.88470447063446</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">1.92853474617004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717247962952</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
     <t xml:space="preserve">1.90223670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593829631805</t>
+    <t xml:space="preserve">1.87593853473663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334184646606</t>
+    <t xml:space="preserve">1.82334172725677</t>
   </si>
   <si>
     <t xml:space="preserve">1.91976881027222</t>
@@ -1061,49 +1061,49 @@
     <t xml:space="preserve">1.8496401309967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730080127716</t>
+    <t xml:space="preserve">1.93730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989713191986</t>
+    <t xml:space="preserve">1.98989737033844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00742936134338</t>
+    <t xml:space="preserve">2.0074291229248</t>
   </si>
   <si>
     <t xml:space="preserve">1.7882776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77074551582336</t>
+    <t xml:space="preserve">1.77074539661407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704356193542</t>
+    <t xml:space="preserve">1.79704368114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733949184418</t>
+    <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542417526245</t>
+    <t xml:space="preserve">1.59542429447174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6217223405838</t>
+    <t xml:space="preserve">1.62172245979309</t>
   </si>
   <si>
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308484554291</t>
+    <t xml:space="preserve">1.68308472633362</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66555273532867</t>
+    <t xml:space="preserve">1.66555285453796</t>
   </si>
   <si>
     <t xml:space="preserve">1.69185090065002</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789206504822</t>
+    <t xml:space="preserve">1.57789194583893</t>
   </si>
   <si>
     <t xml:space="preserve">1.60419023036957</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104132652283</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048839569092</t>
+    <t xml:space="preserve">1.63048851490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">1.63925457000732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58665800094604</t>
+    <t xml:space="preserve">1.58665812015533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597698688507</t>
+    <t xml:space="preserve">1.55597686767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42010271549225</t>
+    <t xml:space="preserve">1.42010295391083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42448592185974</t>
+    <t xml:space="preserve">1.42448580265045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32367610931396</t>
+    <t xml:space="preserve">1.32367599010468</t>
   </si>
   <si>
     <t xml:space="preserve">1.29737794399261</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065576553345</t>
+    <t xml:space="preserve">1.38065564632416</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4025707244873</t>
+    <t xml:space="preserve">1.40257060527802</t>
   </si>
   <si>
     <t xml:space="preserve">1.43325197696686</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874032974243</t>
+    <t xml:space="preserve">1.35874021053314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763494491577</t>
+    <t xml:space="preserve">1.43763482570648</t>
   </si>
   <si>
     <t xml:space="preserve">1.44640111923218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201803207397</t>
+    <t xml:space="preserve">1.44201815128326</t>
   </si>
   <si>
     <t xml:space="preserve">1.4507839679718</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36750638484955</t>
+    <t xml:space="preserve">1.36750650405884</t>
   </si>
   <si>
     <t xml:space="preserve">1.53406167030334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214647293091</t>
+    <t xml:space="preserve">1.5121465921402</t>
   </si>
   <si>
     <t xml:space="preserve">1.52967870235443</t>
@@ -1238,40 +1238,40 @@
     <t xml:space="preserve">1.55159378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035983562469</t>
+    <t xml:space="preserve">1.56035995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091252803802</t>
+    <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584842681885</t>
+    <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
     <t xml:space="preserve">1.5165296792984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5691260099411</t>
+    <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776362419128</t>
+    <t xml:space="preserve">1.50776350498199</t>
   </si>
   <si>
     <t xml:space="preserve">1.52529561519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899744987488</t>
+    <t xml:space="preserve">1.49899733066559</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545694828033</t>
+    <t xml:space="preserve">1.60545706748962</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232108592987</t>
+    <t xml:space="preserve">1.54232096672058</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">1.48820459842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46114611625671</t>
+    <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624334812164</t>
+    <t xml:space="preserve">1.50624322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016572952271</t>
+    <t xml:space="preserve">1.47016561031342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310748577118</t>
+    <t xml:space="preserve">1.44310736656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604912281036</t>
+    <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801025390625</t>
+    <t xml:space="preserve">1.39801013469696</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702962875366</t>
+    <t xml:space="preserve">1.40702974796295</t>
   </si>
   <si>
     <t xml:space="preserve">1.38899087905884</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35291314125061</t>
+    <t xml:space="preserve">1.3529132604599</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">1.3438937664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31683564186096</t>
+    <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
     <t xml:space="preserve">1.28977727890015</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">1.22664129734039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762180328369</t>
+    <t xml:space="preserve">1.21762192249298</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">1.29879677295685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193263530731</t>
+    <t xml:space="preserve">1.36193251609802</t>
   </si>
   <si>
     <t xml:space="preserve">1.37997150421143</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566067218781</t>
+    <t xml:space="preserve">1.23566079139709</t>
   </si>
   <si>
     <t xml:space="preserve">1.45212686061859</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">1.65055406093597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859292984009</t>
+    <t xml:space="preserve">1.66859304904938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153468608856</t>
+    <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251519203186</t>
+    <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
     <t xml:space="preserve">1.59643757343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486489295959</t>
+    <t xml:space="preserve">1.79486477375031</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
@@ -1400,22 +1400,19 @@
     <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369004249573</t>
+    <t xml:space="preserve">1.71369016170502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349581718445</t>
+    <t xml:space="preserve">1.62349569797516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55134057998657</t>
+    <t xml:space="preserve">1.55134046077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6956512928009</t>
+    <t xml:space="preserve">1.69565117359161</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
@@ -1427,7 +1424,7 @@
     <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15448582172394</t>
+    <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
     <t xml:space="preserve">1.1274276971817</t>
@@ -1436,7 +1433,7 @@
     <t xml:space="preserve">1.19958305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25369966030121</t>
+    <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
     <t xml:space="preserve">1.14546644687653</t>
@@ -1448,7 +1445,7 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09134995937347</t>
+    <t xml:space="preserve">1.09135007858276</t>
   </si>
   <si>
     <t xml:space="preserve">1.08233058452606</t>
@@ -1463,7 +1460,7 @@
     <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527234077454</t>
+    <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1478,49 +1475,49 @@
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097490310669</t>
+    <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078055858612</t>
+    <t xml:space="preserve">0.965078175067902</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019812107086</t>
+    <t xml:space="preserve">0.938019752502441</t>
   </si>
   <si>
     <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947039127349854</t>
+    <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432446479797</t>
+    <t xml:space="preserve">0.897432386875153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91096156835556</t>
+    <t xml:space="preserve">0.910961508750916</t>
   </si>
   <si>
     <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0191947221756</t>
+    <t xml:space="preserve">1.01919460296631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95605856180191</t>
+    <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20860242843628</t>
+    <t xml:space="preserve">1.20860254764557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918510437012</t>
+    <t xml:space="preserve">1.47918498516083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098133087158</t>
+    <t xml:space="preserve">1.25098145008087</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1550,7 +1547,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12124991416931</t>
+    <t xml:space="preserve">1.1212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1568,22 +1565,25 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051640987396</t>
+    <t xml:space="preserve">1.13051652908325</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19538223743439</t>
+    <t xml:space="preserve">1.1953821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198353767395</t>
+    <t xml:space="preserve">1.11198341846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -29071,7 +29071,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1037" t="s">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1039" t="s">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29227,7 +29227,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29253,7 +29253,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1044" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29305,7 +29305,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1046" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1051" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1061" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1062" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1065" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1068" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29903,7 +29903,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1069" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29929,7 +29929,7 @@
         <v>1.25</v>
       </c>
       <c r="G1070" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29955,7 +29955,7 @@
         <v>1.25</v>
       </c>
       <c r="G1071" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29981,7 +29981,7 @@
         <v>1.25</v>
       </c>
       <c r="G1072" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>1.25</v>
       </c>
       <c r="G1073" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1080" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1081" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>1.25</v>
       </c>
       <c r="G1084" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1088" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30449,7 +30449,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30501,7 +30501,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1092" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30527,7 +30527,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30553,7 +30553,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1094" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30579,7 +30579,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30605,7 +30605,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30631,7 +30631,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30657,7 +30657,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1098" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30683,7 +30683,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1099" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30709,7 +30709,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1100" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30735,7 +30735,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1101" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30761,7 +30761,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1103" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1104" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30839,7 +30839,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1105" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30865,7 +30865,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30891,7 +30891,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1107" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30943,7 +30943,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1109" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1110" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1111" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1112" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31047,7 +31047,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1113" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31073,7 +31073,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1114" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31099,7 +31099,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1117" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31203,7 +31203,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1119" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1120" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1121" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1122" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1125" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1126" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1128" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1129" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1130" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1131" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31541,7 +31541,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1133" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1134" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1136" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1137" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>1.25</v>
       </c>
       <c r="G1138" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1139" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31749,7 +31749,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1140" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31775,7 +31775,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1141" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31801,7 +31801,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1142" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31827,7 +31827,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1143" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31879,7 +31879,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1145" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31931,7 +31931,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1147" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31957,7 +31957,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1148" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31983,7 +31983,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1149" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32009,7 +32009,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1150" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32035,7 +32035,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1151" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1152" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1153" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32113,7 +32113,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1154" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32139,7 +32139,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32165,7 +32165,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1156" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32191,7 +32191,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1157" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32217,7 +32217,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1158" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32243,7 +32243,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1159" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32269,7 +32269,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1160" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32295,7 +32295,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1161" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32321,7 +32321,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1162" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32347,7 +32347,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1163" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32373,7 +32373,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1164" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32399,7 +32399,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1165" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32425,7 +32425,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1166" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32451,7 +32451,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1167" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32477,7 +32477,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1168" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32503,7 +32503,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32529,7 +32529,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1170" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32555,7 +32555,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32581,7 +32581,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1172" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32607,7 +32607,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1173" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32633,7 +32633,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1174" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32659,7 +32659,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1175" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32685,7 +32685,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1176" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32711,7 +32711,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1177" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32737,7 +32737,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32763,7 +32763,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1179" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32789,7 +32789,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1180" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32815,7 +32815,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32841,7 +32841,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1182" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32867,7 +32867,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1183" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32893,7 +32893,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1184" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32919,7 +32919,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1185" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32945,7 +32945,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1186" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32971,7 +32971,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1187" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32997,7 +32997,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1188" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33023,7 +33023,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1189" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33049,7 +33049,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1190" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33075,7 +33075,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33101,7 +33101,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33127,7 +33127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33153,7 +33153,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1194" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33179,7 +33179,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1195" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33205,7 +33205,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1196" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33231,7 +33231,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33257,7 +33257,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1198" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33283,7 +33283,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33309,7 +33309,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33335,7 +33335,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1201" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33361,7 +33361,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1202" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33387,7 +33387,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33413,7 +33413,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1204" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33439,7 +33439,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33465,7 +33465,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33491,7 +33491,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33517,7 +33517,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1208" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33543,7 +33543,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33569,7 +33569,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33595,7 +33595,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1211" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33621,7 +33621,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1212" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33647,7 +33647,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1213" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33673,7 +33673,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1214" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33699,7 +33699,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33725,7 +33725,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33751,7 +33751,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33777,7 +33777,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1218" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33803,7 +33803,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1219" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33829,7 +33829,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1220" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33855,7 +33855,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1221" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33881,7 +33881,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1222" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33907,7 +33907,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1223" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33933,7 +33933,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1224" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33959,7 +33959,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1225" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33985,7 +33985,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1226" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34011,7 +34011,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1227" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34037,7 +34037,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1228" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34063,7 +34063,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1229" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34089,7 +34089,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1230" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34115,7 +34115,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34141,7 +34141,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34167,7 +34167,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1233" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34193,7 +34193,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1234" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34219,7 +34219,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34245,7 +34245,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34271,7 +34271,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1237" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34297,7 +34297,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1238" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34323,7 +34323,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1239" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34349,7 +34349,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1240" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34375,7 +34375,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34401,7 +34401,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1242" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34427,7 +34427,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1243" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34453,7 +34453,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1244" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34479,7 +34479,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34505,7 +34505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1246" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34531,7 +34531,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1247" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34557,7 +34557,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34583,7 +34583,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1249" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34609,7 +34609,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1250" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34635,7 +34635,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1251" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34661,7 +34661,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34687,7 +34687,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1253" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34713,7 +34713,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1254" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34739,7 +34739,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1255" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34765,7 +34765,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1256" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34791,7 +34791,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1257" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34817,7 +34817,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1258" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34843,7 +34843,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1259" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34869,7 +34869,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1260" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34895,7 +34895,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1261" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34921,7 +34921,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1262" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34947,7 +34947,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34973,7 +34973,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1264" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34999,7 +34999,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1265" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35025,7 +35025,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1266" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35051,7 +35051,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35077,7 +35077,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1268" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35103,7 +35103,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1269" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35129,7 +35129,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1270" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35155,7 +35155,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1271" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35181,7 +35181,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1272" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35207,7 +35207,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1273" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35233,7 +35233,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1274" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35259,7 +35259,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1275" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35285,7 +35285,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1276" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35311,7 +35311,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1277" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35337,7 +35337,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1278" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35363,7 +35363,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1279" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35389,7 +35389,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1280" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35415,7 +35415,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1281" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35441,7 +35441,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1282" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35467,7 +35467,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1283" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35493,7 +35493,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1284" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35519,7 +35519,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1285" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35545,7 +35545,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1286" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35571,7 +35571,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35597,7 +35597,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35623,7 +35623,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1289" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35649,7 +35649,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1290" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35675,7 +35675,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1291" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35701,7 +35701,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1292" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35727,7 +35727,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1293" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35753,7 +35753,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1294" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35779,7 +35779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1295" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35805,7 +35805,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1296" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35831,7 +35831,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1297" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35857,7 +35857,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35883,7 +35883,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35909,7 +35909,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1300" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35935,7 +35935,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1301" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35961,7 +35961,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1302" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35987,7 +35987,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1303" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36013,7 +36013,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1304" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36039,7 +36039,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1305" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36065,7 +36065,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1306" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36091,7 +36091,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1307" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36117,7 +36117,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1308" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36143,7 +36143,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1309" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36169,7 +36169,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1310" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36195,7 +36195,7 @@
         <v>1.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36221,7 +36221,7 @@
         <v>1.25</v>
       </c>
       <c r="G1312" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36247,7 +36247,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1313" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36273,7 +36273,7 @@
         <v>1.25</v>
       </c>
       <c r="G1314" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36299,7 +36299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1315" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36325,7 +36325,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1316" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36351,7 +36351,7 @@
         <v>1.25</v>
       </c>
       <c r="G1317" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36377,7 +36377,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36429,7 +36429,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36455,7 +36455,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1321" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36481,7 +36481,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1322" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36507,7 +36507,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1323" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36533,7 +36533,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1324" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36559,7 +36559,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1325" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36585,7 +36585,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36611,7 +36611,7 @@
         <v>1.25</v>
       </c>
       <c r="G1327" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36637,7 +36637,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1328" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36663,7 +36663,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1329" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36689,7 +36689,7 @@
         <v>1.25</v>
       </c>
       <c r="G1330" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36715,7 +36715,7 @@
         <v>1.25</v>
       </c>
       <c r="G1331" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36741,7 +36741,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36767,7 +36767,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36845,7 +36845,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1336" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37053,7 +37053,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1344" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37105,7 +37105,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1346" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37261,7 +37261,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1352" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37287,7 +37287,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1353" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37365,7 +37365,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1356" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37391,7 +37391,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1357" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37443,7 +37443,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1359" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37469,7 +37469,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1360" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37521,7 +37521,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37547,7 +37547,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37573,7 +37573,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38197,7 +38197,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1388" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38223,7 +38223,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1389" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38249,7 +38249,7 @@
         <v>1.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38275,7 +38275,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1391" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38301,7 +38301,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1392" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38353,7 +38353,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1394" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38379,7 +38379,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1395" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38405,7 +38405,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1396" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38431,7 +38431,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1397" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38561,7 +38561,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38587,7 +38587,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38613,7 +38613,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38639,7 +38639,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1405" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38665,7 +38665,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38691,7 +38691,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1407" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38717,7 +38717,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1408" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38743,7 +38743,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1409" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38769,7 +38769,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1410" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38795,7 +38795,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1411" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38821,7 +38821,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1412" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38847,7 +38847,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1413" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38873,7 +38873,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1414" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38899,7 +38899,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1415" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38925,7 +38925,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1416" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38951,7 +38951,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1417" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38977,7 +38977,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1418" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39003,7 +39003,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1419" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39055,7 +39055,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1421" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39081,7 +39081,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1422" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39107,7 +39107,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1423" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39133,7 +39133,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1424" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39159,7 +39159,7 @@
         <v>1.25</v>
       </c>
       <c r="G1425" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39185,7 +39185,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39211,7 +39211,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1427" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39237,7 +39237,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1428" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39263,7 +39263,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1429" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39289,7 +39289,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1430" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39315,7 +39315,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39341,7 +39341,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1432" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39367,7 +39367,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1433" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39471,7 +39471,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39497,7 +39497,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1438" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39523,7 +39523,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1439" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39549,7 +39549,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1440" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39575,7 +39575,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1441" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39601,7 +39601,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1442" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39627,7 +39627,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1443" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39653,7 +39653,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1444" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39679,7 +39679,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1445" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39705,7 +39705,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1446" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39731,7 +39731,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1447" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39757,7 +39757,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1448" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39783,7 +39783,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1449" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39809,7 +39809,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1450" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39835,7 +39835,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1451" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39861,7 +39861,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1452" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39887,7 +39887,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1453" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39913,7 +39913,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1454" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39939,7 +39939,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1455" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39965,7 +39965,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1456" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39991,7 +39991,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1457" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40173,7 +40173,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1464" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40251,7 +40251,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1467" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40277,7 +40277,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1468" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40537,7 +40537,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41213,7 +41213,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1504" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41525,7 +41525,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1516" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41603,7 +41603,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1519" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41629,7 +41629,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41655,7 +41655,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1521" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41681,7 +41681,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1522" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41785,7 +41785,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1526" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41811,7 +41811,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1527" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41915,7 +41915,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1531" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41941,7 +41941,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1532" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42123,7 +42123,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1539" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42175,7 +42175,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1541" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42279,7 +42279,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1545" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42331,7 +42331,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1547" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42357,7 +42357,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1548" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42383,7 +42383,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1549" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42409,7 +42409,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1550" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42435,7 +42435,7 @@
         <v>1.25</v>
       </c>
       <c r="G1551" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42461,7 +42461,7 @@
         <v>1.25</v>
       </c>
       <c r="G1552" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42487,7 +42487,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1553" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42513,7 +42513,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1554" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42539,7 +42539,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1555" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42565,7 +42565,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1556" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42591,7 +42591,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42617,7 +42617,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1558" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42643,7 +42643,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42669,7 +42669,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1560" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42695,7 +42695,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42721,7 +42721,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1562" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42799,7 +42799,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42825,7 +42825,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1566" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42851,7 +42851,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1567" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42877,7 +42877,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42903,7 +42903,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1569" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42929,7 +42929,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1570" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42955,7 +42955,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1571" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42981,7 +42981,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1572" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43007,7 +43007,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1573" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43033,7 +43033,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1574" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43059,7 +43059,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1575" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43085,7 +43085,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1576" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43111,7 +43111,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1577" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43137,7 +43137,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1578" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43163,7 +43163,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1579" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43189,7 +43189,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1580" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43215,7 +43215,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1581" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43241,7 +43241,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1582" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43267,7 +43267,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1583" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43293,7 +43293,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1584" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43319,7 +43319,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1585" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43345,7 +43345,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1586" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43371,7 +43371,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43527,7 +43527,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1593" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43553,7 +43553,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1594" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43605,7 +43605,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1596" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43631,7 +43631,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43683,7 +43683,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1599" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43787,7 +43787,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43813,7 +43813,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1604" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43839,7 +43839,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43865,7 +43865,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1606" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43891,7 +43891,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1607" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43917,7 +43917,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43943,7 +43943,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1609" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44021,7 +44021,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1612" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44047,7 +44047,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1613" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44073,7 +44073,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44099,7 +44099,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1615" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44125,7 +44125,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1616" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44177,7 +44177,7 @@
         <v>1.25</v>
       </c>
       <c r="G1618" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44203,7 +44203,7 @@
         <v>1.25</v>
       </c>
       <c r="G1619" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44229,7 +44229,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1620" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44255,7 +44255,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44307,7 +44307,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44437,7 +44437,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1628" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44489,7 +44489,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1630" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44619,7 +44619,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1635" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44645,7 +44645,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44671,7 +44671,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1637" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44697,7 +44697,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44723,7 +44723,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1639" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44749,7 +44749,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1640" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44775,7 +44775,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1641" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44801,7 +44801,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45009,7 +45009,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45061,7 +45061,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1652" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45087,7 +45087,7 @@
         <v>1.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45113,7 +45113,7 @@
         <v>1.25</v>
       </c>
       <c r="G1654" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45139,7 +45139,7 @@
         <v>1.25</v>
       </c>
       <c r="G1655" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45165,7 +45165,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1656" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45191,7 +45191,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1657" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45217,7 +45217,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45243,7 +45243,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45269,7 +45269,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1660" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45295,7 +45295,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1661" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45321,7 +45321,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1662" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45347,7 +45347,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1663" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45373,7 +45373,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45425,7 +45425,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45451,7 +45451,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45477,7 +45477,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45503,7 +45503,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45555,7 +45555,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1671" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45581,7 +45581,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1672" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45633,7 +45633,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1674" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45685,7 +45685,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1676" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45737,7 +45737,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45815,7 +45815,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1681" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45867,7 +45867,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1683" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45893,7 +45893,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1684" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45919,7 +45919,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1685" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45997,7 +45997,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1688" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46153,7 +46153,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1694" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46179,7 +46179,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1695" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46205,7 +46205,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1696" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46231,7 +46231,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46283,7 +46283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1699" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46335,7 +46335,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46465,7 +46465,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1706" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46517,7 +46517,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1708" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46621,7 +46621,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1712" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46673,7 +46673,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1714" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46699,7 +46699,7 @@
         <v>1.25</v>
       </c>
       <c r="G1715" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46725,7 +46725,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1716" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46751,7 +46751,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46777,7 +46777,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46803,7 +46803,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46829,7 +46829,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46855,7 +46855,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46881,7 +46881,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46907,7 +46907,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46959,7 +46959,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1725" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46985,7 +46985,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1726" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47011,7 +47011,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1727" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47141,7 +47141,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1732" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47193,7 +47193,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1734" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47219,7 +47219,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47401,7 +47401,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1742" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47427,7 +47427,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1743" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47453,7 +47453,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1744" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47479,7 +47479,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1745" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47505,7 +47505,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1746" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47531,7 +47531,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1747" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47557,7 +47557,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1748" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47583,7 +47583,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1749" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47609,7 +47609,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1750" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47635,7 +47635,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1751" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47661,7 +47661,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1752" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47687,7 +47687,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1753" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47713,7 +47713,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1754" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47739,7 +47739,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1755" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47895,7 +47895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1761" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47947,7 +47947,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47999,7 +47999,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1765" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48025,7 +48025,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1766" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48051,7 +48051,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1767" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48077,7 +48077,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1768" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48103,7 +48103,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1769" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48233,7 +48233,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1774" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48259,7 +48259,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1775" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48389,7 +48389,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1780" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48493,7 +48493,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1784" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48519,7 +48519,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1785" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48545,7 +48545,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1786" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48571,7 +48571,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1787" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48597,7 +48597,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1788" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48623,7 +48623,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1789" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48675,7 +48675,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1791" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48701,7 +48701,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1792" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48935,7 +48935,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1801" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48961,7 +48961,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48987,7 +48987,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1803" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49013,7 +49013,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1804" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49039,7 +49039,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1805" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49065,7 +49065,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49091,7 +49091,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1807" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49117,7 +49117,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1808" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49143,7 +49143,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1809" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49169,7 +49169,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1810" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49195,7 +49195,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1811" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49221,7 +49221,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1812" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49247,7 +49247,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1813" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49325,7 +49325,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49351,7 +49351,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1817" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49377,7 +49377,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1818" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49403,7 +49403,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1819" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49429,7 +49429,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1820" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49455,7 +49455,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1821" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49481,7 +49481,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1822" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49507,7 +49507,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1823" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49533,7 +49533,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1824" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49559,7 +49559,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1825" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49585,7 +49585,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1826" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49611,7 +49611,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49637,7 +49637,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1828" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49663,7 +49663,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1829" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49689,7 +49689,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49715,7 +49715,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49741,7 +49741,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49767,7 +49767,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49793,7 +49793,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1834" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49819,7 +49819,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1835" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49845,7 +49845,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1836" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49871,7 +49871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1837" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49897,7 +49897,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1838" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49923,7 +49923,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49949,7 +49949,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49975,7 +49975,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50001,7 +50001,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1842" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50027,7 +50027,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1843" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50053,7 +50053,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1844" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50079,7 +50079,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1845" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50105,7 +50105,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1846" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50131,7 +50131,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1847" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50157,7 +50157,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1848" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50183,7 +50183,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1849" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50209,7 +50209,7 @@
         <v>1.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50235,7 +50235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1851" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50391,7 +50391,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50443,7 +50443,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1859" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50495,7 +50495,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50651,7 +50651,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50677,7 +50677,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50859,7 +50859,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1875" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50885,7 +50885,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1876" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50911,7 +50911,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1877" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50937,7 +50937,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1878" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50963,7 +50963,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1879" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50989,7 +50989,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1880" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51015,7 +51015,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1881" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51041,7 +51041,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1882" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51067,7 +51067,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1883" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51093,7 +51093,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1884" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51119,7 +51119,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1885" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51145,7 +51145,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1886" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51171,7 +51171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1887" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51197,7 +51197,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1888" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51223,7 +51223,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1889" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51249,7 +51249,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1890" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51275,7 +51275,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1891" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51301,7 +51301,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1892" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51327,7 +51327,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1893" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51353,7 +51353,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1894" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51379,7 +51379,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1895" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51405,7 +51405,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1896" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51431,7 +51431,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1897" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51457,7 +51457,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1898" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51483,7 +51483,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1899" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51509,7 +51509,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1900" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51535,7 +51535,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1901" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51561,7 +51561,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1902" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51587,7 +51587,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1903" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51613,7 +51613,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1904" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51639,7 +51639,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1905" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51665,7 +51665,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1906" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51691,7 +51691,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1907" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51717,7 +51717,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1908" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51743,7 +51743,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1909" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51769,7 +51769,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1910" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51795,7 +51795,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51821,7 +51821,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1912" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51847,7 +51847,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51873,7 +51873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51899,7 +51899,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1915" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51925,7 +51925,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1916" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51951,7 +51951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1917" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51977,7 +51977,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52003,7 +52003,7 @@
         <v>1.25</v>
       </c>
       <c r="G1919" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52029,7 +52029,7 @@
         <v>1.25</v>
       </c>
       <c r="G1920" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52055,7 +52055,7 @@
         <v>1.25</v>
       </c>
       <c r="G1921" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52081,7 +52081,7 @@
         <v>1.25</v>
       </c>
       <c r="G1922" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52107,7 +52107,7 @@
         <v>1.25</v>
       </c>
       <c r="G1923" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52133,7 +52133,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1924" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52159,7 +52159,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1925" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52185,7 +52185,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52211,7 +52211,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52237,7 +52237,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52263,7 +52263,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52289,7 +52289,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1930" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52315,7 +52315,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1931" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52341,7 +52341,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1932" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52367,7 +52367,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52393,7 +52393,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52419,7 +52419,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52445,7 +52445,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1936" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52471,7 +52471,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1937" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52497,7 +52497,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1938" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52523,7 +52523,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1939" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52549,7 +52549,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1940" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52575,7 +52575,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1941" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52601,7 +52601,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1942" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52627,7 +52627,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1943" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52653,7 +52653,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1944" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52679,7 +52679,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1945" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52705,7 +52705,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1946" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52731,7 +52731,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1947" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52757,7 +52757,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1948" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52783,7 +52783,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1949" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52809,7 +52809,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1950" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52835,7 +52835,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1951" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52861,7 +52861,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1952" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52887,7 +52887,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1953" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52913,7 +52913,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1954" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52939,7 +52939,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1955" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52965,7 +52965,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1956" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52991,7 +52991,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53017,7 +53017,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1958" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53043,7 +53043,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53069,7 +53069,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53095,7 +53095,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1961" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53121,7 +53121,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1962" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53147,7 +53147,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1963" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53173,7 +53173,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53199,7 +53199,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1965" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53225,7 +53225,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1966" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53251,7 +53251,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1967" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53277,7 +53277,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1968" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53303,7 +53303,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1969" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53329,7 +53329,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1970" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53355,7 +53355,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1971" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53381,7 +53381,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1972" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53407,7 +53407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1973" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53433,7 +53433,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1974" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53459,7 +53459,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1975" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53485,7 +53485,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1976" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53511,7 +53511,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53537,7 +53537,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53563,7 +53563,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53589,7 +53589,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53615,7 +53615,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53641,7 +53641,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53667,7 +53667,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53693,7 +53693,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1984" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53719,7 +53719,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53745,7 +53745,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53771,7 +53771,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1987" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53797,7 +53797,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1988" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53823,7 +53823,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1989" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53849,7 +53849,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1990" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53875,7 +53875,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53901,7 +53901,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1992" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53927,7 +53927,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53953,7 +53953,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1994" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53979,7 +53979,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1995" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54005,7 +54005,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1996" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54031,7 +54031,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1997" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54057,7 +54057,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54083,7 +54083,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1999" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54109,7 +54109,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54135,7 +54135,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2001" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54161,7 +54161,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2002" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54187,7 +54187,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2003" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54213,7 +54213,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2004" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54239,7 +54239,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2005" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54265,7 +54265,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2006" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54291,7 +54291,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54317,7 +54317,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54343,7 +54343,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2009" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54369,7 +54369,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2010" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54395,7 +54395,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2011" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54421,7 +54421,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2012" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54447,7 +54447,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2013" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54473,7 +54473,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2014" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54499,7 +54499,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54525,7 +54525,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2016" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54551,7 +54551,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2017" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54577,7 +54577,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2018" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54603,7 +54603,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2019" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54629,7 +54629,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2020" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54655,7 +54655,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2021" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54681,7 +54681,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54707,7 +54707,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2023" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54733,7 +54733,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2024" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54759,7 +54759,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2025" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54785,7 +54785,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54811,7 +54811,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54837,7 +54837,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54863,7 +54863,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2029" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54889,7 +54889,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2030" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54915,7 +54915,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2031" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54941,7 +54941,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2032" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54967,7 +54967,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2033" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54993,7 +54993,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2034" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55019,7 +55019,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2035" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55045,7 +55045,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2036" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55071,7 +55071,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2037" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55097,7 +55097,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2038" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55123,7 +55123,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2039" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55149,7 +55149,7 @@
         <v>1.25</v>
       </c>
       <c r="G2040" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55175,7 +55175,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55201,7 +55201,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55227,7 +55227,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2043" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55253,7 +55253,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2044" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55279,7 +55279,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2045" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55305,7 +55305,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2046" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55331,7 +55331,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55357,7 +55357,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55383,7 +55383,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55409,7 +55409,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2050" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55435,7 +55435,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55461,7 +55461,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2052" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55487,7 +55487,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55513,7 +55513,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2054" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55539,7 +55539,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2055" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55565,7 +55565,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55591,7 +55591,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55617,7 +55617,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2058" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55643,7 +55643,7 @@
         <v>1.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55669,7 +55669,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2060" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55695,7 +55695,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55721,7 +55721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2062" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55747,7 +55747,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2063" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55773,7 +55773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2064" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55799,7 +55799,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2065" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55825,7 +55825,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2066" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55851,7 +55851,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2067" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55877,7 +55877,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2068" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55903,7 +55903,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2069" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55929,7 +55929,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55955,7 +55955,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2071" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55981,7 +55981,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2072" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56007,7 +56007,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2073" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56033,7 +56033,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2074" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56059,7 +56059,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2075" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56085,7 +56085,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2076" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56111,7 +56111,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2077" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56137,7 +56137,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2078" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56163,7 +56163,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2079" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56189,7 +56189,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2080" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56215,7 +56215,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56241,7 +56241,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56267,7 +56267,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2083" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56293,7 +56293,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2084" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56319,7 +56319,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2085" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56345,7 +56345,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2086" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56371,7 +56371,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2087" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56397,7 +56397,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2088" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56423,7 +56423,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2089" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56449,7 +56449,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2090" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56475,7 +56475,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2091" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56501,7 +56501,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2092" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56527,7 +56527,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2093" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56553,7 +56553,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2094" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56579,7 +56579,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2095" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56605,7 +56605,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2096" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56631,7 +56631,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2097" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56657,7 +56657,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2098" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56683,7 +56683,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2099" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56709,7 +56709,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2100" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56735,7 +56735,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56761,7 +56761,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2102" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56787,7 +56787,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2103" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56813,7 +56813,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2104" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56839,7 +56839,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56865,7 +56865,7 @@
         <v>1.25</v>
       </c>
       <c r="G2106" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56891,7 +56891,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2107" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56917,7 +56917,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2108" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56943,7 +56943,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2109" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56969,7 +56969,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2110" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56995,7 +56995,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2111" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57021,7 +57021,7 @@
         <v>1.25</v>
       </c>
       <c r="G2112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57047,7 +57047,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2113" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57073,7 +57073,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2114" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57099,7 +57099,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2115" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57125,7 +57125,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2116" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57151,7 +57151,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2117" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57177,7 +57177,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2118" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57203,7 +57203,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2119" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57229,7 +57229,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2120" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57255,7 +57255,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57281,7 +57281,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2122" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57307,7 +57307,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2123" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57333,7 +57333,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2124" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57359,7 +57359,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57385,7 +57385,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2126" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57411,7 +57411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2127" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57437,7 +57437,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57463,7 +57463,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2129" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57489,7 +57489,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2130" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57515,7 +57515,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57541,7 +57541,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57567,7 +57567,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2133" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57593,7 +57593,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -67294,6 +67294,32 @@
         <v>575</v>
       </c>
       <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.3333333333</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>575</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47076904773712</t>
+    <t xml:space="preserve">1.47076916694641</t>
   </si>
   <si>
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781745433807</t>
+    <t xml:space="preserve">1.43781769275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684310913086</t>
+    <t xml:space="preserve">1.48684334754944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424700737</t>
+    <t xml:space="preserve">1.44424724578857</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236236572266</t>
+    <t xml:space="preserve">1.38236224651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593269348145</t>
+    <t xml:space="preserve">1.37593257427216</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414030075073</t>
@@ -74,37 +74,37 @@
     <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3815586566925</t>
+    <t xml:space="preserve">1.38155853748322</t>
   </si>
   <si>
     <t xml:space="preserve">1.40647315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44585454463959</t>
+    <t xml:space="preserve">1.44585466384888</t>
   </si>
   <si>
     <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780323505402</t>
+    <t xml:space="preserve">1.34780335426331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726288795471</t>
+    <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002962589264</t>
+    <t xml:space="preserve">1.31002938747406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217739105225</t>
+    <t xml:space="preserve">1.34217715263367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021424293518</t>
+    <t xml:space="preserve">1.35021436214447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128119468689</t>
+    <t xml:space="preserve">1.32128131389618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557696342468</t>
+    <t xml:space="preserve">1.38557708263397</t>
   </si>
   <si>
     <t xml:space="preserve">1.46273231506348</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">1.43058431148529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693571567535</t>
+    <t xml:space="preserve">1.50693559646606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49889862537384</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">1.47237658500671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49488008022308</t>
+    <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274653434753</t>
+    <t xml:space="preserve">1.55274641513824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543476581573</t>
+    <t xml:space="preserve">1.61543524265289</t>
   </si>
   <si>
     <t xml:space="preserve">1.67169380187988</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">1.6459755897522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113911628723</t>
+    <t xml:space="preserve">1.55113923549652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702808380127</t>
+    <t xml:space="preserve">1.52702820301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095414161682</t>
@@ -155,70 +155,70 @@
     <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4120991230011</t>
+    <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601904392242</t>
+    <t xml:space="preserve">1.45601892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4342622756958</t>
+    <t xml:space="preserve">1.43426239490509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4083217382431</t>
+    <t xml:space="preserve">1.40832185745239</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091523647308</t>
+    <t xml:space="preserve">1.43091511726379</t>
   </si>
   <si>
     <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4133425951004</t>
+    <t xml:space="preserve">1.41334247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497481822968</t>
+    <t xml:space="preserve">1.40497469902039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313498020172</t>
+    <t xml:space="preserve">1.36313509941101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560381412506</t>
+    <t xml:space="preserve">1.35560393333435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37233972549438</t>
+    <t xml:space="preserve">1.3723396062851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886802196503</t>
+    <t xml:space="preserve">1.33886790275574</t>
   </si>
   <si>
     <t xml:space="preserve">1.30288600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32547926902771</t>
+    <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
     <t xml:space="preserve">1.32213222980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439356803894</t>
+    <t xml:space="preserve">1.26439344882965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702842235565</t>
+    <t xml:space="preserve">1.29702818393707</t>
   </si>
   <si>
     <t xml:space="preserve">1.30539631843567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397194862366</t>
+    <t xml:space="preserve">1.36397182941437</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3807076215744</t>
+    <t xml:space="preserve">1.38070774078369</t>
   </si>
   <si>
     <t xml:space="preserve">1.33050012588501</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506427764893</t>
+    <t xml:space="preserve">1.22506439685822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2049812078476</t>
+    <t xml:space="preserve">1.20498132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916533470154</t>
+    <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841131687164</t>
+    <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845303058624</t>
+    <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
     <t xml:space="preserve">1.23008501529694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824529647827</t>
+    <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
     <t xml:space="preserve">1.14473223686218</t>
@@ -257,34 +257,34 @@
     <t xml:space="preserve">1.22171700000763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816234588623</t>
+    <t xml:space="preserve">1.16816222667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.15226316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14222168922424</t>
+    <t xml:space="preserve">1.14222192764282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150938510895</t>
+    <t xml:space="preserve">1.17150950431824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966990470886</t>
+    <t xml:space="preserve">1.12967002391815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293399333954</t>
+    <t xml:space="preserve">1.11293411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04850101470947</t>
+    <t xml:space="preserve">1.04850113391876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343880176544</t>
+    <t xml:space="preserve">1.03343868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02423393726349</t>
+    <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0392963886261</t>
+    <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
     <t xml:space="preserve">1.05435848236084</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">1.06440007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07109427452087</t>
+    <t xml:space="preserve">1.07109451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03762257099152</t>
+    <t xml:space="preserve">1.0376228094101</t>
   </si>
   <si>
     <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067976474762</t>
+    <t xml:space="preserve">0.984068095684052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967277050018</t>
+    <t xml:space="preserve">0.999967098236084</t>
   </si>
   <si>
     <t xml:space="preserve">1.01251900196075</t>
@@ -317,25 +317,25 @@
     <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127439022064</t>
+    <t xml:space="preserve">0.958127319812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842612743378</t>
+    <t xml:space="preserve">0.969842672348022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738745689392</t>
+    <t xml:space="preserve">0.944738686084747</t>
   </si>
   <si>
     <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866080284118652</t>
+    <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269852161407</t>
+    <t xml:space="preserve">0.952269971370697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103891372681</t>
+    <t xml:space="preserve">0.912103831768036</t>
   </si>
   <si>
     <t xml:space="preserve">0.89955198764801</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.896204769611359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937811374664</t>
+    <t xml:space="preserve">0.871937870979309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756673336029</t>
+    <t xml:space="preserve">0.908756613731384</t>
   </si>
   <si>
     <t xml:space="preserve">0.950596392154694</t>
@@ -356,61 +356,61 @@
     <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471727848053</t>
+    <t xml:space="preserve">0.920471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.967332184314728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311267852783</t>
+    <t xml:space="preserve">0.962311327457428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519556999207</t>
+    <t xml:space="preserve">1.05519533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599023342133</t>
+    <t xml:space="preserve">0.991598963737488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088892936707</t>
+    <t xml:space="preserve">0.989088773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0016405582428</t>
+    <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
     <t xml:space="preserve">0.995783090591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762531757355</t>
+    <t xml:space="preserve">0.990762412548065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207579612732</t>
+    <t xml:space="preserve">0.937207639217377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394337654114</t>
+    <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391587257385</t>
+    <t xml:space="preserve">0.94139152765274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98825204372406</t>
+    <t xml:space="preserve">0.988251984119415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352802753448</t>
+    <t xml:space="preserve">0.972352862358093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96816885471344</t>
+    <t xml:space="preserve">0.968168973922729</t>
   </si>
   <si>
     <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231246471405</t>
+    <t xml:space="preserve">0.98323118686676</t>
   </si>
   <si>
     <t xml:space="preserve">0.987415194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005823135376</t>
+    <t xml:space="preserve">0.969005584716797</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109392166138</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">1.10456621646881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636434078217</t>
+    <t xml:space="preserve">1.13636422157288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14807939529419</t>
+    <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
     <t xml:space="preserve">1.19577658176422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661343097687</t>
+    <t xml:space="preserve">1.19661331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602555274963</t>
+    <t xml:space="preserve">1.25602567195892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20581817626953</t>
+    <t xml:space="preserve">1.20581805706024</t>
   </si>
   <si>
     <t xml:space="preserve">1.2133492231369</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15310001373291</t>
+    <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242930412292</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">1.14640581607819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19159245491028</t>
+    <t xml:space="preserve">1.19159269332886</t>
   </si>
   <si>
     <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23761606216431</t>
+    <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518870353699</t>
+    <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
     <t xml:space="preserve">1.23594260215759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146802902222</t>
+    <t xml:space="preserve">1.16146814823151</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385391235352</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130200862885</t>
+    <t xml:space="preserve">1.12130212783813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653036117554</t>
+    <t xml:space="preserve">1.17653024196625</t>
   </si>
   <si>
     <t xml:space="preserve">1.40581142902374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576995372772</t>
+    <t xml:space="preserve">1.39576983451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911711215973</t>
+    <t xml:space="preserve">1.39911699295044</t>
   </si>
   <si>
     <t xml:space="preserve">1.39744341373444</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">1.49534809589386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685577392578</t>
+    <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865413665771</t>
+    <t xml:space="preserve">1.48865389823914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48949062824249</t>
+    <t xml:space="preserve">1.48949074745178</t>
   </si>
   <si>
     <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551423549652</t>
+    <t xml:space="preserve">1.53551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57316994667053</t>
+    <t xml:space="preserve">1.57316982746124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5857218503952</t>
+    <t xml:space="preserve">1.58572173118591</t>
   </si>
   <si>
     <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
     <t xml:space="preserve">1.66438031196594</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65099155902863</t>
+    <t xml:space="preserve">1.65099167823792</t>
   </si>
   <si>
     <t xml:space="preserve">1.60078406333923</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">1.67358505725861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003016471863</t>
+    <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
     <t xml:space="preserve">1.68697369098663</t>
@@ -590,16 +590,16 @@
     <t xml:space="preserve">1.6066415309906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195283412933</t>
+    <t xml:space="preserve">1.68195307254791</t>
   </si>
   <si>
     <t xml:space="preserve">1.68362665176392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542453765869</t>
+    <t xml:space="preserve">1.71542465686798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718118667603</t>
+    <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
     <t xml:space="preserve">1.75224363803864</t>
@@ -611,73 +611,73 @@
     <t xml:space="preserve">1.723792552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601253509521</t>
+    <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220204353333</t>
+    <t xml:space="preserve">1.74220216274261</t>
   </si>
   <si>
     <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337317943573</t>
+    <t xml:space="preserve">1.84337329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80050373077393</t>
+    <t xml:space="preserve">1.8005039691925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335630893707</t>
+    <t xml:space="preserve">1.78335618972778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193007946014</t>
+    <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95483303070068</t>
+    <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323570251465</t>
+    <t xml:space="preserve">2.37323594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926259994507</t>
+    <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
     <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936334609985</t>
+    <t xml:space="preserve">2.82936358451843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505163192749</t>
+    <t xml:space="preserve">2.73505139350891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64416885375977</t>
+    <t xml:space="preserve">2.64416909217834</t>
   </si>
   <si>
     <t xml:space="preserve">2.47783660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.460688829422</t>
+    <t xml:space="preserve">2.46068859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067172050476</t>
+    <t xml:space="preserve">2.40067219734192</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929657936096</t>
+    <t xml:space="preserve">2.5892961025238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7864944934845</t>
+    <t xml:space="preserve">2.78649425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503452301025</t>
+    <t xml:space="preserve">2.67503476142883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012826919556</t>
+    <t xml:space="preserve">2.50012850761414</t>
   </si>
   <si>
     <t xml:space="preserve">2.4624035358429</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953468322754</t>
+    <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211482048035</t>
+    <t xml:space="preserve">2.45211505889893</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641037940979</t>
+    <t xml:space="preserve">2.48641061782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4555447101593</t>
+    <t xml:space="preserve">2.45554447174072</t>
   </si>
   <si>
     <t xml:space="preserve">2.4572594165802</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56186008453369</t>
+    <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781973838806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38180994987488</t>
+    <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639327049255</t>
+    <t xml:space="preserve">2.42639350891113</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208155632019</t>
+    <t xml:space="preserve">2.33208131790161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836342811584</t>
+    <t xml:space="preserve">2.31836366653442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28063869476318</t>
+    <t xml:space="preserve">2.2806384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865214347839</t>
+    <t xml:space="preserve">2.32865190505981</t>
   </si>
   <si>
     <t xml:space="preserve">2.31321907043457</t>
@@ -755,43 +755,43 @@
     <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12630939483643</t>
+    <t xml:space="preserve">2.126309633255</t>
   </si>
   <si>
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800746917725</t>
+    <t xml:space="preserve">2.06800723075867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0577187538147</t>
+    <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773562431335</t>
+    <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12802410125732</t>
+    <t xml:space="preserve">2.1280243396759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515501022339</t>
+    <t xml:space="preserve">2.08515548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629300117493</t>
+    <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
     <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887313842773</t>
+    <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
     <t xml:space="preserve">2.00799059867859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05085968971252</t>
+    <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
     <t xml:space="preserve">2.02342367172241</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401725769043</t>
+    <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15889024734497</t>
+    <t xml:space="preserve">2.15888977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14345717430115</t>
+    <t xml:space="preserve">2.14345741271973</t>
   </si>
   <si>
     <t xml:space="preserve">2.12287998199463</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.1537458896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1520311832428</t>
+    <t xml:space="preserve">2.15203094482422</t>
   </si>
   <si>
     <t xml:space="preserve">2.16917872428894</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491714477539</t>
+    <t xml:space="preserve">2.25491690635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.28235340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23776936531067</t>
+    <t xml:space="preserve">2.23776912689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.22233653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.170893907547</t>
+    <t xml:space="preserve">2.17089366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975567817688</t>
+    <t xml:space="preserve">2.18975591659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.22919535636902</t>
@@ -857,97 +857,97 @@
     <t xml:space="preserve">2.24634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065532684326</t>
+    <t xml:space="preserve">2.34065556526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27034974098206</t>
+    <t xml:space="preserve">2.27034950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206468582153</t>
+    <t xml:space="preserve">2.27206492424011</t>
   </si>
   <si>
     <t xml:space="preserve">2.20175933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20861840248108</t>
+    <t xml:space="preserve">2.2086181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28749775886536</t>
+    <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
     <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462866783142</t>
+    <t xml:space="preserve">2.24462819099426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4366819858551</t>
+    <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471254348755</t>
+    <t xml:space="preserve">2.54471230506897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384663581848</t>
+    <t xml:space="preserve">2.5138463973999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50355815887451</t>
+    <t xml:space="preserve">2.50355792045593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5550012588501</t>
+    <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326920509338</t>
+    <t xml:space="preserve">2.49326944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47269225120544</t>
+    <t xml:space="preserve">2.47269248962402</t>
   </si>
   <si>
     <t xml:space="preserve">2.32007813453674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32179260253906</t>
+    <t xml:space="preserve">2.32179284095764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809182167053</t>
+    <t xml:space="preserve">2.36809158325195</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379626274109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439008712769</t>
+    <t xml:space="preserve">2.41439032554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922885894775</t>
+    <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3578028678894</t>
+    <t xml:space="preserve">2.35780262947083</t>
   </si>
   <si>
     <t xml:space="preserve">2.40410137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39038324356079</t>
+    <t xml:space="preserve">2.39038348197937</t>
   </si>
   <si>
     <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3063600063324</t>
+    <t xml:space="preserve">2.30635976791382</t>
   </si>
   <si>
     <t xml:space="preserve">2.38866853713989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31493377685547</t>
+    <t xml:space="preserve">2.31493401527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832992553711</t>
+    <t xml:space="preserve">2.19832944869995</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
@@ -956,61 +956,61 @@
     <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632650375366</t>
+    <t xml:space="preserve">2.1863260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10058784484863</t>
+    <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
     <t xml:space="preserve">2.09201431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04057145118713</t>
+    <t xml:space="preserve">2.04057121276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914498329163</t>
+    <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90339016914368</t>
+    <t xml:space="preserve">1.9033899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805543422699</t>
+    <t xml:space="preserve">1.98055446147919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198045253754</t>
+    <t xml:space="preserve">1.97198057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053759098053</t>
+    <t xml:space="preserve">1.92053771018982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912823200226</t>
+    <t xml:space="preserve">1.98912811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196382045746</t>
+    <t xml:space="preserve">1.91196393966675</t>
   </si>
   <si>
     <t xml:space="preserve">1.92911148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624215126038</t>
+    <t xml:space="preserve">1.88624238967896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481627941132</t>
+    <t xml:space="preserve">1.89481604099274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909472942352</t>
+    <t xml:space="preserve">1.86909461021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194718837738</t>
+    <t xml:space="preserve">1.85194706916809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625914096832</t>
+    <t xml:space="preserve">1.94625926017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340668201447</t>
+    <t xml:space="preserve">1.96340656280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.06879186630249</t>
@@ -67323,6 +67323,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.3333333333</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>575</v>
+      </c>
+      <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.682662037</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>40800</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>575</v>
+      </c>
+      <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.43781757354736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684310913086</t>
+    <t xml:space="preserve">1.48684322834015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424700737</t>
+    <t xml:space="preserve">1.44424724578857</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">1.37593269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414041996002</t>
+    <t xml:space="preserve">1.33414030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744762420654</t>
+    <t xml:space="preserve">1.35744750499725</t>
   </si>
   <si>
     <t xml:space="preserve">1.36628842353821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290271282196</t>
+    <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
     <t xml:space="preserve">1.3815586566925</t>
@@ -83,58 +83,58 @@
     <t xml:space="preserve">1.44585454463959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3984363079071</t>
+    <t xml:space="preserve">1.39843606948853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780323505402</t>
+    <t xml:space="preserve">1.34780335426331</t>
   </si>
   <si>
     <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002950668335</t>
+    <t xml:space="preserve">1.31002938747406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217727184296</t>
+    <t xml:space="preserve">1.34217739105225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021424293518</t>
+    <t xml:space="preserve">1.35021448135376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128131389618</t>
+    <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557696342468</t>
+    <t xml:space="preserve">1.38557708263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273231506348</t>
+    <t xml:space="preserve">1.46273219585419</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693571567535</t>
+    <t xml:space="preserve">1.50693559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889862537384</t>
+    <t xml:space="preserve">1.49889874458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47237658500671</t>
+    <t xml:space="preserve">1.47237646579742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49487996101379</t>
+    <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
     <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543488502502</t>
+    <t xml:space="preserve">1.6154351234436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169392108917</t>
+    <t xml:space="preserve">1.67169380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490887641907</t>
+    <t xml:space="preserve">1.67490875720978</t>
   </si>
   <si>
     <t xml:space="preserve">1.64597570896149</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862116336823</t>
+    <t xml:space="preserve">1.43862128257751</t>
   </si>
   <si>
     <t xml:space="preserve">1.4120991230011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601892471313</t>
+    <t xml:space="preserve">1.45601880550385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426239490509</t>
+    <t xml:space="preserve">1.43426251411438</t>
   </si>
   <si>
     <t xml:space="preserve">1.40832185745239</t>
@@ -173,40 +173,40 @@
     <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840480804443</t>
+    <t xml:space="preserve">1.42840492725372</t>
   </si>
   <si>
     <t xml:space="preserve">1.41334247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497469902039</t>
+    <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313486099243</t>
+    <t xml:space="preserve">1.36313509941101</t>
   </si>
   <si>
     <t xml:space="preserve">1.35560381412506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37233984470367</t>
+    <t xml:space="preserve">1.37233972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886802196503</t>
+    <t xml:space="preserve">1.33886814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288600921631</t>
+    <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
     <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3221321105957</t>
+    <t xml:space="preserve">1.32213222980499</t>
   </si>
   <si>
     <t xml:space="preserve">1.26439344882965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702842235565</t>
+    <t xml:space="preserve">1.29702830314636</t>
   </si>
   <si>
     <t xml:space="preserve">1.30539619922638</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">1.36397182941437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41250574588776</t>
+    <t xml:space="preserve">1.41250586509705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3807076215744</t>
+    <t xml:space="preserve">1.38070750236511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050012588501</t>
+    <t xml:space="preserve">1.3305002450943</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">1.22506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20498144626617</t>
+    <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916533470154</t>
+    <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841131687164</t>
+    <t xml:space="preserve">1.22841155529022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845303058624</t>
+    <t xml:space="preserve">1.23845279216766</t>
   </si>
   <si>
     <t xml:space="preserve">1.23008501529694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824541568756</t>
+    <t xml:space="preserve">1.18824553489685</t>
   </si>
   <si>
     <t xml:space="preserve">1.14473223686218</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.22171711921692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816222667694</t>
+    <t xml:space="preserve">1.16816246509552</t>
   </si>
   <si>
     <t xml:space="preserve">1.15226328372955</t>
@@ -269,28 +269,28 @@
     <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966978549957</t>
+    <t xml:space="preserve">1.12967002391815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293399333954</t>
+    <t xml:space="preserve">1.11293411254883</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343868255615</t>
+    <t xml:space="preserve">1.03343880176544</t>
   </si>
   <si>
     <t xml:space="preserve">1.02423393726349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0392963886261</t>
+    <t xml:space="preserve">1.03929650783539</t>
   </si>
   <si>
     <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364629745483</t>
+    <t xml:space="preserve">1.08364605903625</t>
   </si>
   <si>
     <t xml:space="preserve">1.06440007686615</t>
@@ -299,64 +299,64 @@
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03762269020081</t>
+    <t xml:space="preserve">1.0376228094101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00833511352539</t>
+    <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
     <t xml:space="preserve">0.984067976474762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999966979026794</t>
+    <t xml:space="preserve">0.999967098236084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251924037933</t>
+    <t xml:space="preserve">1.01251888275146</t>
   </si>
   <si>
     <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127319812775</t>
+    <t xml:space="preserve">0.958127498626709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842433929443</t>
+    <t xml:space="preserve">0.969842493534088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738566875458</t>
+    <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673782348633</t>
+    <t xml:space="preserve">0.888673603534698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866080284118652</t>
+    <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269852161407</t>
+    <t xml:space="preserve">0.952269911766052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103831768036</t>
+    <t xml:space="preserve">0.912103891372681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899552047252655</t>
+    <t xml:space="preserve">0.899551928043365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204769611359</t>
+    <t xml:space="preserve">0.896204888820648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937870979309</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756613731384</t>
+    <t xml:space="preserve">0.908756673336029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596272945404</t>
+    <t xml:space="preserve">0.950596332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124569416046</t>
+    <t xml:space="preserve">0.917124509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471787452698</t>
+    <t xml:space="preserve">0.920471847057343</t>
   </si>
   <si>
     <t xml:space="preserve">0.967332065105438</t>
@@ -365,52 +365,52 @@
     <t xml:space="preserve">0.962311387062073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519545078278</t>
+    <t xml:space="preserve">1.05519533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599023342133</t>
+    <t xml:space="preserve">0.991598963737488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088654518127</t>
+    <t xml:space="preserve">0.989088773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0016405582428</t>
+    <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
     <t xml:space="preserve">0.995783090591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762293338776</t>
+    <t xml:space="preserve">0.990762412548065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207579612732</t>
+    <t xml:space="preserve">0.937207520008087</t>
   </si>
   <si>
     <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391468048096</t>
+    <t xml:space="preserve">0.94139152765274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251805305481</t>
+    <t xml:space="preserve">0.988251984119415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352802753448</t>
+    <t xml:space="preserve">0.972352981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168795108795</t>
+    <t xml:space="preserve">0.968168973922729</t>
   </si>
   <si>
     <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231127262115</t>
+    <t xml:space="preserve">0.98323118686676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415075302124</t>
+    <t xml:space="preserve">0.987415194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005644321442</t>
+    <t xml:space="preserve">0.969005823135376</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109392166138</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">0.953943490982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854260921478</t>
+    <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
     <t xml:space="preserve">1.05937933921814</t>
@@ -431,22 +431,22 @@
     <t xml:space="preserve">1.05268502235413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10456621646881</t>
+    <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636422157288</t>
+    <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14807939529419</t>
+    <t xml:space="preserve">1.14807915687561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577658176422</t>
+    <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661343097687</t>
+    <t xml:space="preserve">1.19661331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602579116821</t>
+    <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
     <t xml:space="preserve">1.20581805706024</t>
@@ -455,79 +455,79 @@
     <t xml:space="preserve">1.21334910392761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753311157227</t>
+    <t xml:space="preserve">1.21753323078156</t>
   </si>
   <si>
     <t xml:space="preserve">1.15644717216492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15310001373291</t>
+    <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493985176086</t>
+    <t xml:space="preserve">1.19493973255157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1547737121582</t>
+    <t xml:space="preserve">1.15477359294891</t>
   </si>
   <si>
     <t xml:space="preserve">1.1464056968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19159269332886</t>
+    <t xml:space="preserve">1.19159245491028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314172744751</t>
+    <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
     <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518882274628</t>
+    <t xml:space="preserve">1.25518894195557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23594260215759</t>
+    <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146814823151</t>
+    <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803768157959</t>
+    <t xml:space="preserve">1.13803780078888</t>
   </si>
   <si>
     <t xml:space="preserve">1.12799632549286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130188941956</t>
+    <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.17653024196625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581142902374</t>
+    <t xml:space="preserve">1.40581154823303</t>
   </si>
   <si>
     <t xml:space="preserve">1.39576995372772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911723136902</t>
+    <t xml:space="preserve">1.39911711215973</t>
   </si>
   <si>
     <t xml:space="preserve">1.39744353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4602028131485</t>
+    <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
     <t xml:space="preserve">1.49534821510315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685565471649</t>
+    <t xml:space="preserve">1.45685577392578</t>
   </si>
   <si>
     <t xml:space="preserve">1.48865389823914</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275483608246</t>
+    <t xml:space="preserve">1.47275495529175</t>
   </si>
   <si>
     <t xml:space="preserve">1.53551423549652</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174545764923</t>
+    <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684914588928</t>
+    <t xml:space="preserve">1.65684902667999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438031196594</t>
+    <t xml:space="preserve">1.66438043117523</t>
   </si>
   <si>
     <t xml:space="preserve">1.73550760746002</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">1.75726425647736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77400004863739</t>
+    <t xml:space="preserve">1.77400016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78236830234528</t>
+    <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
@@ -578,25 +578,25 @@
     <t xml:space="preserve">1.67358493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003040313721</t>
+    <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697369098663</t>
+    <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61668312549591</t>
+    <t xml:space="preserve">1.6166832447052</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664165019989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195295333862</t>
+    <t xml:space="preserve">1.68195307254791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362677097321</t>
+    <t xml:space="preserve">1.68362653255463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7154244184494</t>
+    <t xml:space="preserve">1.71542477607727</t>
   </si>
   <si>
     <t xml:space="preserve">1.73718130588531</t>
@@ -608,31 +608,31 @@
     <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.723792552948</t>
+    <t xml:space="preserve">1.72379243373871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601241588593</t>
+    <t xml:space="preserve">1.65601253509521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220192432404</t>
+    <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74906086921692</t>
+    <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337341785431</t>
+    <t xml:space="preserve">1.84337317943573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8005039691925</t>
+    <t xml:space="preserve">1.80050408840179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335642814636</t>
+    <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548327922821</t>
+    <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
     <t xml:space="preserve">2.37323570251465</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421946525574</t>
+    <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936358451843</t>
+    <t xml:space="preserve">2.82936310768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505139350891</t>
+    <t xml:space="preserve">2.73505163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64416885375977</t>
+    <t xml:space="preserve">2.64416909217834</t>
   </si>
   <si>
     <t xml:space="preserve">2.47783660888672</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067195892334</t>
+    <t xml:space="preserve">2.40067219734192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.364661693573</t>
+    <t xml:space="preserve">2.36466193199158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.58929634094238</t>
@@ -677,22 +677,22 @@
     <t xml:space="preserve">2.67503428459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012850761414</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46240377426147</t>
+    <t xml:space="preserve">2.4624035358429</t>
   </si>
   <si>
     <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354128837585</t>
+    <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953468322754</t>
+    <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
@@ -710,16 +710,16 @@
     <t xml:space="preserve">2.45554447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4572594165802</t>
+    <t xml:space="preserve">2.45725917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613877296448</t>
+    <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897436141968</t>
+    <t xml:space="preserve">2.4589741230011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440719604492</t>
+    <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
     <t xml:space="preserve">2.56186008453369</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639350891113</t>
+    <t xml:space="preserve">2.42639374732971</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">2.2806384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865190505981</t>
+    <t xml:space="preserve">2.32865214347839</t>
   </si>
   <si>
     <t xml:space="preserve">2.31321907043457</t>
@@ -755,31 +755,31 @@
     <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.126309633255</t>
+    <t xml:space="preserve">2.12630939483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800770759583</t>
+    <t xml:space="preserve">2.06800723075867</t>
   </si>
   <si>
     <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09544372558594</t>
+    <t xml:space="preserve">2.09544396400452</t>
   </si>
   <si>
     <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1280243396759</t>
+    <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515524864197</t>
+    <t xml:space="preserve">2.08515548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629300117493</t>
+    <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
     <t xml:space="preserve">2.08344054222107</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799059867859</t>
+    <t xml:space="preserve">2.00799083709717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05085968971252</t>
+    <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
     <t xml:space="preserve">2.02342343330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20690321922302</t>
+    <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
     <t xml:space="preserve">2.17603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172559738159</t>
+    <t xml:space="preserve">2.08172535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401773452759</t>
+    <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15889024734497</t>
+    <t xml:space="preserve">2.15889000892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
@@ -818,31 +818,31 @@
     <t xml:space="preserve">2.12287998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1537458896637</t>
+    <t xml:space="preserve">2.15374565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1520311832428</t>
+    <t xml:space="preserve">2.15203094482422</t>
   </si>
   <si>
     <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27720880508423</t>
+    <t xml:space="preserve">2.27720856666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491714477539</t>
+    <t xml:space="preserve">2.25491690635681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2823531627655</t>
+    <t xml:space="preserve">2.28235340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23776936531067</t>
+    <t xml:space="preserve">2.23776912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233653068542</t>
+    <t xml:space="preserve">2.22233629226685</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089366912842</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634289741516</t>
+    <t xml:space="preserve">2.24634337425232</t>
   </si>
   <si>
     <t xml:space="preserve">2.34065532684326</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">2.25320219993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27034950256348</t>
+    <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
     <t xml:space="preserve">2.27206468582153</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">2.2086181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28749775886536</t>
+    <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20347380638123</t>
+    <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462842941284</t>
+    <t xml:space="preserve">2.24462819099426</t>
   </si>
   <si>
     <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384687423706</t>
+    <t xml:space="preserve">2.5138463973999</t>
   </si>
   <si>
     <t xml:space="preserve">2.50355815887451</t>
@@ -914,28 +914,28 @@
     <t xml:space="preserve">2.32179284095764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809158325195</t>
+    <t xml:space="preserve">2.36809182167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379602432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439008712769</t>
+    <t xml:space="preserve">2.41439032554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922885894775</t>
+    <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410137176514</t>
+    <t xml:space="preserve">2.40410161018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39038324356079</t>
+    <t xml:space="preserve">2.39038372039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33551073074341</t>
+    <t xml:space="preserve">2.33551096916199</t>
   </si>
   <si>
     <t xml:space="preserve">2.3063600063324</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">2.38866853713989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31493377685547</t>
+    <t xml:space="preserve">2.31493401527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832992553711</t>
+    <t xml:space="preserve">2.19832944869995</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632650375366</t>
+    <t xml:space="preserve">2.1863260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10058808326721</t>
+    <t xml:space="preserve">2.10058784484863</t>
   </si>
   <si>
     <t xml:space="preserve">2.09201455116272</t>
@@ -971,82 +971,82 @@
     <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914474487305</t>
+    <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90338981151581</t>
+    <t xml:space="preserve">1.90339004993439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805543422699</t>
+    <t xml:space="preserve">1.98055469989777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198069095612</t>
+    <t xml:space="preserve">1.97198057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053771018982</t>
+    <t xml:space="preserve">1.92053747177124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912823200226</t>
+    <t xml:space="preserve">1.98912811279297</t>
   </si>
   <si>
     <t xml:space="preserve">1.91196382045746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9291113615036</t>
+    <t xml:space="preserve">1.92911159992218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624250888824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481616020203</t>
+    <t xml:space="preserve">1.89481627941132</t>
   </si>
   <si>
     <t xml:space="preserve">1.86909461021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194706916809</t>
+    <t xml:space="preserve">1.85194718837738</t>
   </si>
   <si>
     <t xml:space="preserve">1.94625914096832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340668201447</t>
+    <t xml:space="preserve">1.96340680122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879186630249</t>
+    <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249334335327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236502170563</t>
+    <t xml:space="preserve">1.97236514091492</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100251674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840594768524</t>
+    <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470447063446</t>
+    <t xml:space="preserve">1.88470435142517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02496147155762</t>
+    <t xml:space="preserve">2.0249617099762</t>
   </si>
   <si>
     <t xml:space="preserve">1.99866318702698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606673717499</t>
+    <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853474617004</t>
+    <t xml:space="preserve">1.92853486537933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717247962952</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223670005798</t>
+    <t xml:space="preserve">1.90223658084869</t>
   </si>
   <si>
     <t xml:space="preserve">1.87593829631805</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">1.82334184646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976881027222</t>
+    <t xml:space="preserve">1.91976869106293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8496401309967</t>
+    <t xml:space="preserve">1.84963989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.89347064495087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730080127716</t>
+    <t xml:space="preserve">1.93730092048645</t>
   </si>
   <si>
     <t xml:space="preserve">1.98989713191986</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">1.77074551582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704356193542</t>
+    <t xml:space="preserve">1.79704368114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733949184418</t>
+    <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
     <t xml:space="preserve">1.59542417526245</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419023036957</t>
+    <t xml:space="preserve">1.60419034957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104132652283</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993570327759</t>
+    <t xml:space="preserve">1.66993582248688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048839569092</t>
+    <t xml:space="preserve">1.63048851490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
@@ -1139,28 +1139,28 @@
     <t xml:space="preserve">1.70061707496643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64363753795624</t>
+    <t xml:space="preserve">1.64363765716553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295628547668</t>
+    <t xml:space="preserve">1.61295640468597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58227503299713</t>
+    <t xml:space="preserve">1.58227491378784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925457000732</t>
+    <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58665800094604</t>
+    <t xml:space="preserve">1.58665812015533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597698688507</t>
+    <t xml:space="preserve">1.55597686767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42010271549225</t>
+    <t xml:space="preserve">1.42010283470154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42448592185974</t>
+    <t xml:space="preserve">1.42448580265045</t>
   </si>
   <si>
     <t xml:space="preserve">1.32367610931396</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">1.29737794399261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24478149414062</t>
+    <t xml:space="preserve">1.24478161334991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20971727371216</t>
+    <t xml:space="preserve">1.20971715450287</t>
   </si>
   <si>
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065576553345</t>
+    <t xml:space="preserve">1.38065552711487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41571974754333</t>
+    <t xml:space="preserve">1.41571986675262</t>
   </si>
   <si>
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325197696686</t>
+    <t xml:space="preserve">1.43325185775757</t>
   </si>
   <si>
     <t xml:space="preserve">1.38942158222198</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44640111923218</t>
+    <t xml:space="preserve">1.4464008808136</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4507839679718</t>
+    <t xml:space="preserve">1.45078408718109</t>
   </si>
   <si>
     <t xml:space="preserve">1.39380466938019</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36750638484955</t>
+    <t xml:space="preserve">1.36750626564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406167030334</t>
+    <t xml:space="preserve">1.53406178951263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214647293091</t>
+    <t xml:space="preserve">1.5121465921402</t>
   </si>
   <si>
     <t xml:space="preserve">1.52967870235443</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">1.56035983562469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091252803802</t>
+    <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584842681885</t>
+    <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5165296792984</t>
+    <t xml:space="preserve">1.51652956008911</t>
   </si>
   <si>
     <t xml:space="preserve">1.5691260099411</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529561519623</t>
+    <t xml:space="preserve">1.52529549598694</t>
   </si>
   <si>
     <t xml:space="preserve">1.49899744987488</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232108592987</t>
+    <t xml:space="preserve">1.54232120513916</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46114611625671</t>
+    <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
     <t xml:space="preserve">1.50624334812164</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310748577118</t>
+    <t xml:space="preserve">1.44310736656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604912281036</t>
+    <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
     <t xml:space="preserve">1.39801025390625</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35291314125061</t>
+    <t xml:space="preserve">1.3529132604599</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">1.3438937664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31683564186096</t>
+    <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
     <t xml:space="preserve">1.26271903514862</t>
@@ -1334,16 +1334,16 @@
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056367874146</t>
+    <t xml:space="preserve">1.19056355953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664129734039</t>
+    <t xml:space="preserve">1.22664141654968</t>
   </si>
   <si>
     <t xml:space="preserve">1.21762180328369</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
     <t xml:space="preserve">1.36193263530731</t>
@@ -1370,25 +1370,25 @@
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566067218781</t>
+    <t xml:space="preserve">1.23566079139709</t>
   </si>
   <si>
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055406093597</t>
+    <t xml:space="preserve">1.65055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153468608856</t>
+    <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251519203186</t>
+    <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59643757343292</t>
+    <t xml:space="preserve">1.59643745422363</t>
   </si>
   <si>
     <t xml:space="preserve">1.79486489295959</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.70467066764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72270941734314</t>
+    <t xml:space="preserve">1.72270953655243</t>
   </si>
   <si>
     <t xml:space="preserve">1.71369004249573</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840832233429</t>
+    <t xml:space="preserve">1.118408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350531578064</t>
+    <t xml:space="preserve">1.16350543498993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15448582172394</t>
+    <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1274276971817</t>
+    <t xml:space="preserve">1.12742757797241</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25369966030121</t>
+    <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10036945343018</t>
+    <t xml:space="preserve">1.10036933422089</t>
   </si>
   <si>
     <t xml:space="preserve">1.10938882827759</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233058452606</t>
+    <t xml:space="preserve">1.08233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1460,43 +1460,43 @@
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331120967865</t>
+    <t xml:space="preserve">1.07331132888794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527234077454</t>
+    <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03723347187042</t>
+    <t xml:space="preserve">1.03723335266113</t>
   </si>
   <si>
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097490310669</t>
+    <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078055858612</t>
+    <t xml:space="preserve">0.965078175067902</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019812107086</t>
+    <t xml:space="preserve">0.938019752502441</t>
   </si>
   <si>
     <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947039127349854</t>
+    <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
     <t xml:space="preserve">0.897432446479797</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983116924762726</t>
+    <t xml:space="preserve">0.983117043972015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0191947221756</t>
+    <t xml:space="preserve">1.01919460296631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95605856180191</t>
+    <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
     <t xml:space="preserve">1.20860242843628</t>
@@ -67406,7 +67406,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.5291782407</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>2000</v>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781745433807</t>
+    <t xml:space="preserve">1.43781757354736</t>
   </si>
   <si>
     <t xml:space="preserve">1.48684322834015</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236224651337</t>
+    <t xml:space="preserve">1.38236248493195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593269348145</t>
+    <t xml:space="preserve">1.37593281269073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414053916931</t>
+    <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744750499725</t>
+    <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628842353821</t>
+    <t xml:space="preserve">1.36628818511963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290271282196</t>
+    <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3815586566925</t>
+    <t xml:space="preserve">1.38155853748322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647327899933</t>
+    <t xml:space="preserve">1.40647339820862</t>
   </si>
   <si>
     <t xml:space="preserve">1.44585454463959</t>
@@ -86,13 +86,13 @@
     <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780323505402</t>
+    <t xml:space="preserve">1.34780335426331</t>
   </si>
   <si>
     <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002926826477</t>
+    <t xml:space="preserve">1.31002950668335</t>
   </si>
   <si>
     <t xml:space="preserve">1.34217739105225</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.35021424293518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128131389618</t>
+    <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
     <t xml:space="preserve">1.38557708263397</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">1.46273219585419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43058431148529</t>
+    <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693571567535</t>
+    <t xml:space="preserve">1.50693559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889874458313</t>
+    <t xml:space="preserve">1.49889862537384</t>
   </si>
   <si>
     <t xml:space="preserve">1.47237658500671</t>
@@ -128,43 +128,43 @@
     <t xml:space="preserve">1.55274665355682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6154351234436</t>
+    <t xml:space="preserve">1.61543476581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169404029846</t>
+    <t xml:space="preserve">1.67169392108917</t>
   </si>
   <si>
     <t xml:space="preserve">1.67490887641907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6459755897522</t>
+    <t xml:space="preserve">1.64597547054291</t>
   </si>
   <si>
     <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702808380127</t>
+    <t xml:space="preserve">1.52702820301056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095402240753</t>
+    <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630264282227</t>
+    <t xml:space="preserve">1.45630276203156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862128257751</t>
+    <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41209924221039</t>
+    <t xml:space="preserve">1.41209900379181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601904392242</t>
+    <t xml:space="preserve">1.45601892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426239490509</t>
+    <t xml:space="preserve">1.4342622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832185745239</t>
+    <t xml:space="preserve">1.40832161903381</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840492725372</t>
+    <t xml:space="preserve">1.42840468883514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41334247589111</t>
+    <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497469902039</t>
+    <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313498020172</t>
+    <t xml:space="preserve">1.36313486099243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560381412506</t>
+    <t xml:space="preserve">1.35560393333435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3723396062851</t>
+    <t xml:space="preserve">1.37233972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886790275574</t>
+    <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
     <t xml:space="preserve">1.30288600921631</t>
@@ -200,43 +200,43 @@
     <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213222980499</t>
+    <t xml:space="preserve">1.32213199138641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439356803894</t>
+    <t xml:space="preserve">1.26439344882965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702830314636</t>
+    <t xml:space="preserve">1.29702818393707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539631843567</t>
+    <t xml:space="preserve">1.30539643764496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397171020508</t>
+    <t xml:space="preserve">1.36397194862366</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38070774078369</t>
+    <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050000667572</t>
+    <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2719247341156</t>
+    <t xml:space="preserve">1.27192461490631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267827510834</t>
+    <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506439685822</t>
+    <t xml:space="preserve">1.22506415843964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2049812078476</t>
+    <t xml:space="preserve">1.20498132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916521549225</t>
+    <t xml:space="preserve">1.20916509628296</t>
   </si>
   <si>
     <t xml:space="preserve">1.22841155529022</t>
@@ -251,22 +251,22 @@
     <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14473223686218</t>
+    <t xml:space="preserve">1.1447319984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171711921692</t>
+    <t xml:space="preserve">1.22171700000763</t>
   </si>
   <si>
     <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226316452026</t>
+    <t xml:space="preserve">1.15226328372955</t>
   </si>
   <si>
     <t xml:space="preserve">1.14222180843353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150962352753</t>
+    <t xml:space="preserve">1.17150950431824</t>
   </si>
   <si>
     <t xml:space="preserve">1.12966990470886</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">1.03343880176544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02423417568207</t>
+    <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
     <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435848236084</t>
+    <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364617824554</t>
+    <t xml:space="preserve">1.08364629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06440019607544</t>
+    <t xml:space="preserve">1.06440007686615</t>
   </si>
   <si>
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0376228094101</t>
+    <t xml:space="preserve">1.03762269020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0083349943161</t>
+    <t xml:space="preserve">1.00833523273468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984068036079407</t>
+    <t xml:space="preserve">0.984067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967038631439</t>
+    <t xml:space="preserve">0.999967098236084</t>
   </si>
   <si>
     <t xml:space="preserve">1.01251900196075</t>
@@ -317,121 +317,121 @@
     <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127439022064</t>
+    <t xml:space="preserve">0.958127319812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842612743378</t>
+    <t xml:space="preserve">0.969842553138733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738626480103</t>
+    <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673722743988</t>
+    <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866080224514008</t>
+    <t xml:space="preserve">0.866080284118652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269911766052</t>
+    <t xml:space="preserve">0.952269971370697</t>
   </si>
   <si>
     <t xml:space="preserve">0.912103831768036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89955198764801</t>
+    <t xml:space="preserve">0.899551928043365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204769611359</t>
+    <t xml:space="preserve">0.896204710006714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937930583954</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90875655412674</t>
+    <t xml:space="preserve">0.908756613731384</t>
   </si>
   <si>
     <t xml:space="preserve">0.950596392154694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471727848053</t>
+    <t xml:space="preserve">0.920471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332184314728</t>
+    <t xml:space="preserve">0.967332124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311446666718</t>
+    <t xml:space="preserve">0.962311267852783</t>
   </si>
   <si>
     <t xml:space="preserve">1.05519545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991598963737488</t>
+    <t xml:space="preserve">0.991599082946777</t>
   </si>
   <si>
     <t xml:space="preserve">0.989088773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00164079666138</t>
+    <t xml:space="preserve">1.0016405582428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783090591431</t>
+    <t xml:space="preserve">0.995783269405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99076235294342</t>
+    <t xml:space="preserve">0.990762293338776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207520008087</t>
+    <t xml:space="preserve">0.937207460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394337654114</t>
+    <t xml:space="preserve">0.982394397258759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391587257385</t>
+    <t xml:space="preserve">0.94139152765274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251924514771</t>
+    <t xml:space="preserve">0.988251984119415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352743148804</t>
+    <t xml:space="preserve">0.972352981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168795108795</t>
+    <t xml:space="preserve">0.968168914318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9757000207901</t>
+    <t xml:space="preserve">0.97570013999939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98323130607605</t>
+    <t xml:space="preserve">0.983231127262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415075302124</t>
+    <t xml:space="preserve">0.987415134906769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005644321442</t>
+    <t xml:space="preserve">0.969005763530731</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9539435505867</t>
+    <t xml:space="preserve">0.953943490982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0585423707962</t>
+    <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937945842743</t>
+    <t xml:space="preserve">1.05937933921814</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268490314484</t>
+    <t xml:space="preserve">1.05268502235413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10456621646881</t>
+    <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
     <t xml:space="preserve">1.13636422157288</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577658176422</t>
+    <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
     <t xml:space="preserve">1.19661319255829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602567195892</t>
+    <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
     <t xml:space="preserve">1.20581793785095</t>
@@ -455,43 +455,43 @@
     <t xml:space="preserve">1.21334910392761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753299236298</t>
+    <t xml:space="preserve">1.21753311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644717216492</t>
+    <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
     <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242918491364</t>
+    <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493973255157</t>
+    <t xml:space="preserve">1.19493961334229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1547737121582</t>
+    <t xml:space="preserve">1.15477383136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14640581607819</t>
+    <t xml:space="preserve">1.1464056968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19159269332886</t>
+    <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314160823822</t>
+    <t xml:space="preserve">1.16314148902893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2376161813736</t>
+    <t xml:space="preserve">1.23761606216431</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23594260215759</t>
+    <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146790981293</t>
+    <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385379314423</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130200862885</t>
+    <t xml:space="preserve">1.12130188941956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653024196625</t>
+    <t xml:space="preserve">1.17653036117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581130981445</t>
+    <t xml:space="preserve">1.40581142902374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576983451843</t>
+    <t xml:space="preserve">1.39576995372772</t>
   </si>
   <si>
     <t xml:space="preserve">1.39911699295044</t>
@@ -524,49 +524,49 @@
     <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534809589386</t>
+    <t xml:space="preserve">1.49534821510315</t>
   </si>
   <si>
     <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865389823914</t>
+    <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48949074745178</t>
+    <t xml:space="preserve">1.4894905090332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275471687317</t>
+    <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551435470581</t>
+    <t xml:space="preserve">1.53551423549652</t>
   </si>
   <si>
     <t xml:space="preserve">1.57316982746124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58572196960449</t>
+    <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174533843994</t>
+    <t xml:space="preserve">1.63174545764923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438019275665</t>
+    <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
     <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726413726807</t>
+    <t xml:space="preserve">1.75726401805878</t>
   </si>
   <si>
     <t xml:space="preserve">1.7739999294281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7823680639267</t>
+    <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67358481884003</t>
+    <t xml:space="preserve">1.67358505725861</t>
   </si>
   <si>
     <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697381019592</t>
+    <t xml:space="preserve">1.68697369098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.6166832447052</t>
@@ -590,37 +590,37 @@
     <t xml:space="preserve">1.6066415309906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195295333862</t>
+    <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362665176392</t>
+    <t xml:space="preserve">1.68362653255463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542477607727</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
     <t xml:space="preserve">1.73718118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224375724792</t>
+    <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
     <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.723792552948</t>
+    <t xml:space="preserve">1.72379267215729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601229667664</t>
+    <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220216274261</t>
+    <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74906098842621</t>
+    <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337341785431</t>
+    <t xml:space="preserve">1.84337306022644</t>
   </si>
   <si>
     <t xml:space="preserve">1.80050384998322</t>
@@ -629,22 +629,22 @@
     <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193019866943</t>
+    <t xml:space="preserve">1.79193007946014</t>
   </si>
   <si>
     <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323617935181</t>
+    <t xml:space="preserve">2.37323594093323</t>
   </si>
   <si>
     <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421922683716</t>
+    <t xml:space="preserve">2.82421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936334609985</t>
+    <t xml:space="preserve">2.82936358451843</t>
   </si>
   <si>
     <t xml:space="preserve">2.73505139350891</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">2.64416885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47783660888672</t>
+    <t xml:space="preserve">2.47783637046814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46068859100342</t>
+    <t xml:space="preserve">2.46068906784058</t>
   </si>
   <si>
     <t xml:space="preserve">2.40067195892334</t>
@@ -674,31 +674,31 @@
     <t xml:space="preserve">2.78649425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503452301025</t>
+    <t xml:space="preserve">2.67503476142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.50012850761414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4624035358429</t>
+    <t xml:space="preserve">2.46240377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097754478455</t>
+    <t xml:space="preserve">2.47097730636597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354104995728</t>
+    <t xml:space="preserve">2.44354128837585</t>
   </si>
   <si>
     <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214879989624</t>
+    <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
     <t xml:space="preserve">2.48641037940979</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">2.4555447101593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45725917816162</t>
+    <t xml:space="preserve">2.4572594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5361385345459</t>
+    <t xml:space="preserve">2.53613829612732</t>
   </si>
   <si>
     <t xml:space="preserve">2.4589741230011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440671920776</t>
+    <t xml:space="preserve">2.47440695762634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56185984611511</t>
+    <t xml:space="preserve">2.56186008453369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781973838806</t>
+    <t xml:space="preserve">2.41781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.38180994987488</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208155632019</t>
+    <t xml:space="preserve">2.33208131790161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836366653442</t>
+    <t xml:space="preserve">2.31836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">2.28063869476318</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.126309633255</t>
+    <t xml:space="preserve">2.12630939483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800723075867</t>
+    <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
     <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09544396400452</t>
+    <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773562431335</t>
+    <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
     <t xml:space="preserve">2.12802457809448</t>
@@ -785,52 +785,52 @@
     <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887361526489</t>
+    <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799059867859</t>
+    <t xml:space="preserve">2.00799036026001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0508599281311</t>
+    <t xml:space="preserve">2.05085968971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342343330383</t>
+    <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603802680969</t>
+    <t xml:space="preserve">2.17603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172559738159</t>
+    <t xml:space="preserve">2.08172535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401749610901</t>
+    <t xml:space="preserve">2.10401725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888977050781</t>
+    <t xml:space="preserve">2.15889000892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12287974357605</t>
+    <t xml:space="preserve">2.12288022041321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1537458896637</t>
+    <t xml:space="preserve">2.15374612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15203070640564</t>
+    <t xml:space="preserve">2.15203094482422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917848587036</t>
+    <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062134742737</t>
+    <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
     <t xml:space="preserve">2.25491714477539</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">2.2823531627655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23776912689209</t>
+    <t xml:space="preserve">2.23776960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233653068542</t>
+    <t xml:space="preserve">2.22233629226685</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975591659546</t>
+    <t xml:space="preserve">2.18975567817688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22919511795044</t>
+    <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634313583374</t>
+    <t xml:space="preserve">2.24634289741516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065556526184</t>
+    <t xml:space="preserve">2.34065532684326</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206492424011</t>
+    <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175933837891</t>
+    <t xml:space="preserve">2.20175957679749</t>
   </si>
   <si>
     <t xml:space="preserve">2.20861840248108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2874972820282</t>
+    <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
     <t xml:space="preserve">2.2034740447998</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">2.54471230506897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384687423706</t>
+    <t xml:space="preserve">2.51384663581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.50355792045593</t>
@@ -902,37 +902,37 @@
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326920509338</t>
+    <t xml:space="preserve">2.49326944351196</t>
   </si>
   <si>
     <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32007813453674</t>
+    <t xml:space="preserve">2.32007789611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809134483337</t>
+    <t xml:space="preserve">2.36809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33379602432251</t>
+    <t xml:space="preserve">2.33379626274109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439008712769</t>
+    <t xml:space="preserve">2.41439032554626</t>
   </si>
   <si>
     <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3578028678894</t>
+    <t xml:space="preserve">2.35780262947083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410161018372</t>
+    <t xml:space="preserve">2.40410137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39038372039795</t>
+    <t xml:space="preserve">2.39038348197937</t>
   </si>
   <si>
     <t xml:space="preserve">2.33551096916199</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">2.38866877555847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31493401527405</t>
+    <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832944869995</t>
+    <t xml:space="preserve">2.19832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201407432556</t>
+    <t xml:space="preserve">2.09201455116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.04057145118713</t>
@@ -974,85 +974,85 @@
     <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90338981151581</t>
+    <t xml:space="preserve">1.90339016914368</t>
   </si>
   <si>
     <t xml:space="preserve">1.98055458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198069095612</t>
+    <t xml:space="preserve">1.97198033332825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053759098053</t>
+    <t xml:space="preserve">1.92053735256195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912835121155</t>
+    <t xml:space="preserve">1.98912823200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196393966675</t>
+    <t xml:space="preserve">1.91196405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911148071289</t>
+    <t xml:space="preserve">1.9291113615036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624238967896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481592178345</t>
+    <t xml:space="preserve">1.89481627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909461021423</t>
+    <t xml:space="preserve">1.86909472942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194706916809</t>
+    <t xml:space="preserve">1.85194718837738</t>
   </si>
   <si>
     <t xml:space="preserve">1.94625902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340680122375</t>
+    <t xml:space="preserve">1.96340668201447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879162788391</t>
+    <t xml:space="preserve">2.06879186630249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249334335327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236526012421</t>
+    <t xml:space="preserve">1.97236514091492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100263595581</t>
+    <t xml:space="preserve">1.91100251674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840594768524</t>
+    <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470458984375</t>
+    <t xml:space="preserve">1.88470435142517</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866330623627</t>
+    <t xml:space="preserve">1.99866318702698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606673717499</t>
+    <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853474617004</t>
+    <t xml:space="preserve">1.92853462696075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717224121094</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223670005798</t>
+    <t xml:space="preserve">1.90223658084869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593841552734</t>
+    <t xml:space="preserve">1.87593853473663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334172725677</t>
+    <t xml:space="preserve">1.82334196567535</t>
   </si>
   <si>
     <t xml:space="preserve">1.91976881027222</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">1.84964001178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347052574158</t>
+    <t xml:space="preserve">1.89347040653229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730056285858</t>
+    <t xml:space="preserve">1.93730092048645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989737033844</t>
+    <t xml:space="preserve">1.98989713191986</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">1.77074551582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.797043800354</t>
+    <t xml:space="preserve">1.79704356193542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76197957992554</t>
+    <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
     <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542429447174</t>
+    <t xml:space="preserve">1.59542417526245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62172245979309</t>
+    <t xml:space="preserve">1.6217223405838</t>
   </si>
   <si>
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308472633362</t>
+    <t xml:space="preserve">1.68308484554291</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789194583893</t>
+    <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419023036957</t>
+    <t xml:space="preserve">1.60419034957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993570327759</t>
+    <t xml:space="preserve">1.66993582248688</t>
   </si>
   <si>
     <t xml:space="preserve">1.63048851490021</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">1.57350897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70061707496643</t>
+    <t xml:space="preserve">1.70061695575714</t>
   </si>
   <si>
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295628547668</t>
+    <t xml:space="preserve">1.61295640468597</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925445079803</t>
+    <t xml:space="preserve">1.63925457000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.58665812015533</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">1.42448580265045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32367599010468</t>
+    <t xml:space="preserve">1.32367610931396</t>
   </si>
   <si>
     <t xml:space="preserve">1.29737794399261</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065564632416</t>
+    <t xml:space="preserve">1.38065552711487</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1199,28 +1199,28 @@
     <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763482570648</t>
+    <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44640100002289</t>
+    <t xml:space="preserve">1.4464008808136</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4507839679718</t>
+    <t xml:space="preserve">1.45078408718109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39380466938019</t>
+    <t xml:space="preserve">1.3938045501709</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36750650405884</t>
+    <t xml:space="preserve">1.36750626564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406167030334</t>
+    <t xml:space="preserve">1.53406178951263</t>
   </si>
   <si>
     <t xml:space="preserve">1.5121465921402</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721081256866</t>
+    <t xml:space="preserve">1.54721069335938</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55159389972687</t>
+    <t xml:space="preserve">1.55159378051758</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035995483398</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584830760956</t>
+    <t xml:space="preserve">1.48584842681885</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652956008911</t>
@@ -1253,40 +1253,40 @@
     <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776338577271</t>
+    <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529573440552</t>
+    <t xml:space="preserve">1.52529549598694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899733066559</t>
+    <t xml:space="preserve">1.49899744987488</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545706748962</t>
+    <t xml:space="preserve">1.60545694828033</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232096672058</t>
+    <t xml:space="preserve">1.54232120513916</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
     <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624322891235</t>
+    <t xml:space="preserve">1.50624334812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016561031342</t>
+    <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
     <t xml:space="preserve">1.44310736656189</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801013469696</t>
+    <t xml:space="preserve">1.39801025390625</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702974796295</t>
+    <t xml:space="preserve">1.40702962875366</t>
   </si>
   <si>
     <t xml:space="preserve">1.38899087905884</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
     <t xml:space="preserve">1.26271903514862</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056367874146</t>
+    <t xml:space="preserve">1.19056355953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664129734039</t>
+    <t xml:space="preserve">1.22664141654968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762192249298</t>
+    <t xml:space="preserve">1.21762180328369</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193251609802</t>
+    <t xml:space="preserve">1.36193263530731</t>
   </si>
   <si>
     <t xml:space="preserve">1.37997150421143</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055406093597</t>
+    <t xml:space="preserve">1.65055418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859304904938</t>
+    <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
     <t xml:space="preserve">1.64153480529785</t>
@@ -1388,46 +1388,46 @@
     <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59643757343292</t>
+    <t xml:space="preserve">1.59643745422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486477375031</t>
+    <t xml:space="preserve">1.79486489295959</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72270941734314</t>
+    <t xml:space="preserve">1.72270953655243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369016170502</t>
+    <t xml:space="preserve">1.71369004249573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349569797516</t>
+    <t xml:space="preserve">1.62349581718445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55134046077728</t>
+    <t xml:space="preserve">1.55134057998657</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69565117359161</t>
+    <t xml:space="preserve">1.6956512928009</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840832233429</t>
+    <t xml:space="preserve">1.118408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350531578064</t>
+    <t xml:space="preserve">1.16350543498993</t>
   </si>
   <si>
     <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1274276971817</t>
+    <t xml:space="preserve">1.12742757797241</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10036945343018</t>
+    <t xml:space="preserve">1.10036933422089</t>
   </si>
   <si>
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09135007858276</t>
+    <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233058452606</t>
+    <t xml:space="preserve">1.08233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331120967865</t>
+    <t xml:space="preserve">1.07331132888794</t>
   </si>
   <si>
     <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03723347187042</t>
+    <t xml:space="preserve">1.03723335266113</t>
   </si>
   <si>
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432386875153</t>
+    <t xml:space="preserve">0.897432446479797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910961508750916</t>
+    <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983116924762726</t>
+    <t xml:space="preserve">0.983117043972015</t>
   </si>
   <si>
     <t xml:space="preserve">1.01919460296631</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20860254764557</t>
+    <t xml:space="preserve">1.20860242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918498516083</t>
+    <t xml:space="preserve">1.47918510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098145008087</t>
+    <t xml:space="preserve">1.25098133087158</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1212500333786</t>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1565,25 +1565,22 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051652908325</t>
+    <t xml:space="preserve">1.13051640987396</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1953821182251</t>
+    <t xml:space="preserve">1.19538223743439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198341846466</t>
+    <t xml:space="preserve">1.11198353767395</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -57596,7 +57593,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57622,7 +57619,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2135" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57648,7 +57645,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2136" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57674,7 +57671,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2137" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57700,7 +57697,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2138" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57726,7 +57723,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2139" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57752,7 +57749,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2140" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57778,7 +57775,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57804,7 +57801,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2142" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57830,7 +57827,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2143" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57856,7 +57853,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57882,7 +57879,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57908,7 +57905,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57934,7 +57931,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2147" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57960,7 +57957,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57986,7 +57983,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2149" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58012,7 +58009,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2150" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58038,7 +58035,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2151" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58064,7 +58061,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2152" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58090,7 +58087,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2153" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58116,7 +58113,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2154" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58142,7 +58139,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2155" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58168,7 +58165,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2156" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58194,7 +58191,7 @@
         <v>1</v>
       </c>
       <c r="G2157" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58220,7 +58217,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58246,7 +58243,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2159" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58272,7 +58269,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2160" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58298,7 +58295,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2161" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58324,7 +58321,7 @@
         <v>1</v>
       </c>
       <c r="G2162" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58350,7 +58347,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2163" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58376,7 +58373,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2164" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58402,7 +58399,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58428,7 +58425,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2166" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58454,7 +58451,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2167" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58480,7 +58477,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2168" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58506,7 +58503,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58532,7 +58529,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58558,7 +58555,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2171" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58584,7 +58581,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2172" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58610,7 +58607,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58636,7 +58633,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2174" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58662,7 +58659,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2175" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58688,7 +58685,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2176" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58714,7 +58711,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2177" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58740,7 +58737,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2178" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58766,7 +58763,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2179" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58792,7 +58789,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58818,7 +58815,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2181" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58844,7 +58841,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2182" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58870,7 +58867,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2183" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58896,7 +58893,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2184" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58922,7 +58919,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2185" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58948,7 +58945,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2186" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58974,7 +58971,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2187" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59000,7 +58997,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59026,7 +59023,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2189" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59052,7 +59049,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2190" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59078,7 +59075,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2191" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59104,7 +59101,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2192" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59130,7 +59127,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2193" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59156,7 +59153,7 @@
         <v>1</v>
       </c>
       <c r="G2194" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59182,7 +59179,7 @@
         <v>1</v>
       </c>
       <c r="G2195" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59208,7 +59205,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2196" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59234,7 +59231,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59260,7 +59257,7 @@
         <v>1</v>
       </c>
       <c r="G2198" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59286,7 +59283,7 @@
         <v>1</v>
       </c>
       <c r="G2199" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59312,7 +59309,7 @@
         <v>1</v>
       </c>
       <c r="G2200" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59338,7 +59335,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2201" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59364,7 +59361,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59390,7 +59387,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59416,7 +59413,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59442,7 +59439,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59468,7 +59465,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59494,7 +59491,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59520,7 +59517,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2208" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59546,7 +59543,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2209" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59572,7 +59569,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2210" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59598,7 +59595,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2211" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59624,7 +59621,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2212" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59650,7 +59647,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2213" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59676,7 +59673,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2214" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59702,7 +59699,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59728,7 +59725,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2216" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59754,7 +59751,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2217" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59780,7 +59777,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59806,7 +59803,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2219" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59832,7 +59829,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2220" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59858,7 +59855,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2221" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59884,7 +59881,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59910,7 +59907,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2223" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59936,7 +59933,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2224" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59962,7 +59959,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2225" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59988,7 +59985,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2226" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60014,7 +60011,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2227" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60040,7 +60037,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2228" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60066,7 +60063,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2229" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60092,7 +60089,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2230" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60118,7 +60115,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2231" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60144,7 +60141,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2232" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60170,7 +60167,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2233" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60196,7 +60193,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2234" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60222,7 +60219,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2235" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60248,7 +60245,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G2236" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60274,7 +60271,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2237" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60300,7 +60297,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2238" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60326,7 +60323,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2239" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60352,7 +60349,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60378,7 +60375,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60404,7 +60401,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2242" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60430,7 +60427,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2243" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60456,7 +60453,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2244" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60482,7 +60479,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2245" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60508,7 +60505,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60534,7 +60531,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2247" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60560,7 +60557,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2248" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60586,7 +60583,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2249" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60612,7 +60609,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2250" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60638,7 +60635,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2251" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60664,7 +60661,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2252" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60690,7 +60687,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2253" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60716,7 +60713,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2254" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60742,7 +60739,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2255" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60768,7 +60765,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2256" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60794,7 +60791,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2257" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60820,7 +60817,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2258" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60846,7 +60843,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2259" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60872,7 +60869,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2260" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60898,7 +60895,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2261" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60924,7 +60921,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2262" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60950,7 +60947,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2263" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60976,7 +60973,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2264" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61002,7 +60999,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2265" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61028,7 +61025,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2266" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61054,7 +61051,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2267" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61080,7 +61077,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2268" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61106,7 +61103,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2269" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61132,7 +61129,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2270" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61158,7 +61155,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61184,7 +61181,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2272" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61210,7 +61207,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2273" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61236,7 +61233,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2274" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61262,7 +61259,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2275" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61288,7 +61285,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2276" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61314,7 +61311,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2277" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61340,7 +61337,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2278" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61366,7 +61363,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2279" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61392,7 +61389,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2280" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61418,7 +61415,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2281" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61444,7 +61441,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2282" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61470,7 +61467,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61496,7 +61493,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2284" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61522,7 +61519,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2285" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61548,7 +61545,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2286" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61574,7 +61571,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2287" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61600,7 +61597,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2288" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61626,7 +61623,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2289" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61652,7 +61649,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2290" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61678,7 +61675,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2291" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61704,7 +61701,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2292" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61730,7 +61727,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2293" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61756,7 +61753,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2294" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61782,7 +61779,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61808,7 +61805,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2296" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61834,7 +61831,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2297" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61860,7 +61857,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2298" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61886,7 +61883,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2299" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61912,7 +61909,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61938,7 +61935,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2301" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61964,7 +61961,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2302" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61990,7 +61987,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2303" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62016,7 +62013,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2304" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62042,7 +62039,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2305" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62068,7 +62065,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2306" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62094,7 +62091,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2307" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62120,7 +62117,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2308" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62146,7 +62143,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2309" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62172,7 +62169,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2310" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62198,7 +62195,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2311" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62224,7 +62221,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2312" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62250,7 +62247,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2313" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62276,7 +62273,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2314" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62302,7 +62299,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62328,7 +62325,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2316" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62354,7 +62351,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2317" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62380,7 +62377,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2318" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62406,7 +62403,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2319" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62432,7 +62429,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2320" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62458,7 +62455,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2321" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62484,7 +62481,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2322" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62510,7 +62507,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2323" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62536,7 +62533,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2324" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62562,7 +62559,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2325" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62588,7 +62585,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2326" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62614,7 +62611,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2327" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62640,7 +62637,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2328" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62666,7 +62663,7 @@
         <v>0.875</v>
       </c>
       <c r="G2329" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62692,7 +62689,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2330" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62718,7 +62715,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2331" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62744,7 +62741,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2332" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62770,7 +62767,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2333" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62796,7 +62793,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2334" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62822,7 +62819,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2335" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62848,7 +62845,7 @@
         <v>0.875</v>
       </c>
       <c r="G2336" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62874,7 +62871,7 @@
         <v>0.875</v>
       </c>
       <c r="G2337" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62900,7 +62897,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2338" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62926,7 +62923,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2339" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62952,7 +62949,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2340" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62978,7 +62975,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2341" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63004,7 +63001,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2342" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63030,7 +63027,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2343" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63056,7 +63053,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2344" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63082,7 +63079,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2345" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63108,7 +63105,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2346" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63134,7 +63131,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2347" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63160,7 +63157,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2348" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63186,7 +63183,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2349" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63212,7 +63209,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2350" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63238,7 +63235,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2351" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63264,7 +63261,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2352" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63290,7 +63287,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2353" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63316,7 +63313,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2354" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63342,7 +63339,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2355" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63368,7 +63365,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2356" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63394,7 +63391,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2357" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63420,7 +63417,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2358" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63446,7 +63443,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2359" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63472,7 +63469,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2360" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63498,7 +63495,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2361" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63524,7 +63521,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2362" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63550,7 +63547,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2363" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63576,7 +63573,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2364" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63602,7 +63599,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2365" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63628,7 +63625,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2366" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63654,7 +63651,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2367" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63680,7 +63677,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G2368" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63706,7 +63703,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2369" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63732,7 +63729,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2370" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63758,7 +63755,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2371" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63784,7 +63781,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2372" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63810,7 +63807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2373" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63836,7 +63833,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2374" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63862,7 +63859,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2375" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63888,7 +63885,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2376" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63914,7 +63911,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2377" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63940,7 +63937,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2378" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63966,7 +63963,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2379" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63992,7 +63989,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2380" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64018,7 +64015,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64044,7 +64041,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2382" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64070,7 +64067,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2383" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64096,7 +64093,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64122,7 +64119,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64148,7 +64145,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2386" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64174,7 +64171,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2387" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64200,7 +64197,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2388" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64226,7 +64223,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2389" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64252,7 +64249,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2390" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64278,7 +64275,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2391" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64304,7 +64301,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2392" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64330,7 +64327,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2393" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64356,7 +64353,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2394" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64382,7 +64379,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2395" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64408,7 +64405,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2396" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64434,7 +64431,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2397" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64460,7 +64457,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2398" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64486,7 +64483,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2399" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64512,7 +64509,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2400" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64538,7 +64535,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2401" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64564,7 +64561,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2402" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64590,7 +64587,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2403" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64616,7 +64613,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2404" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64642,7 +64639,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2405" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64668,7 +64665,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2406" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64694,7 +64691,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2407" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64720,7 +64717,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2408" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64746,7 +64743,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2409" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64772,7 +64769,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2410" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64798,7 +64795,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2411" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64824,7 +64821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2412" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64850,7 +64847,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2413" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64876,7 +64873,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2414" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64902,7 +64899,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2415" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64928,7 +64925,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2416" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64954,7 +64951,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2417" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64980,7 +64977,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2418" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65006,7 +65003,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2419" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65032,7 +65029,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65058,7 +65055,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2421" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65084,7 +65081,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2422" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65110,7 +65107,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2423" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65136,7 +65133,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2424" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65162,7 +65159,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2425" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65188,7 +65185,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2426" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65214,7 +65211,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2427" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65240,7 +65237,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2428" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65266,7 +65263,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2429" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65292,7 +65289,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2430" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65318,7 +65315,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2431" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65344,7 +65341,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2432" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65370,7 +65367,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2433" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65396,7 +65393,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2434" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65422,7 +65419,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2435" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65448,7 +65445,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2436" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65474,7 +65471,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2437" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65500,7 +65497,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2438" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65526,7 +65523,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2439" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65552,7 +65549,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2440" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65578,7 +65575,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2441" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65604,7 +65601,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2442" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65630,7 +65627,7 @@
         <v>1</v>
       </c>
       <c r="G2443" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65656,7 +65653,7 @@
         <v>1</v>
       </c>
       <c r="G2444" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65682,7 +65679,7 @@
         <v>1</v>
       </c>
       <c r="G2445" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65708,7 +65705,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65734,7 +65731,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65760,7 +65757,7 @@
         <v>1</v>
       </c>
       <c r="G2448" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65786,7 +65783,7 @@
         <v>1</v>
       </c>
       <c r="G2449" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65812,7 +65809,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2450" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65838,7 +65835,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65864,7 +65861,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2452" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65890,7 +65887,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2453" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65916,7 +65913,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2454" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65942,7 +65939,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65968,7 +65965,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2456" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65994,7 +65991,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2457" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66020,7 +66017,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2458" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66046,7 +66043,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2459" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66072,7 +66069,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2460" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66098,7 +66095,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2461" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66124,7 +66121,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2462" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66150,7 +66147,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2463" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66176,7 +66173,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2464" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66202,7 +66199,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2465" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66228,7 +66225,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66254,7 +66251,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2467" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66280,7 +66277,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66306,7 +66303,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2469" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66332,7 +66329,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2470" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66358,7 +66355,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2471" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66384,7 +66381,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2472" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66410,7 +66407,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2473" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66436,7 +66433,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2474" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66462,7 +66459,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2475" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66488,7 +66485,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2476" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66514,7 +66511,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2477" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66540,7 +66537,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66566,7 +66563,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2479" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66592,7 +66589,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2480" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66618,7 +66615,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66644,7 +66641,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G2482" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66670,7 +66667,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2483" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66696,7 +66693,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2484" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66722,7 +66719,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2485" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66748,7 +66745,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2486" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66774,7 +66771,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2487" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66800,7 +66797,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2488" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66826,7 +66823,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2489" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66852,7 +66849,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2490" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66878,7 +66875,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2491" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66904,7 +66901,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2492" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66930,7 +66927,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2493" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66956,7 +66953,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2494" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66982,7 +66979,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2495" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67008,7 +67005,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2496" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67034,7 +67031,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2497" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67060,7 +67057,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2498" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67086,7 +67083,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2499" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67112,7 +67109,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2500" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67138,7 +67135,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2501" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67164,7 +67161,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2502" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67190,7 +67187,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2503" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67216,7 +67213,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2504" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67242,7 +67239,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2505" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67268,7 +67265,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2506" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67294,7 +67291,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2507" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67320,7 +67317,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2508" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67346,7 +67343,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67372,7 +67369,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2510" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67398,7 +67395,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2511" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67424,7 +67421,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2512" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67450,7 +67447,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2513" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67476,7 +67473,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2514" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67502,7 +67499,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2515" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67528,7 +67525,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2516" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67554,9 +67551,35 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2517" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.3333333333</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>578</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781757354736</t>
+    <t xml:space="preserve">1.43781745433807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684322834015</t>
+    <t xml:space="preserve">1.48684310913086</t>
   </si>
   <si>
     <t xml:space="preserve">1.44424724578857</t>
@@ -56,34 +56,34 @@
     <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236248493195</t>
+    <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593281269073</t>
+    <t xml:space="preserve">1.37593257427216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414041996002</t>
+    <t xml:space="preserve">1.33414053916931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744762420654</t>
+    <t xml:space="preserve">1.35744750499725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628818511963</t>
+    <t xml:space="preserve">1.3662885427475</t>
   </si>
   <si>
     <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38155853748322</t>
+    <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647339820862</t>
+    <t xml:space="preserve">1.40647327899933</t>
   </si>
   <si>
     <t xml:space="preserve">1.44585454463959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3984363079071</t>
+    <t xml:space="preserve">1.39843618869781</t>
   </si>
   <si>
     <t xml:space="preserve">1.34780335426331</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002950668335</t>
+    <t xml:space="preserve">1.31002914905548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217739105225</t>
+    <t xml:space="preserve">1.34217727184296</t>
   </si>
   <si>
     <t xml:space="preserve">1.35021424293518</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557708263397</t>
+    <t xml:space="preserve">1.38557720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273219585419</t>
+    <t xml:space="preserve">1.46273231506348</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693559646606</t>
+    <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889862537384</t>
+    <t xml:space="preserve">1.49889874458313</t>
   </si>
   <si>
     <t xml:space="preserve">1.47237658500671</t>
@@ -125,46 +125,46 @@
     <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274665355682</t>
+    <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543476581573</t>
+    <t xml:space="preserve">1.61543500423431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169392108917</t>
+    <t xml:space="preserve">1.67169404029846</t>
   </si>
   <si>
     <t xml:space="preserve">1.67490887641907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64597547054291</t>
+    <t xml:space="preserve">1.6459755897522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113899707794</t>
+    <t xml:space="preserve">1.55113911628723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702820301056</t>
+    <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095414161682</t>
+    <t xml:space="preserve">1.51095402240753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630276203156</t>
+    <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862116336823</t>
+    <t xml:space="preserve">1.43862128257751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41209900379181</t>
+    <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601892471313</t>
+    <t xml:space="preserve">1.45601904392242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4342622756958</t>
+    <t xml:space="preserve">1.43426251411438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832161903381</t>
+    <t xml:space="preserve">1.40832185745239</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
@@ -173,55 +173,55 @@
     <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840468883514</t>
+    <t xml:space="preserve">1.42840492725372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4133425951004</t>
+    <t xml:space="preserve">1.41334247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4049745798111</t>
+    <t xml:space="preserve">1.40497469902039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313486099243</t>
+    <t xml:space="preserve">1.36313498020172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560393333435</t>
+    <t xml:space="preserve">1.35560381412506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37233972549438</t>
+    <t xml:space="preserve">1.3723396062851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886802196503</t>
+    <t xml:space="preserve">1.33886790275574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288600921631</t>
+    <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
     <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213199138641</t>
+    <t xml:space="preserve">1.32213222980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439344882965</t>
+    <t xml:space="preserve">1.26439356803894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702818393707</t>
+    <t xml:space="preserve">1.29702830314636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539643764496</t>
+    <t xml:space="preserve">1.30539619922638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397194862366</t>
+    <t xml:space="preserve">1.36397171020508</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3807076215744</t>
+    <t xml:space="preserve">1.38070774078369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050012588501</t>
+    <t xml:space="preserve">1.33050000667572</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
@@ -230,37 +230,37 @@
     <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506415843964</t>
+    <t xml:space="preserve">1.22506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20498132705688</t>
+    <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916509628296</t>
+    <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841155529022</t>
+    <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
     <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008501529694</t>
+    <t xml:space="preserve">1.23008513450623</t>
   </si>
   <si>
     <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1447319984436</t>
+    <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171700000763</t>
+    <t xml:space="preserve">1.22171723842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816234588623</t>
+    <t xml:space="preserve">1.16816246509552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226328372955</t>
+    <t xml:space="preserve">1.15226316452026</t>
   </si>
   <si>
     <t xml:space="preserve">1.14222180843353</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293411254883</t>
+    <t xml:space="preserve">1.11293399333954</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850101470947</t>
@@ -290,157 +290,157 @@
     <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364629745483</t>
+    <t xml:space="preserve">1.08364617824554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06440007686615</t>
+    <t xml:space="preserve">1.06440019607544</t>
   </si>
   <si>
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03762269020081</t>
+    <t xml:space="preserve">1.0376228094101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00833523273468</t>
+    <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067916870117</t>
+    <t xml:space="preserve">0.984068036079407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967098236084</t>
+    <t xml:space="preserve">0.999967038631439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251900196075</t>
+    <t xml:space="preserve">1.01251888275146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00415098667145</t>
+    <t xml:space="preserve">1.00415086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127319812775</t>
+    <t xml:space="preserve">0.958127439022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842553138733</t>
+    <t xml:space="preserve">0.969842612743378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738745689392</t>
+    <t xml:space="preserve">0.944738626480103</t>
   </si>
   <si>
     <t xml:space="preserve">0.888673663139343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866080284118652</t>
+    <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269971370697</t>
+    <t xml:space="preserve">0.952269911766052</t>
   </si>
   <si>
     <t xml:space="preserve">0.912103831768036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899551928043365</t>
+    <t xml:space="preserve">0.89955198764801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204710006714</t>
+    <t xml:space="preserve">0.896204829216003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937811374664</t>
+    <t xml:space="preserve">0.871937870979309</t>
   </si>
   <si>
     <t xml:space="preserve">0.908756613731384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596392154694</t>
+    <t xml:space="preserve">0.950596272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124569416046</t>
+    <t xml:space="preserve">0.917124450206757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471787452698</t>
+    <t xml:space="preserve">0.920471727848053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332124710083</t>
+    <t xml:space="preserve">0.967332184314728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311267852783</t>
+    <t xml:space="preserve">0.962311446666718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519545078278</t>
+    <t xml:space="preserve">1.05519533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599082946777</t>
+    <t xml:space="preserve">0.991598963737488</t>
   </si>
   <si>
     <t xml:space="preserve">0.989088773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0016405582428</t>
+    <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783269405365</t>
+    <t xml:space="preserve">0.995783090591431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762293338776</t>
+    <t xml:space="preserve">0.99076235294342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207460403442</t>
+    <t xml:space="preserve">0.937207520008087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394397258759</t>
+    <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94139152765274</t>
+    <t xml:space="preserve">0.941391706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251984119415</t>
+    <t xml:space="preserve">0.988251924514771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352981567383</t>
+    <t xml:space="preserve">0.972352862358093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168914318085</t>
+    <t xml:space="preserve">0.968168795108795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97570013999939</t>
+    <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231127262115</t>
+    <t xml:space="preserve">0.98323130607605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415134906769</t>
+    <t xml:space="preserve">0.987415075302124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005763530731</t>
+    <t xml:space="preserve">0.969005644321442</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943490982056</t>
+    <t xml:space="preserve">0.9539435505867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854249000549</t>
+    <t xml:space="preserve">1.0585423707962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937933921814</t>
+    <t xml:space="preserve">1.05937945842743</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268502235413</t>
+    <t xml:space="preserve">1.05268490314484</t>
   </si>
   <si>
     <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636422157288</t>
+    <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
     <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577646255493</t>
+    <t xml:space="preserve">1.19577658176422</t>
   </si>
   <si>
     <t xml:space="preserve">1.19661319255829</t>
@@ -452,25 +452,25 @@
     <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21334910392761</t>
+    <t xml:space="preserve">1.2133492231369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753311157227</t>
+    <t xml:space="preserve">1.21753299236298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644729137421</t>
+    <t xml:space="preserve">1.15644717216492</t>
   </si>
   <si>
     <t xml:space="preserve">1.1531001329422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242930412292</t>
+    <t xml:space="preserve">1.19242918491364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493961334229</t>
+    <t xml:space="preserve">1.19493973255157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15477383136749</t>
+    <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
     <t xml:space="preserve">1.1464056968689</t>
@@ -479,43 +479,43 @@
     <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314148902893</t>
+    <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23761606216431</t>
+    <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2359424829483</t>
+    <t xml:space="preserve">1.23594260215759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146802902222</t>
+    <t xml:space="preserve">1.16146790981293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13385379314423</t>
+    <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803780078888</t>
+    <t xml:space="preserve">1.13803768157959</t>
   </si>
   <si>
     <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130188941956</t>
+    <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.17653036117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581142902374</t>
+    <t xml:space="preserve">1.40581130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576995372772</t>
+    <t xml:space="preserve">1.39576983451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911699295044</t>
+    <t xml:space="preserve">1.39911711215973</t>
   </si>
   <si>
     <t xml:space="preserve">1.39744341373444</t>
@@ -524,49 +524,49 @@
     <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534821510315</t>
+    <t xml:space="preserve">1.49534809589386</t>
   </si>
   <si>
     <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865401744843</t>
+    <t xml:space="preserve">1.48865389823914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4894905090332</t>
+    <t xml:space="preserve">1.48949074745178</t>
   </si>
   <si>
     <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551423549652</t>
+    <t xml:space="preserve">1.53551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57316982746124</t>
+    <t xml:space="preserve">1.57316994667053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5857218503952</t>
+    <t xml:space="preserve">1.58572196960449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174545764923</t>
+    <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684914588928</t>
+    <t xml:space="preserve">1.65684926509857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438031196594</t>
+    <t xml:space="preserve">1.66438019275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550760746002</t>
+    <t xml:space="preserve">1.73550748825073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726401805878</t>
+    <t xml:space="preserve">1.75726413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7739999294281</t>
+    <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78236818313599</t>
+    <t xml:space="preserve">1.7823680639267</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
@@ -575,52 +575,52 @@
     <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67358505725861</t>
+    <t xml:space="preserve">1.67358493804932</t>
   </si>
   <si>
     <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697369098663</t>
+    <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
     <t xml:space="preserve">1.6166832447052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6066415309906</t>
+    <t xml:space="preserve">1.60664165019989</t>
   </si>
   <si>
     <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362653255463</t>
+    <t xml:space="preserve">1.68362665176392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542453765869</t>
+    <t xml:space="preserve">1.71542465686798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718118667603</t>
+    <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224351882935</t>
+    <t xml:space="preserve">1.75224363803864</t>
   </si>
   <si>
     <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72379267215729</t>
+    <t xml:space="preserve">1.72379243373871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601241588593</t>
+    <t xml:space="preserve">1.65601229667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7490611076355</t>
+    <t xml:space="preserve">1.74906098842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337306022644</t>
+    <t xml:space="preserve">1.84337329864502</t>
   </si>
   <si>
     <t xml:space="preserve">1.80050384998322</t>
@@ -641,25 +641,25 @@
     <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421898841858</t>
+    <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936358451843</t>
+    <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505139350891</t>
+    <t xml:space="preserve">2.73505163192749</t>
   </si>
   <si>
     <t xml:space="preserve">2.64416885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47783637046814</t>
+    <t xml:space="preserve">2.47783660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46068906784058</t>
+    <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067195892334</t>
+    <t xml:space="preserve">2.40067172050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
@@ -671,37 +671,37 @@
     <t xml:space="preserve">2.58929634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78649425506592</t>
+    <t xml:space="preserve">2.7864944934845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503476142883</t>
+    <t xml:space="preserve">2.67503428459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012850761414</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46240377426147</t>
+    <t xml:space="preserve">2.4624035358429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097730636597</t>
+    <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354128837585</t>
+    <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953444480896</t>
+    <t xml:space="preserve">2.41953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211482048035</t>
+    <t xml:space="preserve">2.45211505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52927947044373</t>
+    <t xml:space="preserve">2.5292797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214856147766</t>
+    <t xml:space="preserve">2.57214879989624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641037940979</t>
+    <t xml:space="preserve">2.48641061782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349672794342</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">2.4572594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613829612732</t>
+    <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4589741230011</t>
+    <t xml:space="preserve">2.45897388458252</t>
   </si>
   <si>
     <t xml:space="preserve">2.47440695762634</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">2.56186008453369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781997680664</t>
+    <t xml:space="preserve">2.41781973838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.38180994987488</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">2.33208131790161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836318969727</t>
+    <t xml:space="preserve">2.31836366653442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28063869476318</t>
+    <t xml:space="preserve">2.2806384563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865190505981</t>
+    <t xml:space="preserve">2.32865214347839</t>
   </si>
   <si>
     <t xml:space="preserve">2.31321907043457</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12630939483643</t>
+    <t xml:space="preserve">2.126309633255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12116527557373</t>
+    <t xml:space="preserve">2.12116503715515</t>
   </si>
   <si>
     <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05771899223328</t>
+    <t xml:space="preserve">2.0577187538147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09544372558594</t>
+    <t xml:space="preserve">2.09544396400452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773586273193</t>
+    <t xml:space="preserve">2.11773562431335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12802457809448</t>
+    <t xml:space="preserve">2.1280243396759</t>
   </si>
   <si>
     <t xml:space="preserve">2.08515501022339</t>
@@ -788,58 +788,58 @@
     <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799036026001</t>
+    <t xml:space="preserve">2.00799083709717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05085968971252</t>
+    <t xml:space="preserve">2.05086016654968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342367172241</t>
+    <t xml:space="preserve">2.02342343330383</t>
   </si>
   <si>
     <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603778839111</t>
+    <t xml:space="preserve">2.17603802680969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172535896301</t>
+    <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401725769043</t>
+    <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15889000892639</t>
+    <t xml:space="preserve">2.15888977050781</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12288022041321</t>
+    <t xml:space="preserve">2.12287974357605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15374612808228</t>
+    <t xml:space="preserve">2.15374565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15203094482422</t>
+    <t xml:space="preserve">2.15203070640564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917872428894</t>
+    <t xml:space="preserve">2.16917848587036</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062158584595</t>
+    <t xml:space="preserve">2.22062134742737</t>
   </si>
   <si>
     <t xml:space="preserve">2.25491714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2823531627655</t>
+    <t xml:space="preserve">2.28235340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23776960372925</t>
+    <t xml:space="preserve">2.23776912689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.22233629226685</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">2.17089366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975567817688</t>
+    <t xml:space="preserve">2.18975591659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634289741516</t>
+    <t xml:space="preserve">2.24634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065532684326</t>
+    <t xml:space="preserve">2.34065556526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175957679749</t>
+    <t xml:space="preserve">2.20175933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20861840248108</t>
+    <t xml:space="preserve">2.2086181640625</t>
   </si>
   <si>
     <t xml:space="preserve">2.28749752044678</t>
@@ -884,52 +884,52 @@
     <t xml:space="preserve">2.24462842941284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43668222427368</t>
+    <t xml:space="preserve">2.4366819858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527286529541</t>
+    <t xml:space="preserve">2.50527262687683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384663581848</t>
+    <t xml:space="preserve">2.51384687423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50355792045593</t>
+    <t xml:space="preserve">2.50355815887451</t>
   </si>
   <si>
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326944351196</t>
+    <t xml:space="preserve">2.49326920509338</t>
   </si>
   <si>
     <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32007789611816</t>
+    <t xml:space="preserve">2.32007813453674</t>
   </si>
   <si>
     <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809158325195</t>
+    <t xml:space="preserve">2.36809134483337</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379626274109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439032554626</t>
+    <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922909736633</t>
+    <t xml:space="preserve">2.34922885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35780262947083</t>
+    <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410137176514</t>
+    <t xml:space="preserve">2.40410161018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.39038348197937</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38866877555847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31493377685547</t>
+    <t xml:space="preserve">2.31493401527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832992553711</t>
+    <t xml:space="preserve">2.19832944869995</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430621147156</t>
+    <t xml:space="preserve">2.11430644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632626533508</t>
+    <t xml:space="preserve">2.18632650375366</t>
   </si>
   <si>
     <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201455116272</t>
+    <t xml:space="preserve">2.09201431274414</t>
   </si>
   <si>
     <t xml:space="preserve">2.04057145118713</t>
@@ -974,85 +974,85 @@
     <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90339016914368</t>
+    <t xml:space="preserve">1.90339004993439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98055458068848</t>
+    <t xml:space="preserve">1.9805543422699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198033332825</t>
+    <t xml:space="preserve">1.97198069095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053735256195</t>
+    <t xml:space="preserve">1.92053759098053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912823200226</t>
+    <t xml:space="preserve">1.98912811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196405887604</t>
+    <t xml:space="preserve">1.91196393966675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9291113615036</t>
+    <t xml:space="preserve">1.92911171913147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624238967896</t>
+    <t xml:space="preserve">1.88624227046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481627941132</t>
+    <t xml:space="preserve">1.89481616020203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909472942352</t>
+    <t xml:space="preserve">1.86909461021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194718837738</t>
+    <t xml:space="preserve">1.85194706916809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625902175903</t>
+    <t xml:space="preserve">1.94625926017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340668201447</t>
+    <t xml:space="preserve">1.96340680122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879186630249</t>
+    <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249334335327</t>
+    <t xml:space="preserve">2.04249358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236514091492</t>
+    <t xml:space="preserve">1.97236526012421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100251674652</t>
+    <t xml:space="preserve">1.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840606689453</t>
+    <t xml:space="preserve">1.85840594768524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470435142517</t>
+    <t xml:space="preserve">1.88470458984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866318702698</t>
+    <t xml:space="preserve">1.99866330623627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606685638428</t>
+    <t xml:space="preserve">1.94606673717499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853462696075</t>
+    <t xml:space="preserve">1.92853474617004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717236042023</t>
+    <t xml:space="preserve">1.86717224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223658084869</t>
+    <t xml:space="preserve">1.90223670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593853473663</t>
+    <t xml:space="preserve">1.87593841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334196567535</t>
+    <t xml:space="preserve">1.82334172725677</t>
   </si>
   <si>
     <t xml:space="preserve">1.91976881027222</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">1.84964001178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730092048645</t>
+    <t xml:space="preserve">1.93730056285858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989713191986</t>
+    <t xml:space="preserve">1.98989737033844</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">1.77074551582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704356193542</t>
+    <t xml:space="preserve">1.797043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76197946071625</t>
+    <t xml:space="preserve">1.76197957992554</t>
   </si>
   <si>
     <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542417526245</t>
+    <t xml:space="preserve">1.59542429447174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6217223405838</t>
+    <t xml:space="preserve">1.62172245979309</t>
   </si>
   <si>
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308484554291</t>
+    <t xml:space="preserve">1.68308472633362</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789206504822</t>
+    <t xml:space="preserve">1.57789194583893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419034957886</t>
+    <t xml:space="preserve">1.60419023036957</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993582248688</t>
+    <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
     <t xml:space="preserve">1.63048851490021</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">1.57350897789001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70061695575714</t>
+    <t xml:space="preserve">1.70061707496643</t>
   </si>
   <si>
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295640468597</t>
+    <t xml:space="preserve">1.61295628547668</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925457000732</t>
+    <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.58665812015533</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">1.42448580265045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32367610931396</t>
+    <t xml:space="preserve">1.32367599010468</t>
   </si>
   <si>
     <t xml:space="preserve">1.29737794399261</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065552711487</t>
+    <t xml:space="preserve">1.38065564632416</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1199,28 +1199,28 @@
     <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763494491577</t>
+    <t xml:space="preserve">1.43763482570648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4464008808136</t>
+    <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45078408718109</t>
+    <t xml:space="preserve">1.4507839679718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3938045501709</t>
+    <t xml:space="preserve">1.39380466938019</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36750626564026</t>
+    <t xml:space="preserve">1.36750650405884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406178951263</t>
+    <t xml:space="preserve">1.53406167030334</t>
   </si>
   <si>
     <t xml:space="preserve">1.5121465921402</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721069335938</t>
+    <t xml:space="preserve">1.54721081256866</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55159378051758</t>
+    <t xml:space="preserve">1.55159389972687</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035995483398</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584842681885</t>
+    <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652956008911</t>
@@ -1253,40 +1253,40 @@
     <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776362419128</t>
+    <t xml:space="preserve">1.50776338577271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529549598694</t>
+    <t xml:space="preserve">1.52529573440552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899744987488</t>
+    <t xml:space="preserve">1.49899733066559</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545694828033</t>
+    <t xml:space="preserve">1.60545706748962</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232120513916</t>
+    <t xml:space="preserve">1.54232096672058</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820447921753</t>
+    <t xml:space="preserve">1.48820459842682</t>
   </si>
   <si>
     <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624334812164</t>
+    <t xml:space="preserve">1.50624322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016572952271</t>
+    <t xml:space="preserve">1.47016561031342</t>
   </si>
   <si>
     <t xml:space="preserve">1.44310736656189</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801025390625</t>
+    <t xml:space="preserve">1.39801013469696</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702962875366</t>
+    <t xml:space="preserve">1.40702974796295</t>
   </si>
   <si>
     <t xml:space="preserve">1.38899087905884</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977715969086</t>
+    <t xml:space="preserve">1.28977727890015</t>
   </si>
   <si>
     <t xml:space="preserve">1.26271903514862</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056355953217</t>
+    <t xml:space="preserve">1.19056367874146</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252480983734</t>
+    <t xml:space="preserve">1.17252469062805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664141654968</t>
+    <t xml:space="preserve">1.22664129734039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762180328369</t>
+    <t xml:space="preserve">1.21762192249298</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879665374756</t>
+    <t xml:space="preserve">1.29879677295685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193263530731</t>
+    <t xml:space="preserve">1.36193251609802</t>
   </si>
   <si>
     <t xml:space="preserve">1.37997150421143</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055418014526</t>
+    <t xml:space="preserve">1.65055406093597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859292984009</t>
+    <t xml:space="preserve">1.66859304904938</t>
   </si>
   <si>
     <t xml:space="preserve">1.64153480529785</t>
@@ -1388,46 +1388,46 @@
     <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59643745422363</t>
+    <t xml:space="preserve">1.59643757343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486489295959</t>
+    <t xml:space="preserve">1.79486477375031</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72270953655243</t>
+    <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369004249573</t>
+    <t xml:space="preserve">1.71369016170502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349581718445</t>
+    <t xml:space="preserve">1.62349569797516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55134057998657</t>
+    <t xml:space="preserve">1.55134046077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6956512928009</t>
+    <t xml:space="preserve">1.69565117359161</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.118408203125</t>
+    <t xml:space="preserve">1.11840832233429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350543498993</t>
+    <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
     <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12742757797241</t>
+    <t xml:space="preserve">1.1274276971817</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546656608582</t>
+    <t xml:space="preserve">1.14546644687653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10036933422089</t>
+    <t xml:space="preserve">1.10036945343018</t>
   </si>
   <si>
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09134995937347</t>
+    <t xml:space="preserve">1.09135007858276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233070373535</t>
+    <t xml:space="preserve">1.08233058452606</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331132888794</t>
+    <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
     <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03723335266113</t>
+    <t xml:space="preserve">1.03723347187042</t>
   </si>
   <si>
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136418819427</t>
+    <t xml:space="preserve">0.992136359214783</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432446479797</t>
+    <t xml:space="preserve">0.897432386875153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91096156835556</t>
+    <t xml:space="preserve">0.910961508750916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983117043972015</t>
+    <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
     <t xml:space="preserve">1.01919460296631</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20860242843628</t>
+    <t xml:space="preserve">1.20860254764557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918510437012</t>
+    <t xml:space="preserve">1.47918498516083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098133087158</t>
+    <t xml:space="preserve">1.25098145008087</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12124991416931</t>
+    <t xml:space="preserve">1.1212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1565,22 +1565,25 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051640987396</t>
+    <t xml:space="preserve">1.13051652908325</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19538223743439</t>
+    <t xml:space="preserve">1.1953821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198353767395</t>
+    <t xml:space="preserve">1.11198341846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -57593,7 +57596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57619,7 +57622,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2135" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57645,7 +57648,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2136" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57671,7 +57674,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2137" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57697,7 +57700,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2138" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57723,7 +57726,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2139" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57749,7 +57752,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2140" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57775,7 +57778,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57801,7 +57804,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2142" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57827,7 +57830,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2143" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57853,7 +57856,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57879,7 +57882,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57905,7 +57908,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57931,7 +57934,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2147" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57957,7 +57960,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57983,7 +57986,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2149" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58009,7 +58012,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2150" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58035,7 +58038,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2151" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58061,7 +58064,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2152" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58087,7 +58090,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2153" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58113,7 +58116,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2154" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58139,7 +58142,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2155" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58165,7 +58168,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2156" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58191,7 +58194,7 @@
         <v>1</v>
       </c>
       <c r="G2157" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58217,7 +58220,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58243,7 +58246,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2159" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58269,7 +58272,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2160" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58295,7 +58298,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2161" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58321,7 +58324,7 @@
         <v>1</v>
       </c>
       <c r="G2162" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58347,7 +58350,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2163" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58373,7 +58376,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2164" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58399,7 +58402,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58425,7 +58428,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2166" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58451,7 +58454,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2167" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58477,7 +58480,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2168" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58503,7 +58506,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58529,7 +58532,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58555,7 +58558,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2171" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58581,7 +58584,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2172" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58607,7 +58610,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58633,7 +58636,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2174" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58659,7 +58662,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2175" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58685,7 +58688,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2176" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58711,7 +58714,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2177" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58737,7 +58740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2178" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58763,7 +58766,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2179" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58789,7 +58792,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58815,7 +58818,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2181" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58841,7 +58844,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2182" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58867,7 +58870,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2183" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58893,7 +58896,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2184" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58919,7 +58922,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2185" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58945,7 +58948,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2186" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58971,7 +58974,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2187" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58997,7 +59000,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59023,7 +59026,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2189" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59049,7 +59052,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2190" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59075,7 +59078,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2191" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59101,7 +59104,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2192" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59127,7 +59130,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2193" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59153,7 +59156,7 @@
         <v>1</v>
       </c>
       <c r="G2194" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59179,7 +59182,7 @@
         <v>1</v>
       </c>
       <c r="G2195" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59205,7 +59208,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2196" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59231,7 +59234,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59257,7 +59260,7 @@
         <v>1</v>
       </c>
       <c r="G2198" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59283,7 +59286,7 @@
         <v>1</v>
       </c>
       <c r="G2199" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59309,7 +59312,7 @@
         <v>1</v>
       </c>
       <c r="G2200" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59335,7 +59338,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2201" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59361,7 +59364,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59387,7 +59390,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59413,7 +59416,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59439,7 +59442,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59465,7 +59468,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59491,7 +59494,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59517,7 +59520,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2208" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59543,7 +59546,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2209" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59569,7 +59572,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2210" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59595,7 +59598,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2211" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59621,7 +59624,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2212" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59647,7 +59650,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2213" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59673,7 +59676,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2214" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59699,7 +59702,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59725,7 +59728,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2216" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59751,7 +59754,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2217" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59777,7 +59780,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59803,7 +59806,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2219" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59829,7 +59832,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2220" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59855,7 +59858,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2221" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59881,7 +59884,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59907,7 +59910,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2223" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59933,7 +59936,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2224" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59959,7 +59962,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2225" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59985,7 +59988,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2226" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60011,7 +60014,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2227" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60037,7 +60040,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2228" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60063,7 +60066,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2229" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60089,7 +60092,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2230" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60115,7 +60118,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2231" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60141,7 +60144,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2232" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60167,7 +60170,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2233" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60193,7 +60196,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2234" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60219,7 +60222,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2235" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60245,7 +60248,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G2236" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60271,7 +60274,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2237" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60297,7 +60300,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2238" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60323,7 +60326,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2239" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60349,7 +60352,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60375,7 +60378,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60401,7 +60404,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2242" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60427,7 +60430,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2243" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60453,7 +60456,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2244" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60479,7 +60482,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2245" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60505,7 +60508,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60531,7 +60534,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2247" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60557,7 +60560,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2248" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60583,7 +60586,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2249" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60609,7 +60612,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2250" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60635,7 +60638,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2251" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60661,7 +60664,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2252" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60687,7 +60690,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2253" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60713,7 +60716,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2254" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60739,7 +60742,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2255" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60765,7 +60768,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2256" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60791,7 +60794,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2257" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60817,7 +60820,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2258" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60843,7 +60846,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2259" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60869,7 +60872,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2260" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60895,7 +60898,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2261" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60921,7 +60924,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2262" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60947,7 +60950,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2263" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60973,7 +60976,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2264" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60999,7 +61002,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2265" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61025,7 +61028,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2266" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61051,7 +61054,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2267" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61077,7 +61080,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2268" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61103,7 +61106,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2269" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61129,7 +61132,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2270" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61155,7 +61158,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61181,7 +61184,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2272" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61207,7 +61210,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2273" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61233,7 +61236,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2274" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61259,7 +61262,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2275" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61285,7 +61288,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2276" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61311,7 +61314,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2277" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61337,7 +61340,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2278" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61363,7 +61366,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2279" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61389,7 +61392,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2280" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61415,7 +61418,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2281" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61441,7 +61444,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2282" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61467,7 +61470,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61493,7 +61496,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2284" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61519,7 +61522,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2285" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61545,7 +61548,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2286" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61571,7 +61574,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2287" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61597,7 +61600,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2288" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61623,7 +61626,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2289" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61649,7 +61652,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2290" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61675,7 +61678,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2291" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61701,7 +61704,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2292" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61727,7 +61730,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2293" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61753,7 +61756,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2294" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61779,7 +61782,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61805,7 +61808,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2296" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61831,7 +61834,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2297" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61857,7 +61860,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2298" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61883,7 +61886,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2299" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61909,7 +61912,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61935,7 +61938,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2301" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61961,7 +61964,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2302" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61987,7 +61990,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2303" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62013,7 +62016,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2304" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62039,7 +62042,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2305" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62065,7 +62068,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2306" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62091,7 +62094,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2307" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62117,7 +62120,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2308" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62143,7 +62146,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2309" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62169,7 +62172,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2310" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62195,7 +62198,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2311" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62221,7 +62224,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2312" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62247,7 +62250,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2313" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62273,7 +62276,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2314" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62299,7 +62302,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62325,7 +62328,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2316" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62351,7 +62354,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2317" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62377,7 +62380,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2318" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62403,7 +62406,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2319" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62429,7 +62432,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2320" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62455,7 +62458,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2321" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62481,7 +62484,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2322" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62507,7 +62510,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2323" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62533,7 +62536,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2324" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62559,7 +62562,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2325" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62585,7 +62588,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2326" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62611,7 +62614,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2327" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62637,7 +62640,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2328" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62663,7 +62666,7 @@
         <v>0.875</v>
       </c>
       <c r="G2329" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62689,7 +62692,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2330" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62715,7 +62718,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2331" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62741,7 +62744,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2332" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62767,7 +62770,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2333" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62793,7 +62796,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2334" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62819,7 +62822,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2335" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62845,7 +62848,7 @@
         <v>0.875</v>
       </c>
       <c r="G2336" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62871,7 +62874,7 @@
         <v>0.875</v>
       </c>
       <c r="G2337" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62897,7 +62900,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2338" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62923,7 +62926,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2339" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62949,7 +62952,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2340" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62975,7 +62978,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2341" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63001,7 +63004,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2342" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63027,7 +63030,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2343" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63053,7 +63056,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2344" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63079,7 +63082,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2345" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63105,7 +63108,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2346" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63131,7 +63134,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2347" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63157,7 +63160,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2348" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63183,7 +63186,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2349" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63209,7 +63212,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2350" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63235,7 +63238,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2351" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63261,7 +63264,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2352" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63287,7 +63290,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2353" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63313,7 +63316,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2354" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63339,7 +63342,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2355" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63365,7 +63368,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2356" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63391,7 +63394,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2357" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63417,7 +63420,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2358" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63443,7 +63446,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2359" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63469,7 +63472,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2360" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63495,7 +63498,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2361" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63521,7 +63524,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2362" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63547,7 +63550,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2363" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63573,7 +63576,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2364" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63599,7 +63602,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2365" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63625,7 +63628,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2366" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63651,7 +63654,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2367" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63677,7 +63680,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G2368" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63703,7 +63706,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2369" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63729,7 +63732,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2370" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63755,7 +63758,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2371" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63781,7 +63784,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2372" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63807,7 +63810,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2373" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63833,7 +63836,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2374" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63859,7 +63862,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2375" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63885,7 +63888,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2376" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63911,7 +63914,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2377" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63937,7 +63940,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2378" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63963,7 +63966,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2379" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63989,7 +63992,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2380" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64015,7 +64018,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64041,7 +64044,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2382" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64067,7 +64070,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2383" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64093,7 +64096,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64119,7 +64122,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64145,7 +64148,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2386" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64171,7 +64174,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2387" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64197,7 +64200,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2388" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64223,7 +64226,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2389" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64249,7 +64252,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2390" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64275,7 +64278,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2391" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64301,7 +64304,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2392" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64327,7 +64330,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2393" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64353,7 +64356,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2394" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64379,7 +64382,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2395" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64405,7 +64408,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2396" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64431,7 +64434,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2397" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64457,7 +64460,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2398" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64483,7 +64486,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2399" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64509,7 +64512,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2400" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64535,7 +64538,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2401" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64561,7 +64564,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2402" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64587,7 +64590,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2403" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64613,7 +64616,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2404" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64639,7 +64642,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2405" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64665,7 +64668,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2406" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64691,7 +64694,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2407" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64717,7 +64720,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2408" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64743,7 +64746,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2409" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64769,7 +64772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2410" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64795,7 +64798,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2411" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64821,7 +64824,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2412" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64847,7 +64850,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2413" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64873,7 +64876,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2414" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64899,7 +64902,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2415" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64925,7 +64928,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2416" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64951,7 +64954,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2417" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64977,7 +64980,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2418" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65003,7 +65006,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2419" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65029,7 +65032,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65055,7 +65058,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2421" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65081,7 +65084,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2422" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65107,7 +65110,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2423" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65133,7 +65136,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2424" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65159,7 +65162,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2425" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65185,7 +65188,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2426" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65211,7 +65214,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2427" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65237,7 +65240,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2428" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65263,7 +65266,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2429" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65289,7 +65292,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2430" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65315,7 +65318,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2431" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65341,7 +65344,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2432" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65367,7 +65370,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2433" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65393,7 +65396,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2434" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65419,7 +65422,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2435" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65445,7 +65448,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2436" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65471,7 +65474,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2437" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65497,7 +65500,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2438" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65523,7 +65526,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2439" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65549,7 +65552,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2440" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65575,7 +65578,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2441" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65601,7 +65604,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2442" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65627,7 +65630,7 @@
         <v>1</v>
       </c>
       <c r="G2443" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65653,7 +65656,7 @@
         <v>1</v>
       </c>
       <c r="G2444" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65679,7 +65682,7 @@
         <v>1</v>
       </c>
       <c r="G2445" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65705,7 +65708,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65731,7 +65734,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65757,7 +65760,7 @@
         <v>1</v>
       </c>
       <c r="G2448" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65783,7 +65786,7 @@
         <v>1</v>
       </c>
       <c r="G2449" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65809,7 +65812,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2450" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65835,7 +65838,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65861,7 +65864,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2452" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65887,7 +65890,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2453" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65913,7 +65916,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2454" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65939,7 +65942,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65965,7 +65968,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2456" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65991,7 +65994,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2457" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66017,7 +66020,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2458" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66043,7 +66046,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2459" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66069,7 +66072,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2460" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66095,7 +66098,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2461" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66121,7 +66124,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2462" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66147,7 +66150,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2463" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66173,7 +66176,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2464" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66199,7 +66202,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2465" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66225,7 +66228,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66251,7 +66254,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2467" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66277,7 +66280,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66303,7 +66306,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2469" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66329,7 +66332,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2470" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66355,7 +66358,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2471" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66381,7 +66384,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2472" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66407,7 +66410,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2473" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66433,7 +66436,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2474" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66459,7 +66462,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2475" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66485,7 +66488,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2476" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66511,7 +66514,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2477" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66537,7 +66540,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66563,7 +66566,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2479" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66589,7 +66592,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2480" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66615,7 +66618,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66641,7 +66644,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G2482" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66667,7 +66670,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2483" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66693,7 +66696,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2484" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66719,7 +66722,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2485" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66745,7 +66748,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2486" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66771,7 +66774,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2487" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66797,7 +66800,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2488" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66823,7 +66826,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2489" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66849,7 +66852,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2490" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66875,7 +66878,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2491" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66901,7 +66904,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2492" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66927,7 +66930,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2493" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66953,7 +66956,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2494" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66979,7 +66982,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2495" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67005,7 +67008,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2496" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67031,7 +67034,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2497" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67057,7 +67060,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2498" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67083,7 +67086,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2499" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67109,7 +67112,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2500" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67135,7 +67138,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2501" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67161,7 +67164,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2502" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67187,7 +67190,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2503" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67213,7 +67216,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2504" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67239,7 +67242,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2505" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67265,7 +67268,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2506" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67291,7 +67294,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2507" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67317,7 +67320,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2508" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67343,7 +67346,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67369,7 +67372,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2510" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67395,7 +67398,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2511" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67421,7 +67424,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2512" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67447,7 +67450,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2513" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67473,7 +67476,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2514" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67499,7 +67502,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2515" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67525,7 +67528,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2516" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67551,7 +67554,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2517" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67577,9 +67580,35 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2518" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.3333333333</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.43781745433807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684310913086</t>
+    <t xml:space="preserve">1.48684322834015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424724578857</t>
+    <t xml:space="preserve">1.44424712657928</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593257427216</t>
+    <t xml:space="preserve">1.37593269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414053916931</t>
+    <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744750499725</t>
+    <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3662885427475</t>
+    <t xml:space="preserve">1.36628830432892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290283203125</t>
+    <t xml:space="preserve">1.41290295124054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3815586566925</t>
+    <t xml:space="preserve">1.38155853748322</t>
   </si>
   <si>
     <t xml:space="preserve">1.40647327899933</t>
@@ -83,37 +83,37 @@
     <t xml:space="preserve">1.44585454463959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39843618869781</t>
+    <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
     <t xml:space="preserve">1.34780335426331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726276874542</t>
+    <t xml:space="preserve">1.31726288795471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002914905548</t>
+    <t xml:space="preserve">1.31002926826477</t>
   </si>
   <si>
     <t xml:space="preserve">1.34217727184296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021424293518</t>
+    <t xml:space="preserve">1.35021412372589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128119468689</t>
+    <t xml:space="preserve">1.3212810754776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557720184326</t>
+    <t xml:space="preserve">1.38557708263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273231506348</t>
+    <t xml:space="preserve">1.46273219585419</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693571567535</t>
+    <t xml:space="preserve">1.50693559646606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49889874458313</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274653434753</t>
+    <t xml:space="preserve">1.55274641513824</t>
   </si>
   <si>
     <t xml:space="preserve">1.61543500423431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169404029846</t>
+    <t xml:space="preserve">1.67169392108917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490887641907</t>
+    <t xml:space="preserve">1.67490899562836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6459755897522</t>
+    <t xml:space="preserve">1.64597547054291</t>
   </si>
   <si>
     <t xml:space="preserve">1.55113911628723</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095402240753</t>
+    <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630264282227</t>
+    <t xml:space="preserve">1.45630276203156</t>
   </si>
   <si>
     <t xml:space="preserve">1.43862128257751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41209924221039</t>
+    <t xml:space="preserve">1.4120991230011</t>
   </si>
   <si>
     <t xml:space="preserve">1.45601904392242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426251411438</t>
+    <t xml:space="preserve">1.43426239490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.40832185745239</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840492725372</t>
+    <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41334247589111</t>
+    <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
     <t xml:space="preserve">1.40497469902039</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">1.36313498020172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560381412506</t>
+    <t xml:space="preserve">1.35560393333435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3723396062851</t>
+    <t xml:space="preserve">1.37233972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886790275574</t>
+    <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288589000702</t>
+    <t xml:space="preserve">1.30288600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325479388237</t>
+    <t xml:space="preserve">1.32547926902771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213222980499</t>
+    <t xml:space="preserve">1.32213199138641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439356803894</t>
+    <t xml:space="preserve">1.26439344882965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702830314636</t>
+    <t xml:space="preserve">1.29702842235565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539619922638</t>
+    <t xml:space="preserve">1.30539643764496</t>
   </si>
   <si>
     <t xml:space="preserve">1.36397171020508</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">1.41250574588776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38070774078369</t>
+    <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050000667572</t>
+    <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22506427764893</t>
+    <t xml:space="preserve">1.22506415843964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2049812078476</t>
+    <t xml:space="preserve">1.20498132705688</t>
   </si>
   <si>
     <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841143608093</t>
+    <t xml:space="preserve">1.22841155529022</t>
   </si>
   <si>
     <t xml:space="preserve">1.23845291137695</t>
@@ -251,28 +251,28 @@
     <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14473223686218</t>
+    <t xml:space="preserve">1.14473211765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171723842621</t>
+    <t xml:space="preserve">1.22171711921692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816246509552</t>
+    <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226316452026</t>
+    <t xml:space="preserve">1.15226328372955</t>
   </si>
   <si>
     <t xml:space="preserve">1.14222180843353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17150950431824</t>
+    <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
     <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293399333954</t>
+    <t xml:space="preserve">1.11293411254883</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850101470947</t>
@@ -284,46 +284,46 @@
     <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03929626941681</t>
+    <t xml:space="preserve">1.03929615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435860157013</t>
+    <t xml:space="preserve">1.05435848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364617824554</t>
+    <t xml:space="preserve">1.08364629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06440019607544</t>
+    <t xml:space="preserve">1.06439995765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07109439373016</t>
+    <t xml:space="preserve">1.07109451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0376228094101</t>
+    <t xml:space="preserve">1.03762269020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0083349943161</t>
+    <t xml:space="preserve">1.00833523273468</t>
   </si>
   <si>
     <t xml:space="preserve">0.984068036079407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967038631439</t>
+    <t xml:space="preserve">0.999966979026794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251888275146</t>
+    <t xml:space="preserve">1.01251900196075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00415086746216</t>
+    <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127439022064</t>
+    <t xml:space="preserve">0.958127319812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842612743378</t>
+    <t xml:space="preserve">0.969842553138733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944738626480103</t>
+    <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
     <t xml:space="preserve">0.888673663139343</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">0.89955198764801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204829216003</t>
+    <t xml:space="preserve">0.896204710006714</t>
   </si>
   <si>
     <t xml:space="preserve">0.871937870979309</t>
@@ -350,67 +350,67 @@
     <t xml:space="preserve">0.908756613731384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596272945404</t>
+    <t xml:space="preserve">0.950596392154694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124450206757</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471727848053</t>
+    <t xml:space="preserve">0.920471847057343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332184314728</t>
+    <t xml:space="preserve">0.967332124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311446666718</t>
+    <t xml:space="preserve">0.962311327457428</t>
   </si>
   <si>
     <t xml:space="preserve">1.05519533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991598963737488</t>
+    <t xml:space="preserve">0.991599082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088773727417</t>
+    <t xml:space="preserve">0.989088892936707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00164067745209</t>
+    <t xml:space="preserve">1.0016405582428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783090591431</t>
+    <t xml:space="preserve">0.995783269405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99076235294342</t>
+    <t xml:space="preserve">0.990762293338776</t>
   </si>
   <si>
     <t xml:space="preserve">0.937207520008087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394456863403</t>
+    <t xml:space="preserve">0.982394397258759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391706466675</t>
+    <t xml:space="preserve">0.94139152765274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251924514771</t>
+    <t xml:space="preserve">0.988251984119415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352862358093</t>
+    <t xml:space="preserve">0.972352981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168795108795</t>
+    <t xml:space="preserve">0.968168914318085</t>
   </si>
   <si>
     <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98323130607605</t>
+    <t xml:space="preserve">0.983231127262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415075302124</t>
+    <t xml:space="preserve">0.987415254116058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005644321442</t>
+    <t xml:space="preserve">0.969005882740021</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
@@ -419,91 +419,91 @@
     <t xml:space="preserve">0.9539435505867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0585423707962</t>
+    <t xml:space="preserve">1.05854260921478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937945842743</t>
+    <t xml:space="preserve">1.05937933921814</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268490314484</t>
+    <t xml:space="preserve">1.05268502235413</t>
   </si>
   <si>
     <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636434078217</t>
+    <t xml:space="preserve">1.13636422157288</t>
   </si>
   <si>
     <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577658176422</t>
+    <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
     <t xml:space="preserve">1.19661319255829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602555274963</t>
+    <t xml:space="preserve">1.25602543354034</t>
   </si>
   <si>
     <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2133492231369</t>
+    <t xml:space="preserve">1.21334910392761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21753299236298</t>
+    <t xml:space="preserve">1.21753311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644717216492</t>
+    <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1531001329422</t>
+    <t xml:space="preserve">1.15310001373291</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242918491364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493973255157</t>
+    <t xml:space="preserve">1.19493961334229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1547737121582</t>
+    <t xml:space="preserve">1.15477383136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1464056968689</t>
+    <t xml:space="preserve">1.14640581607819</t>
   </si>
   <si>
     <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314160823822</t>
+    <t xml:space="preserve">1.16314148902893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2376161813736</t>
+    <t xml:space="preserve">1.23761594295502</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518882274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23594260215759</t>
+    <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146790981293</t>
+    <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803768157959</t>
+    <t xml:space="preserve">1.13803780078888</t>
   </si>
   <si>
     <t xml:space="preserve">1.12799644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130200862885</t>
+    <t xml:space="preserve">1.12130188941956</t>
   </si>
   <si>
     <t xml:space="preserve">1.17653036117554</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">1.40581130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576983451843</t>
+    <t xml:space="preserve">1.39576995372772</t>
   </si>
   <si>
     <t xml:space="preserve">1.39911711215973</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534809589386</t>
+    <t xml:space="preserve">1.49534821510315</t>
   </si>
   <si>
     <t xml:space="preserve">1.45685589313507</t>
@@ -533,40 +533,40 @@
     <t xml:space="preserve">1.48865389823914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48949074745178</t>
+    <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275483608246</t>
+    <t xml:space="preserve">1.47275495529175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551435470581</t>
+    <t xml:space="preserve">1.53551423549652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57316994667053</t>
+    <t xml:space="preserve">1.57317006587982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58572196960449</t>
+    <t xml:space="preserve">1.58572173118591</t>
   </si>
   <si>
     <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438019275665</t>
+    <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550748825073</t>
+    <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
     <t xml:space="preserve">1.75726413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77400004863739</t>
+    <t xml:space="preserve">1.7739999294281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7823680639267</t>
+    <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">1.67358493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003028392792</t>
+    <t xml:space="preserve">1.62003016471863</t>
   </si>
   <si>
     <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6166832447052</t>
+    <t xml:space="preserve">1.61668300628662</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664165019989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68195283412933</t>
+    <t xml:space="preserve">1.68195295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362665176392</t>
+    <t xml:space="preserve">1.68362653255463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542465686798</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718130588531</t>
+    <t xml:space="preserve">1.73718118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224363803864</t>
+    <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
     <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72379243373871</t>
+    <t xml:space="preserve">1.72379267215729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601229667664</t>
+    <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
     <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74906098842621</t>
+    <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337329864502</t>
+    <t xml:space="preserve">1.84337306022644</t>
   </si>
   <si>
     <t xml:space="preserve">1.80050384998322</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323594093323</t>
+    <t xml:space="preserve">2.37323570251465</t>
   </si>
   <si>
     <t xml:space="preserve">2.46926283836365</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936334609985</t>
+    <t xml:space="preserve">2.82936358451843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505163192749</t>
+    <t xml:space="preserve">2.73505139350891</t>
   </si>
   <si>
     <t xml:space="preserve">2.64416885375977</t>
@@ -665,43 +665,43 @@
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.58929634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7864944934845</t>
+    <t xml:space="preserve">2.78649401664734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503428459167</t>
+    <t xml:space="preserve">2.67503476142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4624035358429</t>
+    <t xml:space="preserve">2.46240377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097754478455</t>
+    <t xml:space="preserve">2.47097730636597</t>
   </si>
   <si>
     <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41953468322754</t>
+    <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5292797088623</t>
+    <t xml:space="preserve">2.52927947044373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214879989624</t>
+    <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641061782837</t>
+    <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349672794342</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">2.4572594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5361385345459</t>
+    <t xml:space="preserve">2.53613829612732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897388458252</t>
+    <t xml:space="preserve">2.45897436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440695762634</t>
+    <t xml:space="preserve">2.47440671920776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56186008453369</t>
+    <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781973838806</t>
+    <t xml:space="preserve">2.41781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.38180994987488</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208131790161</t>
+    <t xml:space="preserve">2.33208155632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836366653442</t>
+    <t xml:space="preserve">2.31836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2806384563446</t>
+    <t xml:space="preserve">2.28063869476318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865214347839</t>
+    <t xml:space="preserve">2.32865190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31321907043457</t>
+    <t xml:space="preserve">2.31321883201599</t>
   </si>
   <si>
     <t xml:space="preserve">2.26692032814026</t>
@@ -758,28 +758,28 @@
     <t xml:space="preserve">2.126309633255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12116503715515</t>
+    <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800746917725</t>
+    <t xml:space="preserve">2.06800723075867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0577187538147</t>
+    <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09544396400452</t>
+    <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773562431335</t>
+    <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1280243396759</t>
+    <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
     <t xml:space="preserve">2.08515501022339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629300117493</t>
+    <t xml:space="preserve">2.06629276275635</t>
   </si>
   <si>
     <t xml:space="preserve">2.08344054222107</t>
@@ -788,58 +788,58 @@
     <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799083709717</t>
+    <t xml:space="preserve">2.00799036026001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05086016654968</t>
+    <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342343330383</t>
+    <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603802680969</t>
+    <t xml:space="preserve">2.17603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172559738159</t>
+    <t xml:space="preserve">2.08172535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401749610901</t>
+    <t xml:space="preserve">2.10401725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15888977050781</t>
+    <t xml:space="preserve">2.15889000892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12287974357605</t>
+    <t xml:space="preserve">2.12287998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15374565124512</t>
+    <t xml:space="preserve">2.1537458896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15203070640564</t>
+    <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917848587036</t>
+    <t xml:space="preserve">2.16917896270752</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062134742737</t>
+    <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491714477539</t>
+    <t xml:space="preserve">2.25491690635681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28235340118408</t>
+    <t xml:space="preserve">2.2823531627655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23776912689209</t>
+    <t xml:space="preserve">2.23776936531067</t>
   </si>
   <si>
     <t xml:space="preserve">2.22233629226685</t>
@@ -848,52 +848,52 @@
     <t xml:space="preserve">2.17089366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975591659546</t>
+    <t xml:space="preserve">2.18975567817688</t>
   </si>
   <si>
     <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634313583374</t>
+    <t xml:space="preserve">2.24634289741516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065556526184</t>
+    <t xml:space="preserve">2.34065532684326</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27034974098206</t>
+    <t xml:space="preserve">2.27034997940063</t>
   </si>
   <si>
     <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175933837891</t>
+    <t xml:space="preserve">2.20175957679749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2086181640625</t>
+    <t xml:space="preserve">2.20861840248108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28749752044678</t>
+    <t xml:space="preserve">2.2874972820282</t>
   </si>
   <si>
     <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462842941284</t>
+    <t xml:space="preserve">2.24462866783142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4366819858551</t>
+    <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
     <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527262687683</t>
+    <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51384687423706</t>
+    <t xml:space="preserve">2.51384663581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.50355815887451</t>
@@ -908,28 +908,28 @@
     <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32007813453674</t>
+    <t xml:space="preserve">2.32007789611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809134483337</t>
+    <t xml:space="preserve">2.36809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33379626274109</t>
+    <t xml:space="preserve">2.33379602432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439008712769</t>
+    <t xml:space="preserve">2.41439032554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922885894775</t>
+    <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410161018372</t>
+    <t xml:space="preserve">2.40410137176514</t>
   </si>
   <si>
     <t xml:space="preserve">2.39038348197937</t>
@@ -944,34 +944,34 @@
     <t xml:space="preserve">2.38866877555847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31493401527405</t>
+    <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832944869995</t>
+    <t xml:space="preserve">2.19832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430644989014</t>
+    <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632650375366</t>
+    <t xml:space="preserve">2.18632626533508</t>
   </si>
   <si>
     <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201431274414</t>
+    <t xml:space="preserve">2.09201455116272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04057145118713</t>
+    <t xml:space="preserve">2.04057121276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914522171021</t>
+    <t xml:space="preserve">2.04914498329163</t>
   </si>
   <si>
     <t xml:space="preserve">1.90339004993439</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">1.9805543422699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198069095612</t>
+    <t xml:space="preserve">1.97198057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053759098053</t>
+    <t xml:space="preserve">1.92053747177124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912811279297</t>
+    <t xml:space="preserve">1.98912823200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196393966675</t>
+    <t xml:space="preserve">1.91196405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911171913147</t>
+    <t xml:space="preserve">1.9291113615036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624250888824</t>
   </si>
   <si>
     <t xml:space="preserve">1.89481616020203</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">1.86909461021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194706916809</t>
+    <t xml:space="preserve">1.85194718837738</t>
   </si>
   <si>
     <t xml:space="preserve">1.94625926017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340680122375</t>
+    <t xml:space="preserve">1.96340692043304</t>
   </si>
   <si>
     <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249334335327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236526012421</t>
+    <t xml:space="preserve">1.97236514091492</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100263595581</t>
@@ -1028,76 +1028,76 @@
     <t xml:space="preserve">1.85840594768524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470458984375</t>
+    <t xml:space="preserve">1.88470447063446</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866330623627</t>
+    <t xml:space="preserve">1.99866318702698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606673717499</t>
+    <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853474617004</t>
+    <t xml:space="preserve">1.92853462696075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717224121094</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223670005798</t>
+    <t xml:space="preserve">1.9022364616394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593841552734</t>
+    <t xml:space="preserve">1.87593853473663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334172725677</t>
+    <t xml:space="preserve">1.82334196567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976881027222</t>
+    <t xml:space="preserve">1.91976869106293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84964001178741</t>
+    <t xml:space="preserve">1.84963989257812</t>
   </si>
   <si>
     <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730056285858</t>
+    <t xml:space="preserve">1.93730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989737033844</t>
+    <t xml:space="preserve">1.98989713191986</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7882776260376</t>
+    <t xml:space="preserve">1.78827774524689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77074551582336</t>
+    <t xml:space="preserve">1.77074539661407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.797043800354</t>
+    <t xml:space="preserve">1.79704368114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76197957992554</t>
+    <t xml:space="preserve">1.76197946071625</t>
   </si>
   <si>
     <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542429447174</t>
+    <t xml:space="preserve">1.59542417526245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62172245979309</t>
+    <t xml:space="preserve">1.6217223405838</t>
   </si>
   <si>
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308472633362</t>
+    <t xml:space="preserve">1.68308484554291</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">1.69185090065002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66116964817047</t>
+    <t xml:space="preserve">1.66116976737976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789194583893</t>
+    <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
     <t xml:space="preserve">1.60419023036957</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295628547668</t>
+    <t xml:space="preserve">1.61295640468597</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925445079803</t>
+    <t xml:space="preserve">1.63925457000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.58665812015533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597686767578</t>
+    <t xml:space="preserve">1.55597674846649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42010283470154</t>
+    <t xml:space="preserve">1.42010271549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42448580265045</t>
+    <t xml:space="preserve">1.42448592185974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32367599010468</t>
+    <t xml:space="preserve">1.32367610931396</t>
   </si>
   <si>
     <t xml:space="preserve">1.29737794399261</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065564632416</t>
+    <t xml:space="preserve">1.38065552711487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41571974754333</t>
+    <t xml:space="preserve">1.41571986675262</t>
   </si>
   <si>
     <t xml:space="preserve">1.4025707244873</t>
@@ -1193,34 +1193,34 @@
     <t xml:space="preserve">1.38942170143127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38503873348236</t>
+    <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874032974243</t>
+    <t xml:space="preserve">1.35874044895172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763482570648</t>
+    <t xml:space="preserve">1.43763506412506</t>
   </si>
   <si>
     <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201803207397</t>
+    <t xml:space="preserve">1.44201791286469</t>
   </si>
   <si>
     <t xml:space="preserve">1.4507839679718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39380466938019</t>
+    <t xml:space="preserve">1.3938045501709</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36750650405884</t>
+    <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406167030334</t>
+    <t xml:space="preserve">1.53406178951263</t>
   </si>
   <si>
     <t xml:space="preserve">1.5121465921402</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">1.54282772541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55159389972687</t>
+    <t xml:space="preserve">1.55159378051758</t>
   </si>
   <si>
     <t xml:space="preserve">1.56035995483398</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584830760956</t>
+    <t xml:space="preserve">1.48584842681885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51652956008911</t>
+    <t xml:space="preserve">1.51652944087982</t>
   </si>
   <si>
     <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776338577271</t>
+    <t xml:space="preserve">1.50776350498199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529573440552</t>
+    <t xml:space="preserve">1.52529561519623</t>
   </si>
   <si>
     <t xml:space="preserve">1.49899733066559</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545706748962</t>
+    <t xml:space="preserve">1.60545694828033</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232096672058</t>
+    <t xml:space="preserve">1.54232108592987</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
     <t xml:space="preserve">1.46114635467529</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801013469696</t>
+    <t xml:space="preserve">1.39801025390625</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702974796295</t>
+    <t xml:space="preserve">1.40702962875366</t>
   </si>
   <si>
     <t xml:space="preserve">1.38899087905884</t>
@@ -1322,25 +1322,25 @@
     <t xml:space="preserve">1.3438937664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31683552265167</t>
+    <t xml:space="preserve">1.31683564186096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271903514862</t>
+    <t xml:space="preserve">1.26271891593933</t>
   </si>
   <si>
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056367874146</t>
+    <t xml:space="preserve">1.19056355953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
     <t xml:space="preserve">1.22664129734039</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
     <t xml:space="preserve">1.36193251609802</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">1.65055406093597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859304904938</t>
+    <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
     <t xml:space="preserve">1.64153480529785</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">1.59643757343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486477375031</t>
+    <t xml:space="preserve">1.79486489295959</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">1.71369016170502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349569797516</t>
+    <t xml:space="preserve">1.62349581718445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55134046077728</t>
+    <t xml:space="preserve">1.55134057998657</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69565117359161</t>
+    <t xml:space="preserve">1.6956512928009</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840832233429</t>
+    <t xml:space="preserve">1.118408203125</t>
   </si>
   <si>
     <t xml:space="preserve">1.16350531578064</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1274276971817</t>
+    <t xml:space="preserve">1.12742757797241</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25369954109192</t>
+    <t xml:space="preserve">1.25369966030121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">1.08233058452606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04625284671783</t>
+    <t xml:space="preserve">1.04625272750854</t>
   </si>
   <si>
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331120967865</t>
+    <t xml:space="preserve">1.07331132888794</t>
   </si>
   <si>
     <t xml:space="preserve">1.05527222156525</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0101752281189</t>
+    <t xml:space="preserve">1.01017510890961</t>
   </si>
   <si>
     <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00115573406219</t>
+    <t xml:space="preserve">1.00115585327148</t>
   </si>
   <si>
     <t xml:space="preserve">0.965078175067902</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019752502441</t>
+    <t xml:space="preserve">0.938019812107086</t>
   </si>
   <si>
     <t xml:space="preserve">0.919980943202972</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432386875153</t>
+    <t xml:space="preserve">0.897432446479797</t>
   </si>
   <si>
     <t xml:space="preserve">0.910961508750916</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20860254764557</t>
+    <t xml:space="preserve">1.20860242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918498516083</t>
+    <t xml:space="preserve">1.47918510437012</t>
   </si>
   <si>
     <t xml:space="preserve">1.25098145008087</t>
@@ -67612,6 +67612,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.3333333333</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6832060185</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>400</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>574</v>
+      </c>
+      <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781745433807</t>
+    <t xml:space="preserve">1.43781757354736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684322834015</t>
+    <t xml:space="preserve">1.48684298992157</t>
   </si>
   <si>
     <t xml:space="preserve">1.44424712657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42254722118378</t>
+    <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
     <t xml:space="preserve">1.38236236572266</t>
@@ -62,49 +62,49 @@
     <t xml:space="preserve">1.37593269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414041996002</t>
+    <t xml:space="preserve">1.33414030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744762420654</t>
+    <t xml:space="preserve">1.35744774341583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628830432892</t>
+    <t xml:space="preserve">1.3662885427475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290295124054</t>
+    <t xml:space="preserve">1.41290283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38155853748322</t>
+    <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647327899933</t>
+    <t xml:space="preserve">1.40647315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44585454463959</t>
+    <t xml:space="preserve">1.44585466384888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3984363079071</t>
+    <t xml:space="preserve">1.39843618869781</t>
   </si>
   <si>
     <t xml:space="preserve">1.34780335426331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726288795471</t>
+    <t xml:space="preserve">1.31726264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002926826477</t>
+    <t xml:space="preserve">1.31002950668335</t>
   </si>
   <si>
     <t xml:space="preserve">1.34217727184296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021412372589</t>
+    <t xml:space="preserve">1.35021424293518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3212810754776</t>
+    <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557708263397</t>
+    <t xml:space="preserve">1.38557720184326</t>
   </si>
   <si>
     <t xml:space="preserve">1.46273219585419</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693559646606</t>
+    <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889874458313</t>
+    <t xml:space="preserve">1.49889862537384</t>
   </si>
   <si>
     <t xml:space="preserve">1.47237658500671</t>
@@ -125,31 +125,31 @@
     <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274641513824</t>
+    <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
     <t xml:space="preserve">1.61543500423431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169392108917</t>
+    <t xml:space="preserve">1.67169380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490899562836</t>
+    <t xml:space="preserve">1.67490875720978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64597547054291</t>
+    <t xml:space="preserve">1.64597570896149</t>
   </si>
   <si>
     <t xml:space="preserve">1.55113911628723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702808380127</t>
+    <t xml:space="preserve">1.52702820301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630276203156</t>
+    <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
     <t xml:space="preserve">1.43862128257751</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.4120991230011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601904392242</t>
+    <t xml:space="preserve">1.45601892471313</t>
   </si>
   <si>
     <t xml:space="preserve">1.43426239490509</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">1.40832185745239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42254734039307</t>
+    <t xml:space="preserve">1.42254745960236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091523647308</t>
+    <t xml:space="preserve">1.43091511726379</t>
   </si>
   <si>
     <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4133425951004</t>
+    <t xml:space="preserve">1.41334271430969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40497469902039</t>
+    <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313498020172</t>
+    <t xml:space="preserve">1.36313486099243</t>
   </si>
   <si>
     <t xml:space="preserve">1.35560393333435</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288600921631</t>
+    <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32547926902771</t>
+    <t xml:space="preserve">1.325479388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213199138641</t>
+    <t xml:space="preserve">1.32213222980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439344882965</t>
+    <t xml:space="preserve">1.26439356803894</t>
   </si>
   <si>
     <t xml:space="preserve">1.29702842235565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539643764496</t>
+    <t xml:space="preserve">1.30539631843567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397171020508</t>
+    <t xml:space="preserve">1.36397194862366</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050012588501</t>
+    <t xml:space="preserve">1.3305002450943</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
@@ -233,25 +233,25 @@
     <t xml:space="preserve">1.22506415843964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20498132705688</t>
+    <t xml:space="preserve">1.2049812078476</t>
   </si>
   <si>
     <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841155529022</t>
+    <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845291137695</t>
+    <t xml:space="preserve">1.23845303058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008513450623</t>
+    <t xml:space="preserve">1.23008489608765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824541568756</t>
+    <t xml:space="preserve">1.18824529647827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14473211765289</t>
+    <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
     <t xml:space="preserve">1.22171711921692</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">1.15226328372955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14222180843353</t>
+    <t xml:space="preserve">1.14222157001495</t>
   </si>
   <si>
     <t xml:space="preserve">1.17150938510895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966990470886</t>
+    <t xml:space="preserve">1.12966978549957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293411254883</t>
+    <t xml:space="preserve">1.11293399333954</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850101470947</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03929615020752</t>
+    <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435848236084</t>
+    <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08364629745483</t>
+    <t xml:space="preserve">1.08364617824554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06439995765686</t>
+    <t xml:space="preserve">1.06440007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07109451293945</t>
+    <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
     <t xml:space="preserve">1.03762269020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00833523273468</t>
+    <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984068036079407</t>
+    <t xml:space="preserve">0.984067976474762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999966979026794</t>
+    <t xml:space="preserve">0.999967157840729</t>
   </si>
   <si>
     <t xml:space="preserve">1.01251900196075</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">1.00415098667145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127319812775</t>
+    <t xml:space="preserve">0.958127439022064</t>
   </si>
   <si>
     <t xml:space="preserve">0.969842553138733</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269911766052</t>
+    <t xml:space="preserve">0.952269852161407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103831768036</t>
+    <t xml:space="preserve">0.912103891372681</t>
   </si>
   <si>
     <t xml:space="preserve">0.89955198764801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204710006714</t>
+    <t xml:space="preserve">0.896204769611359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937870979309</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
     <t xml:space="preserve">0.908756613731384</t>
@@ -353,106 +353,106 @@
     <t xml:space="preserve">0.950596392154694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124569416046</t>
+    <t xml:space="preserve">0.917124509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471847057343</t>
+    <t xml:space="preserve">0.920471727848053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332124710083</t>
+    <t xml:space="preserve">0.967332065105438</t>
   </si>
   <si>
     <t xml:space="preserve">0.962311327457428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05519533157349</t>
+    <t xml:space="preserve">1.05519545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599082946777</t>
+    <t xml:space="preserve">0.991599023342133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088892936707</t>
+    <t xml:space="preserve">0.989088833332062</t>
   </si>
   <si>
     <t xml:space="preserve">1.0016405582428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783269405365</t>
+    <t xml:space="preserve">0.995783030986786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990762293338776</t>
+    <t xml:space="preserve">0.99076247215271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207520008087</t>
+    <t xml:space="preserve">0.937207639217377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394397258759</t>
+    <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94139152765274</t>
+    <t xml:space="preserve">0.941391706466675</t>
   </si>
   <si>
     <t xml:space="preserve">0.988251984119415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352981567383</t>
+    <t xml:space="preserve">0.972352802753448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168914318085</t>
+    <t xml:space="preserve">0.96816885471344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9757000207901</t>
+    <t xml:space="preserve">0.975700080394745</t>
   </si>
   <si>
     <t xml:space="preserve">0.983231127262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415254116058</t>
+    <t xml:space="preserve">0.987415134906769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005882740021</t>
+    <t xml:space="preserve">0.969005823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994109511375427</t>
+    <t xml:space="preserve">0.994109392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9539435505867</t>
+    <t xml:space="preserve">0.953943490982056</t>
   </si>
   <si>
     <t xml:space="preserve">1.05854260921478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937933921814</t>
+    <t xml:space="preserve">1.05937922000885</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268502235413</t>
+    <t xml:space="preserve">1.05268490314484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10456609725952</t>
+    <t xml:space="preserve">1.10456621646881</t>
   </si>
   <si>
     <t xml:space="preserve">1.13636422157288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1480792760849</t>
+    <t xml:space="preserve">1.14807951450348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577646255493</t>
+    <t xml:space="preserve">1.19577658176422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661319255829</t>
+    <t xml:space="preserve">1.19661331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25602543354034</t>
+    <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
     <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21334910392761</t>
+    <t xml:space="preserve">1.2133492231369</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753311157227</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">1.15310001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242918491364</t>
+    <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493961334229</t>
+    <t xml:space="preserve">1.19493985176086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15477383136749</t>
+    <t xml:space="preserve">1.15477347373962</t>
   </si>
   <si>
     <t xml:space="preserve">1.14640581607819</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">1.19159257411957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16314148902893</t>
+    <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23761594295502</t>
+    <t xml:space="preserve">1.23761606216431</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518882274628</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13803780078888</t>
+    <t xml:space="preserve">1.13803791999817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799644470215</t>
+    <t xml:space="preserve">1.12799632549286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130188941956</t>
+    <t xml:space="preserve">1.12130212783813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653036117554</t>
+    <t xml:space="preserve">1.17653024196625</t>
   </si>
   <si>
     <t xml:space="preserve">1.40581130981445</t>
@@ -524,46 +524,46 @@
     <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534821510315</t>
+    <t xml:space="preserve">1.49534809589386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685589313507</t>
+    <t xml:space="preserve">1.45685577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865389823914</t>
+    <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
     <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275495529175</t>
+    <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
     <t xml:space="preserve">1.53551423549652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57317006587982</t>
+    <t xml:space="preserve">1.57316994667053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58572173118591</t>
+    <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174533843994</t>
+    <t xml:space="preserve">1.63174557685852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684914588928</t>
+    <t xml:space="preserve">1.65684926509857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438031196594</t>
+    <t xml:space="preserve">1.66438019275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550760746002</t>
+    <t xml:space="preserve">1.73550772666931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726413726807</t>
+    <t xml:space="preserve">1.75726425647736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7739999294281</t>
+    <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
     <t xml:space="preserve">1.78236818313599</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67358493804932</t>
+    <t xml:space="preserve">1.67358505725861</t>
   </si>
   <si>
     <t xml:space="preserve">1.62003016471863</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61668300628662</t>
+    <t xml:space="preserve">1.6166832447052</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664165019989</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72379267215729</t>
+    <t xml:space="preserve">1.723792552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601241588593</t>
+    <t xml:space="preserve">1.65601229667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.74220204353333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7490611076355</t>
+    <t xml:space="preserve">1.74906098842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337306022644</t>
+    <t xml:space="preserve">1.84337317943573</t>
   </si>
   <si>
     <t xml:space="preserve">1.80050384998322</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">2.64416885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47783660888672</t>
+    <t xml:space="preserve">2.4778368473053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.460688829422</t>
+    <t xml:space="preserve">2.46068906784058</t>
   </si>
   <si>
     <t xml:space="preserve">2.40067172050476</t>
@@ -665,34 +665,34 @@
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48984003067017</t>
+    <t xml:space="preserve">2.48983979225159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929634094238</t>
+    <t xml:space="preserve">2.58929657936096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78649401664734</t>
+    <t xml:space="preserve">2.78649425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503476142883</t>
+    <t xml:space="preserve">2.67503452301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012826919556</t>
+    <t xml:space="preserve">2.50012874603271</t>
   </si>
   <si>
     <t xml:space="preserve">2.46240377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097730636597</t>
+    <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354104995728</t>
+    <t xml:space="preserve">2.44354128837585</t>
   </si>
   <si>
     <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211482048035</t>
+    <t xml:space="preserve">2.45211505889893</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4349672794342</t>
+    <t xml:space="preserve">2.43496751785278</t>
   </si>
   <si>
     <t xml:space="preserve">2.4555447101593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4572594165802</t>
+    <t xml:space="preserve">2.45725917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613829612732</t>
+    <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897436141968</t>
+    <t xml:space="preserve">2.45897459983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.47440671920776</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781997680664</t>
+    <t xml:space="preserve">2.41781973838806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38180994987488</t>
+    <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639327049255</t>
+    <t xml:space="preserve">2.42639350891113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3835244178772</t>
+    <t xml:space="preserve">2.38352417945862</t>
   </si>
   <si>
     <t xml:space="preserve">2.33208155632019</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">2.32865190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31321883201599</t>
+    <t xml:space="preserve">2.31321907043457</t>
   </si>
   <si>
     <t xml:space="preserve">2.26692032814026</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800723075867</t>
+    <t xml:space="preserve">2.06800770759583</t>
   </si>
   <si>
     <t xml:space="preserve">2.05771899223328</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12802457809448</t>
+    <t xml:space="preserve">2.1280243396759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515501022339</t>
+    <t xml:space="preserve">2.08515524864197</t>
   </si>
   <si>
     <t xml:space="preserve">2.06629276275635</t>
@@ -788,25 +788,25 @@
     <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799036026001</t>
+    <t xml:space="preserve">2.00799059867859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0508599281311</t>
+    <t xml:space="preserve">2.05085968971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342367172241</t>
+    <t xml:space="preserve">2.02342343330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2069034576416</t>
+    <t xml:space="preserve">2.20690369606018</t>
   </si>
   <si>
     <t xml:space="preserve">2.17603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172535896301</t>
+    <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10401725769043</t>
+    <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.15889000892639</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917896270752</t>
+    <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
     <t xml:space="preserve">2.27720880508423</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491690635681</t>
+    <t xml:space="preserve">2.25491714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.2823531627655</t>
@@ -842,52 +842,52 @@
     <t xml:space="preserve">2.23776936531067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233629226685</t>
+    <t xml:space="preserve">2.22233653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089366912842</t>
+    <t xml:space="preserve">2.17089343070984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975567817688</t>
+    <t xml:space="preserve">2.18975591659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634289741516</t>
+    <t xml:space="preserve">2.24634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065532684326</t>
+    <t xml:space="preserve">2.34065508842468</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27034997940063</t>
+    <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
     <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175957679749</t>
+    <t xml:space="preserve">2.20175933837891</t>
   </si>
   <si>
     <t xml:space="preserve">2.20861840248108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2874972820282</t>
+    <t xml:space="preserve">2.28749752044678</t>
   </si>
   <si>
     <t xml:space="preserve">2.2034740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24462866783142</t>
+    <t xml:space="preserve">2.24462842941284</t>
   </si>
   <si>
     <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471254348755</t>
+    <t xml:space="preserve">2.54471230506897</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527286529541</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326920509338</t>
+    <t xml:space="preserve">2.49326944351196</t>
   </si>
   <si>
     <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32007789611816</t>
+    <t xml:space="preserve">2.32007813453674</t>
   </si>
   <si>
     <t xml:space="preserve">2.32179260253906</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">2.33379602432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439032554626</t>
+    <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
     <t xml:space="preserve">2.34922909736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3578028678894</t>
+    <t xml:space="preserve">2.35780262947083</t>
   </si>
   <si>
     <t xml:space="preserve">2.40410137176514</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832992553711</t>
+    <t xml:space="preserve">2.19832968711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430621147156</t>
+    <t xml:space="preserve">2.11430644989014</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632626533508</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201455116272</t>
+    <t xml:space="preserve">2.09201431274414</t>
   </si>
   <si>
     <t xml:space="preserve">2.04057121276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01484966278076</t>
+    <t xml:space="preserve">2.01484942436218</t>
   </si>
   <si>
     <t xml:space="preserve">2.04914498329163</t>
@@ -980,52 +980,52 @@
     <t xml:space="preserve">1.9805543422699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198057174683</t>
+    <t xml:space="preserve">1.97198045253754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053747177124</t>
+    <t xml:space="preserve">1.92053759098053</t>
   </si>
   <si>
     <t xml:space="preserve">1.98912823200226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196405887604</t>
+    <t xml:space="preserve">1.91196382045746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9291113615036</t>
+    <t xml:space="preserve">1.92911148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624250888824</t>
+    <t xml:space="preserve">1.88624227046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481616020203</t>
+    <t xml:space="preserve">1.89481627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909461021423</t>
+    <t xml:space="preserve">1.86909472942352</t>
   </si>
   <si>
     <t xml:space="preserve">1.85194718837738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625926017761</t>
+    <t xml:space="preserve">1.94625902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340692043304</t>
+    <t xml:space="preserve">1.96340656280518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879162788391</t>
+    <t xml:space="preserve">2.06879186630249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249334335327</t>
+    <t xml:space="preserve">2.04249358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236514091492</t>
+    <t xml:space="preserve">1.97236502170563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100263595581</t>
+    <t xml:space="preserve">1.91100251674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840594768524</t>
+    <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
     <t xml:space="preserve">1.88470447063446</t>
@@ -1034,52 +1034,52 @@
     <t xml:space="preserve">2.02496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866318702698</t>
+    <t xml:space="preserve">1.99866330623627</t>
   </si>
   <si>
     <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853462696075</t>
+    <t xml:space="preserve">1.92853474617004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717236042023</t>
+    <t xml:space="preserve">1.86717247962952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9022364616394</t>
+    <t xml:space="preserve">1.90223670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593853473663</t>
+    <t xml:space="preserve">1.87593829631805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334196567535</t>
+    <t xml:space="preserve">1.82334184646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976869106293</t>
+    <t xml:space="preserve">1.91976881027222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84963989257812</t>
+    <t xml:space="preserve">1.84964001178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347052574158</t>
+    <t xml:space="preserve">1.89347040653229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730068206787</t>
+    <t xml:space="preserve">1.93730080127716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989713191986</t>
+    <t xml:space="preserve">1.98989725112915</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78827774524689</t>
+    <t xml:space="preserve">1.78827750682831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77074539661407</t>
+    <t xml:space="preserve">1.77074563503265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704368114471</t>
+    <t xml:space="preserve">1.79704356193542</t>
   </si>
   <si>
     <t xml:space="preserve">1.76197946071625</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542417526245</t>
+    <t xml:space="preserve">1.59542405605316</t>
   </si>
   <si>
     <t xml:space="preserve">1.6217223405838</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308484554291</t>
+    <t xml:space="preserve">1.68308472633362</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">1.69185090065002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66116976737976</t>
+    <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
     <t xml:space="preserve">1.57789206504822</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">1.60419023036957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5647429227829</t>
+    <t xml:space="preserve">1.56474280357361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59980726242065</t>
+    <t xml:space="preserve">1.59980738162994</t>
   </si>
   <si>
     <t xml:space="preserve">1.59104120731354</t>
@@ -1142,34 +1142,34 @@
     <t xml:space="preserve">1.64363753795624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295640468597</t>
+    <t xml:space="preserve">1.61295628547668</t>
   </si>
   <si>
     <t xml:space="preserve">1.58227503299713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63925457000732</t>
+    <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58665812015533</t>
+    <t xml:space="preserve">1.58665800094604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597674846649</t>
+    <t xml:space="preserve">1.55597698688507</t>
   </si>
   <si>
     <t xml:space="preserve">1.42010271549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42448592185974</t>
+    <t xml:space="preserve">1.42448580265045</t>
   </si>
   <si>
     <t xml:space="preserve">1.32367610931396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29737794399261</t>
+    <t xml:space="preserve">1.29737782478333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24478149414062</t>
+    <t xml:space="preserve">1.24478137493134</t>
   </si>
   <si>
     <t xml:space="preserve">1.20971727371216</t>
@@ -1178,34 +1178,34 @@
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065552711487</t>
+    <t xml:space="preserve">1.38065564632416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41571986675262</t>
+    <t xml:space="preserve">1.41571974754333</t>
   </si>
   <si>
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325185775757</t>
+    <t xml:space="preserve">1.43325197696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38942170143127</t>
+    <t xml:space="preserve">1.38942158222198</t>
   </si>
   <si>
     <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874044895172</t>
+    <t xml:space="preserve">1.35874021053314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763506412506</t>
+    <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
     <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201791286469</t>
+    <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
     <t xml:space="preserve">1.4507839679718</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406178951263</t>
+    <t xml:space="preserve">1.53406167030334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5121465921402</t>
+    <t xml:space="preserve">1.51214647293091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52967870235443</t>
+    <t xml:space="preserve">1.52967858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721081256866</t>
+    <t xml:space="preserve">1.54721093177795</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
@@ -1238,28 +1238,28 @@
     <t xml:space="preserve">1.55159378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035995483398</t>
+    <t xml:space="preserve">1.56035983562469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091264724731</t>
+    <t xml:space="preserve">1.52091252803802</t>
   </si>
   <si>
     <t xml:space="preserve">1.48584842681885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51652944087982</t>
+    <t xml:space="preserve">1.5165296792984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56912589073181</t>
+    <t xml:space="preserve">1.5691260099411</t>
   </si>
   <si>
     <t xml:space="preserve">1.50776350498199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529561519623</t>
+    <t xml:space="preserve">1.52529573440552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899733066559</t>
+    <t xml:space="preserve">1.49899744987488</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820447921753</t>
+    <t xml:space="preserve">1.48820459842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46114635467529</t>
+    <t xml:space="preserve">1.46114611625671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624322891235</t>
+    <t xml:space="preserve">1.50624334812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016561031342</t>
+    <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310736656189</t>
+    <t xml:space="preserve">1.44310748577118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604924201965</t>
+    <t xml:space="preserve">1.41604912281036</t>
   </si>
   <si>
     <t xml:space="preserve">1.39801025390625</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3529132604599</t>
+    <t xml:space="preserve">1.35291314125061</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1325,37 +1325,37 @@
     <t xml:space="preserve">1.31683564186096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977715969086</t>
+    <t xml:space="preserve">1.28977727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26271891593933</t>
+    <t xml:space="preserve">1.26271903514862</t>
   </si>
   <si>
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056355953217</t>
+    <t xml:space="preserve">1.19056367874146</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252480983734</t>
+    <t xml:space="preserve">1.17252469062805</t>
   </si>
   <si>
     <t xml:space="preserve">1.22664129734039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762192249298</t>
+    <t xml:space="preserve">1.21762180328369</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879665374756</t>
+    <t xml:space="preserve">1.29879677295685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193251609802</t>
+    <t xml:space="preserve">1.36193263530731</t>
   </si>
   <si>
     <t xml:space="preserve">1.37997150421143</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566079139709</t>
+    <t xml:space="preserve">1.23566067218781</t>
   </si>
   <si>
     <t xml:space="preserve">1.45212686061859</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153480529785</t>
+    <t xml:space="preserve">1.64153468608856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251531124115</t>
+    <t xml:space="preserve">1.63251519203186</t>
   </si>
   <si>
     <t xml:space="preserve">1.59643757343292</t>
@@ -1400,10 +1400,13 @@
     <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369016170502</t>
+    <t xml:space="preserve">1.71369004249573</t>
   </si>
   <si>
     <t xml:space="preserve">1.62349581718445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56035995483398</t>
   </si>
   <si>
     <t xml:space="preserve">1.55134057998657</t>
@@ -1418,16 +1421,16 @@
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.118408203125</t>
+    <t xml:space="preserve">1.11840832233429</t>
   </si>
   <si>
     <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15448594093323</t>
+    <t xml:space="preserve">1.15448582172394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12742757797241</t>
+    <t xml:space="preserve">1.1274276971817</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
@@ -1436,7 +1439,7 @@
     <t xml:space="preserve">1.25369966030121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546656608582</t>
+    <t xml:space="preserve">1.14546644687653</t>
   </si>
   <si>
     <t xml:space="preserve">1.10036945343018</t>
@@ -1445,22 +1448,22 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09135007858276</t>
+    <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
     <t xml:space="preserve">1.08233058452606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04625272750854</t>
+    <t xml:space="preserve">1.04625284671783</t>
   </si>
   <si>
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331132888794</t>
+    <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527222156525</t>
+    <t xml:space="preserve">1.05527234077454</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1469,19 +1472,19 @@
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136418819427</t>
+    <t xml:space="preserve">0.992136359214783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01017510890961</t>
+    <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097549915314</t>
+    <t xml:space="preserve">0.974097490310669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00115585327148</t>
+    <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078175067902</t>
+    <t xml:space="preserve">0.965078055858612</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
@@ -1493,22 +1496,22 @@
     <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947039186954498</t>
+    <t xml:space="preserve">0.947039127349854</t>
   </si>
   <si>
     <t xml:space="preserve">0.897432446479797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910961508750916</t>
+    <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
     <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01919460296631</t>
+    <t xml:space="preserve">1.0191947221756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956058621406555</t>
+    <t xml:space="preserve">0.95605856180191</t>
   </si>
   <si>
     <t xml:space="preserve">1.20860242843628</t>
@@ -1517,7 +1520,7 @@
     <t xml:space="preserve">1.47918510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098145008087</t>
+    <t xml:space="preserve">1.25098133087158</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1547,7 +1550,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1212500333786</t>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1565,25 +1568,22 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051652908325</t>
+    <t xml:space="preserve">1.13051640987396</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1953821182251</t>
+    <t xml:space="preserve">1.19538223743439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198341846466</t>
+    <t xml:space="preserve">1.11198353767395</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -29074,7 +29074,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1037" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29126,7 +29126,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1039" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29230,7 +29230,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29256,7 +29256,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1044" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29308,7 +29308,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1046" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29438,7 +29438,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1051" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29698,7 +29698,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1061" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29724,7 +29724,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1062" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29750,7 +29750,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29776,7 +29776,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29802,7 +29802,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1065" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29828,7 +29828,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29854,7 +29854,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29880,7 +29880,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1068" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29906,7 +29906,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1069" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29932,7 +29932,7 @@
         <v>1.25</v>
       </c>
       <c r="G1070" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29958,7 +29958,7 @@
         <v>1.25</v>
       </c>
       <c r="G1071" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29984,7 +29984,7 @@
         <v>1.25</v>
       </c>
       <c r="G1072" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30010,7 +30010,7 @@
         <v>1.25</v>
       </c>
       <c r="G1073" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30192,7 +30192,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1080" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30218,7 +30218,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1081" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30244,7 +30244,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30296,7 +30296,7 @@
         <v>1.25</v>
       </c>
       <c r="G1084" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30400,7 +30400,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1088" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30452,7 +30452,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30504,7 +30504,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1092" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30530,7 +30530,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30556,7 +30556,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1094" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30582,7 +30582,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30608,7 +30608,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30634,7 +30634,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30660,7 +30660,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1098" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30686,7 +30686,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1099" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30712,7 +30712,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1100" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30738,7 +30738,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1101" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30764,7 +30764,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30790,7 +30790,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1103" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30816,7 +30816,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1104" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30842,7 +30842,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1105" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30868,7 +30868,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30894,7 +30894,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1107" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30920,7 +30920,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30946,7 +30946,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1109" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30972,7 +30972,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1110" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30998,7 +30998,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1111" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31024,7 +31024,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1112" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31050,7 +31050,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1113" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31076,7 +31076,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1114" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31102,7 +31102,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1115" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31128,7 +31128,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31154,7 +31154,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1117" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31180,7 +31180,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31206,7 +31206,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1119" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31232,7 +31232,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1120" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31258,7 +31258,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1121" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31284,7 +31284,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1122" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31310,7 +31310,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31336,7 +31336,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31362,7 +31362,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1125" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31388,7 +31388,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1126" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31414,7 +31414,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31440,7 +31440,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1128" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31466,7 +31466,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1129" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31492,7 +31492,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1130" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31518,7 +31518,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1131" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31544,7 +31544,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31570,7 +31570,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1133" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31596,7 +31596,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1134" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31622,7 +31622,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31648,7 +31648,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1136" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31674,7 +31674,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1137" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31700,7 +31700,7 @@
         <v>1.25</v>
       </c>
       <c r="G1138" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31726,7 +31726,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1139" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31752,7 +31752,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1140" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31778,7 +31778,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1141" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31804,7 +31804,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1142" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31830,7 +31830,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1143" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31856,7 +31856,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31882,7 +31882,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1145" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31908,7 +31908,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31934,7 +31934,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1147" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31960,7 +31960,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1148" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31986,7 +31986,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1149" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32012,7 +32012,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1150" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32038,7 +32038,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1151" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32064,7 +32064,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1152" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32090,7 +32090,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1153" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32116,7 +32116,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1154" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32142,7 +32142,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1155" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32168,7 +32168,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1156" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32194,7 +32194,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1157" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32220,7 +32220,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1158" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32246,7 +32246,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1159" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32272,7 +32272,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1160" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32298,7 +32298,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1161" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32324,7 +32324,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1162" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32350,7 +32350,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1163" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32376,7 +32376,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1164" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32402,7 +32402,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1165" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32428,7 +32428,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1166" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32454,7 +32454,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1167" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32480,7 +32480,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1168" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32506,7 +32506,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32532,7 +32532,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1170" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32558,7 +32558,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32584,7 +32584,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1172" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32610,7 +32610,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1173" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32636,7 +32636,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1174" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32662,7 +32662,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1175" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32688,7 +32688,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1176" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32714,7 +32714,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1177" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32740,7 +32740,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32766,7 +32766,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1179" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32792,7 +32792,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1180" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32818,7 +32818,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32844,7 +32844,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1182" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32870,7 +32870,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1183" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32896,7 +32896,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1184" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32922,7 +32922,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1185" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32948,7 +32948,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1186" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32974,7 +32974,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1187" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33000,7 +33000,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1188" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33026,7 +33026,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1189" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33052,7 +33052,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1190" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33078,7 +33078,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33104,7 +33104,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33130,7 +33130,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33156,7 +33156,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1194" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33182,7 +33182,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1195" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33208,7 +33208,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1196" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33234,7 +33234,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33260,7 +33260,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1198" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33286,7 +33286,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33312,7 +33312,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33338,7 +33338,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1201" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33364,7 +33364,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1202" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33390,7 +33390,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33416,7 +33416,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1204" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33442,7 +33442,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33468,7 +33468,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33494,7 +33494,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33520,7 +33520,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1208" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33546,7 +33546,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33572,7 +33572,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33598,7 +33598,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1211" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33624,7 +33624,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1212" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33650,7 +33650,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1213" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33676,7 +33676,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33702,7 +33702,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33728,7 +33728,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33754,7 +33754,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33780,7 +33780,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1218" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33806,7 +33806,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1219" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33832,7 +33832,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1220" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33858,7 +33858,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1221" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33884,7 +33884,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33910,7 +33910,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33936,7 +33936,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33962,7 +33962,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33988,7 +33988,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1226" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34014,7 +34014,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1227" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34040,7 +34040,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1228" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34066,7 +34066,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1229" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34092,7 +34092,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1230" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34118,7 +34118,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34144,7 +34144,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34170,7 +34170,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1233" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34196,7 +34196,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1234" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34222,7 +34222,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34248,7 +34248,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34274,7 +34274,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1237" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34300,7 +34300,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1238" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34326,7 +34326,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1239" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34352,7 +34352,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1240" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34378,7 +34378,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34404,7 +34404,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1242" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34430,7 +34430,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1243" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34456,7 +34456,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1244" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34482,7 +34482,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34508,7 +34508,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1246" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34534,7 +34534,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1247" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34560,7 +34560,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34586,7 +34586,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1249" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34612,7 +34612,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1250" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34638,7 +34638,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1251" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34664,7 +34664,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34690,7 +34690,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1253" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34716,7 +34716,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1254" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34742,7 +34742,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1255" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34768,7 +34768,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1256" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34794,7 +34794,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1257" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34820,7 +34820,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1258" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34846,7 +34846,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1259" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34872,7 +34872,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1260" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34898,7 +34898,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1261" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34924,7 +34924,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1262" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34950,7 +34950,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34976,7 +34976,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1264" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35002,7 +35002,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1265" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35028,7 +35028,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1266" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35054,7 +35054,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35080,7 +35080,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1268" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35106,7 +35106,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1269" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35132,7 +35132,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1270" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35158,7 +35158,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1271" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35184,7 +35184,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1272" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35210,7 +35210,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1273" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35236,7 +35236,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1274" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35262,7 +35262,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1275" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35288,7 +35288,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1276" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35314,7 +35314,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1277" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35340,7 +35340,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1278" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35366,7 +35366,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1279" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35392,7 +35392,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1280" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35418,7 +35418,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1281" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35444,7 +35444,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1282" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35470,7 +35470,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1283" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35496,7 +35496,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1284" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35522,7 +35522,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1285" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35548,7 +35548,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1286" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35574,7 +35574,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35600,7 +35600,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35626,7 +35626,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1289" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35652,7 +35652,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1290" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35678,7 +35678,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1291" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35704,7 +35704,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1292" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35730,7 +35730,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1293" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35756,7 +35756,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1294" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35782,7 +35782,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1295" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35808,7 +35808,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1296" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35834,7 +35834,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1297" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35860,7 +35860,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35886,7 +35886,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35912,7 +35912,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1300" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35938,7 +35938,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1301" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35964,7 +35964,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1302" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35990,7 +35990,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1303" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36016,7 +36016,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1304" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36042,7 +36042,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1305" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36068,7 +36068,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1306" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36094,7 +36094,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1307" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36120,7 +36120,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1308" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36146,7 +36146,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1309" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36172,7 +36172,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1310" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36198,7 +36198,7 @@
         <v>1.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36224,7 +36224,7 @@
         <v>1.25</v>
       </c>
       <c r="G1312" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36250,7 +36250,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1313" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36276,7 +36276,7 @@
         <v>1.25</v>
       </c>
       <c r="G1314" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36302,7 +36302,7 @@
         <v>1.25</v>
       </c>
       <c r="G1315" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36328,7 +36328,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1316" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36354,7 +36354,7 @@
         <v>1.25</v>
       </c>
       <c r="G1317" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36380,7 +36380,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36432,7 +36432,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36458,7 +36458,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1321" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36484,7 +36484,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1322" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36510,7 +36510,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1323" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36536,7 +36536,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1324" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36562,7 +36562,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1325" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36588,7 +36588,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36614,7 +36614,7 @@
         <v>1.25</v>
       </c>
       <c r="G1327" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36640,7 +36640,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1328" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36666,7 +36666,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1329" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36692,7 +36692,7 @@
         <v>1.25</v>
       </c>
       <c r="G1330" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36718,7 +36718,7 @@
         <v>1.25</v>
       </c>
       <c r="G1331" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36744,7 +36744,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36770,7 +36770,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36848,7 +36848,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1336" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37056,7 +37056,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1344" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37108,7 +37108,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1346" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37264,7 +37264,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1352" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37290,7 +37290,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1353" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37368,7 +37368,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1356" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37394,7 +37394,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1357" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37446,7 +37446,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1359" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37472,7 +37472,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1360" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37524,7 +37524,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37550,7 +37550,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37576,7 +37576,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38200,7 +38200,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1388" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38226,7 +38226,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1389" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38252,7 +38252,7 @@
         <v>1.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38278,7 +38278,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1391" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38304,7 +38304,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1392" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38356,7 +38356,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1394" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38382,7 +38382,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1395" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38408,7 +38408,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1396" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38434,7 +38434,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1397" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38564,7 +38564,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38590,7 +38590,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38616,7 +38616,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38642,7 +38642,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1405" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38668,7 +38668,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38694,7 +38694,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1407" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38720,7 +38720,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1408" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38746,7 +38746,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1409" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38772,7 +38772,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1410" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38798,7 +38798,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1411" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38824,7 +38824,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1412" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38850,7 +38850,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1413" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38876,7 +38876,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1414" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38902,7 +38902,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1415" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38928,7 +38928,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1416" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38954,7 +38954,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1417" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38980,7 +38980,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1418" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39006,7 +39006,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1419" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39058,7 +39058,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1421" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39084,7 +39084,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1422" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39110,7 +39110,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1423" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39136,7 +39136,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1424" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39162,7 +39162,7 @@
         <v>1.25</v>
       </c>
       <c r="G1425" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39188,7 +39188,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39214,7 +39214,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1427" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39240,7 +39240,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1428" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39266,7 +39266,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1429" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39292,7 +39292,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1430" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39318,7 +39318,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39344,7 +39344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1432" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39370,7 +39370,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1433" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39474,7 +39474,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39500,7 +39500,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1438" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39526,7 +39526,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1439" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39552,7 +39552,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1440" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39578,7 +39578,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1441" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39604,7 +39604,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1442" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39630,7 +39630,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1443" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39656,7 +39656,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1444" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39682,7 +39682,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1445" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39708,7 +39708,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1446" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39734,7 +39734,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1447" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39760,7 +39760,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1448" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39786,7 +39786,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1449" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39812,7 +39812,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1450" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39838,7 +39838,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1451" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39864,7 +39864,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1452" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39890,7 +39890,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1453" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39916,7 +39916,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1454" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39942,7 +39942,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1455" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39968,7 +39968,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1456" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39994,7 +39994,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1457" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40176,7 +40176,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1464" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40254,7 +40254,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1467" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40280,7 +40280,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1468" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40540,7 +40540,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41216,7 +41216,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1504" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41528,7 +41528,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1516" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41606,7 +41606,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1519" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41632,7 +41632,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41658,7 +41658,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1521" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41684,7 +41684,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1522" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41788,7 +41788,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1526" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41814,7 +41814,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1527" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41918,7 +41918,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1531" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41944,7 +41944,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1532" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42126,7 +42126,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1539" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42178,7 +42178,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1541" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42282,7 +42282,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1545" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42334,7 +42334,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1547" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42360,7 +42360,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1548" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42386,7 +42386,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1549" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42412,7 +42412,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1550" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42438,7 +42438,7 @@
         <v>1.25</v>
       </c>
       <c r="G1551" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42464,7 +42464,7 @@
         <v>1.25</v>
       </c>
       <c r="G1552" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42490,7 +42490,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1553" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42516,7 +42516,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1554" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42542,7 +42542,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1555" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42568,7 +42568,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1556" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42594,7 +42594,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42620,7 +42620,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1558" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42646,7 +42646,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42672,7 +42672,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1560" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42698,7 +42698,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42724,7 +42724,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1562" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42802,7 +42802,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42828,7 +42828,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1566" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42854,7 +42854,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1567" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42880,7 +42880,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42906,7 +42906,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1569" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42932,7 +42932,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1570" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42958,7 +42958,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1571" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42984,7 +42984,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1572" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43010,7 +43010,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1573" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43036,7 +43036,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1574" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43062,7 +43062,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1575" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43088,7 +43088,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1576" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43114,7 +43114,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1577" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43140,7 +43140,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1578" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43166,7 +43166,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1579" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43192,7 +43192,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1580" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43218,7 +43218,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1581" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43244,7 +43244,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1582" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43270,7 +43270,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1583" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43296,7 +43296,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1584" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43322,7 +43322,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1585" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43348,7 +43348,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1586" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43374,7 +43374,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43530,7 +43530,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1593" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43556,7 +43556,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1594" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43608,7 +43608,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1596" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43634,7 +43634,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43686,7 +43686,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1599" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43790,7 +43790,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43816,7 +43816,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1604" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43842,7 +43842,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43868,7 +43868,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1606" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43894,7 +43894,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1607" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43920,7 +43920,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43946,7 +43946,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1609" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44024,7 +44024,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1612" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44050,7 +44050,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1613" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44076,7 +44076,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44102,7 +44102,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1615" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44128,7 +44128,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1616" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44180,7 +44180,7 @@
         <v>1.25</v>
       </c>
       <c r="G1618" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44206,7 +44206,7 @@
         <v>1.25</v>
       </c>
       <c r="G1619" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44232,7 +44232,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1620" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44258,7 +44258,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44310,7 +44310,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44440,7 +44440,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1628" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44492,7 +44492,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1630" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44622,7 +44622,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1635" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44648,7 +44648,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44674,7 +44674,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1637" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44700,7 +44700,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44726,7 +44726,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1639" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44752,7 +44752,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1640" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44778,7 +44778,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1641" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44804,7 +44804,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45012,7 +45012,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45064,7 +45064,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1652" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45090,7 +45090,7 @@
         <v>1.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45116,7 +45116,7 @@
         <v>1.25</v>
       </c>
       <c r="G1654" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45142,7 +45142,7 @@
         <v>1.25</v>
       </c>
       <c r="G1655" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45168,7 +45168,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1656" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45194,7 +45194,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1657" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45220,7 +45220,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45246,7 +45246,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45272,7 +45272,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1660" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45298,7 +45298,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1661" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45324,7 +45324,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1662" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45350,7 +45350,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1663" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45376,7 +45376,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45428,7 +45428,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45454,7 +45454,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45480,7 +45480,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45506,7 +45506,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45558,7 +45558,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1671" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45584,7 +45584,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1672" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45636,7 +45636,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1674" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45688,7 +45688,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1676" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45740,7 +45740,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45818,7 +45818,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1681" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45870,7 +45870,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1683" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45896,7 +45896,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1684" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45922,7 +45922,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1685" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46000,7 +46000,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1688" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46156,7 +46156,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1694" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46182,7 +46182,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1695" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46208,7 +46208,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1696" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46234,7 +46234,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46286,7 +46286,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1699" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46338,7 +46338,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46468,7 +46468,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1706" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46520,7 +46520,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1708" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46624,7 +46624,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1712" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46676,7 +46676,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1714" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46702,7 +46702,7 @@
         <v>1.25</v>
       </c>
       <c r="G1715" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46728,7 +46728,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1716" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46754,7 +46754,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46780,7 +46780,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46806,7 +46806,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46832,7 +46832,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46858,7 +46858,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46884,7 +46884,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46910,7 +46910,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46962,7 +46962,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1725" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46988,7 +46988,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1726" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47014,7 +47014,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1727" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47144,7 +47144,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1732" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47196,7 +47196,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1734" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47222,7 +47222,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47404,7 +47404,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1742" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47430,7 +47430,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1743" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47456,7 +47456,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1744" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47482,7 +47482,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1745" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47508,7 +47508,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1746" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47534,7 +47534,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1747" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47560,7 +47560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1748" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47586,7 +47586,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1749" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47612,7 +47612,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1750" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47638,7 +47638,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1751" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47664,7 +47664,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1752" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47690,7 +47690,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1753" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47716,7 +47716,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1754" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47742,7 +47742,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1755" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47898,7 +47898,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1761" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47950,7 +47950,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48002,7 +48002,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1765" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48028,7 +48028,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1766" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48054,7 +48054,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1767" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48080,7 +48080,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1768" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48106,7 +48106,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1769" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48236,7 +48236,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1774" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48262,7 +48262,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1775" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48392,7 +48392,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1780" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48496,7 +48496,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1784" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48522,7 +48522,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1785" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48548,7 +48548,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1786" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48574,7 +48574,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1787" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48600,7 +48600,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1788" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48626,7 +48626,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1789" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48678,7 +48678,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1791" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48704,7 +48704,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1792" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48938,7 +48938,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1801" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48964,7 +48964,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48990,7 +48990,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1803" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49016,7 +49016,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1804" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49042,7 +49042,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1805" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49068,7 +49068,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49094,7 +49094,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1807" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49120,7 +49120,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1808" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49146,7 +49146,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1809" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49172,7 +49172,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1810" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49198,7 +49198,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1811" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49224,7 +49224,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1812" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49250,7 +49250,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1813" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49328,7 +49328,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49354,7 +49354,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1817" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49380,7 +49380,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1818" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49406,7 +49406,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1819" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49432,7 +49432,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1820" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49458,7 +49458,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1821" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49484,7 +49484,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1822" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49510,7 +49510,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1823" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49536,7 +49536,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1824" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49562,7 +49562,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1825" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49588,7 +49588,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49614,7 +49614,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49640,7 +49640,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1828" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49666,7 +49666,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1829" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49692,7 +49692,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49718,7 +49718,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49744,7 +49744,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49770,7 +49770,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49796,7 +49796,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1834" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49822,7 +49822,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1835" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49848,7 +49848,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1836" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49874,7 +49874,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1837" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49900,7 +49900,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1838" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49926,7 +49926,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49952,7 +49952,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49978,7 +49978,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50004,7 +50004,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1842" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50030,7 +50030,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1843" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50056,7 +50056,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1844" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50082,7 +50082,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1845" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50108,7 +50108,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1846" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50134,7 +50134,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1847" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50160,7 +50160,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1848" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50186,7 +50186,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1849" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50212,7 +50212,7 @@
         <v>1.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50238,7 +50238,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1851" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50394,7 +50394,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50446,7 +50446,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1859" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50498,7 +50498,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1861" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50654,7 +50654,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50680,7 +50680,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50862,7 +50862,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1875" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50888,7 +50888,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1876" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50914,7 +50914,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1877" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50940,7 +50940,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1878" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50966,7 +50966,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1879" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50992,7 +50992,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1880" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51018,7 +51018,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1881" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51044,7 +51044,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1882" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51070,7 +51070,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1883" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51096,7 +51096,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1884" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51122,7 +51122,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1885" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51148,7 +51148,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1886" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51174,7 +51174,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1887" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51200,7 +51200,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1888" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51226,7 +51226,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1889" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51252,7 +51252,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1890" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51278,7 +51278,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1891" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51304,7 +51304,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1892" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51330,7 +51330,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1893" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51356,7 +51356,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1894" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51382,7 +51382,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1895" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51408,7 +51408,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1896" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51434,7 +51434,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1897" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51460,7 +51460,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1898" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51486,7 +51486,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1899" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51512,7 +51512,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1900" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51538,7 +51538,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1901" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51564,7 +51564,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1902" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51590,7 +51590,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1903" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51616,7 +51616,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1904" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51642,7 +51642,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1905" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51668,7 +51668,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1906" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51694,7 +51694,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1907" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51720,7 +51720,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1908" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51746,7 +51746,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1909" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51772,7 +51772,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1910" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51798,7 +51798,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51824,7 +51824,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1912" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51850,7 +51850,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51876,7 +51876,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51902,7 +51902,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1915" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51928,7 +51928,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1916" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51954,7 +51954,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1917" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51980,7 +51980,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52006,7 +52006,7 @@
         <v>1.25</v>
       </c>
       <c r="G1919" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52032,7 +52032,7 @@
         <v>1.25</v>
       </c>
       <c r="G1920" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52058,7 +52058,7 @@
         <v>1.25</v>
       </c>
       <c r="G1921" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52084,7 +52084,7 @@
         <v>1.25</v>
       </c>
       <c r="G1922" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52110,7 +52110,7 @@
         <v>1.25</v>
       </c>
       <c r="G1923" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52136,7 +52136,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1924" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52162,7 +52162,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1925" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52188,7 +52188,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52214,7 +52214,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52240,7 +52240,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52266,7 +52266,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52292,7 +52292,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1930" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52318,7 +52318,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1931" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52344,7 +52344,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1932" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52370,7 +52370,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52396,7 +52396,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52422,7 +52422,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52448,7 +52448,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1936" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52474,7 +52474,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1937" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52500,7 +52500,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1938" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52526,7 +52526,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1939" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52552,7 +52552,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1940" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52578,7 +52578,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1941" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52604,7 +52604,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1942" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52630,7 +52630,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1943" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52656,7 +52656,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1944" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52682,7 +52682,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1945" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52708,7 +52708,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1946" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52734,7 +52734,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1947" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52760,7 +52760,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1948" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52786,7 +52786,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1949" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52812,7 +52812,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1950" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52838,7 +52838,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1951" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52864,7 +52864,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1952" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52890,7 +52890,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1953" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52916,7 +52916,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1954" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52942,7 +52942,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1955" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52968,7 +52968,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1956" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52994,7 +52994,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53020,7 +53020,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1958" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53046,7 +53046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53072,7 +53072,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1960" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53098,7 +53098,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1961" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53124,7 +53124,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1962" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53150,7 +53150,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1963" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53176,7 +53176,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53202,7 +53202,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1965" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53228,7 +53228,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1966" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53254,7 +53254,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1967" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53280,7 +53280,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1968" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53306,7 +53306,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1969" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53332,7 +53332,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1970" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53358,7 +53358,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1971" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53384,7 +53384,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1972" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53410,7 +53410,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1973" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53436,7 +53436,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1974" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53462,7 +53462,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1975" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53488,7 +53488,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1976" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53514,7 +53514,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53540,7 +53540,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1978" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53566,7 +53566,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1979" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53592,7 +53592,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53618,7 +53618,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53644,7 +53644,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53670,7 +53670,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53696,7 +53696,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1984" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53722,7 +53722,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53748,7 +53748,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53774,7 +53774,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1987" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53800,7 +53800,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1988" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53826,7 +53826,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1989" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53852,7 +53852,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1990" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53878,7 +53878,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53904,7 +53904,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1992" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53930,7 +53930,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53956,7 +53956,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1994" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53982,7 +53982,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1995" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54008,7 +54008,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1996" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54034,7 +54034,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1997" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54060,7 +54060,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54086,7 +54086,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1999" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54112,7 +54112,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54138,7 +54138,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2001" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54164,7 +54164,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2002" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54190,7 +54190,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2003" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54216,7 +54216,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2004" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54242,7 +54242,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2005" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54268,7 +54268,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2006" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54294,7 +54294,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2007" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54320,7 +54320,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54346,7 +54346,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2009" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54372,7 +54372,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2010" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54398,7 +54398,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2011" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54424,7 +54424,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2012" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54450,7 +54450,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2013" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54476,7 +54476,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2014" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54502,7 +54502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54528,7 +54528,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2016" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54554,7 +54554,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2017" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54580,7 +54580,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2018" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54606,7 +54606,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2019" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54632,7 +54632,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2020" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54658,7 +54658,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2021" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54684,7 +54684,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54710,7 +54710,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2023" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54736,7 +54736,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2024" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54762,7 +54762,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2025" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54788,7 +54788,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54814,7 +54814,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54840,7 +54840,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54866,7 +54866,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2029" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54892,7 +54892,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2030" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54918,7 +54918,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2031" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54944,7 +54944,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2032" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54970,7 +54970,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2033" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54996,7 +54996,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2034" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55022,7 +55022,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2035" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55048,7 +55048,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2036" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55074,7 +55074,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2037" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55100,7 +55100,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2038" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55126,7 +55126,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2039" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55152,7 +55152,7 @@
         <v>1.25</v>
       </c>
       <c r="G2040" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55178,7 +55178,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55204,7 +55204,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55230,7 +55230,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2043" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55256,7 +55256,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2044" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55282,7 +55282,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2045" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55308,7 +55308,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2046" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55334,7 +55334,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55360,7 +55360,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2048" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55386,7 +55386,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55412,7 +55412,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2050" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55438,7 +55438,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2051" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55464,7 +55464,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2052" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55490,7 +55490,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55516,7 +55516,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2054" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55542,7 +55542,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2055" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55568,7 +55568,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2056" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55594,7 +55594,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55620,7 +55620,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2058" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55646,7 +55646,7 @@
         <v>1.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55672,7 +55672,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2060" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55698,7 +55698,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55724,7 +55724,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2062" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55750,7 +55750,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2063" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55776,7 +55776,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2064" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55802,7 +55802,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2065" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55828,7 +55828,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2066" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55854,7 +55854,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2067" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55880,7 +55880,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2068" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55906,7 +55906,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2069" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55932,7 +55932,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55958,7 +55958,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2071" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55984,7 +55984,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2072" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56010,7 +56010,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2073" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56036,7 +56036,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2074" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56062,7 +56062,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2075" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56088,7 +56088,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2076" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56114,7 +56114,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2077" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56140,7 +56140,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2078" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56166,7 +56166,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2079" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56192,7 +56192,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2080" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56218,7 +56218,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56244,7 +56244,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56270,7 +56270,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2083" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56296,7 +56296,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2084" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56322,7 +56322,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2085" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56348,7 +56348,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2086" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56374,7 +56374,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2087" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56400,7 +56400,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2088" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56426,7 +56426,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2089" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56452,7 +56452,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2090" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56478,7 +56478,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2091" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56504,7 +56504,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2092" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56530,7 +56530,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2093" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56556,7 +56556,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2094" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56582,7 +56582,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2095" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56608,7 +56608,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2096" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56634,7 +56634,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2097" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56660,7 +56660,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2098" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56686,7 +56686,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2099" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56712,7 +56712,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2100" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56738,7 +56738,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2101" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56764,7 +56764,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2102" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56790,7 +56790,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2103" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56816,7 +56816,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G2104" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56842,7 +56842,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2105" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56868,7 +56868,7 @@
         <v>1.25</v>
       </c>
       <c r="G2106" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56894,7 +56894,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2107" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56920,7 +56920,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2108" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56946,7 +56946,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2109" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56972,7 +56972,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2110" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56998,7 +56998,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2111" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57024,7 +57024,7 @@
         <v>1.25</v>
       </c>
       <c r="G2112" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57050,7 +57050,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2113" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57076,7 +57076,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2114" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57102,7 +57102,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2115" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57128,7 +57128,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2116" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57154,7 +57154,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2117" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57180,7 +57180,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2118" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57206,7 +57206,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G2119" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57232,7 +57232,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2120" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57258,7 +57258,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2121" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57284,7 +57284,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G2122" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57310,7 +57310,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2123" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57336,7 +57336,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2124" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57362,7 +57362,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57388,7 +57388,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2126" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57414,7 +57414,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2127" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57440,7 +57440,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57466,7 +57466,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2129" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57492,7 +57492,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G2130" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57518,7 +57518,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G2131" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57544,7 +57544,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57570,7 +57570,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G2133" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57596,7 +57596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -67640,7 +67640,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6832060185</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>400</v>
@@ -67661,6 +67661,32 @@
         <v>574</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.5166666667</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>574</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781757354736</t>
+    <t xml:space="preserve">1.43781769275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684298992157</t>
+    <t xml:space="preserve">1.48684310913086</t>
   </si>
   <si>
     <t xml:space="preserve">1.44424712657928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42254734039307</t>
+    <t xml:space="preserve">1.42254722118378</t>
   </si>
   <si>
     <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593269348145</t>
+    <t xml:space="preserve">1.37593293190002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414030075073</t>
+    <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744774341583</t>
+    <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3662885427475</t>
+    <t xml:space="preserve">1.36628842353821</t>
   </si>
   <si>
     <t xml:space="preserve">1.41290283203125</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647315979004</t>
+    <t xml:space="preserve">1.40647327899933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44585466384888</t>
+    <t xml:space="preserve">1.4458544254303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39843618869781</t>
+    <t xml:space="preserve">1.39843642711639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34780335426331</t>
+    <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
     <t xml:space="preserve">1.31726264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002950668335</t>
+    <t xml:space="preserve">1.31002938747406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217727184296</t>
+    <t xml:space="preserve">1.34217739105225</t>
   </si>
   <si>
     <t xml:space="preserve">1.35021424293518</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557720184326</t>
+    <t xml:space="preserve">1.38557708263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273219585419</t>
+    <t xml:space="preserve">1.46273231506348</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693571567535</t>
+    <t xml:space="preserve">1.50693559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889862537384</t>
+    <t xml:space="preserve">1.49889874458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47237658500671</t>
+    <t xml:space="preserve">1.472376704216</t>
   </si>
   <si>
     <t xml:space="preserve">1.49488019943237</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61543500423431</t>
+    <t xml:space="preserve">1.61543488502502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169380187988</t>
+    <t xml:space="preserve">1.67169404029846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490875720978</t>
+    <t xml:space="preserve">1.67490887641907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64597570896149</t>
+    <t xml:space="preserve">1.6459755897522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113911628723</t>
+    <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702820301056</t>
+    <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
     <t xml:space="preserve">1.51095414161682</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862128257751</t>
+    <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4120991230011</t>
+    <t xml:space="preserve">1.41209924221039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601892471313</t>
+    <t xml:space="preserve">1.45601904392242</t>
   </si>
   <si>
     <t xml:space="preserve">1.43426239490509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832185745239</t>
+    <t xml:space="preserve">1.4083217382431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42254745960236</t>
+    <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091511726379</t>
+    <t xml:space="preserve">1.43091523647308</t>
   </si>
   <si>
     <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41334271430969</t>
+    <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
     <t xml:space="preserve">1.4049745798111</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">1.36313486099243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560393333435</t>
+    <t xml:space="preserve">1.35560381412506</t>
   </si>
   <si>
     <t xml:space="preserve">1.37233972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33886802196503</t>
+    <t xml:space="preserve">1.33886814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288589000702</t>
+    <t xml:space="preserve">1.30288600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325479388237</t>
+    <t xml:space="preserve">1.32547926902771</t>
   </si>
   <si>
     <t xml:space="preserve">1.32213222980499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26439356803894</t>
+    <t xml:space="preserve">1.26439344882965</t>
   </si>
   <si>
     <t xml:space="preserve">1.29702842235565</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">1.30539631843567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397194862366</t>
+    <t xml:space="preserve">1.36397182941437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41250574588776</t>
+    <t xml:space="preserve">1.41250562667847</t>
   </si>
   <si>
     <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3305002450943</t>
+    <t xml:space="preserve">1.33050012588501</t>
   </si>
   <si>
     <t xml:space="preserve">1.27192461490631</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">1.22506415843964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2049812078476</t>
+    <t xml:space="preserve">1.20498132705688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20916521549225</t>
+    <t xml:space="preserve">1.20916533470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845303058624</t>
+    <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008489608765</t>
+    <t xml:space="preserve">1.23008501529694</t>
   </si>
   <si>
     <t xml:space="preserve">1.18824529647827</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">1.15226328372955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14222157001495</t>
+    <t xml:space="preserve">1.14222192764282</t>
   </si>
   <si>
     <t xml:space="preserve">1.17150938510895</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">1.12966978549957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293399333954</t>
+    <t xml:space="preserve">1.11293411254883</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850101470947</t>
@@ -299,28 +299,28 @@
     <t xml:space="preserve">1.07109439373016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03762269020081</t>
+    <t xml:space="preserve">1.0376228094101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0083349943161</t>
+    <t xml:space="preserve">1.00833511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067976474762</t>
+    <t xml:space="preserve">0.984068036079407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967157840729</t>
+    <t xml:space="preserve">0.999967098236084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251900196075</t>
+    <t xml:space="preserve">1.01251888275146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00415098667145</t>
+    <t xml:space="preserve">1.00415110588074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127439022064</t>
+    <t xml:space="preserve">0.958127379417419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842553138733</t>
+    <t xml:space="preserve">0.969842612743378</t>
   </si>
   <si>
     <t xml:space="preserve">0.944738745689392</t>
@@ -347,49 +347,49 @@
     <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756613731384</t>
+    <t xml:space="preserve">0.908756673336029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596392154694</t>
+    <t xml:space="preserve">0.950596213340759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471727848053</t>
+    <t xml:space="preserve">0.920471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.967332065105438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311327457428</t>
+    <t xml:space="preserve">0.962311267852783</t>
   </si>
   <si>
     <t xml:space="preserve">1.05519545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599023342133</t>
+    <t xml:space="preserve">0.991598963737488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088833332062</t>
+    <t xml:space="preserve">0.989088892936707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0016405582428</t>
+    <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783030986786</t>
+    <t xml:space="preserve">0.995783150196075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99076247215271</t>
+    <t xml:space="preserve">0.990762412548065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207639217377</t>
+    <t xml:space="preserve">0.937207579612732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394456863403</t>
+    <t xml:space="preserve">0.982394397258759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391706466675</t>
+    <t xml:space="preserve">0.941391587257385</t>
   </si>
   <si>
     <t xml:space="preserve">0.988251984119415</t>
@@ -401,49 +401,49 @@
     <t xml:space="preserve">0.96816885471344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975700080394745</t>
+    <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
     <t xml:space="preserve">0.983231127262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415134906769</t>
+    <t xml:space="preserve">0.987415254116058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005823135376</t>
+    <t xml:space="preserve">0.969005703926086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994109392166138</t>
+    <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943490982056</t>
+    <t xml:space="preserve">0.953943371772766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854260921478</t>
+    <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05937922000885</t>
+    <t xml:space="preserve">1.05937933921814</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507078647614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268490314484</t>
+    <t xml:space="preserve">1.05268502235413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10456621646881</t>
+    <t xml:space="preserve">1.10456609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636422157288</t>
+    <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14807951450348</t>
+    <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577658176422</t>
+    <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661331176758</t>
+    <t xml:space="preserve">1.19661319255829</t>
   </si>
   <si>
     <t xml:space="preserve">1.25602555274963</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2133492231369</t>
+    <t xml:space="preserve">1.21334898471832</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753311157227</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">1.15310001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19242930412292</t>
+    <t xml:space="preserve">1.19242918491364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493985176086</t>
+    <t xml:space="preserve">1.19493961334229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15477347373962</t>
+    <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14640581607819</t>
+    <t xml:space="preserve">1.1464056968689</t>
   </si>
   <si>
     <t xml:space="preserve">1.19159257411957</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23761606216431</t>
+    <t xml:space="preserve">1.23761594295502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518882274628</t>
+    <t xml:space="preserve">1.25518870353699</t>
   </si>
   <si>
     <t xml:space="preserve">1.2359424829483</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">1.17653024196625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581130981445</t>
+    <t xml:space="preserve">1.40581142902374</t>
   </si>
   <si>
     <t xml:space="preserve">1.39576995372772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911711215973</t>
+    <t xml:space="preserve">1.39911699295044</t>
   </si>
   <si>
     <t xml:space="preserve">1.39744341373444</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534809589386</t>
+    <t xml:space="preserve">1.49534821510315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685577392578</t>
+    <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
     <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48949062824249</t>
+    <t xml:space="preserve">1.4894905090332</t>
   </si>
   <si>
     <t xml:space="preserve">1.47275483608246</t>
@@ -551,25 +551,25 @@
     <t xml:space="preserve">1.63174557685852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684926509857</t>
+    <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
     <t xml:space="preserve">1.66438019275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550772666931</t>
+    <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726425647736</t>
+    <t xml:space="preserve">1.75726413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77400004863739</t>
+    <t xml:space="preserve">1.7739999294281</t>
   </si>
   <si>
     <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65099167823792</t>
+    <t xml:space="preserve">1.65099155902863</t>
   </si>
   <si>
     <t xml:space="preserve">1.60078406333923</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">1.67358505725861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003016471863</t>
+    <t xml:space="preserve">1.62003028392792</t>
   </si>
   <si>
     <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6166832447052</t>
+    <t xml:space="preserve">1.61668312549591</t>
   </si>
   <si>
     <t xml:space="preserve">1.60664165019989</t>
@@ -593,37 +593,37 @@
     <t xml:space="preserve">1.68195295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362653255463</t>
+    <t xml:space="preserve">1.68362641334534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542453765869</t>
+    <t xml:space="preserve">1.7154244184494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718118667603</t>
+    <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
     <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052834510803</t>
+    <t xml:space="preserve">1.74052846431732</t>
   </si>
   <si>
     <t xml:space="preserve">1.723792552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601229667664</t>
+    <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74220204353333</t>
+    <t xml:space="preserve">1.74220192432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74906098842621</t>
+    <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
     <t xml:space="preserve">1.84337317943573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80050384998322</t>
+    <t xml:space="preserve">1.8005039691925</t>
   </si>
   <si>
     <t xml:space="preserve">1.78335630893707</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421922683716</t>
+    <t xml:space="preserve">2.82421898841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82936358451843</t>
+    <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
     <t xml:space="preserve">2.73505139350891</t>
@@ -653,46 +653,46 @@
     <t xml:space="preserve">2.64416885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4778368473053</t>
+    <t xml:space="preserve">2.47783637046814</t>
   </si>
   <si>
     <t xml:space="preserve">2.46068906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067172050476</t>
+    <t xml:space="preserve">2.40067195892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929657936096</t>
+    <t xml:space="preserve">2.5892961025238</t>
   </si>
   <si>
     <t xml:space="preserve">2.78649425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67503452301025</t>
+    <t xml:space="preserve">2.67503476142883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012874603271</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46240377426147</t>
+    <t xml:space="preserve">2.4624035358429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47097754478455</t>
+    <t xml:space="preserve">2.47097730636597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354128837585</t>
+    <t xml:space="preserve">2.44354104995728</t>
   </si>
   <si>
     <t xml:space="preserve">2.41953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43496751785278</t>
+    <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
     <t xml:space="preserve">2.4555447101593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45725917816162</t>
+    <t xml:space="preserve">2.4572594165802</t>
   </si>
   <si>
     <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897459983826</t>
+    <t xml:space="preserve">2.45897436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440671920776</t>
+    <t xml:space="preserve">2.47440695762634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56185984611511</t>
+    <t xml:space="preserve">2.56186008453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781973838806</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639350891113</t>
+    <t xml:space="preserve">2.42639327049255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38352417945862</t>
+    <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
     <t xml:space="preserve">2.33208155632019</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.126309633255</t>
+    <t xml:space="preserve">2.12630939483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800770759583</t>
+    <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05771899223328</t>
+    <t xml:space="preserve">2.0577187538147</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544372558594</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1280243396759</t>
+    <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
     <t xml:space="preserve">2.08515524864197</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">2.05085968971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342343330383</t>
+    <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20690369606018</t>
+    <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603778839111</t>
+    <t xml:space="preserve">2.17603754997253</t>
   </si>
   <si>
     <t xml:space="preserve">2.08172559738159</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12287998199463</t>
+    <t xml:space="preserve">2.12288022041321</t>
   </si>
   <si>
     <t xml:space="preserve">2.1537458896637</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">2.23776936531067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233653068542</t>
+    <t xml:space="preserve">2.22233629226685</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089343070984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975591659546</t>
+    <t xml:space="preserve">2.18975567817688</t>
   </si>
   <si>
     <t xml:space="preserve">2.22919535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24634313583374</t>
+    <t xml:space="preserve">2.24634289741516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065508842468</t>
+    <t xml:space="preserve">2.34065532684326</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">2.20861840248108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28749752044678</t>
+    <t xml:space="preserve">2.28749775886536</t>
   </si>
   <si>
     <t xml:space="preserve">2.2034740447998</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32007813453674</t>
+    <t xml:space="preserve">2.32007789611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809158325195</t>
+    <t xml:space="preserve">2.36809182167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379602432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439008712769</t>
+    <t xml:space="preserve">2.41439032554626</t>
   </si>
   <si>
     <t xml:space="preserve">2.34922909736633</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832968711853</t>
+    <t xml:space="preserve">2.19832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430644989014</t>
+    <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632626533508</t>
@@ -968,34 +968,34 @@
     <t xml:space="preserve">2.04057121276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01484942436218</t>
+    <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914498329163</t>
+    <t xml:space="preserve">2.04914522171021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90339004993439</t>
+    <t xml:space="preserve">1.90339016914368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805543422699</t>
+    <t xml:space="preserve">1.98055458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198045253754</t>
+    <t xml:space="preserve">1.97198057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053759098053</t>
+    <t xml:space="preserve">1.92053735256195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912823200226</t>
+    <t xml:space="preserve">1.98912799358368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196382045746</t>
+    <t xml:space="preserve">1.91196405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911148071289</t>
+    <t xml:space="preserve">1.9291113615036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624215126038</t>
   </si>
   <si>
     <t xml:space="preserve">1.89481627941132</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">1.86909472942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194718837738</t>
+    <t xml:space="preserve">1.85194730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625902175903</t>
+    <t xml:space="preserve">1.94625926017761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340656280518</t>
+    <t xml:space="preserve">1.96340668201447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879186630249</t>
+    <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249334335327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236502170563</t>
+    <t xml:space="preserve">1.97236514091492</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100251674652</t>
@@ -1028,25 +1028,25 @@
     <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470447063446</t>
+    <t xml:space="preserve">1.88470435142517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02496147155762</t>
+    <t xml:space="preserve">2.0249617099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866330623627</t>
+    <t xml:space="preserve">1.99866318702698</t>
   </si>
   <si>
     <t xml:space="preserve">1.94606685638428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853474617004</t>
+    <t xml:space="preserve">1.92853486537933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717247962952</t>
+    <t xml:space="preserve">1.86717236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90223670005798</t>
+    <t xml:space="preserve">1.90223658084869</t>
   </si>
   <si>
     <t xml:space="preserve">1.87593829631805</t>
@@ -1055,31 +1055,31 @@
     <t xml:space="preserve">1.82334184646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976881027222</t>
+    <t xml:space="preserve">1.91976869106293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84964001178741</t>
+    <t xml:space="preserve">1.84963989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.89347064495087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730080127716</t>
+    <t xml:space="preserve">1.93730092048645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989725112915</t>
+    <t xml:space="preserve">1.98989713191986</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78827750682831</t>
+    <t xml:space="preserve">1.7882776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77074563503265</t>
+    <t xml:space="preserve">1.77074551582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704356193542</t>
+    <t xml:space="preserve">1.79704368114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.76197946071625</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542405605316</t>
+    <t xml:space="preserve">1.59542417526245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6217223405838</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308472633362</t>
+    <t xml:space="preserve">1.68308484554291</t>
   </si>
   <si>
     <t xml:space="preserve">1.63487148284912</t>
@@ -1115,19 +1115,19 @@
     <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419023036957</t>
+    <t xml:space="preserve">1.60419034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56474280357361</t>
+    <t xml:space="preserve">1.5647429227829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59980738162994</t>
+    <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
     <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993570327759</t>
+    <t xml:space="preserve">1.66993582248688</t>
   </si>
   <si>
     <t xml:space="preserve">1.63048851490021</t>
@@ -1139,25 +1139,25 @@
     <t xml:space="preserve">1.70061707496643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64363753795624</t>
+    <t xml:space="preserve">1.64363765716553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61295628547668</t>
+    <t xml:space="preserve">1.61295640468597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58227503299713</t>
+    <t xml:space="preserve">1.58227491378784</t>
   </si>
   <si>
     <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58665800094604</t>
+    <t xml:space="preserve">1.58665812015533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597698688507</t>
+    <t xml:space="preserve">1.55597686767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42010271549225</t>
+    <t xml:space="preserve">1.42010283470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.42448580265045</t>
@@ -1166,28 +1166,28 @@
     <t xml:space="preserve">1.32367610931396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29737782478333</t>
+    <t xml:space="preserve">1.29737794399261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24478137493134</t>
+    <t xml:space="preserve">1.24478161334991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20971727371216</t>
+    <t xml:space="preserve">1.20971715450287</t>
   </si>
   <si>
     <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065564632416</t>
+    <t xml:space="preserve">1.38065552711487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41571974754333</t>
+    <t xml:space="preserve">1.41571986675262</t>
   </si>
   <si>
     <t xml:space="preserve">1.4025707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325197696686</t>
+    <t xml:space="preserve">1.43325185775757</t>
   </si>
   <si>
     <t xml:space="preserve">1.38942158222198</t>
@@ -1196,40 +1196,40 @@
     <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874021053314</t>
+    <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
     <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44640100002289</t>
+    <t xml:space="preserve">1.4464008808136</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4507839679718</t>
+    <t xml:space="preserve">1.45078408718109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3938045501709</t>
+    <t xml:space="preserve">1.39380466938019</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36750638484955</t>
+    <t xml:space="preserve">1.36750626564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406167030334</t>
+    <t xml:space="preserve">1.53406178951263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214647293091</t>
+    <t xml:space="preserve">1.5121465921402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52967858314514</t>
+    <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721093177795</t>
+    <t xml:space="preserve">1.54721081256866</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">1.56035983562469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091252803802</t>
+    <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48584842681885</t>
+    <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5165296792984</t>
+    <t xml:space="preserve">1.51652956008911</t>
   </si>
   <si>
     <t xml:space="preserve">1.5691260099411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776350498199</t>
+    <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529573440552</t>
+    <t xml:space="preserve">1.52529549598694</t>
   </si>
   <si>
     <t xml:space="preserve">1.49899744987488</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232108592987</t>
+    <t xml:space="preserve">1.54232120513916</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46114611625671</t>
+    <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
     <t xml:space="preserve">1.50624334812164</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310748577118</t>
+    <t xml:space="preserve">1.44310736656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604912281036</t>
+    <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
     <t xml:space="preserve">1.39801025390625</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35291314125061</t>
+    <t xml:space="preserve">1.3529132604599</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">1.3438937664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31683564186096</t>
+    <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
     <t xml:space="preserve">1.26271903514862</t>
@@ -1334,16 +1334,16 @@
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056367874146</t>
+    <t xml:space="preserve">1.19056355953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664129734039</t>
+    <t xml:space="preserve">1.22664141654968</t>
   </si>
   <si>
     <t xml:space="preserve">1.21762180328369</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
     <t xml:space="preserve">1.36193263530731</t>
@@ -1370,25 +1370,25 @@
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566067218781</t>
+    <t xml:space="preserve">1.23566079139709</t>
   </si>
   <si>
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055406093597</t>
+    <t xml:space="preserve">1.65055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153468608856</t>
+    <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251519203186</t>
+    <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59643757343292</t>
+    <t xml:space="preserve">1.59643745422363</t>
   </si>
   <si>
     <t xml:space="preserve">1.79486489295959</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.70467066764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72270941734314</t>
+    <t xml:space="preserve">1.72270953655243</t>
   </si>
   <si>
     <t xml:space="preserve">1.71369004249573</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840832233429</t>
+    <t xml:space="preserve">1.118408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350531578064</t>
+    <t xml:space="preserve">1.16350543498993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15448582172394</t>
+    <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1274276971817</t>
+    <t xml:space="preserve">1.12742757797241</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25369966030121</t>
+    <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10036945343018</t>
+    <t xml:space="preserve">1.10036933422089</t>
   </si>
   <si>
     <t xml:space="preserve">1.10938882827759</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233058452606</t>
+    <t xml:space="preserve">1.08233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1460,43 +1460,43 @@
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331120967865</t>
+    <t xml:space="preserve">1.07331132888794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527234077454</t>
+    <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03723347187042</t>
+    <t xml:space="preserve">1.03723335266113</t>
   </si>
   <si>
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097490310669</t>
+    <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078055858612</t>
+    <t xml:space="preserve">0.965078175067902</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019812107086</t>
+    <t xml:space="preserve">0.938019752502441</t>
   </si>
   <si>
     <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947039127349854</t>
+    <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
     <t xml:space="preserve">0.897432446479797</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983116924762726</t>
+    <t xml:space="preserve">0.983117043972015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0191947221756</t>
+    <t xml:space="preserve">1.01919460296631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95605856180191</t>
+    <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
     <t xml:space="preserve">1.20860242843628</t>
@@ -67666,7 +67666,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.5166666667</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>1600</v>
@@ -67687,6 +67687,32 @@
         <v>574</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.4054050926</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>400</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>574</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">LMG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43781757354736</t>
+    <t xml:space="preserve">1.43781769275665</t>
   </si>
   <si>
     <t xml:space="preserve">1.48684310913086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424724578857</t>
+    <t xml:space="preserve">1.44424712657928</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
@@ -59,52 +59,52 @@
     <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593269348145</t>
+    <t xml:space="preserve">1.37593281269073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414030075073</t>
+    <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744762420654</t>
+    <t xml:space="preserve">1.35744750499725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628830432892</t>
+    <t xml:space="preserve">1.36628842353821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41290295124054</t>
+    <t xml:space="preserve">1.41290271282196</t>
   </si>
   <si>
     <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647327899933</t>
+    <t xml:space="preserve">1.40647315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44585454463959</t>
+    <t xml:space="preserve">1.4458544254303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39843618869781</t>
+    <t xml:space="preserve">1.3984363079071</t>
   </si>
   <si>
     <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726276874542</t>
+    <t xml:space="preserve">1.31726288795471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002938747406</t>
+    <t xml:space="preserve">1.31002914905548</t>
   </si>
   <si>
     <t xml:space="preserve">1.34217739105225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021436214447</t>
+    <t xml:space="preserve">1.35021424293518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3212810754776</t>
+    <t xml:space="preserve">1.32128119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557708263397</t>
+    <t xml:space="preserve">1.38557720184326</t>
   </si>
   <si>
     <t xml:space="preserve">1.46273219585419</t>
@@ -113,40 +113,40 @@
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693559646606</t>
+    <t xml:space="preserve">1.50693571567535</t>
   </si>
   <si>
     <t xml:space="preserve">1.49889874458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47237646579742</t>
+    <t xml:space="preserve">1.472376704216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49488008022308</t>
+    <t xml:space="preserve">1.49488019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274653434753</t>
+    <t xml:space="preserve">1.55274665355682</t>
   </si>
   <si>
     <t xml:space="preserve">1.61543488502502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169392108917</t>
+    <t xml:space="preserve">1.67169380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490875720978</t>
+    <t xml:space="preserve">1.67490887641907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6459755897522</t>
+    <t xml:space="preserve">1.64597570896149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55113911628723</t>
+    <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
     <t xml:space="preserve">1.52702808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095414161682</t>
+    <t xml:space="preserve">1.51095402240753</t>
   </si>
   <si>
     <t xml:space="preserve">1.45630276203156</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">1.45601892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426239490509</t>
+    <t xml:space="preserve">1.43426251411438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40832185745239</t>
+    <t xml:space="preserve">1.4083217382431</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43091511726379</t>
+    <t xml:space="preserve">1.43091535568237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42840492725372</t>
+    <t xml:space="preserve">1.42840480804443</t>
   </si>
   <si>
     <t xml:space="preserve">1.4133425951004</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">1.4049745798111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313498020172</t>
+    <t xml:space="preserve">1.36313474178314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35560393333435</t>
+    <t xml:space="preserve">1.35560381412506</t>
   </si>
   <si>
     <t xml:space="preserve">1.37233972549438</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288589000702</t>
+    <t xml:space="preserve">1.30288600921631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325479388237</t>
+    <t xml:space="preserve">1.32547950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32213222980499</t>
+    <t xml:space="preserve">1.3221321105957</t>
   </si>
   <si>
     <t xml:space="preserve">1.26439356803894</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">1.30539631843567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397194862366</t>
+    <t xml:space="preserve">1.36397159099579</t>
   </si>
   <si>
     <t xml:space="preserve">1.41250574588776</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">1.3807076215744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33050012588501</t>
+    <t xml:space="preserve">1.3305002450943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27192461490631</t>
+    <t xml:space="preserve">1.2719247341156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267839431763</t>
+    <t xml:space="preserve">1.25267827510834</t>
   </si>
   <si>
     <t xml:space="preserve">1.22506427764893</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841131687164</t>
+    <t xml:space="preserve">1.22841155529022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845303058624</t>
+    <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
     <t xml:space="preserve">1.23008501529694</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171711921692</t>
+    <t xml:space="preserve">1.22171723842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816234588623</t>
+    <t xml:space="preserve">1.16816246509552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226328372955</t>
+    <t xml:space="preserve">1.15226316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14222168922424</t>
+    <t xml:space="preserve">1.14222180843353</t>
   </si>
   <si>
     <t xml:space="preserve">1.17150950431824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12966978549957</t>
+    <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293399333954</t>
+    <t xml:space="preserve">1.11293423175812</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850089550018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343880176544</t>
+    <t xml:space="preserve">1.03343868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02423393726349</t>
+    <t xml:space="preserve">1.02423405647278</t>
   </si>
   <si>
     <t xml:space="preserve">1.03929626941681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05435848236084</t>
+    <t xml:space="preserve">1.05435860157013</t>
   </si>
   <si>
     <t xml:space="preserve">1.08364629745483</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">1.06440007686615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07109439373016</t>
+    <t xml:space="preserve">1.07109451293945</t>
   </si>
   <si>
     <t xml:space="preserve">1.03762269020081</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984067976474762</t>
+    <t xml:space="preserve">0.984068036079407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967157840729</t>
+    <t xml:space="preserve">0.999967217445374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251888275146</t>
+    <t xml:space="preserve">1.01251900196075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00415098667145</t>
+    <t xml:space="preserve">1.00415086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127379417419</t>
+    <t xml:space="preserve">0.958127439022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969842672348022</t>
+    <t xml:space="preserve">0.969842612743378</t>
   </si>
   <si>
     <t xml:space="preserve">0.944738745689392</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">0.866080224514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952269852161407</t>
+    <t xml:space="preserve">0.952269911766052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912103950977325</t>
+    <t xml:space="preserve">0.912103831768036</t>
   </si>
   <si>
     <t xml:space="preserve">0.89955198764801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204769611359</t>
+    <t xml:space="preserve">0.896204710006714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937811374664</t>
+    <t xml:space="preserve">0.871937870979309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756613731384</t>
+    <t xml:space="preserve">0.908756673336029</t>
   </si>
   <si>
     <t xml:space="preserve">0.950596392154694</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">0.917124509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471787452698</t>
+    <t xml:space="preserve">0.920471727848053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332184314728</t>
+    <t xml:space="preserve">0.967332065105438</t>
   </si>
   <si>
     <t xml:space="preserve">0.962311327457428</t>
@@ -368,55 +368,55 @@
     <t xml:space="preserve">1.05519545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599142551422</t>
+    <t xml:space="preserve">0.991599082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088833332062</t>
+    <t xml:space="preserve">0.989088892936707</t>
   </si>
   <si>
     <t xml:space="preserve">1.0016405582428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995783150196075</t>
+    <t xml:space="preserve">0.99578320980072</t>
   </si>
   <si>
     <t xml:space="preserve">0.99076235294342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207639217377</t>
+    <t xml:space="preserve">0.937207520008087</t>
   </si>
   <si>
     <t xml:space="preserve">0.982394456863403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94139176607132</t>
+    <t xml:space="preserve">0.941391468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988251864910126</t>
+    <t xml:space="preserve">0.98825204372406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352802753448</t>
+    <t xml:space="preserve">0.972352862358093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96816885471344</t>
+    <t xml:space="preserve">0.968168795108795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975700080394745</t>
+    <t xml:space="preserve">0.97570013999939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231127262115</t>
+    <t xml:space="preserve">0.983231067657471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987415134906769</t>
+    <t xml:space="preserve">0.987415194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005823135376</t>
+    <t xml:space="preserve">0.969005882740021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994109392166138</t>
+    <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943490982056</t>
+    <t xml:space="preserve">0.953943431377411</t>
   </si>
   <si>
     <t xml:space="preserve">1.05854260921478</t>
@@ -425,25 +425,25 @@
     <t xml:space="preserve">1.05937933921814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507078647614</t>
+    <t xml:space="preserve">1.02507090568542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05268490314484</t>
+    <t xml:space="preserve">1.05268502235413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10456609725952</t>
+    <t xml:space="preserve">1.10456621646881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636422157288</t>
+    <t xml:space="preserve">1.13636434078217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14807951450348</t>
+    <t xml:space="preserve">1.1480792760849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577658176422</t>
+    <t xml:space="preserve">1.19577634334564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19661331176758</t>
+    <t xml:space="preserve">1.19661319255829</t>
   </si>
   <si>
     <t xml:space="preserve">1.25602555274963</t>
@@ -452,28 +452,28 @@
     <t xml:space="preserve">1.20581805706024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2133492231369</t>
+    <t xml:space="preserve">1.21334910392761</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644717216492</t>
+    <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15310001373291</t>
+    <t xml:space="preserve">1.15309989452362</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242930412292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19493973255157</t>
+    <t xml:space="preserve">1.19493961334229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15477347373962</t>
+    <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14640581607819</t>
+    <t xml:space="preserve">1.14640557765961</t>
   </si>
   <si>
     <t xml:space="preserve">1.19159257411957</t>
@@ -485,52 +485,52 @@
     <t xml:space="preserve">1.23761606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518882274628</t>
+    <t xml:space="preserve">1.25518870353699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23594260215759</t>
+    <t xml:space="preserve">1.2359424829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16146814823151</t>
+    <t xml:space="preserve">1.16146802902222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13385403156281</t>
+    <t xml:space="preserve">1.13385391235352</t>
   </si>
   <si>
     <t xml:space="preserve">1.13803791999817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12799644470215</t>
+    <t xml:space="preserve">1.12799632549286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12130212783813</t>
+    <t xml:space="preserve">1.12130200862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17653024196625</t>
+    <t xml:space="preserve">1.17653036117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581130981445</t>
+    <t xml:space="preserve">1.40581119060516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39576995372772</t>
+    <t xml:space="preserve">1.39577007293701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911711215973</t>
+    <t xml:space="preserve">1.39911699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39744341373444</t>
+    <t xml:space="preserve">1.39744353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46020293235779</t>
+    <t xml:space="preserve">1.4602028131485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534809589386</t>
+    <t xml:space="preserve">1.49534821510315</t>
   </si>
   <si>
     <t xml:space="preserve">1.45685577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865389823914</t>
+    <t xml:space="preserve">1.48865401744843</t>
   </si>
   <si>
     <t xml:space="preserve">1.48949062824249</t>
@@ -539,49 +539,49 @@
     <t xml:space="preserve">1.47275483608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53551423549652</t>
+    <t xml:space="preserve">1.53551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57316994667053</t>
+    <t xml:space="preserve">1.57316970825195</t>
   </si>
   <si>
     <t xml:space="preserve">1.5857218503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63174545764923</t>
+    <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
     <t xml:space="preserve">1.65684914588928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438031196594</t>
+    <t xml:space="preserve">1.66438043117523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550772666931</t>
+    <t xml:space="preserve">1.73550748825073</t>
   </si>
   <si>
     <t xml:space="preserve">1.75726413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77400016784668</t>
+    <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78236818313599</t>
+    <t xml:space="preserve">1.7823680639267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65099155902863</t>
+    <t xml:space="preserve">1.65099167823792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60078406333923</t>
+    <t xml:space="preserve">1.60078418254852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67358505725861</t>
+    <t xml:space="preserve">1.67358493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62003028392792</t>
+    <t xml:space="preserve">1.62003016471863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697369098663</t>
+    <t xml:space="preserve">1.68697381019592</t>
   </si>
   <si>
     <t xml:space="preserve">1.6166832447052</t>
@@ -593,25 +593,25 @@
     <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362665176392</t>
+    <t xml:space="preserve">1.68362653255463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71542453765869</t>
+    <t xml:space="preserve">1.7154244184494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73718118667603</t>
+    <t xml:space="preserve">1.73718130588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75224363803864</t>
+    <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052834510803</t>
+    <t xml:space="preserve">1.74052822589874</t>
   </si>
   <si>
     <t xml:space="preserve">1.723792552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601229667664</t>
+    <t xml:space="preserve">1.65601241588593</t>
   </si>
   <si>
     <t xml:space="preserve">1.74220204353333</t>
@@ -620,34 +620,34 @@
     <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337306022644</t>
+    <t xml:space="preserve">1.84337329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80050373077393</t>
+    <t xml:space="preserve">1.80050384998322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335630893707</t>
+    <t xml:space="preserve">1.78335618972778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193007946014</t>
+    <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
     <t xml:space="preserve">1.95483291149139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37323594093323</t>
+    <t xml:space="preserve">2.37323570251465</t>
   </si>
   <si>
     <t xml:space="preserve">2.46926283836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82421898841858</t>
+    <t xml:space="preserve">2.82421922683716</t>
   </si>
   <si>
     <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505139350891</t>
+    <t xml:space="preserve">2.73505163192749</t>
   </si>
   <si>
     <t xml:space="preserve">2.64416885375977</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">2.47783660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.460688829422</t>
+    <t xml:space="preserve">2.46068859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067195892334</t>
+    <t xml:space="preserve">2.40067172050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">2.48983979225159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929634094238</t>
+    <t xml:space="preserve">2.58929657936096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7864944934845</t>
+    <t xml:space="preserve">2.78649425506592</t>
   </si>
   <si>
     <t xml:space="preserve">2.67503452301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012874603271</t>
+    <t xml:space="preserve">2.50012826919556</t>
   </si>
   <si>
     <t xml:space="preserve">2.4624035358429</t>
@@ -692,31 +692,31 @@
     <t xml:space="preserve">2.41953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45211505889893</t>
+    <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52927947044373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57214832305908</t>
+    <t xml:space="preserve">2.57214856147766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48641014099121</t>
+    <t xml:space="preserve">2.48641037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43496751785278</t>
+    <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4555447101593</t>
+    <t xml:space="preserve">2.45554494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45725917816162</t>
+    <t xml:space="preserve">2.4572594165802</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613829612732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45897459983826</t>
+    <t xml:space="preserve">2.4589741230011</t>
   </si>
   <si>
     <t xml:space="preserve">2.47440671920776</t>
@@ -725,31 +725,31 @@
     <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781973838806</t>
+    <t xml:space="preserve">2.41781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639374732971</t>
+    <t xml:space="preserve">2.42639327049255</t>
   </si>
   <si>
     <t xml:space="preserve">2.3835244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33208131790161</t>
+    <t xml:space="preserve">2.33208155632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.31836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28063869476318</t>
+    <t xml:space="preserve">2.28063893318176</t>
   </si>
   <si>
     <t xml:space="preserve">2.32865214347839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31321907043457</t>
+    <t xml:space="preserve">2.31321883201599</t>
   </si>
   <si>
     <t xml:space="preserve">2.26692032814026</t>
@@ -761,49 +761,49 @@
     <t xml:space="preserve">2.12116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06800770759583</t>
+    <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05771899223328</t>
+    <t xml:space="preserve">2.0577187538147</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773586273193</t>
+    <t xml:space="preserve">2.11773562431335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1280243396759</t>
+    <t xml:space="preserve">2.12802457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515524864197</t>
+    <t xml:space="preserve">2.08515501022339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06629276275635</t>
+    <t xml:space="preserve">2.06629300117493</t>
   </si>
   <si>
     <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887313842773</t>
+    <t xml:space="preserve">2.09887337684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799059867859</t>
+    <t xml:space="preserve">2.00799036026001</t>
   </si>
   <si>
     <t xml:space="preserve">2.0508599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02342343330383</t>
+    <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20690369606018</t>
+    <t xml:space="preserve">2.2069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603778839111</t>
+    <t xml:space="preserve">2.17603802680969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08172535896301</t>
+    <t xml:space="preserve">2.08172559738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.10401749610901</t>
@@ -821,37 +821,37 @@
     <t xml:space="preserve">2.1537458896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15203094482422</t>
+    <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.16917872428894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27720880508423</t>
+    <t xml:space="preserve">2.27720856666565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22062134742737</t>
+    <t xml:space="preserve">2.22062158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25491738319397</t>
+    <t xml:space="preserve">2.25491714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2823531627655</t>
+    <t xml:space="preserve">2.28235340118408</t>
   </si>
   <si>
     <t xml:space="preserve">2.23776936531067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22233653068542</t>
+    <t xml:space="preserve">2.22233629226685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089343070984</t>
+    <t xml:space="preserve">2.17089366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975591659546</t>
+    <t xml:space="preserve">2.18975567817688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22919535636902</t>
+    <t xml:space="preserve">2.22919511795044</t>
   </si>
   <si>
     <t xml:space="preserve">2.24634289741516</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">2.27034974098206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27206492424011</t>
+    <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175933837891</t>
+    <t xml:space="preserve">2.20175957679749</t>
   </si>
   <si>
     <t xml:space="preserve">2.20861840248108</t>
@@ -884,25 +884,25 @@
     <t xml:space="preserve">2.24462842941284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43668222427368</t>
+    <t xml:space="preserve">2.4366819858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471230506897</t>
+    <t xml:space="preserve">2.54471254348755</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5138463973999</t>
+    <t xml:space="preserve">2.51384663581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50355792045593</t>
+    <t xml:space="preserve">2.50355815887451</t>
   </si>
   <si>
     <t xml:space="preserve">2.55500102043152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49326944351196</t>
+    <t xml:space="preserve">2.49326920509338</t>
   </si>
   <si>
     <t xml:space="preserve">2.47269225120544</t>
@@ -914,25 +914,25 @@
     <t xml:space="preserve">2.32179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809158325195</t>
+    <t xml:space="preserve">2.36809182167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.33379602432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41439032554626</t>
+    <t xml:space="preserve">2.41439008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34922909736633</t>
+    <t xml:space="preserve">2.34922885894775</t>
   </si>
   <si>
     <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410137176514</t>
+    <t xml:space="preserve">2.40410161018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39038348197937</t>
+    <t xml:space="preserve">2.39038372039795</t>
   </si>
   <si>
     <t xml:space="preserve">2.33551096916199</t>
@@ -941,19 +941,19 @@
     <t xml:space="preserve">2.3063600063324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38866877555847</t>
+    <t xml:space="preserve">2.38866853713989</t>
   </si>
   <si>
     <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832968711853</t>
+    <t xml:space="preserve">2.19832944869995</t>
   </si>
   <si>
     <t xml:space="preserve">2.1348831653595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430621147156</t>
+    <t xml:space="preserve">2.11430644989014</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632626533508</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201431274414</t>
+    <t xml:space="preserve">2.09201407432556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04057121276855</t>
+    <t xml:space="preserve">2.04057145118713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01484966278076</t>
+    <t xml:space="preserve">2.01484942436218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914498329163</t>
+    <t xml:space="preserve">2.04914546012878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90339016914368</t>
+    <t xml:space="preserve">1.90339004993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.9805543422699</t>
@@ -983,28 +983,28 @@
     <t xml:space="preserve">1.97198045253754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053782939911</t>
+    <t xml:space="preserve">1.92053747177124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912823200226</t>
+    <t xml:space="preserve">1.98912835121155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196382045746</t>
+    <t xml:space="preserve">1.91196405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92911148071289</t>
+    <t xml:space="preserve">1.9291113615036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624227046967</t>
+    <t xml:space="preserve">1.88624215126038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481627941132</t>
+    <t xml:space="preserve">1.89481604099274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909461021423</t>
+    <t xml:space="preserve">1.86909472942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194718837738</t>
+    <t xml:space="preserve">1.85194730758667</t>
   </si>
   <si>
     <t xml:space="preserve">1.94625926017761</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">2.06879162788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249358177185</t>
+    <t xml:space="preserve">2.04249334335327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97236514091492</t>
+    <t xml:space="preserve">1.97236502170563</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840618610382</t>
+    <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
     <t xml:space="preserve">1.88470447063446</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">1.99866330623627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606685638428</t>
+    <t xml:space="preserve">1.94606697559357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853450775146</t>
+    <t xml:space="preserve">1.92853462696075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86717247962952</t>
+    <t xml:space="preserve">1.86717224121094</t>
   </si>
   <si>
     <t xml:space="preserve">1.90223670005798</t>
@@ -1055,25 +1055,25 @@
     <t xml:space="preserve">1.82334184646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976881027222</t>
+    <t xml:space="preserve">1.91976892948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8496401309967</t>
+    <t xml:space="preserve">1.84964001178741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.893470287323</t>
+    <t xml:space="preserve">1.89347040653229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730080127716</t>
+    <t xml:space="preserve">1.93730056285858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989701271057</t>
+    <t xml:space="preserve">1.98989737033844</t>
   </si>
   <si>
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78827750682831</t>
+    <t xml:space="preserve">1.78827774524689</t>
   </si>
   <si>
     <t xml:space="preserve">1.77074551582336</t>
@@ -1088,19 +1088,19 @@
     <t xml:space="preserve">1.61733937263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59542405605316</t>
+    <t xml:space="preserve">1.59542429447174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6217223405838</t>
+    <t xml:space="preserve">1.62172245979309</t>
   </si>
   <si>
     <t xml:space="preserve">1.65678668022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68308472633362</t>
+    <t xml:space="preserve">1.68308484554291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63487148284912</t>
+    <t xml:space="preserve">1.63487160205841</t>
   </si>
   <si>
     <t xml:space="preserve">1.66555273532867</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">1.66116964817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57789194583893</t>
+    <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
     <t xml:space="preserve">1.60419023036957</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">1.5647429227829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59980738162994</t>
+    <t xml:space="preserve">1.59980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104120731354</t>
+    <t xml:space="preserve">1.59104108810425</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993570327759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048839569092</t>
+    <t xml:space="preserve">1.63048851490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.57350897789001</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">1.58665800094604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597686767578</t>
+    <t xml:space="preserve">1.55597674846649</t>
   </si>
   <si>
     <t xml:space="preserve">1.42010283470154</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">1.20971727371216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29299485683441</t>
+    <t xml:space="preserve">1.2929949760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065564632416</t>
+    <t xml:space="preserve">1.38065552711487</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
@@ -1196,40 +1196,40 @@
     <t xml:space="preserve">1.38503861427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35874021053314</t>
+    <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763494491577</t>
+    <t xml:space="preserve">1.43763482570648</t>
   </si>
   <si>
     <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201803207397</t>
+    <t xml:space="preserve">1.44201791286469</t>
   </si>
   <si>
     <t xml:space="preserve">1.4507839679718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3938045501709</t>
+    <t xml:space="preserve">1.39380466938019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41133666038513</t>
+    <t xml:space="preserve">1.41133677959442</t>
   </si>
   <si>
     <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406178951263</t>
+    <t xml:space="preserve">1.53406155109406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51214647293091</t>
+    <t xml:space="preserve">1.5121465921402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52967858314514</t>
+    <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721093177795</t>
+    <t xml:space="preserve">1.54721069335938</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">1.56035995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091252803802</t>
+    <t xml:space="preserve">1.52091264724731</t>
   </si>
   <si>
     <t xml:space="preserve">1.48584830760956</t>
@@ -1253,25 +1253,25 @@
     <t xml:space="preserve">1.56912589073181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776362419128</t>
+    <t xml:space="preserve">1.50776350498199</t>
   </si>
   <si>
     <t xml:space="preserve">1.52529573440552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899744987488</t>
+    <t xml:space="preserve">1.49899733066559</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545694828033</t>
+    <t xml:space="preserve">1.60545706748962</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232108592987</t>
+    <t xml:space="preserve">1.54232096672058</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">1.48820459842682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46114611625671</t>
+    <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624334812164</t>
+    <t xml:space="preserve">1.50624322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016572952271</t>
+    <t xml:space="preserve">1.47016561031342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44310748577118</t>
+    <t xml:space="preserve">1.44310736656189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41604912281036</t>
+    <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801025390625</t>
+    <t xml:space="preserve">1.39801013469696</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702962875366</t>
+    <t xml:space="preserve">1.40702974796295</t>
   </si>
   <si>
     <t xml:space="preserve">1.38899087905884</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.37095201015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35291314125061</t>
+    <t xml:space="preserve">1.3529132604599</t>
   </si>
   <si>
     <t xml:space="preserve">1.33487439155579</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">1.3438937664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31683564186096</t>
+    <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
     <t xml:space="preserve">1.28977727890015</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">1.22664129734039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762180328369</t>
+    <t xml:space="preserve">1.21762192249298</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">1.29879677295685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193263530731</t>
+    <t xml:space="preserve">1.36193251609802</t>
   </si>
   <si>
     <t xml:space="preserve">1.37997150421143</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">1.27173840999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23566067218781</t>
+    <t xml:space="preserve">1.23566079139709</t>
   </si>
   <si>
     <t xml:space="preserve">1.45212686061859</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">1.65055406093597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859292984009</t>
+    <t xml:space="preserve">1.66859304904938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64153468608856</t>
+    <t xml:space="preserve">1.64153480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63251519203186</t>
+    <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
     <t xml:space="preserve">1.59643757343292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486489295959</t>
+    <t xml:space="preserve">1.79486477375031</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
@@ -1400,19 +1400,19 @@
     <t xml:space="preserve">1.72270941734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369004249573</t>
+    <t xml:space="preserve">1.71369016170502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349581718445</t>
+    <t xml:space="preserve">1.62349569797516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55134057998657</t>
+    <t xml:space="preserve">1.55134046077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6956512928009</t>
+    <t xml:space="preserve">1.69565117359161</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">1.16350531578064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15448582172394</t>
+    <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
     <t xml:space="preserve">1.1274276971817</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">1.19958305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25369966030121</t>
+    <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
     <t xml:space="preserve">1.14546644687653</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09134995937347</t>
+    <t xml:space="preserve">1.09135007858276</t>
   </si>
   <si>
     <t xml:space="preserve">1.08233058452606</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">1.07331120967865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05527234077454</t>
+    <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
     <t xml:space="preserve">1.03723347187042</t>
@@ -1475,49 +1475,49 @@
     <t xml:space="preserve">1.0101752281189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974097490310669</t>
+    <t xml:space="preserve">0.974097549915314</t>
   </si>
   <si>
     <t xml:space="preserve">1.00115573406219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965078055858612</t>
+    <t xml:space="preserve">0.965078175067902</t>
   </si>
   <si>
     <t xml:space="preserve">0.929000377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938019812107086</t>
+    <t xml:space="preserve">0.938019752502441</t>
   </si>
   <si>
     <t xml:space="preserve">0.919980943202972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947039127349854</t>
+    <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432446479797</t>
+    <t xml:space="preserve">0.897432386875153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91096156835556</t>
+    <t xml:space="preserve">0.910961508750916</t>
   </si>
   <si>
     <t xml:space="preserve">0.983116924762726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0191947221756</t>
+    <t xml:space="preserve">1.01919460296631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95605856180191</t>
+    <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20860242843628</t>
+    <t xml:space="preserve">1.20860254764557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918510437012</t>
+    <t xml:space="preserve">1.47918498516083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098133087158</t>
+    <t xml:space="preserve">1.25098145008087</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12124991416931</t>
+    <t xml:space="preserve">1.1212500333786</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1565,22 +1565,25 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051640987396</t>
+    <t xml:space="preserve">1.13051652908325</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19538223743439</t>
+    <t xml:space="preserve">1.1953821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198353767395</t>
+    <t xml:space="preserve">1.11198341846466</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -57599,7 +57602,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2134" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57625,7 +57628,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2135" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57651,7 +57654,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2136" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57677,7 +57680,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2137" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57703,7 +57706,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2138" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57729,7 +57732,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2139" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57755,7 +57758,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2140" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57781,7 +57784,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57807,7 +57810,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2142" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57833,7 +57836,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2143" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57859,7 +57862,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57885,7 +57888,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57911,7 +57914,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57937,7 +57940,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2147" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57963,7 +57966,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57989,7 +57992,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2149" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58015,7 +58018,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2150" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58041,7 +58044,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2151" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58067,7 +58070,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2152" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58093,7 +58096,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2153" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58119,7 +58122,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2154" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58145,7 +58148,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2155" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58171,7 +58174,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2156" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58197,7 +58200,7 @@
         <v>1</v>
       </c>
       <c r="G2157" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58223,7 +58226,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58249,7 +58252,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2159" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58275,7 +58278,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2160" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58301,7 +58304,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2161" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58327,7 +58330,7 @@
         <v>1</v>
       </c>
       <c r="G2162" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58353,7 +58356,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2163" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58379,7 +58382,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2164" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58405,7 +58408,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58431,7 +58434,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2166" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58457,7 +58460,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2167" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58483,7 +58486,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2168" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58509,7 +58512,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2169" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58535,7 +58538,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58561,7 +58564,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2171" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58587,7 +58590,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2172" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58613,7 +58616,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58639,7 +58642,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2174" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58665,7 +58668,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2175" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58691,7 +58694,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2176" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58717,7 +58720,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2177" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58743,7 +58746,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2178" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58769,7 +58772,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2179" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58795,7 +58798,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58821,7 +58824,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2181" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58847,7 +58850,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2182" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58873,7 +58876,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2183" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58899,7 +58902,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2184" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58925,7 +58928,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2185" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58951,7 +58954,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2186" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58977,7 +58980,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2187" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59003,7 +59006,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59029,7 +59032,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2189" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59055,7 +59058,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2190" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59081,7 +59084,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2191" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59107,7 +59110,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2192" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59133,7 +59136,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2193" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59159,7 +59162,7 @@
         <v>1</v>
       </c>
       <c r="G2194" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59185,7 +59188,7 @@
         <v>1</v>
       </c>
       <c r="G2195" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59211,7 +59214,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2196" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59237,7 +59240,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59263,7 +59266,7 @@
         <v>1</v>
       </c>
       <c r="G2198" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59289,7 +59292,7 @@
         <v>1</v>
       </c>
       <c r="G2199" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59315,7 +59318,7 @@
         <v>1</v>
       </c>
       <c r="G2200" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59341,7 +59344,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2201" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59367,7 +59370,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59393,7 +59396,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59419,7 +59422,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59445,7 +59448,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59471,7 +59474,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2206" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59497,7 +59500,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59523,7 +59526,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2208" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59549,7 +59552,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2209" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59575,7 +59578,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2210" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59601,7 +59604,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2211" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59627,7 +59630,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2212" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59653,7 +59656,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2213" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59679,7 +59682,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2214" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59705,7 +59708,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59731,7 +59734,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2216" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59757,7 +59760,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2217" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59783,7 +59786,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59809,7 +59812,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2219" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59835,7 +59838,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2220" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59861,7 +59864,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2221" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59887,7 +59890,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59913,7 +59916,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2223" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59939,7 +59942,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2224" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59965,7 +59968,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2225" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59991,7 +59994,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2226" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60017,7 +60020,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2227" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60043,7 +60046,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2228" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60069,7 +60072,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2229" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60095,7 +60098,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2230" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60121,7 +60124,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2231" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60147,7 +60150,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2232" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60173,7 +60176,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2233" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60199,7 +60202,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2234" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60225,7 +60228,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2235" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60251,7 +60254,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G2236" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60277,7 +60280,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2237" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60303,7 +60306,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2238" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60329,7 +60332,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2239" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60355,7 +60358,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60381,7 +60384,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60407,7 +60410,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2242" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60433,7 +60436,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2243" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60459,7 +60462,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2244" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60485,7 +60488,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2245" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60511,7 +60514,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60537,7 +60540,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2247" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60563,7 +60566,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2248" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60589,7 +60592,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2249" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60615,7 +60618,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2250" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60641,7 +60644,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2251" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60667,7 +60670,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G2252" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60693,7 +60696,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2253" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60719,7 +60722,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2254" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60745,7 +60748,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2255" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60771,7 +60774,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2256" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60797,7 +60800,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2257" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60823,7 +60826,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2258" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60849,7 +60852,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2259" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60875,7 +60878,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2260" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60901,7 +60904,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2261" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60927,7 +60930,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2262" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60953,7 +60956,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2263" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60979,7 +60982,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2264" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61005,7 +61008,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2265" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61031,7 +61034,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2266" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61057,7 +61060,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2267" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61083,7 +61086,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2268" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61109,7 +61112,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2269" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61135,7 +61138,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2270" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61161,7 +61164,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61187,7 +61190,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2272" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61213,7 +61216,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2273" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61239,7 +61242,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2274" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61265,7 +61268,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2275" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61291,7 +61294,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2276" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61317,7 +61320,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2277" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61343,7 +61346,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2278" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61369,7 +61372,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2279" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61395,7 +61398,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2280" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61421,7 +61424,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2281" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61447,7 +61450,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2282" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61473,7 +61476,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61499,7 +61502,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2284" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61525,7 +61528,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2285" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61551,7 +61554,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2286" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61577,7 +61580,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2287" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61603,7 +61606,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2288" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61629,7 +61632,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2289" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61655,7 +61658,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2290" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61681,7 +61684,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2291" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61707,7 +61710,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2292" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61733,7 +61736,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2293" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61759,7 +61762,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2294" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61785,7 +61788,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61811,7 +61814,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2296" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61837,7 +61840,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2297" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61863,7 +61866,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2298" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61889,7 +61892,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2299" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61915,7 +61918,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61941,7 +61944,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2301" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61967,7 +61970,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2302" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61993,7 +61996,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2303" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62019,7 +62022,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2304" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62045,7 +62048,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2305" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62071,7 +62074,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2306" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62097,7 +62100,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2307" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62123,7 +62126,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G2308" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62149,7 +62152,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2309" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62175,7 +62178,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2310" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62201,7 +62204,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G2311" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62227,7 +62230,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2312" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62253,7 +62256,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2313" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62279,7 +62282,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2314" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62305,7 +62308,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62331,7 +62334,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2316" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62357,7 +62360,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G2317" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62383,7 +62386,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2318" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62409,7 +62412,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G2319" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62435,7 +62438,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2320" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62461,7 +62464,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2321" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62487,7 +62490,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2322" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62513,7 +62516,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2323" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62539,7 +62542,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2324" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62565,7 +62568,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2325" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62591,7 +62594,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2326" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62617,7 +62620,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2327" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62643,7 +62646,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2328" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62669,7 +62672,7 @@
         <v>0.875</v>
       </c>
       <c r="G2329" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62695,7 +62698,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2330" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62721,7 +62724,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2331" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62747,7 +62750,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2332" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62773,7 +62776,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G2333" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62799,7 +62802,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2334" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62825,7 +62828,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G2335" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62851,7 +62854,7 @@
         <v>0.875</v>
       </c>
       <c r="G2336" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62877,7 +62880,7 @@
         <v>0.875</v>
       </c>
       <c r="G2337" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62903,7 +62906,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2338" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62929,7 +62932,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2339" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62955,7 +62958,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2340" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62981,7 +62984,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2341" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63007,7 +63010,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2342" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63033,7 +63036,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G2343" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63059,7 +63062,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G2344" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63085,7 +63088,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2345" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63111,7 +63114,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2346" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63137,7 +63140,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2347" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63163,7 +63166,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G2348" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63189,7 +63192,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2349" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63215,7 +63218,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2350" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63241,7 +63244,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2351" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63267,7 +63270,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2352" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63293,7 +63296,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2353" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63319,7 +63322,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2354" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63345,7 +63348,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G2355" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63371,7 +63374,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2356" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63397,7 +63400,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2357" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63423,7 +63426,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2358" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63449,7 +63452,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2359" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63475,7 +63478,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2360" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63501,7 +63504,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2361" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63527,7 +63530,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2362" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63553,7 +63556,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2363" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63579,7 +63582,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2364" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63605,7 +63608,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2365" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63631,7 +63634,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2366" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63657,7 +63660,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2367" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63683,7 +63686,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G2368" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63709,7 +63712,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2369" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63735,7 +63738,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2370" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63761,7 +63764,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2371" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63787,7 +63790,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2372" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63813,7 +63816,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2373" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63839,7 +63842,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2374" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63865,7 +63868,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2375" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63891,7 +63894,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2376" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63917,7 +63920,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2377" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63943,7 +63946,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2378" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63969,7 +63972,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2379" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63995,7 +63998,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2380" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64021,7 +64024,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64047,7 +64050,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2382" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64073,7 +64076,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G2383" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64099,7 +64102,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64125,7 +64128,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64151,7 +64154,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2386" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64177,7 +64180,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2387" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64203,7 +64206,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2388" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64229,7 +64232,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2389" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64255,7 +64258,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G2390" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64281,7 +64284,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2391" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64307,7 +64310,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2392" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64333,7 +64336,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2393" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64359,7 +64362,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2394" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64385,7 +64388,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2395" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64411,7 +64414,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2396" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64437,7 +64440,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2397" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64463,7 +64466,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2398" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64489,7 +64492,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2399" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64515,7 +64518,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2400" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64541,7 +64544,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2401" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64567,7 +64570,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2402" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64593,7 +64596,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2403" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64619,7 +64622,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2404" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64645,7 +64648,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2405" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64671,7 +64674,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2406" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64697,7 +64700,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2407" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64723,7 +64726,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2408" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64749,7 +64752,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2409" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64775,7 +64778,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2410" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64801,7 +64804,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2411" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64827,7 +64830,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2412" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64853,7 +64856,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2413" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64879,7 +64882,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2414" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64905,7 +64908,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2415" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64931,7 +64934,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2416" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64957,7 +64960,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2417" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64983,7 +64986,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2418" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65009,7 +65012,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2419" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65035,7 +65038,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65061,7 +65064,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2421" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65087,7 +65090,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2422" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65113,7 +65116,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2423" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65139,7 +65142,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2424" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65165,7 +65168,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2425" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65191,7 +65194,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2426" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65217,7 +65220,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2427" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65243,7 +65246,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2428" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65269,7 +65272,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2429" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65295,7 +65298,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2430" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65321,7 +65324,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2431" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65347,7 +65350,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2432" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65373,7 +65376,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2433" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65399,7 +65402,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2434" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65425,7 +65428,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2435" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65451,7 +65454,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2436" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65477,7 +65480,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2437" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65503,7 +65506,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2438" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65529,7 +65532,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2439" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65555,7 +65558,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2440" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65581,7 +65584,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2441" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65607,7 +65610,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2442" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65633,7 +65636,7 @@
         <v>1</v>
       </c>
       <c r="G2443" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65659,7 +65662,7 @@
         <v>1</v>
       </c>
       <c r="G2444" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65685,7 +65688,7 @@
         <v>1</v>
       </c>
       <c r="G2445" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65711,7 +65714,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65737,7 +65740,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65763,7 +65766,7 @@
         <v>1</v>
       </c>
       <c r="G2448" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65789,7 +65792,7 @@
         <v>1</v>
       </c>
       <c r="G2449" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65815,7 +65818,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2450" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65841,7 +65844,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65867,7 +65870,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2452" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65893,7 +65896,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2453" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65919,7 +65922,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2454" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65945,7 +65948,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65971,7 +65974,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2456" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65997,7 +66000,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2457" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66023,7 +66026,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2458" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66049,7 +66052,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2459" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66075,7 +66078,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2460" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66101,7 +66104,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2461" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66127,7 +66130,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2462" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66153,7 +66156,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2463" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66179,7 +66182,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2464" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66205,7 +66208,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2465" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66231,7 +66234,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66257,7 +66260,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2467" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66283,7 +66286,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66309,7 +66312,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2469" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66335,7 +66338,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2470" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66361,7 +66364,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2471" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66387,7 +66390,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2472" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66413,7 +66416,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2473" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66439,7 +66442,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2474" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66465,7 +66468,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2475" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66491,7 +66494,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2476" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66517,7 +66520,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2477" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66543,7 +66546,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66569,7 +66572,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2479" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66595,7 +66598,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2480" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66621,7 +66624,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66647,7 +66650,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G2482" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66673,7 +66676,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2483" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66699,7 +66702,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G2484" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66725,7 +66728,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2485" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66751,7 +66754,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2486" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66777,7 +66780,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2487" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66803,7 +66806,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2488" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66829,7 +66832,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G2489" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66855,7 +66858,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2490" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66881,7 +66884,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2491" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66907,7 +66910,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2492" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66933,7 +66936,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2493" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66959,7 +66962,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2494" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66985,7 +66988,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2495" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67011,7 +67014,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2496" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67037,7 +67040,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2497" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67063,7 +67066,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2498" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67089,7 +67092,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2499" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67115,7 +67118,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G2500" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67141,7 +67144,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2501" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67167,7 +67170,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2502" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67193,7 +67196,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2503" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67219,7 +67222,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2504" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67245,7 +67248,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2505" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67271,7 +67274,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2506" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67297,7 +67300,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2507" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67323,7 +67326,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2508" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67349,7 +67352,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67375,7 +67378,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2510" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67401,7 +67404,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2511" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67427,7 +67430,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2512" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67453,7 +67456,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2513" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67479,7 +67482,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2514" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67505,7 +67508,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2515" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67531,7 +67534,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2516" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67557,7 +67560,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2517" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67583,7 +67586,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2518" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -67609,7 +67612,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2519" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -67635,7 +67638,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2520" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -67661,7 +67664,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2521" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -67687,7 +67690,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2522" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -67713,7 +67716,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2523" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -67739,7 +67742,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G2524" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -67765,9 +67768,35 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G2525" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.3333333333</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>591</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.43781769275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48684310913086</t>
+    <t xml:space="preserve">1.48684322834015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44424712657928</t>
+    <t xml:space="preserve">1.44424724578857</t>
   </si>
   <si>
     <t xml:space="preserve">1.42254722118378</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">1.38236236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37593281269073</t>
+    <t xml:space="preserve">1.37593269348145</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414041996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744750499725</t>
+    <t xml:space="preserve">1.35744762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36628842353821</t>
+    <t xml:space="preserve">1.36628830432892</t>
   </si>
   <si>
     <t xml:space="preserve">1.41290271282196</t>
@@ -77,91 +77,91 @@
     <t xml:space="preserve">1.3815586566925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40647315979004</t>
+    <t xml:space="preserve">1.40647327899933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4458544254303</t>
+    <t xml:space="preserve">1.44585454463959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3984363079071</t>
+    <t xml:space="preserve">1.39843642711639</t>
   </si>
   <si>
     <t xml:space="preserve">1.34780323505402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31726288795471</t>
+    <t xml:space="preserve">1.31726276874542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31002914905548</t>
+    <t xml:space="preserve">1.31002926826477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34217739105225</t>
+    <t xml:space="preserve">1.34217715263367</t>
   </si>
   <si>
     <t xml:space="preserve">1.35021424293518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32128119468689</t>
+    <t xml:space="preserve">1.32128131389618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38557720184326</t>
+    <t xml:space="preserve">1.38557696342468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46273219585419</t>
+    <t xml:space="preserve">1.46273231506348</t>
   </si>
   <si>
     <t xml:space="preserve">1.430584192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50693571567535</t>
+    <t xml:space="preserve">1.50693559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49889874458313</t>
+    <t xml:space="preserve">1.49889862537384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.472376704216</t>
+    <t xml:space="preserve">1.47237658500671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49488019943237</t>
+    <t xml:space="preserve">1.49487996101379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55274665355682</t>
+    <t xml:space="preserve">1.55274653434753</t>
   </si>
   <si>
     <t xml:space="preserve">1.61543488502502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67169380187988</t>
+    <t xml:space="preserve">1.67169392108917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67490887641907</t>
+    <t xml:space="preserve">1.67490863800049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64597570896149</t>
+    <t xml:space="preserve">1.6459755897522</t>
   </si>
   <si>
     <t xml:space="preserve">1.55113899707794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52702808380127</t>
+    <t xml:space="preserve">1.52702796459198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51095402240753</t>
+    <t xml:space="preserve">1.51095414161682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45630276203156</t>
+    <t xml:space="preserve">1.45630264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862128257751</t>
+    <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
     <t xml:space="preserve">1.4120991230011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45601892471313</t>
+    <t xml:space="preserve">1.45601904392242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43426251411438</t>
+    <t xml:space="preserve">1.4342622756958</t>
   </si>
   <si>
     <t xml:space="preserve">1.4083217382431</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">1.4133425951004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4049745798111</t>
+    <t xml:space="preserve">1.40497469902039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36313474178314</t>
+    <t xml:space="preserve">1.36313486099243</t>
   </si>
   <si>
     <t xml:space="preserve">1.35560381412506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37233972549438</t>
+    <t xml:space="preserve">1.37233984470367</t>
   </si>
   <si>
     <t xml:space="preserve">1.33886802196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30288600921631</t>
+    <t xml:space="preserve">1.30288589000702</t>
   </si>
   <si>
     <t xml:space="preserve">1.32547950744629</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">1.26439356803894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29702830314636</t>
+    <t xml:space="preserve">1.29702842235565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30539631843567</t>
+    <t xml:space="preserve">1.30539643764496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36397159099579</t>
+    <t xml:space="preserve">1.36397182941437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41250574588776</t>
+    <t xml:space="preserve">1.41250586509705</t>
   </si>
   <si>
     <t xml:space="preserve">1.3807076215744</t>
@@ -224,46 +224,46 @@
     <t xml:space="preserve">1.3305002450943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2719247341156</t>
+    <t xml:space="preserve">1.27192461490631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25267827510834</t>
+    <t xml:space="preserve">1.25267839431763</t>
   </si>
   <si>
     <t xml:space="preserve">1.22506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2049812078476</t>
+    <t xml:space="preserve">1.20498132705688</t>
   </si>
   <si>
     <t xml:space="preserve">1.20916521549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22841155529022</t>
+    <t xml:space="preserve">1.22841143608093</t>
   </si>
   <si>
     <t xml:space="preserve">1.23845291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23008501529694</t>
+    <t xml:space="preserve">1.23008513450623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18824529647827</t>
+    <t xml:space="preserve">1.18824541568756</t>
   </si>
   <si>
     <t xml:space="preserve">1.14473223686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22171723842621</t>
+    <t xml:space="preserve">1.22171700000763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16816246509552</t>
+    <t xml:space="preserve">1.16816234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15226316452026</t>
+    <t xml:space="preserve">1.15226328372955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14222180843353</t>
+    <t xml:space="preserve">1.14222192764282</t>
   </si>
   <si>
     <t xml:space="preserve">1.17150950431824</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">1.12966990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11293423175812</t>
+    <t xml:space="preserve">1.11293411254883</t>
   </si>
   <si>
     <t xml:space="preserve">1.04850089550018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03343868255615</t>
+    <t xml:space="preserve">1.03343880176544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02423405647278</t>
+    <t xml:space="preserve">1.0242338180542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03929626941681</t>
+    <t xml:space="preserve">1.0392963886261</t>
   </si>
   <si>
     <t xml:space="preserve">1.05435860157013</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">1.0083349943161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984068036079407</t>
+    <t xml:space="preserve">0.984067857265472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999967217445374</t>
+    <t xml:space="preserve">0.999967038631439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01251900196075</t>
+    <t xml:space="preserve">1.01251912117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.00415086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958127439022064</t>
+    <t xml:space="preserve">0.958127498626709</t>
   </si>
   <si>
     <t xml:space="preserve">0.969842612743378</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">0.944738745689392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888673663139343</t>
+    <t xml:space="preserve">0.888673722743988</t>
   </si>
   <si>
     <t xml:space="preserve">0.866080224514008</t>
@@ -338,88 +338,88 @@
     <t xml:space="preserve">0.912103831768036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89955198764801</t>
+    <t xml:space="preserve">0.899551928043365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896204710006714</t>
+    <t xml:space="preserve">0.896204769611359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871937870979309</t>
+    <t xml:space="preserve">0.871937811374664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908756673336029</t>
+    <t xml:space="preserve">0.908756613731384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950596392154694</t>
+    <t xml:space="preserve">0.950596451759338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917124509811401</t>
+    <t xml:space="preserve">0.917124569416046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920471727848053</t>
+    <t xml:space="preserve">0.920471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967332065105438</t>
+    <t xml:space="preserve">0.967332124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962311327457428</t>
+    <t xml:space="preserve">0.962311387062073</t>
   </si>
   <si>
     <t xml:space="preserve">1.05519545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991599082946777</t>
+    <t xml:space="preserve">0.991599142551422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989088892936707</t>
+    <t xml:space="preserve">0.989088773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0016405582428</t>
+    <t xml:space="preserve">1.00164067745209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99578320980072</t>
+    <t xml:space="preserve">0.995782971382141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99076235294342</t>
+    <t xml:space="preserve">0.990762412548065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937207520008087</t>
+    <t xml:space="preserve">0.937207639217377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982394456863403</t>
+    <t xml:space="preserve">0.982394337654114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941391468048096</t>
+    <t xml:space="preserve">0.94139152765274</t>
   </si>
   <si>
     <t xml:space="preserve">0.98825204372406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972352862358093</t>
+    <t xml:space="preserve">0.972352921962738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968168795108795</t>
+    <t xml:space="preserve">0.968168973922729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97570013999939</t>
+    <t xml:space="preserve">0.9757000207901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983231067657471</t>
+    <t xml:space="preserve">0.983231127262115</t>
   </si>
   <si>
     <t xml:space="preserve">0.987415194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969005882740021</t>
+    <t xml:space="preserve">0.969005703926086</t>
   </si>
   <si>
     <t xml:space="preserve">0.994109511375427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953943431377411</t>
+    <t xml:space="preserve">0.953943490982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05854260921478</t>
+    <t xml:space="preserve">1.05854249000549</t>
   </si>
   <si>
     <t xml:space="preserve">1.05937933921814</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">1.10456621646881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13636434078217</t>
+    <t xml:space="preserve">1.13636422157288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1480792760849</t>
+    <t xml:space="preserve">1.14807939529419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19577634334564</t>
+    <t xml:space="preserve">1.19577646255493</t>
   </si>
   <si>
     <t xml:space="preserve">1.19661319255829</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">1.25602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20581805706024</t>
+    <t xml:space="preserve">1.20581793785095</t>
   </si>
   <si>
     <t xml:space="preserve">1.21334910392761</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.15644729137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15309989452362</t>
+    <t xml:space="preserve">1.15310001373291</t>
   </si>
   <si>
     <t xml:space="preserve">1.19242930412292</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">1.1547737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14640557765961</t>
+    <t xml:space="preserve">1.1464056968689</t>
   </si>
   <si>
     <t xml:space="preserve">1.19159257411957</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">1.16314160823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23761606216431</t>
+    <t xml:space="preserve">1.2376161813736</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518870353699</t>
@@ -509,40 +509,40 @@
     <t xml:space="preserve">1.17653036117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40581119060516</t>
+    <t xml:space="preserve">1.40581130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39577007293701</t>
+    <t xml:space="preserve">1.39576983451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39911699295044</t>
+    <t xml:space="preserve">1.39911723136902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39744353294373</t>
+    <t xml:space="preserve">1.39744341373444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4602028131485</t>
+    <t xml:space="preserve">1.46020293235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49534821510315</t>
+    <t xml:space="preserve">1.49534833431244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45685577392578</t>
+    <t xml:space="preserve">1.45685589313507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48865401744843</t>
+    <t xml:space="preserve">1.48865389823914</t>
   </si>
   <si>
     <t xml:space="preserve">1.48949062824249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47275483608246</t>
+    <t xml:space="preserve">1.47275495529175</t>
   </si>
   <si>
     <t xml:space="preserve">1.53551435470581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57316970825195</t>
+    <t xml:space="preserve">1.57316982746124</t>
   </si>
   <si>
     <t xml:space="preserve">1.5857218503952</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">1.63174533843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65684914588928</t>
+    <t xml:space="preserve">1.65684926509857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66438043117523</t>
+    <t xml:space="preserve">1.66438031196594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73550748825073</t>
+    <t xml:space="preserve">1.73550760746002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75726413726807</t>
+    <t xml:space="preserve">1.75726425647736</t>
   </si>
   <si>
     <t xml:space="preserve">1.77400004863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7823680639267</t>
+    <t xml:space="preserve">1.78236818313599</t>
   </si>
   <si>
     <t xml:space="preserve">1.65099167823792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60078418254852</t>
+    <t xml:space="preserve">1.60078406333923</t>
   </si>
   <si>
     <t xml:space="preserve">1.67358493804932</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">1.62003016471863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68697381019592</t>
+    <t xml:space="preserve">1.68697369098663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6166832447052</t>
+    <t xml:space="preserve">1.61668312549591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60664165019989</t>
+    <t xml:space="preserve">1.6066415309906</t>
   </si>
   <si>
     <t xml:space="preserve">1.68195283412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68362653255463</t>
+    <t xml:space="preserve">1.68362665176392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7154244184494</t>
+    <t xml:space="preserve">1.71542453765869</t>
   </si>
   <si>
     <t xml:space="preserve">1.73718130588531</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">1.75224351882935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052822589874</t>
+    <t xml:space="preserve">1.74052834510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.723792552948</t>
+    <t xml:space="preserve">1.72379267215729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65601241588593</t>
+    <t xml:space="preserve">1.65601229667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.74220204353333</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">1.7490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84337329864502</t>
+    <t xml:space="preserve">1.84337317943573</t>
   </si>
   <si>
     <t xml:space="preserve">1.80050384998322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78335618972778</t>
+    <t xml:space="preserve">1.78335630893707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193019866943</t>
+    <t xml:space="preserve">1.79193007946014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95483291149139</t>
+    <t xml:space="preserve">1.9548327922821</t>
   </si>
   <si>
     <t xml:space="preserve">2.37323570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46926283836365</t>
+    <t xml:space="preserve">2.46926259994507</t>
   </si>
   <si>
     <t xml:space="preserve">2.82421922683716</t>
@@ -647,28 +647,28 @@
     <t xml:space="preserve">2.82936334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73505163192749</t>
+    <t xml:space="preserve">2.73505139350891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64416885375977</t>
+    <t xml:space="preserve">2.64416909217834</t>
   </si>
   <si>
     <t xml:space="preserve">2.47783660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46068859100342</t>
+    <t xml:space="preserve">2.460688829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40067172050476</t>
+    <t xml:space="preserve">2.40067195892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.364661693573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983979225159</t>
+    <t xml:space="preserve">2.48984003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58929657936096</t>
+    <t xml:space="preserve">2.5892961025238</t>
   </si>
   <si>
     <t xml:space="preserve">2.78649425506592</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">2.67503452301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50012826919556</t>
+    <t xml:space="preserve">2.50012850761414</t>
   </si>
   <si>
     <t xml:space="preserve">2.4624035358429</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.47097754478455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44354104995728</t>
+    <t xml:space="preserve">2.44354128837585</t>
   </si>
   <si>
     <t xml:space="preserve">2.41953468322754</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">2.45211482048035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52927947044373</t>
+    <t xml:space="preserve">2.52927923202515</t>
   </si>
   <si>
     <t xml:space="preserve">2.57214856147766</t>
@@ -707,55 +707,55 @@
     <t xml:space="preserve">2.4349672794342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45554494857788</t>
+    <t xml:space="preserve">2.45554447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4572594165802</t>
+    <t xml:space="preserve">2.45725965499878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613829612732</t>
+    <t xml:space="preserve">2.5361385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4589741230011</t>
+    <t xml:space="preserve">2.45897436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47440671920776</t>
+    <t xml:space="preserve">2.47440695762634</t>
   </si>
   <si>
     <t xml:space="preserve">2.56185984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41781997680664</t>
+    <t xml:space="preserve">2.41781973838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.3818097114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42639327049255</t>
+    <t xml:space="preserve">2.42639350891113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3835244178772</t>
+    <t xml:space="preserve">2.38352465629578</t>
   </si>
   <si>
     <t xml:space="preserve">2.33208155632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31836318969727</t>
+    <t xml:space="preserve">2.31836342811584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28063893318176</t>
+    <t xml:space="preserve">2.28063869476318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32865214347839</t>
+    <t xml:space="preserve">2.32865190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31321883201599</t>
+    <t xml:space="preserve">2.31321907043457</t>
   </si>
   <si>
     <t xml:space="preserve">2.26692032814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.126309633255</t>
+    <t xml:space="preserve">2.12630939483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.12116527557373</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">2.06800746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0577187538147</t>
+    <t xml:space="preserve">2.05771899223328</t>
   </si>
   <si>
     <t xml:space="preserve">2.09544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11773562431335</t>
+    <t xml:space="preserve">2.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12802457809448</t>
+    <t xml:space="preserve">2.1280243396759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08515501022339</t>
+    <t xml:space="preserve">2.08515524864197</t>
   </si>
   <si>
     <t xml:space="preserve">2.06629300117493</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">2.08344054222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09887337684631</t>
+    <t xml:space="preserve">2.09887313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00799036026001</t>
+    <t xml:space="preserve">2.00799059867859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0508599281311</t>
+    <t xml:space="preserve">2.05085968971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.02342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2069034576416</t>
+    <t xml:space="preserve">2.20690321922302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17603802680969</t>
+    <t xml:space="preserve">2.17603754997253</t>
   </si>
   <si>
     <t xml:space="preserve">2.08172559738159</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">2.10401749610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15889000892639</t>
+    <t xml:space="preserve">2.15889024734497</t>
   </si>
   <si>
     <t xml:space="preserve">2.14345717430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12287998199463</t>
+    <t xml:space="preserve">2.12288022041321</t>
   </si>
   <si>
     <t xml:space="preserve">2.1537458896637</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">2.1520311832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917872428894</t>
+    <t xml:space="preserve">2.16917848587036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27720856666565</t>
+    <t xml:space="preserve">2.27720880508423</t>
   </si>
   <si>
     <t xml:space="preserve">2.22062158584595</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">2.25491714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28235340118408</t>
+    <t xml:space="preserve">2.2823531627655</t>
   </si>
   <si>
     <t xml:space="preserve">2.23776936531067</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">2.17089366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18975567817688</t>
+    <t xml:space="preserve">2.18975591659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.22919511795044</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.24634289741516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065532684326</t>
+    <t xml:space="preserve">2.34065556526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.25320219993591</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">2.27206468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20175957679749</t>
+    <t xml:space="preserve">2.20175933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20861840248108</t>
+    <t xml:space="preserve">2.2086181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28749752044678</t>
+    <t xml:space="preserve">2.28749775886536</t>
   </si>
   <si>
     <t xml:space="preserve">2.2034740447998</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">2.24462842941284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4366819858551</t>
+    <t xml:space="preserve">2.43668222427368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54471254348755</t>
+    <t xml:space="preserve">2.54471230506897</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527286529541</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">2.47269225120544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32007813453674</t>
+    <t xml:space="preserve">2.32007789611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.32179260253906</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">2.3578028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40410161018372</t>
+    <t xml:space="preserve">2.40410137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39038372039795</t>
+    <t xml:space="preserve">2.39038348197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33551096916199</t>
+    <t xml:space="preserve">2.33551073074341</t>
   </si>
   <si>
     <t xml:space="preserve">2.3063600063324</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">2.31493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19832944869995</t>
+    <t xml:space="preserve">2.19832992553711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1348831653595</t>
+    <t xml:space="preserve">2.13488340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11430644989014</t>
+    <t xml:space="preserve">2.11430621147156</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632626533508</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">2.10058808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09201407432556</t>
+    <t xml:space="preserve">2.09201455116272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04057145118713</t>
+    <t xml:space="preserve">2.04057121276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01484942436218</t>
+    <t xml:space="preserve">2.01484966278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04914546012878</t>
+    <t xml:space="preserve">2.04914498329163</t>
   </si>
   <si>
     <t xml:space="preserve">1.90339004993439</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">1.9805543422699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97198045253754</t>
+    <t xml:space="preserve">1.97198069095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92053747177124</t>
+    <t xml:space="preserve">1.92053759098053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98912835121155</t>
+    <t xml:space="preserve">1.98912799358368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91196405887604</t>
+    <t xml:space="preserve">1.91196382045746</t>
   </si>
   <si>
     <t xml:space="preserve">1.9291113615036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88624215126038</t>
+    <t xml:space="preserve">1.88624227046967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89481604099274</t>
+    <t xml:space="preserve">1.89481639862061</t>
   </si>
   <si>
     <t xml:space="preserve">1.86909472942352</t>
@@ -1007,40 +1007,40 @@
     <t xml:space="preserve">1.85194730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94625926017761</t>
+    <t xml:space="preserve">1.94625914096832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340680122375</t>
+    <t xml:space="preserve">1.96340692043304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06879162788391</t>
+    <t xml:space="preserve">2.06879186630249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04249334335327</t>
+    <t xml:space="preserve">2.04249358177185</t>
   </si>
   <si>
     <t xml:space="preserve">1.97236502170563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100263595581</t>
+    <t xml:space="preserve">1.9110027551651</t>
   </si>
   <si>
     <t xml:space="preserve">1.85840606689453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88470447063446</t>
+    <t xml:space="preserve">1.88470435142517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02496147155762</t>
+    <t xml:space="preserve">2.0249617099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99866330623627</t>
+    <t xml:space="preserve">1.99866318702698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94606697559357</t>
+    <t xml:space="preserve">1.94606673717499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853462696075</t>
+    <t xml:space="preserve">1.92853486537933</t>
   </si>
   <si>
     <t xml:space="preserve">1.86717224121094</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">1.90223670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87593841552734</t>
+    <t xml:space="preserve">1.87593853473663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82334184646606</t>
+    <t xml:space="preserve">1.82334172725677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91976892948151</t>
+    <t xml:space="preserve">1.91976869106293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84964001178741</t>
+    <t xml:space="preserve">1.84963989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89347040653229</t>
+    <t xml:space="preserve">1.89347052574158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93730056285858</t>
+    <t xml:space="preserve">1.93730080127716</t>
   </si>
   <si>
     <t xml:space="preserve">1.98989737033844</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">2.00742936134338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78827774524689</t>
+    <t xml:space="preserve">1.7882776260376</t>
   </si>
   <si>
     <t xml:space="preserve">1.77074551582336</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">1.79704368114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76197946071625</t>
+    <t xml:space="preserve">1.76197934150696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733937263489</t>
+    <t xml:space="preserve">1.61733949184418</t>
   </si>
   <si>
     <t xml:space="preserve">1.59542429447174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62172245979309</t>
+    <t xml:space="preserve">1.6217223405838</t>
   </si>
   <si>
     <t xml:space="preserve">1.65678668022156</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">1.68308484554291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63487160205841</t>
+    <t xml:space="preserve">1.63487148284912</t>
   </si>
   <si>
     <t xml:space="preserve">1.66555273532867</t>
@@ -1115,28 +1115,28 @@
     <t xml:space="preserve">1.57789206504822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60419023036957</t>
+    <t xml:space="preserve">1.60419034957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.5647429227829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59980726242065</t>
+    <t xml:space="preserve">1.59980714321136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59104108810425</t>
+    <t xml:space="preserve">1.59104120731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993570327759</t>
+    <t xml:space="preserve">1.6699355840683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63048851490021</t>
+    <t xml:space="preserve">1.63048839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57350897789001</t>
+    <t xml:space="preserve">1.57350885868073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70061707496643</t>
+    <t xml:space="preserve">1.70061695575714</t>
   </si>
   <si>
     <t xml:space="preserve">1.64363753795624</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">1.63925445079803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58665800094604</t>
+    <t xml:space="preserve">1.58665812015533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55597674846649</t>
+    <t xml:space="preserve">1.55597698688507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42010283470154</t>
+    <t xml:space="preserve">1.42010295391083</t>
   </si>
   <si>
     <t xml:space="preserve">1.42448580265045</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">1.20971727371216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2929949760437</t>
+    <t xml:space="preserve">1.29299485683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065552711487</t>
+    <t xml:space="preserve">1.38065576553345</t>
   </si>
   <si>
     <t xml:space="preserve">1.41571974754333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4025707244873</t>
+    <t xml:space="preserve">1.40257060527802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43325185775757</t>
+    <t xml:space="preserve">1.43325197696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38942170143127</t>
+    <t xml:space="preserve">1.38942158222198</t>
   </si>
   <si>
     <t xml:space="preserve">1.38503861427307</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">1.35874032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43763482570648</t>
+    <t xml:space="preserve">1.43763494491577</t>
   </si>
   <si>
     <t xml:space="preserve">1.44640100002289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201791286469</t>
+    <t xml:space="preserve">1.44201803207397</t>
   </si>
   <si>
     <t xml:space="preserve">1.4507839679718</t>
@@ -1220,73 +1220,73 @@
     <t xml:space="preserve">1.36750638484955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53406155109406</t>
+    <t xml:space="preserve">1.53406167030334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5121465921402</t>
+    <t xml:space="preserve">1.51214647293091</t>
   </si>
   <si>
     <t xml:space="preserve">1.52967870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54721069335938</t>
+    <t xml:space="preserve">1.54721081256866</t>
   </si>
   <si>
     <t xml:space="preserve">1.54282772541046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55159378051758</t>
+    <t xml:space="preserve">1.55159366130829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56035995483398</t>
+    <t xml:space="preserve">1.56035983562469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52091264724731</t>
+    <t xml:space="preserve">1.52091252803802</t>
   </si>
   <si>
     <t xml:space="preserve">1.48584830760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51652956008911</t>
+    <t xml:space="preserve">1.5165296792984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56912589073181</t>
+    <t xml:space="preserve">1.5691260099411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50776350498199</t>
+    <t xml:space="preserve">1.50776362419128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52529573440552</t>
+    <t xml:space="preserve">1.52529561519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49899733066559</t>
+    <t xml:space="preserve">1.49899756908417</t>
   </si>
   <si>
     <t xml:space="preserve">1.57839870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60545706748962</t>
+    <t xml:space="preserve">1.60545694828033</t>
   </si>
   <si>
     <t xml:space="preserve">1.5693793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54232096672058</t>
+    <t xml:space="preserve">1.54232120513916</t>
   </si>
   <si>
     <t xml:space="preserve">1.51526272296906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48820459842682</t>
+    <t xml:space="preserve">1.48820447921753</t>
   </si>
   <si>
     <t xml:space="preserve">1.46114635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50624322891235</t>
+    <t xml:space="preserve">1.50624334812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47016561031342</t>
+    <t xml:space="preserve">1.47016572952271</t>
   </si>
   <si>
     <t xml:space="preserve">1.44310736656189</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.41604924201965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39801013469696</t>
+    <t xml:space="preserve">1.39801025390625</t>
   </si>
   <si>
     <t xml:space="preserve">1.42506861686707</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.43408799171448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40702974796295</t>
+    <t xml:space="preserve">1.40702962875366</t>
   </si>
   <si>
     <t xml:space="preserve">1.38899087905884</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">1.31683552265167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28977727890015</t>
+    <t xml:space="preserve">1.28977715969086</t>
   </si>
   <si>
     <t xml:space="preserve">1.26271903514862</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">1.24468016624451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19056367874146</t>
+    <t xml:space="preserve">1.19056355953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.18154418468475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17252469062805</t>
+    <t xml:space="preserve">1.17252480983734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22664129734039</t>
+    <t xml:space="preserve">1.22664141654968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21762192249298</t>
+    <t xml:space="preserve">1.21762180328369</t>
   </si>
   <si>
     <t xml:space="preserve">1.28075778484344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29879677295685</t>
+    <t xml:space="preserve">1.29879665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36193251609802</t>
+    <t xml:space="preserve">1.36193263530731</t>
   </si>
   <si>
     <t xml:space="preserve">1.37997150421143</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">1.45212686061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65055406093597</t>
+    <t xml:space="preserve">1.65055418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66859304904938</t>
+    <t xml:space="preserve">1.66859292984009</t>
   </si>
   <si>
     <t xml:space="preserve">1.64153480529785</t>
@@ -1388,46 +1388,49 @@
     <t xml:space="preserve">1.63251531124115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59643757343292</t>
+    <t xml:space="preserve">1.59643745422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79486477375031</t>
+    <t xml:space="preserve">1.79486489295959</t>
   </si>
   <si>
     <t xml:space="preserve">1.70467066764832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72270941734314</t>
+    <t xml:space="preserve">1.72270953655243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71369016170502</t>
+    <t xml:space="preserve">1.71369004249573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62349569797516</t>
+    <t xml:space="preserve">1.62349581718445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55134046077728</t>
+    <t xml:space="preserve">1.56035995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55134057998657</t>
   </si>
   <si>
     <t xml:space="preserve">1.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69565117359161</t>
+    <t xml:space="preserve">1.6956512928009</t>
   </si>
   <si>
     <t xml:space="preserve">1.13644707202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840832233429</t>
+    <t xml:space="preserve">1.118408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16350531578064</t>
+    <t xml:space="preserve">1.16350543498993</t>
   </si>
   <si>
     <t xml:space="preserve">1.15448594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1274276971817</t>
+    <t xml:space="preserve">1.12742757797241</t>
   </si>
   <si>
     <t xml:space="preserve">1.19958305358887</t>
@@ -1436,19 +1439,19 @@
     <t xml:space="preserve">1.25369954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546644687653</t>
+    <t xml:space="preserve">1.14546656608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10036945343018</t>
+    <t xml:space="preserve">1.10036933422089</t>
   </si>
   <si>
     <t xml:space="preserve">1.10938882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09135007858276</t>
+    <t xml:space="preserve">1.09134995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08233058452606</t>
+    <t xml:space="preserve">1.08233070373535</t>
   </si>
   <si>
     <t xml:space="preserve">1.04625284671783</t>
@@ -1457,19 +1460,19 @@
     <t xml:space="preserve">1.06429171562195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07331120967865</t>
+    <t xml:space="preserve">1.07331132888794</t>
   </si>
   <si>
     <t xml:space="preserve">1.05527222156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03723347187042</t>
+    <t xml:space="preserve">1.03723335266113</t>
   </si>
   <si>
     <t xml:space="preserve">1.02821397781372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992136359214783</t>
+    <t xml:space="preserve">0.992136418819427</t>
   </si>
   <si>
     <t xml:space="preserve">1.0101752281189</t>
@@ -1496,13 +1499,13 @@
     <t xml:space="preserve">0.947039186954498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897432386875153</t>
+    <t xml:space="preserve">0.897432446479797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910961508750916</t>
+    <t xml:space="preserve">0.91096156835556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983116924762726</t>
+    <t xml:space="preserve">0.983117043972015</t>
   </si>
   <si>
     <t xml:space="preserve">1.01919460296631</t>
@@ -1511,13 +1514,13 @@
     <t xml:space="preserve">0.956058621406555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20860254764557</t>
+    <t xml:space="preserve">1.20860242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47918498516083</t>
+    <t xml:space="preserve">1.47918510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25098145008087</t>
+    <t xml:space="preserve">1.25098133087158</t>
   </si>
   <si>
     <t xml:space="preserve">1.24171483516693</t>
@@ -1547,7 +1550,7 @@
     <t xml:space="preserve">1.1397830247879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1212500333786</t>
+    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.1027170419693</t>
@@ -1565,25 +1568,22 @@
     <t xml:space="preserve">1.09345030784607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13051652908325</t>
+    <t xml:space="preserve">1.13051640987396</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1953821182251</t>
+    <t xml:space="preserve">1.19538223743439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11198341846466</t>
+    <t xml:space="preserve">1.11198353767395</t>
   </si>
   <si>
     <t xml:space="preserve">1.08418381214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.15958333015442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12124991416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.10208332538605</t>
@@ -29080,7 +29080,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1037" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29132,7 +29132,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1039" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29236,7 +29236,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29262,7 +29262,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1044" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29314,7 +29314,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1046" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29444,7 +29444,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1051" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29704,7 +29704,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1061" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29730,7 +29730,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1062" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29756,7 +29756,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29782,7 +29782,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29808,7 +29808,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1065" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29834,7 +29834,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29860,7 +29860,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29886,7 +29886,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1068" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29912,7 +29912,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1069" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29938,7 +29938,7 @@
         <v>1.25</v>
       </c>
       <c r="G1070" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29964,7 +29964,7 @@
         <v>1.25</v>
       </c>
       <c r="G1071" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29990,7 +29990,7 @@
         <v>1.25</v>
       </c>
       <c r="G1072" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30016,7 +30016,7 @@
         <v>1.25</v>
       </c>
       <c r="G1073" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30198,7 +30198,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1080" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30224,7 +30224,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1081" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30250,7 +30250,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30302,7 +30302,7 @@
         <v>1.25</v>
       </c>
       <c r="G1084" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30406,7 +30406,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1088" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30458,7 +30458,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30510,7 +30510,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1092" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30536,7 +30536,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1093" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30562,7 +30562,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1094" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30588,7 +30588,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30614,7 +30614,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30640,7 +30640,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30666,7 +30666,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1098" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30692,7 +30692,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1099" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30718,7 +30718,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1100" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30744,7 +30744,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1101" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30770,7 +30770,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30796,7 +30796,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1103" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30822,7 +30822,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1104" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30848,7 +30848,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1105" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30874,7 +30874,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30900,7 +30900,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1107" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30926,7 +30926,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30952,7 +30952,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1109" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30978,7 +30978,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1110" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31004,7 +31004,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1111" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31030,7 +31030,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1112" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31056,7 +31056,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1113" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31082,7 +31082,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1114" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31108,7 +31108,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1115" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31134,7 +31134,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31160,7 +31160,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1117" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31186,7 +31186,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31212,7 +31212,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1119" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31238,7 +31238,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1120" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31264,7 +31264,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1121" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31290,7 +31290,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1122" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31316,7 +31316,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31342,7 +31342,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31368,7 +31368,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1125" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31394,7 +31394,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1126" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31420,7 +31420,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31446,7 +31446,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1128" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31472,7 +31472,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1129" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31498,7 +31498,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1130" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31524,7 +31524,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1131" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31550,7 +31550,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31576,7 +31576,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1133" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31602,7 +31602,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1134" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31628,7 +31628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31654,7 +31654,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1136" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31680,7 +31680,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1137" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31706,7 +31706,7 @@
         <v>1.25</v>
       </c>
       <c r="G1138" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31732,7 +31732,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1139" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31758,7 +31758,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1140" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31784,7 +31784,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1141" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31810,7 +31810,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1142" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31836,7 +31836,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1143" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31862,7 +31862,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31888,7 +31888,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1145" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31914,7 +31914,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31940,7 +31940,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1147" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31966,7 +31966,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1148" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31992,7 +31992,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1149" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32018,7 +32018,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1150" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32044,7 +32044,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1151" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32070,7 +32070,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1152" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32096,7 +32096,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1153" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32122,7 +32122,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1154" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32148,7 +32148,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1155" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32174,7 +32174,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1156" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32200,7 +32200,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1157" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32226,7 +32226,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1158" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32252,7 +32252,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1159" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32278,7 +32278,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1160" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32304,7 +32304,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1161" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32330,7 +32330,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1162" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32356,7 +32356,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1163" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32382,7 +32382,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1164" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32408,7 +32408,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1165" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32434,7 +32434,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1166" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32460,7 +32460,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1167" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32486,7 +32486,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1168" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32512,7 +32512,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32538,7 +32538,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1170" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32564,7 +32564,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1171" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32590,7 +32590,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1172" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32616,7 +32616,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1173" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32642,7 +32642,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1174" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32668,7 +32668,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1175" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32694,7 +32694,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1176" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32720,7 +32720,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1177" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32746,7 +32746,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1178" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32772,7 +32772,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1179" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32798,7 +32798,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1180" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32824,7 +32824,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32850,7 +32850,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1182" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32876,7 +32876,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1183" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32902,7 +32902,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1184" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32928,7 +32928,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1185" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32954,7 +32954,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1186" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32980,7 +32980,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1187" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33006,7 +33006,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1188" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33032,7 +33032,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1189" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33058,7 +33058,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1190" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33084,7 +33084,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33110,7 +33110,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33136,7 +33136,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33162,7 +33162,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1194" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33188,7 +33188,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1195" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33214,7 +33214,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1196" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33240,7 +33240,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33266,7 +33266,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1198" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33292,7 +33292,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33318,7 +33318,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33344,7 +33344,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1201" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33370,7 +33370,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1202" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33396,7 +33396,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33422,7 +33422,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1204" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33448,7 +33448,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1205" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33474,7 +33474,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33500,7 +33500,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33526,7 +33526,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1208" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33552,7 +33552,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1209" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33578,7 +33578,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33604,7 +33604,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1211" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33630,7 +33630,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1212" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33656,7 +33656,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1213" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33682,7 +33682,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33708,7 +33708,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33734,7 +33734,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1216" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33760,7 +33760,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33786,7 +33786,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1218" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33812,7 +33812,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1219" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33838,7 +33838,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1220" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33864,7 +33864,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1221" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33890,7 +33890,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33916,7 +33916,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33942,7 +33942,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33968,7 +33968,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33994,7 +33994,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1226" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34020,7 +34020,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1227" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34046,7 +34046,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1228" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34072,7 +34072,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1229" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34098,7 +34098,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1230" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34124,7 +34124,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34150,7 +34150,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34176,7 +34176,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1233" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34202,7 +34202,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1234" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34228,7 +34228,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34254,7 +34254,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34280,7 +34280,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1237" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34306,7 +34306,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1238" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34332,7 +34332,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1239" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34358,7 +34358,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1240" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34384,7 +34384,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34410,7 +34410,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1242" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34436,7 +34436,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1243" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34462,7 +34462,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1244" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34488,7 +34488,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1245" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34514,7 +34514,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1246" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34540,7 +34540,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1247" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34566,7 +34566,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1248" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34592,7 +34592,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1249" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34618,7 +34618,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1250" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34644,7 +34644,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1251" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34670,7 +34670,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1252" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34696,7 +34696,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1253" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34722,7 +34722,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1254" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34748,7 +34748,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1255" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34774,7 +34774,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1256" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34800,7 +34800,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1257" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34826,7 +34826,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1258" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34852,7 +34852,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1259" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34878,7 +34878,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1260" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34904,7 +34904,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1261" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34930,7 +34930,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1262" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34956,7 +34956,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34982,7 +34982,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1264" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35008,7 +35008,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1265" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35034,7 +35034,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1266" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35060,7 +35060,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1267" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35086,7 +35086,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1268" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35112,7 +35112,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1269" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35138,7 +35138,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1270" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35164,7 +35164,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1271" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35190,7 +35190,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1272" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35216,7 +35216,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1273" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35242,7 +35242,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1274" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35268,7 +35268,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1275" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35294,7 +35294,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1276" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35320,7 +35320,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1277" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35346,7 +35346,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1278" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35372,7 +35372,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1279" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35398,7 +35398,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1280" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35424,7 +35424,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1281" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35450,7 +35450,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1282" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35476,7 +35476,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1283" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35502,7 +35502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1284" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35528,7 +35528,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1285" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35554,7 +35554,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1286" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35580,7 +35580,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35606,7 +35606,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1288" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35632,7 +35632,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1289" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35658,7 +35658,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1290" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35684,7 +35684,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1291" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35710,7 +35710,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1292" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35736,7 +35736,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1293" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35762,7 +35762,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1294" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35788,7 +35788,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1295" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35814,7 +35814,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1296" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35840,7 +35840,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1297" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35866,7 +35866,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35892,7 +35892,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35918,7 +35918,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1300" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35944,7 +35944,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1301" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35970,7 +35970,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1302" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35996,7 +35996,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1303" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36022,7 +36022,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1304" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36048,7 +36048,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1305" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36074,7 +36074,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1306" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36100,7 +36100,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1307" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36126,7 +36126,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1308" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36152,7 +36152,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1309" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36178,7 +36178,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1310" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36204,7 +36204,7 @@
         <v>1.25</v>
       </c>
       <c r="G1311" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36230,7 +36230,7 @@
         <v>1.25</v>
       </c>
       <c r="G1312" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36256,7 +36256,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1313" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36282,7 +36282,7 @@
         <v>1.25</v>
       </c>
       <c r="G1314" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36308,7 +36308,7 @@
         <v>1.25</v>
       </c>
       <c r="G1315" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36334,7 +36334,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1316" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36360,7 +36360,7 @@
         <v>1.25</v>
       </c>
       <c r="G1317" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36386,7 +36386,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36438,7 +36438,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36464,7 +36464,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1321" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36490,7 +36490,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1322" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36516,7 +36516,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1323" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36542,7 +36542,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1324" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36568,7 +36568,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1325" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36594,7 +36594,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36620,7 +36620,7 @@
         <v>1.25</v>
       </c>
       <c r="G1327" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36646,7 +36646,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1328" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36672,7 +36672,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1329" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36698,7 +36698,7 @@
         <v>1.25</v>
       </c>
       <c r="G1330" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36724,7 +36724,7 @@
         <v>1.25</v>
       </c>
       <c r="G1331" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36750,7 +36750,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36776,7 +36776,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36854,7 +36854,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1336" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37062,7 +37062,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1344" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37114,7 +37114,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1346" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37270,7 +37270,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1352" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37296,7 +37296,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1353" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37374,7 +37374,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1356" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37400,7 +37400,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1357" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37452,7 +37452,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1359" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37478,7 +37478,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1360" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37530,7 +37530,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37556,7 +37556,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37582,7 +37582,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38206,7 +38206,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1388" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38232,7 +38232,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1389" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38258,7 +38258,7 @@
         <v>1.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38284,7 +38284,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1391" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38310,7 +38310,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1392" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38362,7 +38362,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1394" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38388,7 +38388,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1395" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38414,7 +38414,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1396" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38440,7 +38440,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1397" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38570,7 +38570,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38596,7 +38596,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38622,7 +38622,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38648,7 +38648,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1405" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38674,7 +38674,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38700,7 +38700,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1407" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38726,7 +38726,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1408" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38752,7 +38752,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1409" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38778,7 +38778,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1410" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38804,7 +38804,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1411" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38830,7 +38830,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1412" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38856,7 +38856,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1413" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38882,7 +38882,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1414" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38908,7 +38908,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1415" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38934,7 +38934,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1416" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38960,7 +38960,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1417" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38986,7 +38986,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1418" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39012,7 +39012,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1419" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39064,7 +39064,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1421" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39090,7 +39090,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1422" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39116,7 +39116,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1423" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39142,7 +39142,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1424" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39168,7 +39168,7 @@
         <v>1.25</v>
       </c>
       <c r="G1425" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39194,7 +39194,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39220,7 +39220,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1427" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39246,7 +39246,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1428" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39272,7 +39272,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1429" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39298,7 +39298,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1430" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39324,7 +39324,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39350,7 +39350,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1432" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39376,7 +39376,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1433" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39480,7 +39480,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39506,7 +39506,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1438" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39532,7 +39532,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1439" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39558,7 +39558,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1440" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39584,7 +39584,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1441" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39610,7 +39610,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1442" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39636,7 +39636,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1443" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39662,7 +39662,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1444" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39688,7 +39688,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1445" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39714,7 +39714,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1446" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39740,7 +39740,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1447" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39766,7 +39766,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1448" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39792,7 +39792,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1449" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39818,7 +39818,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1450" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39844,7 +39844,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1451" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39870,7 +39870,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1452" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39896,7 +39896,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1453" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39922,7 +39922,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1454" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39948,7 +39948,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1455" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39974,7 +39974,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1456" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40000,7 +40000,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1457" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40182,7 +40182,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1464" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40260,7 +40260,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1467" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40286,7 +40286,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1468" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40546,7 +40546,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41222,7 +41222,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1504" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41534,7 +41534,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1516" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41612,7 +41612,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1519" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41638,7 +41638,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41664,7 +41664,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1521" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41690,7 +41690,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1522" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41794,7 +41794,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1526" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41820,7 +41820,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1527" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41924,7 +41924,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1531" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41950,7 +41950,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1532" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42132,7 +42132,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1539" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42184,7 +42184,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1541" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42288,7 +42288,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1545" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42340,7 +42340,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1547" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42366,7 +42366,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1548" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42392,7 +42392,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1549" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42418,7 +42418,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1550" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42444,7 +42444,7 @@
         <v>1.25</v>
       </c>
       <c r="G1551" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42470,7 +42470,7 @@
         <v>1.25</v>
       </c>
       <c r="G1552" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42496,7 +42496,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1553" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42522,7 +42522,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1554" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42548,7 +42548,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1555" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42574,7 +42574,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1556" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42600,7 +42600,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42626,7 +42626,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1558" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42652,7 +42652,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42678,7 +42678,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1560" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42704,7 +42704,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42730,7 +42730,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1562" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42808,7 +42808,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42834,7 +42834,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1566" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42860,7 +42860,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1567" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42886,7 +42886,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42912,7 +42912,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1569" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42938,7 +42938,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1570" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42964,7 +42964,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1571" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42990,7 +42990,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1572" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43016,7 +43016,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1573" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43042,7 +43042,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1574" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43068,7 +43068,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1575" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43094,7 +43094,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1576" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43120,7 +43120,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1577" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43146,7 +43146,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1578" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43172,7 +43172,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1579" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43198,7 +43198,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1580" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43224,7 +43224,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1581" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43250,7 +43250,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1582" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43276,7 +43276,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1583" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43302,7 +43302,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1584" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43328,7 +43328,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1585" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43354,7 +43354,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1586" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43380,7 +43380,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43536,7 +43536,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1593" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43562,7 +43562,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1594" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43614,7 +43614,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1596" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43640,7 +43640,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43692,7 +43692,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1599" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43796,7 +43796,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43822,7 +43822,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1604" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43848,7 +43848,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43874,7 +43874,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1606" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43900,7 +43900,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1607" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43926,7 +43926,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43952,7 +43952,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1609" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44030,7 +44030,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1612" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44056,7 +44056,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1613" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44082,7 +44082,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44108,7 +44108,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1615" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44134,7 +44134,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1616" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44186,7 +44186,7 @@
         <v>1.25</v>
       </c>
       <c r="G1618" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44212,7 +44212,7 @@
         <v>1.25</v>
       </c>
       <c r="G1619" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44238,7 +44238,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1620" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44264,7 +44264,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44316,7 +44316,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44446,7 +44446,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1628" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44498,7 +44498,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1630" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44628,7 +44628,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1635" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44654,7 +44654,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44680,7 +44680,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1637" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44706,7 +44706,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44732,7 +44732,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1639" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44758,7 +44758,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1640" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44784,7 +44784,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1641" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44810,7 +44810,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45018,7 +45018,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45070,7 +45070,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1652" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45096,7 +45096,7 @@
         <v>1.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45122,7 +45122,7 @@
         <v>1.25</v>
       </c>
       <c r="G1654" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45148,7 +45148,7 @@
         <v>1.25</v>
       </c>
       <c r="G1655" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45174,7 +45174,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1656" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45200,7 +45200,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1657" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45226,7 +45226,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45252,7 +45252,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45278,7 +45278,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1660" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45304,7 +45304,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1661" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45330,7 +45330,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1662" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45356,7 +45356,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1663" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45382,7 +45382,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45434,7 +45434,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45460,7 +45460,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45486,7 +45486,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45512,7 +45512,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45564,7 +45564,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1671" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45590,7 +45590,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1672" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45642,7 +45642,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1674" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45694,7 +45694,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1676" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45746,7 +45746,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45824,7 +45824,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1681" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45876,7 +45876,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1683" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45902,7 +45902,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1684" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45928,7 +45928,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1685" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46006,7 +46006,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1688" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46162,7 +46162,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1694" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46188,7 +46188,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1695" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46214,7 +46214,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1696" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46240,7 +46240,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46292,7 +46292,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1699" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46344,7 +46344,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46474,7 +46474,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1706" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46526,7 +46526,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1708" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46630,7 +46630,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1712" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46682,7 +46682,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1714" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46708,7 +46708,7 @@
         <v>1.25</v>
       </c>
       <c r="G1715" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46734,7 +46734,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1716" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46760,7 +46760,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46786,7 +46786,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46812,7 +46812,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46838,7 +46838,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46864,7 +46864,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46890,7 +46890,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46916,7 +46916,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46968,7 +46968,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1725" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46994,7 +46994,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1726" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47020,7 +47020,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1727" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47150,7 +47150,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1732" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47202,7 +47202,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1734" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47228,7 +47228,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47410,7 +47410,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1742" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47436,7 +47436,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1743" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47462,7 +47462,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1744" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47488,7 +47488,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1745" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47514,7 +47514,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1746" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47540,7 +47540,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1747" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47566,7 +47566,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1748" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47592,7 +47592,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1749" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47618,7 +47618,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1750" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47644,7 +47644,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1751" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47670,7 +47670,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1752" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47696,7 +47696,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1753" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47722,7 +47722,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1754" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47748,7 +47748,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1755" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47904,7 +47904,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1761" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47956,7 +47956,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48008,7 +48008,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1765" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48034,7 +48034,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1766" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48060,7 +48060,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1767" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48086,7 +48086,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1768" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48112,7 +48112,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1769" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48242,7 +48242,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1774" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48268,7 +48268,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1775" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48398,7 +48398,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1780" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48502,7 +48502,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1784" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48528,7 +48528,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1785" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48554,7 +48554,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1786" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48580,7 +48580,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1787" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48606,7 +48606,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1788" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48632,7 +48632,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1789" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48684,7 +48684,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1791" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48710,7 +48710,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1792" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48944,7 +48944,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1801" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48970,7 +48970,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48996,7 +48996,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1803" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49022,7 +49022,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1804" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49048,7 +49048,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1805" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49074,7 +49074,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49100,7 +49100,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1807" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49126,7 +49126,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1808" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49152,7 +49152,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1809" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49178,7 +49178,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1810" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49204,7 +49204,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1811" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49230,7 +49230,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1812" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49256,7 +49256,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1813" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49334,7 +49334,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49360,7 +49360,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1817" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49386,7 +49386,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1818" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49412,7 +49412,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1819" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49438,7 +49438,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1820" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49464,7 +49464,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1821" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49490,7 +49490,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1822" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49516,7 +49516,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1823" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49542,7 +49542,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1824" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49568,7 +49568,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1825" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49594,7 +49594,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49620,7 +49620,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49646,7 +49646,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1828" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49672,7 +49672,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1829" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49698,7 +49698,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49724,7 +49724,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49750,7 +49750,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49776,7 +49776,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49802,7 +49802,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1834" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49828,7 +49828,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1835" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49854,7 +49854,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1836" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49880,7 +49880,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1837" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49906,7 +49906,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1838" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49932,7 +49932,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49958,7 +49958,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49984,7 +49984,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50010,7 +50010,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1842" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50036,7 +50036,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1843" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50062,7 +50062,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1844" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50088,7 +50088,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1845" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
 